--- a/financial_models/opportunities/9618.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9618.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF7F62CF-1088-411A-9ADE-422B9C1CD86C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE56799B-F40D-46EF-850B-E246B22F04EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-195" yWindow="120" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5357,7 +5357,7 @@
         <v>538</v>
       </c>
       <c r="F3" s="429">
-        <v>46038</v>
+        <v>46045</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="12.4">
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>115.7</v>
+        <v>114.8</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5422,7 +5422,7 @@
         <v>346</v>
       </c>
       <c r="C9" s="48">
-        <v>2584105173</v>
+        <v>3187553771</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>298980.96851610002</v>
+        <v>365931.17291079997</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.1520364330127415</v>
+        <v>0.17769847372279465</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1</v>
+        <v>1.1196808250427246</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>164.68961997937771</v>
+        <v>175.00654575317373</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5561,13 +5561,13 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>82.316613124025665</v>
+        <v>87.070956798586039</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5576,13 +5576,13 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>102.51263218235289</v>
+        <v>108.47186728635059</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
       </c>
       <c r="E23" s="443">
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>126.51123371392191</v>
+        <v>133.90599748625249</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>142.66730347977182</v>
+        <v>151.03023235844438</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="C44" s="286">
         <f>Normalized_FCF!C46</f>
-        <v>565.023935957135</v>
+        <v>566.20066072323493</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="C46" s="285">
         <f>Normalized_FCF!C10</f>
-        <v>-6160.316064042865</v>
+        <v>-6159.139339276765</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="C52" s="285">
         <f>Normalized_FCF!C12</f>
-        <v>-8172.2055490968023</v>
+        <v>-8172.4997302883276</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C61" s="285">
         <f>Normalized_FCF!C19</f>
-        <v>21215.616647290408</v>
+        <v>21216.499190864983</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.0959756243307359E-2</v>
+        <v>6.4918512215237631E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,14 +5913,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.033707865168539E-2</v>
+        <v>3.0574912891986061E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
       </c>
       <c r="F63" s="258">
         <f>Normalized_FCF!C90</f>
-        <v>0.47502791656952054</v>
+        <v>0.58593359795439359</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!E119</f>
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="C67" s="263">
         <f>Normalized_FCF!E116</f>
-        <v>3.152381864639775E-2</v>
+        <v>3.9404773307997187E-2</v>
       </c>
       <c r="D67" s="263">
         <f>Normalized_FCF!G116</f>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-43.376330488078011</v>
+        <v>-39.373109605250939</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="C84" s="285">
         <f>DCF!F5</f>
-        <v>31164.344007144173</v>
+        <v>30968.223212794182</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.060013784564399</v>
+        <v>10.878099071605792</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>38.129910898947763</v>
+        <v>34.610884419449761</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.8135941954341535</v>
+        <v>6.1158738858046107</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-67.151814025643745</v>
+        <v>-60.954343165330592</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>166.32301654396133</v>
+        <v>150.91012353067066</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6360,7 +6360,7 @@
     <row r="118" spans="2:6">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
-        <v>Snowball Scenario (15yrs)</v>
+        <v>Snowball Scenario (10yrs)</v>
       </c>
       <c r="C118" s="206">
         <f>DCF!C90</f>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>213.64 HKD</v>
+        <v>213.78 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,13 +6376,13 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-6.514312199132416E-2</v>
+        <v>-4.6971301605721064E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
-        <v>Optimistic (15yrs)</v>
+        <v>Optimistic (10yrs)</v>
       </c>
       <c r="C119" s="198">
         <f>DCF!C91</f>
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>174.46 HKD</v>
+        <v>183.44 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,13 +6398,13 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>1.4862806382593514E-3</v>
+        <v>3.8768037037718284E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
-        <v>Base (15yrs)</v>
+        <v>Base (10yrs)</v>
       </c>
       <c r="C120" s="198">
         <f>DCF!C92</f>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>158.03 HKD</v>
+        <v>169.96 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,13 +6420,13 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>3.5774608242128844E-2</v>
+        <v>3.0247813917575962E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
-        <v>Pessimistic (15yrs)</v>
+        <v>Pessimistic (10yrs)</v>
       </c>
       <c r="C121" s="198">
         <f>DCF!C93</f>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>143.4 HKD</v>
+        <v>157.52 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,13 +6442,13 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.0627621002389604E-2</v>
+        <v>5.7247388467611501E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
-        <v>Devil's advocate (15yrs)</v>
+        <v>Devil's advocate (10yrs)</v>
       </c>
       <c r="C122" s="198">
         <f>DCF!C94</f>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>130.38 HKD</v>
+        <v>146.03 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.1059725914407207</v>
+        <v>8.4870434968403255E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>164.68961997937771</v>
+        <v>175.00654575317373</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6585,19 +6585,19 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>6.4227790321465204</v>
+        <v>6.4227790321465186</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>75.893834091879143</v>
+        <v>80.648177766439517</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>82.316613124025665</v>
+        <v>87.070956798586039</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6606,19 +6606,19 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>7.3850538549144664</v>
+        <v>7.3850538549144646</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>95.127578327438428</v>
+        <v>101.08681343143613</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>102.51263218235289</v>
+        <v>108.47186728635059</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>118.04299674187726</v>
+        <v>125.43776051420784</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>126.51123371392191</v>
+        <v>133.90599748625249</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>133.49786643239455</v>
+        <v>141.86079531106711</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>142.66730347977182</v>
+        <v>151.03023235844438</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,6 +6796,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6812,18 +6824,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10003,11 +10003,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>89.753699819709311</v>
+        <v>81.470290840980525</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-67.151814025643745</v>
+        <v>-60.954343165330592</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10198,7 +10198,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>31164.344007144173</v>
+        <v>30968.223212794182</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10265,11 +10265,11 @@
       </c>
       <c r="C73" s="285">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
-        <v>-94110.584181225</v>
+        <v>-94306.70497557499</v>
       </c>
       <c r="D73" s="285">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-94170.655992855827</v>
+        <v>-94366.776787205818</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10281,11 +10281,11 @@
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
-        <v>1.331784316189637</v>
+        <v>1.3290147294665973</v>
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>1.330934766022108</v>
+        <v>1.3281687079619831</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10298,7 +10298,7 @@
       <c r="C75" s="261"/>
       <c r="D75" s="262">
         <f>MAX(-D73*D76,G5)</f>
-        <v>94170.655992855827</v>
+        <v>94366.776787205818</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10413,11 +10413,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-112089</v>
+        <v>-125503.90399821395</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-43.376330488078011</v>
+        <v>-39.373109605250939</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10430,11 +10430,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>31164.344007144173</v>
+        <v>34674.525717008648</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>12.060013784564399</v>
+        <v>10.878099071605792</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10447,11 +10447,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>98531.7</v>
+        <v>110324.05514886223</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>38.129910898947763</v>
+        <v>34.610884419449761</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10464,11 +10464,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>17607.04400714417</v>
+        <v>19494.676867656919</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.813594195434149</v>
+        <v>6.1158738858046142</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -10949,7 +10949,7 @@
       </c>
       <c r="C10" s="266">
         <f>C48</f>
-        <v>-6160.316064042865</v>
+        <v>-6159.139339276765</v>
       </c>
       <c r="E10" s="237"/>
       <c r="G10" s="266">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="C11" s="267">
         <f>SUM(C8:C10)</f>
-        <v>32688.822196387209</v>
+        <v>32689.99892115331</v>
       </c>
       <c r="E11" s="237"/>
       <c r="G11" s="267">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="C12" s="266">
         <f>-C11*C41</f>
-        <v>-8172.2055490968023</v>
+        <v>-8172.4997302883276</v>
       </c>
       <c r="E12" s="237"/>
       <c r="G12" s="266">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="C14" s="269">
         <f>SUM(C11:C13)</f>
-        <v>21215.616647290408</v>
+        <v>21216.499190864983</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="243"/>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="C19" s="267">
         <f>C14+C17</f>
-        <v>21215.616647290408</v>
+        <v>21216.499190864983</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="234"/>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="C46" s="266">
         <f>BS!D75*C51</f>
-        <v>565.023935957135</v>
+        <v>566.20066072323493</v>
       </c>
       <c r="E46" s="237"/>
       <c r="G46" s="274">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="C48" s="267">
         <f>C45+C46</f>
-        <v>-6160.316064042865</v>
+        <v>-6159.139339276765</v>
       </c>
       <c r="E48" s="237"/>
       <c r="G48" s="267">
@@ -13344,7 +13344,7 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>5.3160295646195524E-3</v>
+        <v>5.3150141128828271E-3</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="234"/>
@@ -13401,7 +13401,7 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>2.820873854880461E-2</v>
+        <v>2.8209754000541334E-2</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="234"/>
@@ -13458,7 +13458,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>7.0521846372011525E-3</v>
+        <v>7.0524385001353336E-3</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="234"/>
@@ -13573,7 +13573,7 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>1.8307964097318396E-2</v>
+        <v>1.8308725686120939E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="234"/>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>1.8307964097318396E-2</v>
+        <v>1.8308725686120939E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="234"/>
@@ -13921,20 +13921,20 @@
       </c>
       <c r="C89" s="71">
         <f>C88*Common_Shares/scaling_factor</f>
-        <v>10078.010174699999</v>
+        <v>12431.459706899999</v>
       </c>
       <c r="E89" s="237"/>
       <c r="G89" s="71">
         <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
-        <v>10078.010174699999</v>
+        <v>12431.459706899999</v>
       </c>
       <c r="H89" s="71">
         <f t="shared" si="36"/>
-        <v>7659.2877327720007</v>
+        <v>9447.9093772439992</v>
       </c>
       <c r="I89" s="71">
         <f t="shared" si="36"/>
-        <v>6248.366308314</v>
+        <v>7707.5050182780005</v>
       </c>
       <c r="J89" s="71" t="str">
         <f t="shared" si="36"/>
@@ -13976,20 +13976,20 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.47502791656952054</v>
+        <v>0.58593359795439359</v>
       </c>
       <c r="E90" s="237"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.34966380454860868</v>
+        <v>0.43131842713552143</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
-        <v>0.41077377093060174</v>
+        <v>0.50669899052043332</v>
       </c>
       <c r="I90" s="152">
         <f t="shared" si="37"/>
-        <v>0.63325897520158103</v>
+        <v>0.78113965929644269</v>
       </c>
       <c r="J90" s="152" t="str">
         <f t="shared" si="37"/>
@@ -14052,20 +14052,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.033707865168539E-2</v>
+        <v>3.0574912891986061E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.033707865168539E-2</v>
+        <v>3.0574912891986061E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>2.3056179775280902E-2</v>
+        <v>2.323693379790941E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>1.8808988764044944E-2</v>
+        <v>1.8956445993031361E-2</v>
       </c>
       <c r="J92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>-0.16184656300127664</v>
+        <v>-0.1618163913450088</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="234"/>
@@ -14863,7 +14863,7 @@
       <c r="D115" s="52"/>
       <c r="E115" s="451" t="str">
         <f>DCF!F15&amp;"yrs Projection"</f>
-        <v>8yrs Projection</v>
+        <v>5yrs Projection</v>
       </c>
       <c r="F115" s="52"/>
       <c r="G115" s="22" t="str">
@@ -14918,11 +14918,11 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>2.820873854880461E-2</v>
+        <v>2.8209754000541334E-2</v>
       </c>
       <c r="E116" s="22">
         <f>E119/E117/E118</f>
-        <v>3.152381864639775E-2</v>
+        <v>3.9404773307997187E-2</v>
       </c>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
@@ -15092,11 +15092,11 @@
       </c>
       <c r="C119" s="62">
         <f>C11/C104</f>
-        <v>0.10738066551602132</v>
+        <v>0.10738453098072831</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="453">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
@@ -15215,22 +15215,22 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>8.2100437973506626</v>
+        <v>7.45264520230928</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>11.153570799341455</v>
+        <v>10.124202776744752</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.2156505837388378</v>
+        <v>6.5497149738110698</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>3.8183430392444015</v>
+        <v>3.4659464575026186</v>
       </c>
       <c r="J123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15272,22 +15272,22 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.0959756243307359E-2</v>
+        <v>6.4918512215237631E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>9.6400784782553636E-2</v>
+        <v>8.8189919658055338E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.2365173584605339E-2</v>
+        <v>5.705326632239608E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.3002100598482291E-2</v>
+        <v>3.0191171232601208E-2</v>
       </c>
       <c r="J124" s="74" t="str">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
@@ -15329,15 +15329,15 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1493740562205553</v>
+        <v>0.12204480871293903</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7787559908675655E-2</v>
+        <v>6.3555667627335943E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2413434367071232E-2</v>
+        <v>2.6483122284753517E-2</v>
       </c>
       <c r="J125" s="22" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16120,7 +16120,7 @@
       </c>
       <c r="C4" s="275">
         <f>Normalized_FCF!C19</f>
-        <v>21215.616647290408</v>
+        <v>21216.499190864983</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="F5" s="275">
         <f>BS!D66</f>
-        <v>31164.344007144173</v>
+        <v>30968.223212794182</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16180,7 +16180,7 @@
       </c>
       <c r="C6" s="283">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>412189.1234330709</v>
+        <v>412206.26999394834</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16202,7 +16202,7 @@
       </c>
       <c r="I6" s="305">
         <f>I7+I8</f>
-        <v>-6160.316064042865</v>
+        <v>-6159.139339276765</v>
       </c>
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
@@ -16213,14 +16213,14 @@
       </c>
       <c r="C7" s="275">
         <f>F7</f>
-        <v>17607.04400714417</v>
+        <v>17410.92321279418</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>424</v>
       </c>
       <c r="F7" s="283">
         <f>SUM(F4:F6)</f>
-        <v>17607.04400714417</v>
+        <v>17410.92321279418</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="C8" s="283">
         <f>C6+C7</f>
-        <v>429796.16744021507</v>
+        <v>429617.19320674252</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16254,7 +16254,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.8135941954341535</v>
+        <v>6.1158738858046107</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16266,7 +16266,7 @@
       </c>
       <c r="I8" s="313">
         <f>Normalized_FCF!C10</f>
-        <v>-6160.316064042865</v>
+        <v>-6159.139339276765</v>
       </c>
       <c r="J8" s="313"/>
       <c r="N8" s="304"/>
@@ -16279,7 +16279,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1</v>
+        <v>1.1196808250427246</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>429796.16744021507</v>
+        <v>481034.13334226509</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16326,7 +16326,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>166.32301654396133</v>
+        <v>150.91012353067066</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16375,7 +16375,7 @@
       </c>
       <c r="C15" s="148">
         <f>Scenarios!C45</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E15" s="308" t="str">
         <f>IF(F14="II","Change year","Terminal Year")</f>
@@ -16383,7 +16383,7 @@
       </c>
       <c r="F15" s="310">
         <f>IF(F14="II",_xlfn.CEILING.MATH(C15/2),C15+1)</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H15" s="97" t="s">
         <v>429</v>
@@ -16416,14 +16416,14 @@
       </c>
       <c r="C17" s="306">
         <f>Normalized_FCF!C77</f>
-        <v>2.820873854880461E-2</v>
+        <v>2.8209754000541334E-2</v>
       </c>
       <c r="E17" s="308" t="s">
         <v>551</v>
       </c>
       <c r="F17" s="311">
         <f>Scenarios!C40</f>
-        <v>3.152381864639775E-2</v>
+        <v>3.9404773307997187E-2</v>
       </c>
       <c r="H17" s="106" t="s">
         <v>412</v>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>164.13667399109832</v>
+        <v>175.03262541019447</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16516,11 +16516,11 @@
       </c>
       <c r="E21" s="299">
         <f>$C$17</f>
-        <v>2.820873854880461E-2</v>
+        <v>2.8209754000541334E-2</v>
       </c>
       <c r="F21" s="277">
         <f>C21*E21</f>
-        <v>33468.644030362062</v>
+        <v>33469.848826976689</v>
       </c>
       <c r="G21" s="299">
         <f t="shared" ref="G21:G50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16528,7 +16528,7 @@
       </c>
       <c r="H21" s="277">
         <f>(F21*(1-$I$10)+C21*(G21-$I$9))</f>
-        <v>21721.734640266794</v>
+        <v>21722.638237727762</v>
       </c>
       <c r="I21" s="299">
         <f>H21/C4-1</f>
@@ -16536,7 +16536,7 @@
       </c>
       <c r="J21" s="299">
         <f>H21/C21</f>
-        <v>1.8307964097318396E-2</v>
+        <v>1.8308725686120939E-2</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="L21" s="277">
         <f t="shared" ref="L21:L51" si="4">H21*K21</f>
-        <v>20253.36563195039</v>
+        <v>20254.20814706551</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16565,11 +16565,11 @@
       </c>
       <c r="E22" s="299">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
-        <v>2.820873854880461E-2</v>
+        <v>2.8209754000541334E-2</v>
       </c>
       <c r="F22" s="277">
         <f t="shared" ref="F22:F50" si="7">IF(A22="", 0,C22*E22)</f>
-        <v>34267.069229398236</v>
+        <v>34268.302767541078</v>
       </c>
       <c r="G22" s="299">
         <f t="shared" si="2"/>
@@ -16577,15 +16577,15 @@
       </c>
       <c r="H22" s="277">
         <f t="shared" ref="H22:H50" si="8">IF(A22="", 0,F22*(1-$I$10)+C22*(G22-$I$9))</f>
-        <v>22239.926542150613</v>
+        <v>22240.851695757745</v>
       </c>
       <c r="I22" s="299">
         <f t="shared" ref="I22:I50" si="9">IF(A22="", 0,H22/H21-1)</f>
-        <v>2.3855917147759476E-2</v>
+        <v>2.3855917147759254E-2</v>
       </c>
       <c r="J22" s="299">
         <f>IF(A22="", 0,H22/C22)</f>
-        <v>1.8307964097318396E-2</v>
+        <v>1.8308725686120939E-2</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16593,7 +16593,7 @@
       </c>
       <c r="L22" s="277">
         <f t="shared" si="4"/>
-        <v>19334.758269864316</v>
+        <v>19335.562572042312</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16614,11 +16614,11 @@
       </c>
       <c r="E23" s="299">
         <f t="shared" si="6"/>
-        <v>2.820873854880461E-2</v>
+        <v>2.8209754000541334E-2</v>
       </c>
       <c r="F23" s="277">
         <f t="shared" si="7"/>
-        <v>35084.541593831294</v>
+        <v>35085.80455915787</v>
       </c>
       <c r="G23" s="299">
         <f t="shared" si="2"/>
@@ -16626,7 +16626,7 @@
       </c>
       <c r="H23" s="277">
         <f t="shared" si="8"/>
-        <v>22770.480387112417</v>
+        <v>22771.427611107349</v>
       </c>
       <c r="I23" s="299">
         <f t="shared" si="9"/>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="J23" s="299">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,H23/C23)</f>
-        <v>1.8307964097318399E-2</v>
+        <v>1.8308725686120939E-2</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16642,7 +16642,7 @@
       </c>
       <c r="L23" s="277">
         <f t="shared" si="4"/>
-        <v>18457.815068738608</v>
+        <v>18458.582891157366</v>
       </c>
       <c r="N23" s="275"/>
       <c r="O23" s="275"/>
@@ -16671,11 +16671,11 @@
       </c>
       <c r="E24" s="299">
         <f t="shared" si="6"/>
-        <v>2.820873854880461E-2</v>
+        <v>2.8209754000541334E-2</v>
       </c>
       <c r="F24" s="277">
         <f t="shared" si="7"/>
-        <v>35921.515511260855</v>
+        <v>35922.808605783626</v>
       </c>
       <c r="G24" s="299">
         <f t="shared" si="2"/>
@@ -16683,15 +16683,15 @@
       </c>
       <c r="H24" s="277">
         <f t="shared" si="8"/>
-        <v>23313.691080642049</v>
+        <v>23314.660901534131</v>
       </c>
       <c r="I24" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759254E-2</v>
+        <v>2.3855917147759698E-2</v>
       </c>
       <c r="J24" s="299">
         <f t="shared" si="10"/>
-        <v>1.8307964097318396E-2</v>
+        <v>1.8308725686120943E-2</v>
       </c>
       <c r="K24" s="119">
         <f t="shared" si="3"/>
@@ -16699,7 +16699,7 @@
       </c>
       <c r="L24" s="277">
         <f t="shared" si="4"/>
-        <v>17620.646317712912</v>
+        <v>17621.379314940667</v>
       </c>
       <c r="N24" s="275"/>
       <c r="O24" s="275"/>
@@ -16713,7 +16713,7 @@
     <row r="25" spans="1:21">
       <c r="A25" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="B25" s="117">
         <v>5</v>
@@ -16728,11 +16728,11 @@
       </c>
       <c r="E25" s="299">
         <f t="shared" si="6"/>
-        <v>2.820873854880461E-2</v>
+        <v>3.9404773307997187E-2</v>
       </c>
       <c r="F25" s="277">
         <f t="shared" si="7"/>
-        <v>36778.456209119446</v>
+        <v>51375.807784920165</v>
       </c>
       <c r="G25" s="299">
         <f t="shared" si="2"/>
@@ -16740,15 +16740,15 @@
       </c>
       <c r="H25" s="277">
         <f t="shared" si="8"/>
-        <v>23869.860563470305</v>
+        <v>34817.874245320847</v>
       </c>
       <c r="I25" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759476E-2</v>
+        <v>0.49338969124915688</v>
       </c>
       <c r="J25" s="299">
         <f t="shared" si="10"/>
-        <v>1.8307964097318396E-2</v>
+        <v>2.6704990166712832E-2</v>
       </c>
       <c r="K25" s="119">
         <f t="shared" si="3"/>
@@ -16756,7 +16756,7 @@
       </c>
       <c r="L25" s="277">
         <f t="shared" si="4"/>
-        <v>16821.448015252441</v>
+        <v>24536.67712309886</v>
       </c>
       <c r="N25" s="275"/>
       <c r="O25" s="275"/>
@@ -16770,7 +16770,7 @@
     <row r="26" spans="1:21">
       <c r="A26" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="B26" s="117">
         <v>6</v>
@@ -16785,11 +16785,11 @@
       </c>
       <c r="E26" s="299">
         <f t="shared" si="6"/>
-        <v>2.820873854880461E-2</v>
+        <v>3.9404773307997187E-2</v>
       </c>
       <c r="F26" s="277">
         <f t="shared" si="7"/>
-        <v>37655.840013266701</v>
+        <v>52601.424798836437</v>
       </c>
       <c r="G26" s="299">
         <f t="shared" si="2"/>
@@ -16797,15 +16797,15 @@
       </c>
       <c r="H26" s="277">
         <f t="shared" si="8"/>
-        <v>24439.297979401024</v>
+        <v>35648.486568578322</v>
       </c>
       <c r="I26" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759476E-2</v>
+        <v>2.3855917147759254E-2</v>
       </c>
       <c r="J26" s="299">
         <f t="shared" si="10"/>
-        <v>1.8307964097318396E-2</v>
+        <v>2.6704990166712829E-2</v>
       </c>
       <c r="K26" s="119">
         <f t="shared" si="3"/>
@@ -16813,13 +16813,13 @@
       </c>
       <c r="L26" s="277">
         <f t="shared" si="4"/>
-        <v>16058.497981733937</v>
+        <v>23423.796792194709</v>
       </c>
     </row>
     <row r="27" spans="1:21">
       <c r="A27" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="B27" s="117">
         <v>7</v>
@@ -16834,11 +16834,11 @@
       </c>
       <c r="E27" s="299">
         <f t="shared" si="6"/>
-        <v>2.820873854880461E-2</v>
+        <v>3.9404773307997187E-2</v>
       </c>
       <c r="F27" s="277">
         <f t="shared" si="7"/>
-        <v>38554.154612752478</v>
+        <v>53856.280030691581</v>
       </c>
       <c r="G27" s="299">
         <f t="shared" si="2"/>
@@ -16846,7 +16846,7 @@
       </c>
       <c r="H27" s="277">
         <f t="shared" si="8"/>
-        <v>25022.31984714702</v>
+        <v>36498.913910601346</v>
       </c>
       <c r="I27" s="299">
         <f t="shared" si="9"/>
@@ -16854,7 +16854,7 @@
       </c>
       <c r="J27" s="299">
         <f t="shared" si="10"/>
-        <v>1.8307964097318396E-2</v>
+        <v>2.6704990166712829E-2</v>
       </c>
       <c r="K27" s="119">
         <f t="shared" si="3"/>
@@ -16862,7 +16862,7 @@
       </c>
       <c r="L27" s="277">
         <f t="shared" si="4"/>
-        <v>15330.152148348388</v>
+        <v>22361.392025879035</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -16883,11 +16883,11 @@
       </c>
       <c r="E28" s="299">
         <f t="shared" si="6"/>
-        <v>3.152381864639775E-2</v>
+        <v>3.9404773307997187E-2</v>
       </c>
       <c r="F28" s="277">
         <f t="shared" si="7"/>
-        <v>44112.856787992234</v>
+        <v>55141.070984990292</v>
       </c>
       <c r="G28" s="299">
         <f t="shared" si="2"/>
@@ -16895,15 +16895,15 @@
       </c>
       <c r="H28" s="277">
         <f t="shared" si="8"/>
-        <v>29098.468329087314</v>
+        <v>37369.628976835862</v>
       </c>
       <c r="I28" s="299">
         <f t="shared" si="9"/>
-        <v>0.16290050270479006</v>
+        <v>2.3855917147759698E-2</v>
       </c>
       <c r="J28" s="299">
         <f t="shared" si="10"/>
-        <v>2.0794274170513251E-2</v>
+        <v>2.6704990166712832E-2</v>
       </c>
       <c r="K28" s="119">
         <f t="shared" si="3"/>
@@ -16911,7 +16911,7 @@
       </c>
       <c r="L28" s="277">
         <f t="shared" si="4"/>
-        <v>16622.323207324247</v>
+        <v>21347.173465134711</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -16932,11 +16932,11 @@
       </c>
       <c r="E29" s="299">
         <f t="shared" si="6"/>
-        <v>3.152381864639775E-2</v>
+        <v>3.9404773307997187E-2</v>
       </c>
       <c r="F29" s="277">
         <f t="shared" si="7"/>
-        <v>45165.209444677559</v>
+        <v>56456.511805846945</v>
       </c>
       <c r="G29" s="299">
         <f t="shared" si="2"/>
@@ -16944,7 +16944,7 @@
       </c>
       <c r="H29" s="277">
         <f t="shared" si="8"/>
-        <v>29792.638978672723</v>
+        <v>38261.115749549768</v>
       </c>
       <c r="I29" s="299">
         <f t="shared" si="9"/>
@@ -16952,7 +16952,7 @@
       </c>
       <c r="J29" s="299">
         <f t="shared" si="10"/>
-        <v>2.0794274170513251E-2</v>
+        <v>2.6704990166712829E-2</v>
       </c>
       <c r="K29" s="119">
         <f t="shared" si="3"/>
@@ -16960,7 +16960,7 @@
       </c>
       <c r="L29" s="277">
         <f t="shared" si="4"/>
-        <v>15868.404636420935</v>
+        <v>20378.955586627329</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -16981,11 +16981,11 @@
       </c>
       <c r="E30" s="299">
         <f t="shared" si="6"/>
-        <v>3.152381864639775E-2</v>
+        <v>3.9404773307997187E-2</v>
       </c>
       <c r="F30" s="277">
         <f t="shared" si="7"/>
-        <v>46242.666939150993</v>
+        <v>57803.333673938738</v>
       </c>
       <c r="G30" s="299">
         <f t="shared" si="2"/>
@@ -16993,15 +16993,15 @@
       </c>
       <c r="H30" s="277">
         <f t="shared" si="8"/>
-        <v>30503.369705761052</v>
+        <v>39173.869756851869</v>
       </c>
       <c r="I30" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759476E-2</v>
+        <v>2.3855917147759698E-2</v>
       </c>
       <c r="J30" s="299">
         <f t="shared" si="10"/>
-        <v>2.0794274170513251E-2</v>
+        <v>2.6704990166712832E-2</v>
       </c>
       <c r="K30" s="119">
         <f t="shared" si="3"/>
@@ -17009,32 +17009,32 @@
       </c>
       <c r="L30" s="277">
         <f t="shared" si="4"/>
-        <v>15148.680636545005</v>
+        <v>19454.651993155978</v>
       </c>
     </row>
     <row r="31" spans="1:21">
       <c r="A31" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v/>
       </c>
       <c r="B31" s="117">
         <v>11</v>
       </c>
       <c r="C31" s="277">
         <f t="shared" si="5"/>
-        <v>1501906.5012846424</v>
+        <v>0</v>
       </c>
       <c r="D31" s="299">
         <f t="shared" si="1"/>
-        <v>2.38559171477595E-2</v>
+        <v>0</v>
       </c>
       <c r="E31" s="299">
         <f t="shared" si="6"/>
-        <v>3.152381864639775E-2</v>
+        <v>0</v>
       </c>
       <c r="F31" s="277">
         <f t="shared" si="7"/>
-        <v>47345.828170342815</v>
+        <v>0</v>
       </c>
       <c r="G31" s="299">
         <f t="shared" si="2"/>
@@ -17042,48 +17042,48 @@
       </c>
       <c r="H31" s="277">
         <f t="shared" si="8"/>
-        <v>31231.05556618917</v>
+        <v>0</v>
       </c>
       <c r="I31" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759698E-2</v>
+        <v>0</v>
       </c>
       <c r="J31" s="299">
         <f t="shared" si="10"/>
-        <v>2.0794274170513254E-2</v>
+        <v>0</v>
       </c>
       <c r="K31" s="119">
         <f t="shared" si="3"/>
-        <v>0.46305192135840806</v>
+        <v>0</v>
       </c>
       <c r="L31" s="277">
         <f t="shared" si="4"/>
-        <v>14461.600285975101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:21">
       <c r="A32" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v/>
       </c>
       <c r="B32" s="117">
         <v>12</v>
       </c>
       <c r="C32" s="277">
         <f t="shared" si="5"/>
-        <v>1537735.85834297</v>
+        <v>0</v>
       </c>
       <c r="D32" s="299">
         <f t="shared" si="1"/>
-        <v>2.38559171477595E-2</v>
+        <v>0</v>
       </c>
       <c r="E32" s="299">
         <f t="shared" si="6"/>
-        <v>3.152381864639775E-2</v>
+        <v>0</v>
       </c>
       <c r="F32" s="277">
         <f t="shared" si="7"/>
-        <v>48475.306324466568</v>
+        <v>0</v>
       </c>
       <c r="G32" s="299">
         <f t="shared" si="2"/>
@@ -17091,48 +17091,48 @@
       </c>
       <c r="H32" s="277">
         <f t="shared" si="8"/>
-        <v>31976.101040213245</v>
+        <v>0</v>
       </c>
       <c r="I32" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759254E-2</v>
+        <v>0</v>
       </c>
       <c r="J32" s="299">
         <f t="shared" si="10"/>
-        <v>2.0794274170513251E-2</v>
+        <v>0</v>
       </c>
       <c r="K32" s="119">
         <f t="shared" si="3"/>
-        <v>0.43175004322462285</v>
+        <v>0</v>
       </c>
       <c r="L32" s="277">
         <f t="shared" si="4"/>
-        <v>13805.683006266976</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:21">
       <c r="A33" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v/>
       </c>
       <c r="B33" s="117">
         <v>13</v>
       </c>
       <c r="C33" s="277">
         <f t="shared" si="5"/>
-        <v>1574419.9575747387</v>
+        <v>0</v>
       </c>
       <c r="D33" s="299">
         <f t="shared" si="1"/>
-        <v>2.38559171477595E-2</v>
+        <v>0</v>
       </c>
       <c r="E33" s="299">
         <f t="shared" si="6"/>
-        <v>3.152381864639775E-2</v>
+        <v>0</v>
       </c>
       <c r="F33" s="277">
         <f t="shared" si="7"/>
-        <v>49631.729215855303</v>
+        <v>0</v>
       </c>
       <c r="G33" s="299">
         <f t="shared" si="2"/>
@@ -17140,23 +17140,23 @@
       </c>
       <c r="H33" s="277">
         <f t="shared" si="8"/>
-        <v>32738.920257336958</v>
+        <v>0</v>
       </c>
       <c r="I33" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759476E-2</v>
+        <v>0</v>
       </c>
       <c r="J33" s="299">
         <f t="shared" si="10"/>
-        <v>2.0794274170513251E-2</v>
+        <v>0</v>
       </c>
       <c r="K33" s="119">
         <f t="shared" si="3"/>
-        <v>0.40256414286678116</v>
+        <v>0</v>
       </c>
       <c r="L33" s="277">
         <f t="shared" si="4"/>
-        <v>13179.515371778751</v>
+        <v>0</v>
       </c>
       <c r="N33" s="275"/>
       <c r="O33" s="275"/>
@@ -17170,26 +17170,26 @@
     <row r="34" spans="1:21">
       <c r="A34" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v/>
       </c>
       <c r="B34" s="117">
         <v>14</v>
       </c>
       <c r="C34" s="277">
         <f t="shared" si="5"/>
-        <v>1611979.1896384207</v>
+        <v>0</v>
       </c>
       <c r="D34" s="299">
         <f t="shared" si="1"/>
-        <v>2.38559171477595E-2</v>
+        <v>0</v>
       </c>
       <c r="E34" s="299">
         <f t="shared" si="6"/>
-        <v>3.152381864639775E-2</v>
+        <v>0</v>
       </c>
       <c r="F34" s="277">
         <f t="shared" si="7"/>
-        <v>50815.739635928781</v>
+        <v>0</v>
       </c>
       <c r="G34" s="299">
         <f t="shared" si="2"/>
@@ -17197,23 +17197,23 @@
       </c>
       <c r="H34" s="277">
         <f t="shared" si="8"/>
-        <v>33519.937226503098</v>
+        <v>0</v>
       </c>
       <c r="I34" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759698E-2</v>
+        <v>0</v>
       </c>
       <c r="J34" s="299">
         <f t="shared" si="10"/>
-        <v>2.0794274170513254E-2</v>
+        <v>0</v>
       </c>
       <c r="K34" s="119">
         <f t="shared" si="3"/>
-        <v>0.37535118216016894</v>
+        <v>0</v>
       </c>
       <c r="L34" s="277">
         <f t="shared" si="4"/>
-        <v>12581.748063902593</v>
+        <v>0</v>
       </c>
       <c r="N34" s="275"/>
       <c r="O34" s="275"/>
@@ -17227,26 +17227,26 @@
     <row r="35" spans="1:21">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v/>
       </c>
       <c r="B35" s="117">
         <v>15</v>
       </c>
       <c r="C35" s="277">
         <f t="shared" si="5"/>
-        <v>1650434.4316303474</v>
+        <v>0</v>
       </c>
       <c r="D35" s="299">
         <f t="shared" si="1"/>
-        <v>2.38559171477595E-2</v>
+        <v>0</v>
       </c>
       <c r="E35" s="299">
         <f t="shared" si="6"/>
-        <v>3.152381864639775E-2</v>
+        <v>0</v>
       </c>
       <c r="F35" s="277">
         <f t="shared" si="7"/>
-        <v>52027.995710485615</v>
+        <v>0</v>
       </c>
       <c r="G35" s="299">
         <f t="shared" si="2"/>
@@ -17254,23 +17254,23 @@
       </c>
       <c r="H35" s="277">
         <f t="shared" si="8"/>
-        <v>34319.586071776648</v>
+        <v>0</v>
       </c>
       <c r="I35" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759254E-2</v>
+        <v>0</v>
       </c>
       <c r="J35" s="299">
         <f t="shared" si="10"/>
-        <v>2.0794274170513251E-2</v>
+        <v>0</v>
       </c>
       <c r="K35" s="119">
         <f t="shared" si="3"/>
-        <v>0.34997779222393377</v>
+        <v>0</v>
       </c>
       <c r="L35" s="277">
         <f t="shared" si="4"/>
-        <v>12011.09296343966</v>
+        <v>0</v>
       </c>
       <c r="N35" s="275"/>
       <c r="O35" s="275"/>
@@ -18054,11 +18054,11 @@
       </c>
       <c r="B51" s="316">
         <f>C15+1</f>
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C51" s="277">
         <f>VLOOKUP(C15,B21:C50,2,FALSE)*(1+Terminal_Growth)</f>
-        <v>1683443.1202629544</v>
+        <v>1496250.2102620071</v>
       </c>
       <c r="D51" s="301">
         <f>Terminal_Growth</f>
@@ -18066,11 +18066,11 @@
       </c>
       <c r="E51" s="301">
         <f>F17</f>
-        <v>3.152381864639775E-2</v>
+        <v>3.9404773307997187E-2</v>
       </c>
       <c r="F51" s="277">
         <f>C51*E51</f>
-        <v>53068.555624695335</v>
+        <v>58959.400347417519</v>
       </c>
       <c r="G51" s="299">
         <f>F18</f>
@@ -18078,20 +18078,20 @@
       </c>
       <c r="H51" s="277">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/Equity_Cost</f>
-        <v>482841.07300982339</v>
+        <v>551135.82278605388</v>
       </c>
       <c r="I51" s="415">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/VLOOKUP(C15,B21:H50,COLUMN(H20)-1,FALSE)-1</f>
-        <v>2.0000000000000462E-2</v>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="J51" s="454"/>
       <c r="K51" s="119">
         <f>1/(1+Equity_Cost)^C15</f>
-        <v>0.34997779222393377</v>
+        <v>0.49662318565689262</v>
       </c>
       <c r="L51" s="277">
         <f t="shared" si="4"/>
-        <v>168983.65272701322</v>
+        <v>273706.82804164273</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18104,7 +18104,7 @@
       <c r="K52" s="468"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
-        <v>406539.38433226751</v>
+        <v>480879.20795293921</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18128,7 +18128,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>406539.38433226751</v>
+        <v>480879.20795293921</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18163,19 +18163,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>335881.27265561995</v>
+        <v>425732.60916437849</v>
       </c>
       <c r="C56" s="118">
-        <v>339240.08538217616</v>
+        <v>429989.9352560222</v>
       </c>
       <c r="D56" s="118">
-        <v>342598.89810873242</v>
+        <v>434247.26134766615</v>
       </c>
       <c r="E56" s="118">
-        <v>345957.71083528857</v>
+        <v>438504.58743930992</v>
       </c>
       <c r="F56" s="118">
-        <v>352675.33628840098</v>
+        <v>447019.23962259752</v>
       </c>
       <c r="G56" s="295"/>
       <c r="H56" s="295"/>
@@ -18189,19 +18189,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>335462.29123300221</v>
+        <v>425194.53340951959</v>
       </c>
       <c r="C57" s="118">
-        <v>342005.29053327732</v>
+        <v>433541.14246640983</v>
       </c>
       <c r="D57" s="118">
-        <v>348611.42599965032</v>
+        <v>441968.83397325611</v>
       </c>
       <c r="E57" s="118">
-        <v>355280.69763212116</v>
+        <v>450477.6079300589</v>
       </c>
       <c r="F57" s="118">
-        <v>368808.64939535683</v>
+        <v>467738.40319353342</v>
       </c>
       <c r="G57" s="295"/>
       <c r="H57" s="295"/>
@@ -18215,19 +18215,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>335071.63256389473</v>
+        <v>424692.83107398672</v>
       </c>
       <c r="C58" s="118">
-        <v>344609.35319305555</v>
+        <v>436885.40286966495</v>
       </c>
       <c r="D58" s="118">
-        <v>354329.63434346032</v>
+        <v>449312.42751927185</v>
       </c>
       <c r="E58" s="118">
-        <v>364234.24206171342</v>
+        <v>461976.17306336574</v>
       </c>
       <c r="F58" s="118">
-        <v>384603.50138818054</v>
+        <v>488022.89899724693</v>
       </c>
       <c r="G58" s="295"/>
       <c r="H58" s="295"/>
@@ -18241,19 +18241,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>334707.38205656834</v>
+        <v>424225.04334854812</v>
       </c>
       <c r="C59" s="118">
-        <v>347061.66394958313</v>
+        <v>440034.77630303346</v>
       </c>
       <c r="D59" s="118">
-        <v>359767.93039072014</v>
+        <v>456296.5444581398</v>
       </c>
       <c r="E59" s="118">
-        <v>372832.9840313915</v>
+        <v>473019.08410048054</v>
       </c>
       <c r="F59" s="118">
-        <v>400066.99284968642</v>
+        <v>507881.84593794547</v>
       </c>
       <c r="G59" s="295"/>
       <c r="H59" s="295"/>
@@ -18267,19 +18267,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>331862.93585441378</v>
+        <v>415330.10959385836</v>
       </c>
       <c r="C60" s="118">
-        <v>346815.90060871071</v>
+        <v>434371.83053504658</v>
       </c>
       <c r="D60" s="118">
-        <v>362334.00277740869</v>
+        <v>454138.27927457797</v>
       </c>
       <c r="E60" s="118">
-        <v>378433.62116460834</v>
+        <v>474650.49024716648</v>
       </c>
       <c r="F60" s="118">
-        <v>412444.512794243</v>
+        <v>517998.37984638795</v>
       </c>
       <c r="G60" s="295"/>
       <c r="H60" s="295"/>
@@ -18293,19 +18293,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>331546.26684494189</v>
+        <v>414923.42827790068</v>
       </c>
       <c r="C61" s="118">
-        <v>348990.72226495814</v>
+        <v>437164.83934450021</v>
       </c>
       <c r="D61" s="118">
-        <v>367252.90950586076</v>
+        <v>460455.37189041753</v>
       </c>
       <c r="E61" s="118">
-        <v>386364.38038076699</v>
+        <v>484835.54624601488</v>
       </c>
       <c r="F61" s="118">
-        <v>427265.99221355515</v>
+        <v>537032.82456435403</v>
       </c>
       <c r="G61" s="295"/>
       <c r="H61" s="295"/>
@@ -18319,19 +18319,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>328915.50908366649</v>
+        <v>406657.27502915217</v>
       </c>
       <c r="C62" s="118">
-        <v>348632.54293834127</v>
+        <v>431669.13932001765</v>
       </c>
       <c r="D62" s="118">
-        <v>369452.58431348647</v>
+        <v>458093.52774163929</v>
       </c>
       <c r="E62" s="118">
-        <v>391428.8083346379</v>
+        <v>485998.70097900811</v>
       </c>
       <c r="F62" s="118">
-        <v>439072.90377984883</v>
+        <v>546537.79948063416</v>
       </c>
       <c r="G62" s="295"/>
       <c r="H62" s="295"/>
@@ -18345,19 +18345,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>328640.20607229671</v>
+        <v>406303.71788398759</v>
       </c>
       <c r="C63" s="118">
-        <v>350561.27453318192</v>
+        <v>434146.10763601138</v>
       </c>
       <c r="D63" s="118">
-        <v>373901.70646368701</v>
+        <v>463807.30078787968</v>
       </c>
       <c r="E63" s="118">
-        <v>398743.47622053081</v>
+        <v>495392.54335906752</v>
       </c>
       <c r="F63" s="118">
-        <v>453279.02616326697</v>
+        <v>564781.9735953653</v>
       </c>
       <c r="G63" s="295"/>
       <c r="H63" s="295"/>
@@ -18371,19 +18371,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>326205.89530963835</v>
+        <v>398620.24902084155</v>
       </c>
       <c r="C64" s="118">
-        <v>350111.57118161034</v>
+        <v>428826.32437775761</v>
       </c>
       <c r="D64" s="118">
-        <v>375775.91568596452</v>
+        <v>461281.37620356132</v>
       </c>
       <c r="E64" s="118">
-        <v>403317.35725301254</v>
+        <v>496137.35554911941</v>
       </c>
       <c r="F64" s="118">
-        <v>464540.20974460174</v>
+        <v>573704.79853197373</v>
       </c>
       <c r="G64" s="295"/>
       <c r="H64" s="295"/>
@@ -18397,19 +18397,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>325966.55471803562</v>
+        <v>398312.87651565892</v>
       </c>
       <c r="C65" s="118">
-        <v>351822.05882286152</v>
+        <v>431023.01348867989</v>
       </c>
       <c r="D65" s="118">
-        <v>379800.12045344012</v>
+        <v>466449.45025428559</v>
       </c>
       <c r="E65" s="118">
-        <v>410063.79411014233</v>
+        <v>504801.44877269905</v>
       </c>
       <c r="F65" s="118">
-        <v>478156.52343793615</v>
+        <v>591191.51243723708</v>
       </c>
       <c r="G65" s="295"/>
       <c r="H65" s="295"/>
@@ -18423,19 +18423,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>319302.98988067359</v>
+        <v>377850.06405640912</v>
       </c>
       <c r="C66" s="277">
-        <v>352954.40457184298</v>
+        <v>419845.11706335627</v>
       </c>
       <c r="D66" s="118">
-        <v>390750.83689731208</v>
+        <v>467116.37371734786</v>
       </c>
       <c r="E66" s="118">
-        <v>433206.25078271062</v>
+        <v>520322.16713043768</v>
       </c>
       <c r="F66" s="118">
-        <v>534459.04101677751</v>
+        <v>647567.46558868885</v>
       </c>
       <c r="G66" s="295"/>
       <c r="H66" s="295"/>
@@ -18458,19 +18458,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>315435.56851623469</v>
+        <v>366227.43151217012</v>
       </c>
       <c r="C67" s="277">
-        <v>354803.22478163568</v>
+        <v>414977.28938032209</v>
       </c>
       <c r="D67" s="118">
-        <v>400489.47791872779</v>
+        <v>471749.4844506185</v>
       </c>
       <c r="E67" s="118">
-        <v>453568.72641554428</v>
+        <v>537919.06884123036</v>
       </c>
       <c r="F67" s="118">
-        <v>587132.51263309864</v>
+        <v>705142.17727197718</v>
       </c>
       <c r="G67" s="295"/>
       <c r="H67" s="295"/>
@@ -18493,19 +18493,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>310942.50449930388</v>
+        <v>352067.49067624839</v>
       </c>
       <c r="C68" s="277">
-        <v>354264.97958038311</v>
+        <v>404929.92029805295</v>
       </c>
       <c r="D68" s="118">
-        <v>406013.43240071903</v>
+        <v>468420.29340423224</v>
       </c>
       <c r="E68" s="118">
-        <v>467999.80875472003</v>
+        <v>544851.41285058844</v>
       </c>
       <c r="F68" s="118">
-        <v>631989.5981761358</v>
+        <v>748421.72936403961</v>
       </c>
       <c r="G68" s="295"/>
       <c r="H68" s="295"/>
@@ -18528,19 +18528,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>308360.02611143579</v>
+        <v>344060.4324212338</v>
       </c>
       <c r="C69" s="277">
-        <v>354614.49004356016</v>
+        <v>400014.77431201236</v>
       </c>
       <c r="D69" s="118">
-        <v>411259.3275759751</v>
+        <v>469031.08139142004</v>
       </c>
       <c r="E69" s="118">
-        <v>480978.93783483584</v>
+        <v>554531.93290110049</v>
       </c>
       <c r="F69" s="118">
-        <v>674164.27333690226</v>
+        <v>793526.38970606239</v>
       </c>
       <c r="G69" s="295"/>
       <c r="H69" s="295"/>
@@ -18637,23 +18637,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>166.32301654396133</v>
+        <v>150.91012353067066</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>166.32301654396133</v>
+        <v>150.91012353067066</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>166.32301654396133</v>
+        <v>150.91012353067066</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>166.32301654396133</v>
+        <v>150.91012353067066</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>166.32301654396133</v>
+        <v>150.91012353067066</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18668,23 +18668,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>136.79331644709498</v>
+        <v>155.66147321453923</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>138.0931136696116</v>
+        <v>157.15692920782655</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>139.39291089212824</v>
+        <v>158.65238520111396</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>140.6927081146448</v>
+        <v>160.14784119440131</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>143.29230255967803</v>
+        <v>163.13875318097601</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18699,23 +18699,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>136.63117853297467</v>
+        <v>155.47246523273915</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>139.16319594799305</v>
+        <v>158.40434930012418</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>141.7196458693806</v>
+        <v>161.36471491511139</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>144.30052829713728</v>
+        <v>164.35356207770099</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>149.53559067175823</v>
+        <v>170.41670104568695</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18730,23 +18730,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>136.48000099067133</v>
+        <v>155.29623401427753</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>140.17091911924271</v>
+        <v>159.57907591384958</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>143.93248472886535</v>
+        <v>163.94427324450763</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>147.76538124629096</v>
+        <v>168.39262269289787</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>155.64790071155696</v>
+        <v>177.54196468945986</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18761,23 +18761,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>136.33904290926958</v>
+        <v>155.13191586186574</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>141.11991716396264</v>
+        <v>160.68534526570286</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>146.03700280501869</v>
+        <v>166.39755948784941</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>151.09293233032651</v>
+        <v>172.27162729304024</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>161.63198047080053</v>
+        <v>184.51774727776902</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18792,23 +18792,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>135.23829583756572</v>
+        <v>152.00742370246698</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>141.02481138288209</v>
+        <v>158.69614218233576</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>147.03002445657535</v>
+        <v>165.6394332521833</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>153.26027334714544</v>
+        <v>172.84468560406225</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>166.42184741347879</v>
+        <v>188.07134663544323</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18823,23 +18823,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>135.11575089907768</v>
+        <v>151.86457018403425</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>141.86642637555769</v>
+        <v>159.67723258356196</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>148.93354865514405</v>
+        <v>167.85841620278481</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>156.32932769486436</v>
+        <v>176.42235447592546</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>172.15748061222556</v>
+        <v>194.75750922191975</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18855,23 +18855,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>134.09769722666417</v>
+        <v>148.96094754598076</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>141.7278177266686</v>
+        <v>157.74677732549443</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>149.78478134900226</v>
+        <v>167.02877949855542</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>158.28916586506989</v>
+        <v>176.83093175639016</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>176.72653286662219</v>
+        <v>198.09628839894748</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18886,23 +18886,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>133.99116014982755</v>
+        <v>148.83675476856024</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>142.47420050357451</v>
+        <v>158.61685329186363</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>151.50650776969408</v>
+        <v>169.0358365015544</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>161.11980447928735</v>
+        <v>180.13067379748725</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>182.22403448995036</v>
+        <v>204.50485540442162</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18918,23 +18918,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>133.04912776349389</v>
+        <v>146.13780962945489</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>142.30017378195717</v>
+        <v>156.7481916988134</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>152.23179141598686</v>
+        <v>168.14856383864398</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>162.88981023612411</v>
+        <v>180.39230136124675</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>186.5819002993598</v>
+        <v>207.63914480139675</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18950,23 +18950,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>132.95650746533289</v>
+        <v>146.02983996841596</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>142.96210026201041</v>
+        <v>157.51981497257805</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>153.78908281787039</v>
+        <v>169.96393507085429</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>165.50055415151112</v>
+        <v>183.43570697751699</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>191.8511570755949</v>
+        <v>213.7816414177249</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18982,23 +18982,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>130.37783345972883</v>
+        <v>138.84193965893206</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>143.4002967258435</v>
+        <v>153.59339452890907</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>158.02680369637426</v>
+        <v>170.19820293486828</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>174.45624872399679</v>
+        <v>188.88761523837638</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>213.63917025985603</v>
+        <v>233.58462460548282</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19014,23 +19014,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>128.88121427996492</v>
+        <v>134.75929831976518</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>144.11575530280473</v>
+        <v>151.88348978443301</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>161.79547423005448</v>
+        <v>171.8256594802414</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>182.33614302767717</v>
+        <v>195.06881713840107</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>234.02281105229721</v>
+        <v>253.80869149515831</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19046,23 +19046,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>127.1424831850093</v>
+        <v>129.78538560275803</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>143.90746455408583</v>
+        <v>148.35418571248488</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>163.93314050606685</v>
+        <v>170.65622622661093</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>187.92069991412234</v>
+        <v>197.50391728651343</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>251.3816577477514</v>
+        <v>269.01134785025954</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19078,23 +19078,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>126.14311272019576</v>
+        <v>126.9727743537477</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>144.04271851620351</v>
+        <v>146.62765963379576</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>165.9632030708834</v>
+        <v>170.87077557904624</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>192.94337825389277</v>
+        <v>200.9043595866913</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>267.70246217995032</v>
+        <v>284.85510357431883</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19137,11 +19137,11 @@
       </c>
       <c r="D90" s="133">
         <f>Scenarios!D29</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>213.63917025985603</v>
+        <v>213.7816414177249</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19165,11 +19165,11 @@
       </c>
       <c r="D91" s="133">
         <f>Scenarios!D22</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>174.45624872399679</v>
+        <v>183.43570697751699</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19193,11 +19193,11 @@
       </c>
       <c r="D92" s="133">
         <f>Scenarios!D23</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>158.02680369637426</v>
+        <v>169.96393507085429</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19221,11 +19221,11 @@
       </c>
       <c r="D93" s="133">
         <f>Scenarios!D24</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>143.4002967258435</v>
+        <v>157.51981497257805</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19249,11 +19249,11 @@
       </c>
       <c r="D94" s="133">
         <f>Scenarios!D30</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>130.37783345972883</v>
+        <v>146.02983996841596</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19475,7 +19475,7 @@
       </c>
       <c r="C9" s="447">
         <f>Normalized_FCF!C19</f>
-        <v>21215.616647290408</v>
+        <v>21216.499190864983</v>
       </c>
       <c r="D9" s="469"/>
       <c r="E9" s="469"/>
@@ -19561,7 +19561,7 @@
         <v>111</v>
       </c>
       <c r="C18" s="137">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E18" s="450" t="s">
         <v>544</v>
@@ -19609,11 +19609,11 @@
       </c>
       <c r="D22" s="325">
         <f>C18</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>174.45624872399679</v>
+        <v>183.43570697751699</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19633,11 +19633,11 @@
       </c>
       <c r="D23" s="325">
         <f>C18</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>158.02680369637426</v>
+        <v>169.96393507085429</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19656,11 +19656,11 @@
       </c>
       <c r="D24" s="325">
         <f>C18</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>143.4002967258435</v>
+        <v>157.51981497257805</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19676,7 +19676,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>157.65606595926607</v>
+        <v>169.54725942761775</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19719,11 +19719,11 @@
       </c>
       <c r="D29" s="325">
         <f>C18</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>213.63917025985603</v>
+        <v>213.7816414177249</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19742,11 +19742,11 @@
       </c>
       <c r="D30" s="325">
         <f>C18</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>130.37783345972883</v>
+        <v>146.02983996841596</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19791,7 +19791,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>115.7</v>
+        <v>114.8</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19802,7 +19802,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.1520364330127415</v>
+        <v>0.17769847372279465</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19811,7 +19811,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>166.32301654396133</v>
+        <v>150.91012353067066</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19822,7 +19822,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>1.7887835002344692E-2</v>
+        <v>7.27906152286414E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19831,7 +19831,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>164.68961997937771</v>
+        <v>175.00654575317373</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19869,7 +19869,7 @@
       </c>
       <c r="C40" s="126">
         <f>Normalized_FCF!E116</f>
-        <v>3.152381864639775E-2</v>
+        <v>3.9404773307997187E-2</v>
       </c>
       <c r="E40" s="97" t="s">
         <v>401</v>
@@ -19909,7 +19909,7 @@
       </c>
       <c r="C45" s="150">
         <f>C18</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D45" s="137"/>
       <c r="E45" s="221" t="s">
@@ -19934,7 +19934,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>164.13667399109832</v>
+        <v>175.03262541019447</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="C49" s="218" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
-        <v xml:space="preserve">Negative Growth </v>
+        <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="E49" s="222" t="s">
         <v>254</v>
@@ -19962,7 +19962,7 @@
       </c>
       <c r="C50" s="218" t="str">
         <f>IF(C36&lt;C35,"Y","N")</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E50" s="126"/>
     </row>
@@ -19972,7 +19972,7 @@
       </c>
       <c r="C51" s="218" t="str">
         <f>IF(C50="Y","N",IF(C46&gt;8%,"N","Y"))</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E51" s="221" t="s">
         <v>247</v>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>4.1372335404546691E-2</v>
+        <v>3.4946543624890122E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20075,23 +20075,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>6.4227790321465204</v>
+        <v>6.4227790321465186</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>75.893834091879143</v>
+        <v>80.648177766439517</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>82.316613124025665</v>
+        <v>87.070956798586039</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.50017121216058857</v>
+        <v>0.50247028518927839</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20100,23 +20100,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>7.3850538549144664</v>
+        <v>7.3850538549144646</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>95.127578327438428</v>
+        <v>101.08681343143613</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>102.51263218235289</v>
+        <v>108.47186728635059</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.37754041696623364</v>
+        <v>0.38018394215186968</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20150,11 +20150,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>118.04299674187726</v>
+        <v>125.43776051420784</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>126.51123371392191</v>
+        <v>133.90599748625249</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20162,7 +20162,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.23182023414855446</v>
+        <v>0.23485149135443628</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20175,11 +20175,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>133.49786643239455</v>
+        <v>141.86079531106711</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>142.66730347977182</v>
+        <v>151.03023235844438</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20187,7 +20187,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.1337201245735069</v>
+        <v>0.13700238063406578</v>
       </c>
     </row>
   </sheetData>
@@ -20235,7 +20235,7 @@
       </c>
       <c r="F3" s="436">
         <f>Thesis!F3</f>
-        <v>46038</v>
+        <v>46045</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -20298,7 +20298,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>115.7</v>
+        <v>114.8</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20307,7 +20307,7 @@
       </c>
       <c r="C9" s="353">
         <f>Common_Shares</f>
-        <v>2584105173</v>
+        <v>3187553771</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -20316,14 +20316,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>298980.96851610002</v>
+        <v>365931.17291079997</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.1520364330127415</v>
+        <v>0.17769847372279465</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20331,13 +20331,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20375,7 +20375,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1</v>
+        <v>1.1196808250427246</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20401,7 +20401,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>164.68961997937771</v>
+        <v>175.00654575317373</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20417,7 +20417,7 @@
       </c>
       <c r="C19" s="352" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
-        <v xml:space="preserve">Negative Growth </v>
+        <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D19" s="343" t="s">
         <v>363</v>
@@ -20453,14 +20453,14 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>82.316613124025665</v>
+        <v>87.070956798586039</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20469,14 +20469,14 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>102.51263218235289</v>
+        <v>108.47186728635059</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20485,7 +20485,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>126.51123371392191</v>
+        <v>133.90599748625249</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20501,7 +20501,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>142.66730347977182</v>
+        <v>151.03023235844438</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20522,22 +20522,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20646,7 +20646,7 @@
       </c>
       <c r="C44" s="376">
         <f>Normalized_FCF!C46</f>
-        <v>565.023935957135</v>
+        <v>566.20066072323493</v>
       </c>
       <c r="D44" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20676,7 +20676,7 @@
       </c>
       <c r="C46" s="373">
         <f>Normalized_FCF!C10</f>
-        <v>-6160.316064042865</v>
+        <v>-6159.139339276765</v>
       </c>
       <c r="D46" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20716,7 +20716,7 @@
       </c>
       <c r="C52" s="373">
         <f>Normalized_FCF!C12</f>
-        <v>-8172.2055490968023</v>
+        <v>-8172.4997302883276</v>
       </c>
       <c r="D52" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20727,10 +20727,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20746,22 +20746,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20782,7 +20782,7 @@
       </c>
       <c r="C61" s="373">
         <f>Normalized_FCF!C19</f>
-        <v>21215.616647290408</v>
+        <v>21216.499190864983</v>
       </c>
       <c r="D61" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20795,7 +20795,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.0959756243307359E-2</v>
+        <v>6.4918512215237631E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20805,14 +20805,14 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.033707865168539E-2</v>
+        <v>3.0574912891986061E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
       </c>
       <c r="F63" s="380">
         <f>Normalized_FCF!C90</f>
-        <v>0.47502791656952054</v>
+        <v>0.58593359795439359</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -20832,7 +20832,7 @@
       </c>
       <c r="C66" s="378">
         <f>Normalized_FCF!E119</f>
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="D66" s="378">
         <f>Normalized_FCF!G119</f>
@@ -20846,7 +20846,7 @@
       </c>
       <c r="C67" s="383">
         <f>Normalized_FCF!E116</f>
-        <v>3.152381864639775E-2</v>
+        <v>3.9404773307997187E-2</v>
       </c>
       <c r="D67" s="383">
         <f>Normalized_FCF!G116</f>
@@ -20896,22 +20896,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20919,13 +20919,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20946,7 +20946,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-43.376330488078011</v>
+        <v>-39.373109605250939</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -20982,7 +20982,7 @@
       </c>
       <c r="C84" s="373">
         <f>DCF!F5</f>
-        <v>31164.344007144173</v>
+        <v>30968.223212794182</v>
       </c>
       <c r="D84" s="343" t="str">
         <f>Reporting_currency</f>
@@ -21008,7 +21008,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.060013784564399</v>
+        <v>10.878099071605792</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21039,7 +21039,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>38.129910898947763</v>
+        <v>34.610884419449761</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21052,7 +21052,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>6.8135941954341535</v>
+        <v>6.1158738858046107</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21074,33 +21074,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21163,23 +21163,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21197,7 +21197,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-67.151814025643745</v>
+        <v>-60.954343165330592</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21211,7 +21211,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>166.32301654396133</v>
+        <v>150.91012353067066</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21223,13 +21223,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21270,11 +21270,11 @@
       </c>
       <c r="D118" s="397">
         <f>DCF!D90</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>213.64 HKD</v>
+        <v>213.78 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21293,11 +21293,11 @@
       </c>
       <c r="D119" s="402">
         <f>DCF!D91</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>174.46 HKD</v>
+        <v>183.44 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21315,11 +21315,11 @@
       </c>
       <c r="D120" s="402">
         <f>DCF!D92</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>158.03 HKD</v>
+        <v>169.96 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21337,11 +21337,11 @@
       </c>
       <c r="D121" s="402">
         <f>DCF!D93</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>143.4 HKD</v>
+        <v>157.52 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21359,11 +21359,11 @@
       </c>
       <c r="D122" s="402">
         <f>DCF!D94</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>130.38 HKD</v>
+        <v>146.03 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21385,7 +21385,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>164.68961997937771</v>
+        <v>175.00654575317373</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21393,13 +21393,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21412,22 +21412,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21488,19 +21488,19 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>6.4227790321465204</v>
+        <v>6.4227790321465186</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>75.893834091879143</v>
+        <v>80.648177766439517</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>82.316613124025665</v>
+        <v>87.070956798586039</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21509,19 +21509,19 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>7.3850538549144664</v>
+        <v>7.3850538549144646</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>95.127578327438428</v>
+        <v>101.08681343143613</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>102.51263218235289</v>
+        <v>108.47186728635059</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21553,11 +21553,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>118.04299674187726</v>
+        <v>125.43776051420784</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>126.51123371392191</v>
+        <v>133.90599748625249</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21574,11 +21574,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>133.49786643239455</v>
+        <v>141.86079531106711</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>142.66730347977182</v>
+        <v>151.03023235844438</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21596,13 +21596,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21610,13 +21610,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21653,22 +21653,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21692,12 +21692,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21712,15 +21715,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9618.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9618.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE56799B-F40D-46EF-850B-E246B22F04EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6975E8-84FC-4E64-BAFF-6387013B7792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5422,7 +5422,8 @@
         <v>346</v>
       </c>
       <c r="C9" s="48">
-        <v>3187553771</v>
+        <f>2865069999*(1-0.063)+322483772</f>
+        <v>3007054361.0630002</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -5431,14 +5432,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>365931.17291079997</v>
+        <v>345209.84065003239</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.17769847372279465</v>
+        <v>0.19986540491955213</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5447,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5511,7 +5512,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>175.00654575317373</v>
+        <v>185.53286313493385</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5561,7 +5562,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>87.070956798586039</v>
+        <v>91.921794301701311</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5576,7 +5577,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>108.47186728635059</v>
+        <v>114.55205061155499</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5591,7 +5592,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>133.90599748625249</v>
+        <v>141.45084486980141</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5606,7 +5607,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>151.03023235844438</v>
+        <v>159.56289465999788</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5630,22 +5631,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5658,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5684,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5719,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5741,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5754,7 +5755,7 @@
       </c>
       <c r="C44" s="286">
         <f>Normalized_FCF!C46</f>
-        <v>566.20066072323493</v>
+        <v>565.84868687385779</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5784,7 +5785,7 @@
       </c>
       <c r="C46" s="285">
         <f>Normalized_FCF!C10</f>
-        <v>-6159.139339276765</v>
+        <v>-6159.4913131261419</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5810,13 +5811,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5824,7 +5825,7 @@
       </c>
       <c r="C52" s="285">
         <f>Normalized_FCF!C12</f>
-        <v>-8172.4997302883276</v>
+        <v>-8172.4117368259831</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5832,7 +5833,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5855,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5890,7 +5891,7 @@
       </c>
       <c r="C61" s="285">
         <f>Normalized_FCF!C19</f>
-        <v>21216.499190864983</v>
+        <v>21216.235210477949</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5903,7 +5904,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.4918512215237631E-2</v>
+        <v>6.881441067855093E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5920,7 +5921,7 @@
       </c>
       <c r="F63" s="258">
         <f>Normalized_FCF!C90</f>
-        <v>0.58593359795439359</v>
+        <v>0.55276121761479602</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -6004,13 +6005,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6030,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6059,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-39.373109605250939</v>
+        <v>-41.736493235143264</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6101,7 +6102,7 @@
       </c>
       <c r="C84" s="285">
         <f>DCF!F5</f>
-        <v>30968.223212794182</v>
+        <v>31026.885521023709</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6129,7 +6130,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>10.878099071605792</v>
+        <v>11.552903475414809</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6167,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>34.610884419449761</v>
+        <v>36.688413943358988</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6184,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.1158738858046107</v>
+        <v>6.5048241836305305</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6205,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6279,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6307,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-60.954343165330592</v>
+        <v>-64.613147314967009</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6320,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>150.91012353067066</v>
+        <v>159.98848576107054</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6328,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6369,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>213.78 HKD</v>
+        <v>226.64 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6377,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.6971301605721064E-2</v>
+        <v>-4.7960154682011633E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6391,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>183.44 HKD</v>
+        <v>194.47 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6399,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>3.8768037037718284E-3</v>
+        <v>2.7761914692564695E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6413,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>169.96 HKD</v>
+        <v>180.19 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6421,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>3.0247813917575962E-2</v>
+        <v>2.9085969533860979E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6435,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>157.52 HKD</v>
+        <v>167 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6443,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.7247388467611501E-2</v>
+        <v>5.6020469089006444E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6457,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>146.03 HKD</v>
+        <v>154.82 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6465,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>8.4870434968403255E-2</v>
+        <v>8.3574386321419752E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6483,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>175.00654575317373</v>
+        <v>185.53286313493385</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6510,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6590,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>80.648177766439517</v>
+        <v>85.499015269554789</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>87.070956798586039</v>
+        <v>91.921794301701311</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6611,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>101.08681343143613</v>
+        <v>107.16699675664053</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>108.47186728635059</v>
+        <v>114.55205061155499</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6658,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>125.43776051420784</v>
+        <v>132.98260789775676</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>133.90599748625249</v>
+        <v>141.45084486980141</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6679,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>141.86079531106711</v>
+        <v>150.39345761262058</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>151.03023235844438</v>
+        <v>159.56289465999788</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6701,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6744,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6758,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,18 +6797,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6824,6 +6813,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10003,11 +10004,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>81.470290840980525</v>
+        <v>86.360571380835609</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-60.954343165330592</v>
+        <v>-64.613147314967009</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10198,7 +10199,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>30968.223212794182</v>
+        <v>31026.885521023709</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10265,11 +10266,11 @@
       </c>
       <c r="C73" s="285">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
-        <v>-94306.70497557499</v>
+        <v>-94248.042667345479</v>
       </c>
       <c r="D73" s="285">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-94366.776787205818</v>
+        <v>-94308.114478976291</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10281,11 +10282,11 @@
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
-        <v>1.3290147294665973</v>
+        <v>1.3298419410403879</v>
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>1.3281687079619831</v>
+        <v>1.3289948663743076</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10298,7 +10299,7 @@
       <c r="C75" s="261"/>
       <c r="D75" s="262">
         <f>MAX(-D73*D76,G5)</f>
-        <v>94366.776787205818</v>
+        <v>94308.114478976291</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10417,7 +10418,7 @@
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-39.373109605250939</v>
+        <v>-41.736493235143264</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10430,11 +10431,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>34674.525717008648</v>
+        <v>34740.208778685992</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>10.878099071605792</v>
+        <v>11.552903475414809</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10451,7 +10452,7 @@
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>34.610884419449761</v>
+        <v>36.688413943358988</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10464,11 +10465,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>19494.676867656919</v>
+        <v>19560.35992933427</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.1158738858046142</v>
+        <v>6.5048241836305323</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -10949,7 +10950,7 @@
       </c>
       <c r="C10" s="266">
         <f>C48</f>
-        <v>-6159.139339276765</v>
+        <v>-6159.4913131261419</v>
       </c>
       <c r="E10" s="237"/>
       <c r="G10" s="266">
@@ -11004,7 +11005,7 @@
       </c>
       <c r="C11" s="267">
         <f>SUM(C8:C10)</f>
-        <v>32689.99892115331</v>
+        <v>32689.646947303932</v>
       </c>
       <c r="E11" s="237"/>
       <c r="G11" s="267">
@@ -11059,7 +11060,7 @@
       </c>
       <c r="C12" s="266">
         <f>-C11*C41</f>
-        <v>-8172.4997302883276</v>
+        <v>-8172.4117368259831</v>
       </c>
       <c r="E12" s="237"/>
       <c r="G12" s="266">
@@ -11171,7 +11172,7 @@
       </c>
       <c r="C14" s="269">
         <f>SUM(C11:C13)</f>
-        <v>21216.499190864983</v>
+        <v>21216.235210477949</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="243"/>
@@ -11389,7 +11390,7 @@
       </c>
       <c r="C19" s="267">
         <f>C14+C17</f>
-        <v>21216.499190864983</v>
+        <v>21216.235210477949</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="234"/>
@@ -12267,7 +12268,7 @@
       </c>
       <c r="C46" s="266">
         <f>BS!D75*C51</f>
-        <v>566.20066072323493</v>
+        <v>565.84868687385779</v>
       </c>
       <c r="E46" s="237"/>
       <c r="G46" s="274">
@@ -12379,7 +12380,7 @@
       </c>
       <c r="C48" s="267">
         <f>C45+C46</f>
-        <v>-6159.139339276765</v>
+        <v>-6159.4913131261419</v>
       </c>
       <c r="E48" s="237"/>
       <c r="G48" s="267">
@@ -13344,7 +13345,7 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>5.3150141128828271E-3</v>
+        <v>5.3153178478486645E-3</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="234"/>
@@ -13401,7 +13402,7 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>2.8209754000541334E-2</v>
+        <v>2.8209450265575496E-2</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="234"/>
@@ -13458,7 +13459,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>7.0524385001353336E-3</v>
+        <v>7.052362566393874E-3</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="234"/>
@@ -13573,7 +13574,7 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>1.8308725686120939E-2</v>
+        <v>1.8308497884896562E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="234"/>
@@ -13796,7 +13797,7 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>1.8308725686120939E-2</v>
+        <v>1.8308497884896562E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="234"/>
@@ -13921,20 +13922,20 @@
       </c>
       <c r="C89" s="71">
         <f>C88*Common_Shares/scaling_factor</f>
-        <v>12431.459706899999</v>
+        <v>11727.512008145701</v>
       </c>
       <c r="E89" s="237"/>
       <c r="G89" s="71">
         <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
-        <v>12431.459706899999</v>
+        <v>11727.512008145701</v>
       </c>
       <c r="H89" s="71">
         <f t="shared" si="36"/>
-        <v>9447.9093772439992</v>
+        <v>8912.9091261907324</v>
       </c>
       <c r="I89" s="71">
         <f t="shared" si="36"/>
-        <v>7707.5050182780005</v>
+        <v>7271.0574450503345</v>
       </c>
       <c r="J89" s="71" t="str">
         <f t="shared" si="36"/>
@@ -13976,20 +13977,20 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.58593359795439359</v>
+        <v>0.55276121761479602</v>
       </c>
       <c r="E90" s="237"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.43131842713552143</v>
+        <v>0.4068944559067969</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
-        <v>0.50669899052043332</v>
+        <v>0.47800649609518031</v>
       </c>
       <c r="I90" s="152">
         <f t="shared" si="37"/>
-        <v>0.78113965929644269</v>
+        <v>0.73690660231583405</v>
       </c>
       <c r="J90" s="152" t="str">
         <f t="shared" si="37"/>
@@ -14189,7 +14190,7 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>-0.1618163913450088</v>
+        <v>-0.16182541608410217</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="234"/>
@@ -14918,7 +14919,7 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>2.8209754000541334E-2</v>
+        <v>2.8209450265575496E-2</v>
       </c>
       <c r="E116" s="22">
         <f>E119/E117/E118</f>
@@ -15092,7 +15093,7 @@
       </c>
       <c r="C119" s="62">
         <f>C11/C104</f>
-        <v>0.10738453098072831</v>
+        <v>0.10738337476941046</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="453">
@@ -15215,22 +15216,22 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>7.45264520230928</v>
+        <v>7.8998943458976463</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.124202776744752</v>
+        <v>10.731911320676419</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>6.5497149738110698</v>
+        <v>6.9428637320565025</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>3.4659464575026186</v>
+        <v>3.6739910138475551</v>
       </c>
       <c r="J123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15272,22 +15273,22 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.4918512215237631E-2</v>
+        <v>6.881441067855093E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>8.8189919658055338E-2</v>
+        <v>9.3483548089515853E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.705326632239608E-2</v>
+        <v>6.0477907073662913E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.0191171232601208E-2</v>
+        <v>3.2003406043968251E-2</v>
       </c>
       <c r="J124" s="74" t="str">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
@@ -15329,15 +15330,15 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12204480871293903</v>
+        <v>0.12937058780220437</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3555667627335943E-2</v>
+        <v>6.7370617118581888E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6483122284753517E-2</v>
+        <v>2.8072780259542379E-2</v>
       </c>
       <c r="J125" s="22" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16061,7 +16062,7 @@
       <formula>ISBLANK(G4)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1" xr:uid="{00000000-0002-0000-0100-000001000000}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16120,7 +16121,7 @@
       </c>
       <c r="C4" s="275">
         <f>Normalized_FCF!C19</f>
-        <v>21216.499190864983</v>
+        <v>21216.235210477949</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16159,7 +16160,7 @@
       </c>
       <c r="F5" s="275">
         <f>BS!D66</f>
-        <v>30968.223212794182</v>
+        <v>31026.885521023709</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16180,7 +16181,7 @@
       </c>
       <c r="C6" s="283">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>412206.26999394834</v>
+        <v>412201.1412321431</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16202,7 +16203,7 @@
       </c>
       <c r="I6" s="305">
         <f>I7+I8</f>
-        <v>-6159.139339276765</v>
+        <v>-6159.4913131261419</v>
       </c>
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
@@ -16213,14 +16214,14 @@
       </c>
       <c r="C7" s="275">
         <f>F7</f>
-        <v>17410.92321279418</v>
+        <v>17469.585521023706</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>424</v>
       </c>
       <c r="F7" s="283">
         <f>SUM(F4:F6)</f>
-        <v>17410.92321279418</v>
+        <v>17469.585521023706</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16243,7 +16244,7 @@
       </c>
       <c r="C8" s="283">
         <f>C6+C7</f>
-        <v>429617.19320674252</v>
+        <v>429670.72675316682</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16254,7 +16255,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.1158738858046107</v>
+        <v>6.5048241836305305</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16266,7 +16267,7 @@
       </c>
       <c r="I8" s="313">
         <f>Normalized_FCF!C10</f>
-        <v>-6159.139339276765</v>
+        <v>-6159.4913131261419</v>
       </c>
       <c r="J8" s="313"/>
       <c r="N8" s="304"/>
@@ -16304,7 +16305,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>481034.13334226509</v>
+        <v>481094.07382769289</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16326,7 +16327,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>150.91012353067066</v>
+        <v>159.98848576107054</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16416,7 +16417,7 @@
       </c>
       <c r="C17" s="306">
         <f>Normalized_FCF!C77</f>
-        <v>2.8209754000541334E-2</v>
+        <v>2.8209450265575496E-2</v>
       </c>
       <c r="E17" s="308" t="s">
         <v>551</v>
@@ -16449,7 +16450,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>175.03262541019447</v>
+        <v>185.56050774542021</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16516,11 +16517,11 @@
       </c>
       <c r="E21" s="299">
         <f>$C$17</f>
-        <v>2.8209754000541334E-2</v>
+        <v>2.8209450265575496E-2</v>
       </c>
       <c r="F21" s="277">
         <f>C21*E21</f>
-        <v>33469.848826976689</v>
+        <v>33469.488456468323</v>
       </c>
       <c r="G21" s="299">
         <f t="shared" ref="G21:G50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16528,7 +16529,7 @@
       </c>
       <c r="H21" s="277">
         <f>(F21*(1-$I$10)+C21*(G21-$I$9))</f>
-        <v>21722.638237727762</v>
+        <v>21722.367959846488</v>
       </c>
       <c r="I21" s="299">
         <f>H21/C4-1</f>
@@ -16536,7 +16537,7 @@
       </c>
       <c r="J21" s="299">
         <f>H21/C21</f>
-        <v>1.8308725686120939E-2</v>
+        <v>1.8308497884896562E-2</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16544,7 +16545,7 @@
       </c>
       <c r="L21" s="277">
         <f t="shared" ref="L21:L51" si="4">H21*K21</f>
-        <v>20254.20814706551</v>
+        <v>20253.956139717004</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16565,11 +16566,11 @@
       </c>
       <c r="E22" s="299">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
-        <v>2.8209754000541334E-2</v>
+        <v>2.8209450265575496E-2</v>
       </c>
       <c r="F22" s="277">
         <f t="shared" ref="F22:F50" si="7">IF(A22="", 0,C22*E22)</f>
-        <v>34268.302767541078</v>
+        <v>34267.933800063722</v>
       </c>
       <c r="G22" s="299">
         <f t="shared" si="2"/>
@@ -16577,15 +16578,15 @@
       </c>
       <c r="H22" s="277">
         <f t="shared" ref="H22:H50" si="8">IF(A22="", 0,F22*(1-$I$10)+C22*(G22-$I$9))</f>
-        <v>22240.851695757745</v>
+        <v>22240.57497014973</v>
       </c>
       <c r="I22" s="299">
         <f t="shared" ref="I22:I50" si="9">IF(A22="", 0,H22/H21-1)</f>
-        <v>2.3855917147759254E-2</v>
+        <v>2.3855917147759476E-2</v>
       </c>
       <c r="J22" s="299">
         <f>IF(A22="", 0,H22/C22)</f>
-        <v>1.8308725686120939E-2</v>
+        <v>1.8308497884896562E-2</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16593,7 +16594,7 @@
       </c>
       <c r="L22" s="277">
         <f t="shared" si="4"/>
-        <v>19335.562572042312</v>
+        <v>19335.321994685732</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16614,11 +16615,11 @@
       </c>
       <c r="E23" s="299">
         <f t="shared" si="6"/>
-        <v>2.8209754000541334E-2</v>
+        <v>2.8209450265575496E-2</v>
       </c>
       <c r="F23" s="277">
         <f t="shared" si="7"/>
-        <v>35085.80455915787</v>
+        <v>35085.426789622943</v>
       </c>
       <c r="G23" s="299">
         <f t="shared" si="2"/>
@@ -16626,15 +16627,15 @@
       </c>
       <c r="H23" s="277">
         <f t="shared" si="8"/>
-        <v>22771.427611107349</v>
+        <v>22771.14428395615</v>
       </c>
       <c r="I23" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759476E-2</v>
+        <v>2.3855917147759254E-2</v>
       </c>
       <c r="J23" s="299">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,H23/C23)</f>
-        <v>1.8308725686120939E-2</v>
+        <v>1.8308497884896559E-2</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16642,7 +16643,7 @@
       </c>
       <c r="L23" s="277">
         <f t="shared" si="4"/>
-        <v>18458.582891157366</v>
+        <v>18458.353225376413</v>
       </c>
       <c r="N23" s="275"/>
       <c r="O23" s="275"/>
@@ -16671,11 +16672,11 @@
       </c>
       <c r="E24" s="299">
         <f t="shared" si="6"/>
-        <v>2.8209754000541334E-2</v>
+        <v>2.8209450265575496E-2</v>
       </c>
       <c r="F24" s="277">
         <f t="shared" si="7"/>
-        <v>35922.808605783626</v>
+        <v>35922.421824209967</v>
       </c>
       <c r="G24" s="299">
         <f t="shared" si="2"/>
@@ -16683,15 +16684,15 @@
       </c>
       <c r="H24" s="277">
         <f t="shared" si="8"/>
-        <v>23314.660901534131</v>
+        <v>23314.370815353883</v>
       </c>
       <c r="I24" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759698E-2</v>
+        <v>2.3855917147759476E-2</v>
       </c>
       <c r="J24" s="299">
         <f t="shared" si="10"/>
-        <v>1.8308725686120943E-2</v>
+        <v>1.8308497884896559E-2</v>
       </c>
       <c r="K24" s="119">
         <f t="shared" si="3"/>
@@ -16699,7 +16700,7 @@
       </c>
       <c r="L24" s="277">
         <f t="shared" si="4"/>
-        <v>17621.379314940667</v>
+        <v>17621.160065832231</v>
       </c>
       <c r="N24" s="275"/>
       <c r="O24" s="275"/>
@@ -16744,7 +16745,7 @@
       </c>
       <c r="I25" s="299">
         <f t="shared" si="9"/>
-        <v>0.49338969124915688</v>
+        <v>0.49340827256600162</v>
       </c>
       <c r="J25" s="299">
         <f t="shared" si="10"/>
@@ -18104,7 +18105,7 @@
       <c r="K52" s="468"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
-        <v>480879.20795293921</v>
+        <v>480878.26645334472</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18128,7 +18129,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>480879.20795293921</v>
+        <v>480878.26645334472</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18163,19 +18164,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>425732.60916437849</v>
+        <v>425732.36302881944</v>
       </c>
       <c r="C56" s="118">
-        <v>429989.9352560222</v>
+        <v>429989.68665910763</v>
       </c>
       <c r="D56" s="118">
-        <v>434247.26134766615</v>
+        <v>434247.01028939598</v>
       </c>
       <c r="E56" s="118">
-        <v>438504.58743930992</v>
+        <v>438504.33391968417</v>
       </c>
       <c r="F56" s="118">
-        <v>447019.23962259752</v>
+        <v>447018.98118026054</v>
       </c>
       <c r="G56" s="295"/>
       <c r="H56" s="295"/>
@@ -18189,19 +18190,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>425194.53340951959</v>
+        <v>425194.28727396054</v>
       </c>
       <c r="C57" s="118">
-        <v>433541.14246640983</v>
+        <v>433540.89386949519</v>
       </c>
       <c r="D57" s="118">
-        <v>441968.83397325611</v>
+        <v>441968.58291498595</v>
       </c>
       <c r="E57" s="118">
-        <v>450477.6079300589</v>
+        <v>450477.35441043309</v>
       </c>
       <c r="F57" s="118">
-        <v>467738.40319353342</v>
+        <v>467738.14475119644</v>
       </c>
       <c r="G57" s="295"/>
       <c r="H57" s="295"/>
@@ -18215,19 +18216,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>424692.83107398672</v>
+        <v>424692.58493842767</v>
       </c>
       <c r="C58" s="118">
-        <v>436885.40286966495</v>
+        <v>436885.15427275037</v>
       </c>
       <c r="D58" s="118">
-        <v>449312.42751927185</v>
+        <v>449312.17646100163</v>
       </c>
       <c r="E58" s="118">
-        <v>461976.17306336574</v>
+        <v>461975.91954373999</v>
       </c>
       <c r="F58" s="118">
-        <v>488022.89899724693</v>
+        <v>488022.64055490994</v>
       </c>
       <c r="G58" s="295"/>
       <c r="H58" s="295"/>
@@ -18241,19 +18242,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>424225.04334854812</v>
+        <v>424224.79721298913</v>
       </c>
       <c r="C59" s="118">
-        <v>440034.77630303346</v>
+        <v>440034.52770611882</v>
       </c>
       <c r="D59" s="118">
-        <v>456296.5444581398</v>
+        <v>456296.29339986964</v>
       </c>
       <c r="E59" s="118">
-        <v>473019.08410048054</v>
+        <v>473018.83058085479</v>
       </c>
       <c r="F59" s="118">
-        <v>507881.84593794547</v>
+        <v>507881.58749560849</v>
       </c>
       <c r="G59" s="295"/>
       <c r="H59" s="295"/>
@@ -18267,19 +18268,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>415330.10959385836</v>
+        <v>415329.63396127464</v>
       </c>
       <c r="C60" s="118">
-        <v>434371.83053504658</v>
+        <v>434371.34782821708</v>
       </c>
       <c r="D60" s="118">
-        <v>454138.27927457797</v>
+        <v>454137.78944760328</v>
       </c>
       <c r="E60" s="118">
-        <v>474650.49024716648</v>
+        <v>474649.99325414718</v>
       </c>
       <c r="F60" s="118">
-        <v>517998.37984638795</v>
+        <v>517997.86838358123</v>
       </c>
       <c r="G60" s="295"/>
       <c r="H60" s="295"/>
@@ -18293,19 +18294,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>414923.42827790068</v>
+        <v>414922.95264531695</v>
       </c>
       <c r="C61" s="118">
-        <v>437164.83934450021</v>
+        <v>437164.35663767077</v>
       </c>
       <c r="D61" s="118">
-        <v>460455.37189041753</v>
+        <v>460454.88206344284</v>
       </c>
       <c r="E61" s="118">
-        <v>484835.54624601488</v>
+        <v>484835.04925299564</v>
       </c>
       <c r="F61" s="118">
-        <v>537032.82456435403</v>
+        <v>537032.3131015473</v>
       </c>
       <c r="G61" s="295"/>
       <c r="H61" s="295"/>
@@ -18319,19 +18320,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>406657.27502915217</v>
+        <v>406656.58541332866</v>
       </c>
       <c r="C62" s="118">
-        <v>431669.13932001765</v>
+        <v>431668.43614604214</v>
       </c>
       <c r="D62" s="118">
-        <v>458093.52774163929</v>
+        <v>458092.81083393865</v>
       </c>
       <c r="E62" s="118">
-        <v>485998.70097900811</v>
+        <v>485997.97016072512</v>
       </c>
       <c r="F62" s="118">
-        <v>546537.79948063416</v>
+        <v>546537.04030547943</v>
       </c>
       <c r="G62" s="295"/>
       <c r="H62" s="295"/>
@@ -18345,19 +18346,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>406303.71788398759</v>
+        <v>406303.02826816408</v>
       </c>
       <c r="C63" s="118">
-        <v>434146.10763601138</v>
+        <v>434145.40446203586</v>
       </c>
       <c r="D63" s="118">
-        <v>463807.30078787968</v>
+        <v>463806.58388017898</v>
       </c>
       <c r="E63" s="118">
-        <v>495392.54335906752</v>
+        <v>495391.81254078454</v>
       </c>
       <c r="F63" s="118">
-        <v>564781.9735953653</v>
+        <v>564781.21442021057</v>
       </c>
       <c r="G63" s="295"/>
       <c r="H63" s="295"/>
@@ -18371,19 +18372,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>398620.24902084155</v>
+        <v>398619.35988684569</v>
       </c>
       <c r="C64" s="118">
-        <v>428826.32437775761</v>
+        <v>428825.41358437197</v>
       </c>
       <c r="D64" s="118">
-        <v>461281.37620356132</v>
+        <v>461280.44333097438</v>
       </c>
       <c r="E64" s="118">
-        <v>496137.35554911941</v>
+        <v>496136.40017137572</v>
       </c>
       <c r="F64" s="118">
-        <v>573704.79853197373</v>
+        <v>573703.7968412335</v>
       </c>
       <c r="G64" s="295"/>
       <c r="H64" s="295"/>
@@ -18397,19 +18398,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>398312.87651565892</v>
+        <v>398311.987381663</v>
       </c>
       <c r="C65" s="118">
-        <v>431023.01348867989</v>
+        <v>431022.10269529419</v>
       </c>
       <c r="D65" s="118">
-        <v>466449.45025428559</v>
+        <v>466448.51738169871</v>
       </c>
       <c r="E65" s="118">
-        <v>504801.44877269905</v>
+        <v>504800.49339495535</v>
       </c>
       <c r="F65" s="118">
-        <v>591191.51243723708</v>
+        <v>591190.51074649696</v>
       </c>
       <c r="G65" s="295"/>
       <c r="H65" s="295"/>
@@ -18423,19 +18424,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>377850.06405640912</v>
+        <v>377848.65370608249</v>
       </c>
       <c r="C66" s="277">
-        <v>419845.11706335627</v>
+        <v>419843.65322674008</v>
       </c>
       <c r="D66" s="118">
-        <v>467116.37371734786</v>
+        <v>467114.8543356958</v>
       </c>
       <c r="E66" s="118">
-        <v>520322.16713043768</v>
+        <v>520320.59006954031</v>
       </c>
       <c r="F66" s="118">
-        <v>647567.46558868885</v>
+        <v>647565.76645292563</v>
       </c>
       <c r="G66" s="295"/>
       <c r="H66" s="295"/>
@@ -18458,19 +18459,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>366227.43151217012</v>
+        <v>366225.72976120922</v>
       </c>
       <c r="C67" s="277">
-        <v>414977.28938032209</v>
+        <v>414975.50847604114</v>
       </c>
       <c r="D67" s="118">
-        <v>471749.4844506185</v>
+        <v>471747.62035189278</v>
       </c>
       <c r="E67" s="118">
-        <v>537919.06884123036</v>
+        <v>537917.11729936081</v>
       </c>
       <c r="F67" s="118">
-        <v>705142.17727197718</v>
+        <v>705140.03721799445</v>
       </c>
       <c r="G67" s="295"/>
       <c r="H67" s="295"/>
@@ -18493,19 +18494,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>352067.49067624839</v>
+        <v>352065.42161633779</v>
       </c>
       <c r="C68" s="277">
-        <v>404929.92029805295</v>
+        <v>404927.72977538285</v>
       </c>
       <c r="D68" s="118">
-        <v>468420.29340423224</v>
+        <v>468417.97296493349</v>
       </c>
       <c r="E68" s="118">
-        <v>544851.41285058844</v>
+        <v>544848.95341982238</v>
       </c>
       <c r="F68" s="118">
-        <v>748421.72936403961</v>
+        <v>748418.96201773675</v>
       </c>
       <c r="G68" s="295"/>
       <c r="H68" s="295"/>
@@ -18528,19 +18529,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>344060.4324212338</v>
+        <v>344058.15800693462</v>
       </c>
       <c r="C69" s="277">
-        <v>400014.77431201236</v>
+        <v>400012.3489492088</v>
       </c>
       <c r="D69" s="118">
-        <v>469031.08139142004</v>
+        <v>469028.49274077325</v>
       </c>
       <c r="E69" s="118">
-        <v>554531.93290110049</v>
+        <v>554529.16753518628</v>
       </c>
       <c r="F69" s="118">
-        <v>793526.38970606239</v>
+        <v>793523.22579142265</v>
       </c>
       <c r="G69" s="295"/>
       <c r="H69" s="295"/>
@@ -18637,23 +18638,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>150.91012353067066</v>
+        <v>159.98848576107054</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>150.91012353067066</v>
+        <v>159.98848576107054</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>150.91012353067066</v>
+        <v>159.98848576107054</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>150.91012353067066</v>
+        <v>159.98848576107054</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>150.91012353067066</v>
+        <v>159.98848576107054</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18668,23 +18669,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>155.66147321453923</v>
+        <v>165.0268547979984</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>157.15692920782655</v>
+        <v>166.61207510414206</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>158.65238520111396</v>
+        <v>168.19729541028579</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>160.14784119440131</v>
+        <v>169.78251571642949</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>163.13875318097601</v>
+        <v>172.95295632871685</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18699,23 +18700,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>155.47246523273915</v>
+        <v>164.82650155100126</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>158.40434930012418</v>
+        <v>167.93437199066022</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>161.36471491511139</v>
+        <v>171.07243359202178</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>164.35356207770099</v>
+        <v>174.24068635508604</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>170.41670104568695</v>
+        <v>180.66776536632261</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18730,23 +18731,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>155.29623401427753</v>
+        <v>164.63969199669154</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>159.57907591384958</v>
+        <v>169.17961194905948</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>163.94427324450763</v>
+        <v>173.80683074388256</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>168.39262269289787</v>
+        <v>178.52219288918053</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>177.54196468945986</v>
+        <v>188.22072526327929</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18761,23 +18762,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>155.13191586186574</v>
+        <v>164.46551059407173</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>160.68534526570286</v>
+        <v>170.35228547631661</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>166.39755948784941</v>
+        <v>176.40737628691102</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>172.27162729304024</v>
+        <v>182.63403599418487</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>184.51774727776902</v>
+        <v>195.61523145610406</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18792,23 +18793,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>152.00742370246698</v>
+        <v>161.15338432940104</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>158.69614218233576</v>
+        <v>168.24359266378866</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>165.6394332521833</v>
+        <v>175.60365437305867</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>172.84468560406225</v>
+        <v>183.24140165789214</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>188.07134663544323</v>
+        <v>199.38204255126666</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18823,23 +18824,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>151.86457018403425</v>
+        <v>161.00195598235243</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>159.67723258356196</v>
+        <v>169.28357333344812</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>167.85841620278481</v>
+        <v>177.95583249247059</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>176.42235447592546</v>
+        <v>187.0338212601323</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>194.75750922191975</v>
+        <v>206.4695442080403</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18855,23 +18856,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>148.96094754598076</v>
+        <v>157.92396278001246</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>157.74677732549443</v>
+        <v>167.23715978332504</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>167.02877949855542</v>
+        <v>177.07631202310134</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>176.83093175639016</v>
+        <v>187.46683645875532</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>198.09628839894748</v>
+        <v>210.00864244826721</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18886,23 +18887,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>148.83675476856024</v>
+        <v>157.79231529098678</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>158.61685329186363</v>
+        <v>168.15946234079402</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>169.0358365015544</v>
+        <v>179.203843271409</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>180.13067379748725</v>
+        <v>190.96464658238341</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>204.50485540442162</v>
+        <v>216.80188575956674</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18918,23 +18919,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>146.13780962945489</v>
+        <v>154.93129080671108</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>156.7481916988134</v>
+        <v>166.17855642427548</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>168.14856383864398</v>
+        <v>178.26323136530849</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>180.39230136124675</v>
+        <v>191.24189481019474</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>207.63914480139675</v>
+        <v>220.12422158962173</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18950,23 +18951,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>146.02983996841596</v>
+        <v>154.8168402318712</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>157.51981497257805</v>
+        <v>166.99649663444524</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>169.96393507085429</v>
+        <v>180.18757084248088</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>183.43570697751699</v>
+        <v>194.46798183224493</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>213.7816414177249</v>
+        <v>226.6354235506698</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18982,23 +18983,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>138.84193965893206</v>
+        <v>147.19728980748212</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>153.59339452890907</v>
+        <v>162.83418560817415</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>170.19820293486828</v>
+        <v>180.43568232329363</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>188.88761523837638</v>
+        <v>200.24691116400436</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>233.58462460548282</v>
+        <v>247.62682751020935</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19014,23 +19015,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>134.75929831976518</v>
+        <v>142.86947809894883</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>151.88348978443301</v>
+        <v>161.02152521816939</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>171.8256594802414</v>
+        <v>182.16069911793903</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>195.06881713840107</v>
+        <v>206.79900226740807</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>253.80869149515831</v>
+        <v>269.06468637508107</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19046,23 +19047,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>129.78538560275803</v>
+        <v>137.59686789548579</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>148.35418571248488</v>
+        <v>157.28022100662108</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>170.65622622661093</v>
+        <v>180.92090033624558</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>197.50391728651343</v>
+        <v>209.38008097583409</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>269.01134785025954</v>
+        <v>285.17965351841104</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19078,23 +19079,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>126.9727743537477</v>
+        <v>134.61535228319676</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>146.62765963379576</v>
+        <v>155.44997219897922</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>170.87077557904624</v>
+        <v>181.14822821404141</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>200.9043595866913</v>
+        <v>212.98452200876883</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>284.85510357431883</v>
+        <v>301.97428813792379</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19141,7 +19142,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>213.7816414177249</v>
+        <v>226.6354235506698</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19169,7 +19170,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>183.43570697751699</v>
+        <v>194.46798183224493</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19197,7 +19198,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>169.96393507085429</v>
+        <v>180.18757084248088</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19225,7 +19226,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>157.51981497257805</v>
+        <v>166.99649663444524</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19253,7 +19254,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>146.02983996841596</v>
+        <v>154.8168402318712</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19475,7 +19476,7 @@
       </c>
       <c r="C9" s="447">
         <f>Normalized_FCF!C19</f>
-        <v>21216.499190864983</v>
+        <v>21216.235210477949</v>
       </c>
       <c r="D9" s="469"/>
       <c r="E9" s="469"/>
@@ -19613,7 +19614,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>183.43570697751699</v>
+        <v>194.46798183224493</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19637,7 +19638,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>169.96393507085429</v>
+        <v>180.18757084248088</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19660,7 +19661,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>157.51981497257805</v>
+        <v>166.99649663444524</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19676,7 +19677,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>169.54725942761775</v>
+        <v>179.74588448842476</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19723,7 +19724,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>213.7816414177249</v>
+        <v>226.6354235506698</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19746,7 +19747,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>146.02983996841596</v>
+        <v>154.8168402318712</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19802,7 +19803,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.17769847372279465</v>
+        <v>0.19986540491955213</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19811,7 +19812,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>150.91012353067066</v>
+        <v>159.98848576107054</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19822,7 +19823,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>7.27906152286414E-2</v>
+        <v>7.1528706990175162E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19831,7 +19832,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>175.00654575317373</v>
+        <v>185.53286313493385</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19934,7 +19935,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>175.03262541019447</v>
+        <v>185.56050774542021</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20001,7 +20002,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>3.4946543624890122E-2</v>
+        <v>3.5060226386415011E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20079,11 +20080,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>80.648177766439517</v>
+        <v>85.499015269554789</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>87.070956798586039</v>
+        <v>91.921794301701311</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20091,7 +20092,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.50247028518927839</v>
+        <v>0.50455249410532366</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20104,11 +20105,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>101.08681343143613</v>
+        <v>107.16699675664053</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>108.47186728635059</v>
+        <v>114.55205061155499</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20116,7 +20117,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.38018394215186968</v>
+        <v>0.38257811216849558</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20150,11 +20151,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>125.43776051420784</v>
+        <v>132.98260789775676</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>133.90599748625249</v>
+        <v>141.45084486980141</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20162,7 +20163,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.23485149135443628</v>
+        <v>0.2375968198856101</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20175,11 +20176,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>141.86079531106711</v>
+        <v>150.39345761262058</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>151.03023235844438</v>
+        <v>159.56289465999788</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20187,7 +20188,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.13700238063406578</v>
+        <v>0.13997503211088058</v>
       </c>
     </row>
   </sheetData>
@@ -20307,7 +20308,7 @@
       </c>
       <c r="C9" s="353">
         <f>Common_Shares</f>
-        <v>3187553771</v>
+        <v>3007054361.0630002</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -20316,14 +20317,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>365931.17291079997</v>
+        <v>345209.84065003239</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.17769847372279465</v>
+        <v>0.19986540491955213</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20331,13 +20332,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20401,7 +20402,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>175.00654575317373</v>
+        <v>185.53286313493385</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20453,7 +20454,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>87.070956798586039</v>
+        <v>91.921794301701311</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20469,7 +20470,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>108.47186728635059</v>
+        <v>114.55205061155499</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20485,7 +20486,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>133.90599748625249</v>
+        <v>141.45084486980141</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20501,7 +20502,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>151.03023235844438</v>
+        <v>159.56289465999788</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20522,22 +20523,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20646,7 +20647,7 @@
       </c>
       <c r="C44" s="376">
         <f>Normalized_FCF!C46</f>
-        <v>566.20066072323493</v>
+        <v>565.84868687385779</v>
       </c>
       <c r="D44" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20676,7 +20677,7 @@
       </c>
       <c r="C46" s="373">
         <f>Normalized_FCF!C10</f>
-        <v>-6159.139339276765</v>
+        <v>-6159.4913131261419</v>
       </c>
       <c r="D46" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20716,7 +20717,7 @@
       </c>
       <c r="C52" s="373">
         <f>Normalized_FCF!C12</f>
-        <v>-8172.4997302883276</v>
+        <v>-8172.4117368259831</v>
       </c>
       <c r="D52" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20727,10 +20728,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20746,22 +20747,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20782,7 +20783,7 @@
       </c>
       <c r="C61" s="373">
         <f>Normalized_FCF!C19</f>
-        <v>21216.499190864983</v>
+        <v>21216.235210477949</v>
       </c>
       <c r="D61" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20795,7 +20796,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.4918512215237631E-2</v>
+        <v>6.881441067855093E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20812,7 +20813,7 @@
       </c>
       <c r="F63" s="380">
         <f>Normalized_FCF!C90</f>
-        <v>0.58593359795439359</v>
+        <v>0.55276121761479602</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -20896,22 +20897,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20919,13 +20920,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20946,7 +20947,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-39.373109605250939</v>
+        <v>-41.736493235143264</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -20982,7 +20983,7 @@
       </c>
       <c r="C84" s="373">
         <f>DCF!F5</f>
-        <v>30968.223212794182</v>
+        <v>31026.885521023709</v>
       </c>
       <c r="D84" s="343" t="str">
         <f>Reporting_currency</f>
@@ -21008,7 +21009,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>10.878099071605792</v>
+        <v>11.552903475414809</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21039,7 +21040,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>34.610884419449761</v>
+        <v>36.688413943358988</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21052,7 +21053,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>6.1158738858046107</v>
+        <v>6.5048241836305305</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21074,33 +21075,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21163,23 +21164,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21197,7 +21198,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-60.954343165330592</v>
+        <v>-64.613147314967009</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21211,7 +21212,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>150.91012353067066</v>
+        <v>159.98848576107054</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21223,13 +21224,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21274,7 +21275,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>213.78 HKD</v>
+        <v>226.64 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21297,7 +21298,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>183.44 HKD</v>
+        <v>194.47 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21319,7 +21320,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>169.96 HKD</v>
+        <v>180.19 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21341,7 +21342,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>157.52 HKD</v>
+        <v>167 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21363,7 +21364,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>146.03 HKD</v>
+        <v>154.82 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21385,7 +21386,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>175.00654575317373</v>
+        <v>185.53286313493385</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21393,13 +21394,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21412,22 +21413,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21492,11 +21493,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>80.648177766439517</v>
+        <v>85.499015269554789</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>87.070956798586039</v>
+        <v>91.921794301701311</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21513,11 +21514,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>101.08681343143613</v>
+        <v>107.16699675664053</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>108.47186728635059</v>
+        <v>114.55205061155499</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21553,11 +21554,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>125.43776051420784</v>
+        <v>132.98260789775676</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>133.90599748625249</v>
+        <v>141.45084486980141</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21574,11 +21575,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>141.86079531106711</v>
+        <v>150.39345761262058</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>151.03023235844438</v>
+        <v>159.56289465999788</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21596,13 +21597,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21610,13 +21611,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21653,22 +21654,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21692,15 +21693,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21715,12 +21713,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9618.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9618.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6975E8-84FC-4E64-BAFF-6387013B7792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008D575C-DFE3-4047-9AEA-994BBDD9502C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -6946,8 +6946,12 @@
       <c r="E4" s="287">
         <v>1046236</v>
       </c>
-      <c r="F4" s="287"/>
-      <c r="G4" s="287"/>
+      <c r="F4" s="287">
+        <v>951592</v>
+      </c>
+      <c r="G4" s="287">
+        <v>745802</v>
+      </c>
       <c r="H4" s="287"/>
       <c r="I4" s="287"/>
       <c r="J4" s="287"/>
@@ -6968,8 +6972,12 @@
       <c r="E5" s="287">
         <v>899163</v>
       </c>
-      <c r="F5" s="287"/>
-      <c r="G5" s="287"/>
+      <c r="F5" s="287">
+        <v>822526</v>
+      </c>
+      <c r="G5" s="287">
+        <v>636694</v>
+      </c>
       <c r="H5" s="287"/>
       <c r="I5" s="287"/>
       <c r="J5" s="287"/>
@@ -6993,8 +7001,14 @@
         <f>63011+11053+E7</f>
         <v>111836</v>
       </c>
-      <c r="F6" s="287"/>
-      <c r="G6" s="287"/>
+      <c r="F6" s="287">
+        <f>59055+11562+F7</f>
+        <v>109360</v>
+      </c>
+      <c r="G6" s="287">
+        <f>48700+6409+G7</f>
+        <v>82265</v>
+      </c>
       <c r="H6" s="287"/>
       <c r="I6" s="287"/>
       <c r="J6" s="287"/>
@@ -7015,8 +7029,12 @@
       <c r="E7" s="288">
         <v>37772</v>
       </c>
-      <c r="F7" s="288"/>
-      <c r="G7" s="288"/>
+      <c r="F7" s="288">
+        <v>38743</v>
+      </c>
+      <c r="G7" s="288">
+        <v>27156</v>
+      </c>
       <c r="H7" s="288"/>
       <c r="I7" s="288"/>
       <c r="J7" s="288"/>
@@ -7037,8 +7055,12 @@
       <c r="E8" s="287">
         <v>16893</v>
       </c>
-      <c r="F8" s="287"/>
-      <c r="G8" s="287"/>
+      <c r="F8" s="287">
+        <v>11562</v>
+      </c>
+      <c r="G8" s="287">
+        <v>16149</v>
+      </c>
       <c r="H8" s="287"/>
       <c r="I8" s="287"/>
       <c r="J8" s="287"/>
@@ -7059,8 +7081,12 @@
       <c r="E9" s="287">
         <v>-2195</v>
       </c>
-      <c r="F9" s="287"/>
-      <c r="G9" s="287"/>
+      <c r="F9" s="287">
+        <v>-4918</v>
+      </c>
+      <c r="G9" s="287">
+        <v>4291</v>
+      </c>
       <c r="H9" s="287"/>
       <c r="I9" s="287"/>
       <c r="J9" s="287"/>
@@ -7113,8 +7139,12 @@
       <c r="E12" s="287">
         <v>2106</v>
       </c>
-      <c r="F12" s="287"/>
-      <c r="G12" s="287"/>
+      <c r="F12" s="287">
+        <v>1213</v>
+      </c>
+      <c r="G12" s="287">
+        <v>1125</v>
+      </c>
       <c r="H12" s="287"/>
       <c r="I12" s="287"/>
       <c r="J12" s="287"/>
@@ -7151,8 +7181,12 @@
       <c r="E14" s="287">
         <v>4176</v>
       </c>
-      <c r="F14" s="287"/>
-      <c r="G14" s="287"/>
+      <c r="F14" s="287">
+        <v>1887</v>
+      </c>
+      <c r="G14" s="287">
+        <v>1482</v>
+      </c>
       <c r="H14" s="287"/>
       <c r="I14" s="287"/>
       <c r="J14" s="287"/>
@@ -7173,8 +7207,12 @@
       <c r="E15" s="289">
         <v>9691</v>
       </c>
-      <c r="F15" s="289"/>
-      <c r="G15" s="289"/>
+      <c r="F15" s="289">
+        <v>-4467</v>
+      </c>
+      <c r="G15" s="289">
+        <v>49337</v>
+      </c>
       <c r="H15" s="289"/>
       <c r="I15" s="289"/>
       <c r="J15" s="289"/>
@@ -7195,8 +7233,12 @@
       <c r="E16" s="287">
         <v>-697</v>
       </c>
-      <c r="F16" s="287"/>
-      <c r="G16" s="287"/>
+      <c r="F16" s="287">
+        <v>-923</v>
+      </c>
+      <c r="G16" s="287">
+        <v>-75</v>
+      </c>
       <c r="H16" s="287"/>
       <c r="I16" s="287"/>
       <c r="J16" s="287"/>
@@ -7507,13 +7549,13 @@
         <f t="shared" si="1"/>
         <v>1046236</v>
       </c>
-      <c r="F36" s="270" t="str">
+      <c r="F36" s="270">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G36" s="270" t="str">
+        <v>951592</v>
+      </c>
+      <c r="G36" s="270">
         <f t="shared" si="1"/>
-        <v/>
+        <v>745802</v>
       </c>
       <c r="H36" s="270" t="str">
         <f t="shared" si="1"/>
@@ -7556,13 +7598,13 @@
         <f t="shared" si="2"/>
         <v>-899163</v>
       </c>
-      <c r="F37" s="270" t="str">
+      <c r="F37" s="270">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G37" s="270" t="str">
+        <v>-822526</v>
+      </c>
+      <c r="G37" s="270">
         <f t="shared" si="2"/>
-        <v/>
+        <v>-636694</v>
       </c>
       <c r="H37" s="270" t="str">
         <f t="shared" si="2"/>
@@ -7605,13 +7647,13 @@
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
         <v>147073</v>
       </c>
-      <c r="F38" s="267" t="str">
+      <c r="F38" s="267">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
-        <v/>
-      </c>
-      <c r="G38" s="267" t="str">
+        <v>129066</v>
+      </c>
+      <c r="G38" s="267">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
-        <v/>
+        <v>109108</v>
       </c>
       <c r="H38" s="267" t="str">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
@@ -7654,13 +7696,13 @@
         <f t="shared" si="13"/>
         <v>-111836</v>
       </c>
-      <c r="F39" s="270" t="str">
+      <c r="F39" s="270">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="G39" s="270" t="str">
+        <v>-109360</v>
+      </c>
+      <c r="G39" s="270">
         <f t="shared" si="13"/>
-        <v/>
+        <v>-82265</v>
       </c>
       <c r="H39" s="270" t="str">
         <f t="shared" si="13"/>
@@ -7703,13 +7745,13 @@
         <f t="shared" si="14"/>
         <v>-37772</v>
       </c>
-      <c r="F40" s="282" t="str">
+      <c r="F40" s="282">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G40" s="282" t="str">
+        <v>-38743</v>
+      </c>
+      <c r="G40" s="282">
         <f t="shared" si="14"/>
-        <v/>
+        <v>-27156</v>
       </c>
       <c r="H40" s="282" t="str">
         <f t="shared" si="14"/>
@@ -7752,13 +7794,13 @@
         <f t="shared" si="15"/>
         <v>-74064</v>
       </c>
-      <c r="F41" s="282" t="str">
+      <c r="F41" s="282">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="G41" s="282" t="str">
+        <v>-70617</v>
+      </c>
+      <c r="G41" s="282">
         <f t="shared" si="15"/>
-        <v/>
+        <v>-55109</v>
       </c>
       <c r="H41" s="282" t="str">
         <f t="shared" si="15"/>
@@ -7801,13 +7843,13 @@
         <f t="shared" si="16"/>
         <v>-16893</v>
       </c>
-      <c r="F42" s="270" t="str">
+      <c r="F42" s="270">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="G42" s="270" t="str">
+        <v>-11562</v>
+      </c>
+      <c r="G42" s="270">
         <f t="shared" si="16"/>
-        <v/>
+        <v>-16149</v>
       </c>
       <c r="H42" s="270" t="str">
         <f t="shared" si="16"/>
@@ -7850,13 +7892,13 @@
         <f t="shared" si="17"/>
         <v>18344</v>
       </c>
-      <c r="F43" s="271" t="str">
+      <c r="F43" s="271">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="G43" s="271" t="str">
+        <v>8144</v>
+      </c>
+      <c r="G43" s="271">
         <f t="shared" si="17"/>
-        <v/>
+        <v>10694</v>
       </c>
       <c r="H43" s="271" t="str">
         <f t="shared" si="17"/>
@@ -7899,13 +7941,13 @@
         <f t="shared" si="18"/>
         <v>-2371</v>
       </c>
-      <c r="F44" s="290" t="str">
+      <c r="F44" s="290">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="G44" s="290" t="str">
+        <v>-9511</v>
+      </c>
+      <c r="G44" s="290">
         <f t="shared" si="18"/>
-        <v/>
+        <v>41250</v>
       </c>
       <c r="H44" s="290" t="str">
         <f t="shared" si="18"/>
@@ -7948,13 +7990,13 @@
         <f t="shared" si="19"/>
         <v>-2106</v>
       </c>
-      <c r="F45" s="285" t="str">
+      <c r="F45" s="285">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="G45" s="285" t="str">
+        <v>-1213</v>
+      </c>
+      <c r="G45" s="285">
         <f t="shared" si="19"/>
-        <v/>
+        <v>-1125</v>
       </c>
       <c r="H45" s="285" t="str">
         <f t="shared" si="19"/>
@@ -7997,13 +8039,13 @@
         <f t="shared" si="20"/>
         <v>-4176</v>
       </c>
-      <c r="F46" s="270" t="str">
+      <c r="F46" s="270">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="G46" s="270" t="str">
+        <v>-1887</v>
+      </c>
+      <c r="G46" s="270">
         <f t="shared" si="20"/>
-        <v/>
+        <v>-1482</v>
       </c>
       <c r="H46" s="270" t="str">
         <f t="shared" si="20"/>
@@ -8046,13 +8088,13 @@
         <f t="shared" si="21"/>
         <v>9691</v>
       </c>
-      <c r="F47" s="271" t="str">
+      <c r="F47" s="271">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="G47" s="271" t="str">
+        <v>-4467</v>
+      </c>
+      <c r="G47" s="271">
         <f t="shared" si="21"/>
-        <v/>
+        <v>49337</v>
       </c>
       <c r="H47" s="271" t="str">
         <f t="shared" si="21"/>
@@ -8095,13 +8137,13 @@
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F48" s="270" t="str">
+      <c r="F48" s="270">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="G48" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="G48" s="270">
         <f t="shared" si="22"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H48" s="270" t="str">
         <f t="shared" si="22"/>
@@ -8149,13 +8191,13 @@
         <f t="shared" si="23"/>
         <v>-2106</v>
       </c>
-      <c r="F51" s="270" t="str">
+      <c r="F51" s="270">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="G51" s="270" t="str">
+        <v>-1213</v>
+      </c>
+      <c r="G51" s="270">
         <f t="shared" si="23"/>
-        <v/>
+        <v>-1125</v>
       </c>
       <c r="H51" s="270" t="str">
         <f t="shared" si="23"/>
@@ -8198,13 +8240,13 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="F52" s="270" t="str">
+      <c r="F52" s="270">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="G52" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="G52" s="270">
         <f t="shared" si="24"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H52" s="270" t="str">
         <f t="shared" si="24"/>
@@ -8252,13 +8294,13 @@
         <f t="shared" si="25"/>
         <v>-2195</v>
       </c>
-      <c r="F55" s="285" t="str">
+      <c r="F55" s="285">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="G55" s="285" t="str">
+        <v>-4918</v>
+      </c>
+      <c r="G55" s="285">
         <f t="shared" si="25"/>
-        <v/>
+        <v>4291</v>
       </c>
       <c r="H55" s="285" t="str">
         <f t="shared" si="25"/>
@@ -8301,13 +8343,13 @@
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="F56" s="285" t="str">
+      <c r="F56" s="285">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="G56" s="285" t="str">
+        <v>0</v>
+      </c>
+      <c r="G56" s="285">
         <f t="shared" si="26"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H56" s="285" t="str">
         <f t="shared" si="26"/>
@@ -8350,13 +8392,13 @@
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="F57" s="285" t="str">
+      <c r="F57" s="285">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="G57" s="285" t="str">
+        <v>0</v>
+      </c>
+      <c r="G57" s="285">
         <f t="shared" si="27"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H57" s="285" t="str">
         <f t="shared" si="27"/>
@@ -8399,13 +8441,13 @@
         <f t="shared" si="28"/>
         <v>-176</v>
       </c>
-      <c r="F58" s="285" t="str">
+      <c r="F58" s="285">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="G58" s="285" t="str">
+        <v>-4593</v>
+      </c>
+      <c r="G58" s="285">
         <f t="shared" si="28"/>
-        <v/>
+        <v>36959</v>
       </c>
       <c r="H58" s="285" t="str">
         <f t="shared" si="28"/>
@@ -8454,13 +8496,13 @@
         <f t="shared" si="29"/>
         <v>-7236</v>
       </c>
-      <c r="F61" s="270" t="str">
+      <c r="F61" s="270">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="G61" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="G61" s="270">
         <f t="shared" si="29"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H61" s="270" t="str">
         <f t="shared" si="29"/>
@@ -8503,13 +8545,13 @@
         <f t="shared" si="30"/>
         <v>-7236</v>
       </c>
-      <c r="F62" s="270" t="str">
+      <c r="F62" s="270">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="G62" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="G62" s="270">
         <f t="shared" si="30"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H62" s="270" t="str">
         <f t="shared" si="30"/>
@@ -8552,13 +8594,13 @@
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="F63" s="270" t="str">
+      <c r="F63" s="270">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="G63" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="G63" s="270">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H63" s="270" t="str">
         <f t="shared" si="31"/>
@@ -8601,13 +8643,13 @@
         <f t="shared" si="32"/>
         <v>4973</v>
       </c>
-      <c r="F64" s="270" t="str">
+      <c r="F64" s="270">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="G64" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="G64" s="270">
         <f t="shared" si="32"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H64" s="270" t="str">
         <f t="shared" si="32"/>
@@ -8650,13 +8692,13 @@
         <f t="shared" si="33"/>
         <v>2.4180000000000001</v>
       </c>
-      <c r="F65" s="70" t="str">
+      <c r="F65" s="70">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="G65" s="70" t="str">
+        <v>0</v>
+      </c>
+      <c r="G65" s="70">
         <f t="shared" si="33"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H65" s="70" t="str">
         <f t="shared" si="33"/>
@@ -8701,13 +8743,13 @@
         <f t="shared" si="34"/>
         <v>3.6727851077577034E-2</v>
       </c>
-      <c r="E68" s="89" t="str">
+      <c r="E68" s="89">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="F68" s="89" t="str">
+        <v>9.945859149719638E-2</v>
+      </c>
+      <c r="F68" s="89">
         <f t="shared" si="34"/>
-        <v/>
+        <v>0.27593114526375628</v>
       </c>
       <c r="G68" s="89" t="str">
         <f t="shared" si="34"/>
@@ -8750,13 +8792,13 @@
         <f t="shared" ref="D69:M69" si="35">IF(E$36="","",D38/E38-1)</f>
         <v>8.5882520924982941E-2</v>
       </c>
-      <c r="E69" s="89" t="str">
+      <c r="E69" s="89">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="F69" s="89" t="str">
+        <v>0.13951776610416378</v>
+      </c>
+      <c r="F69" s="89">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0.18291967591743963</v>
       </c>
       <c r="G69" s="89" t="str">
         <f t="shared" si="35"/>
@@ -8800,13 +8842,13 @@
         <f t="shared" ref="D70:M70" si="36">IF(E$36="","",D43/E43-1)</f>
         <v>0.57599215002180548</v>
       </c>
-      <c r="E70" s="98" t="str">
+      <c r="E70" s="98">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="F70" s="98" t="str">
+        <v>1.2524557956777995</v>
+      </c>
+      <c r="F70" s="98">
         <f t="shared" si="36"/>
-        <v/>
+        <v>-0.23845146811296059</v>
       </c>
       <c r="G70" s="98" t="str">
         <f t="shared" si="36"/>
@@ -8849,13 +8891,13 @@
         <f t="shared" ref="D71:M71" si="37">IF(E$36="","",D44/E44-1)</f>
         <v>-3.3707296499367354</v>
       </c>
-      <c r="E71" s="98" t="str">
+      <c r="E71" s="98">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="F71" s="98" t="str">
+        <v>-0.75070970455262331</v>
+      </c>
+      <c r="F71" s="98">
         <f t="shared" si="37"/>
-        <v/>
+        <v>-1.2305696969696971</v>
       </c>
       <c r="G71" s="98" t="str">
         <f t="shared" si="37"/>
@@ -8899,13 +8941,13 @@
         <f t="shared" ref="D72:M72" si="38">IF(E$36="","",D47/E47-1)</f>
         <v>1.3998555360643898</v>
       </c>
-      <c r="E72" s="98" t="str">
+      <c r="E72" s="98">
         <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="F72" s="98" t="str">
+        <v>-3.1694649653010969</v>
+      </c>
+      <c r="F72" s="98">
         <f t="shared" si="38"/>
-        <v/>
+        <v>-1.0905405679307618</v>
       </c>
       <c r="G72" s="98" t="str">
         <f t="shared" si="38"/>
@@ -8974,13 +9016,13 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="F76" s="285" t="str">
+      <c r="F76" s="285">
         <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="G76" s="285" t="str">
+        <v>0</v>
+      </c>
+      <c r="G76" s="285">
         <f t="shared" si="39"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H76" s="285" t="str">
         <f t="shared" si="39"/>
@@ -9023,13 +9065,13 @@
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="F77" s="282" t="str">
+      <c r="F77" s="282">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="G77" s="282" t="str">
+        <v>0</v>
+      </c>
+      <c r="G77" s="282">
         <f t="shared" si="40"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H77" s="282" t="str">
         <f t="shared" si="40"/>
@@ -9057,13 +9099,13 @@
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="F78" s="282" t="str">
+      <c r="F78" s="282">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="G78" s="282" t="str">
+        <v>0</v>
+      </c>
+      <c r="G78" s="282">
         <f t="shared" si="40"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H78" s="282" t="str">
         <f t="shared" si="40"/>
@@ -9091,13 +9133,13 @@
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="F79" s="270" t="str">
+      <c r="F79" s="270">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="G79" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="G79" s="270">
         <f t="shared" si="41"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H79" s="270" t="str">
         <f t="shared" si="41"/>
@@ -9140,13 +9182,13 @@
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="F80" s="270" t="str">
+      <c r="F80" s="270">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="G80" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="G80" s="270">
         <f t="shared" si="42"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H80" s="270" t="str">
         <f t="shared" si="42"/>
@@ -10631,13 +10673,13 @@
         <f>Data!E36</f>
         <v>1046236</v>
       </c>
-      <c r="J4" s="270" t="str">
+      <c r="J4" s="270">
         <f>Data!F36</f>
-        <v/>
-      </c>
-      <c r="K4" s="270" t="str">
+        <v>951592</v>
+      </c>
+      <c r="K4" s="270">
         <f>Data!G36</f>
-        <v/>
+        <v>745802</v>
       </c>
       <c r="L4" s="270" t="str">
         <f>Data!H36</f>
@@ -10686,13 +10728,13 @@
         <f t="shared" si="1"/>
         <v>-953828</v>
       </c>
-      <c r="J5" s="270" t="str">
+      <c r="J5" s="270">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K5" s="270" t="str">
+        <v>-872831</v>
+      </c>
+      <c r="K5" s="270">
         <f t="shared" si="1"/>
-        <v/>
+        <v>-679999</v>
       </c>
       <c r="L5" s="270" t="str">
         <f t="shared" si="1"/>
@@ -10741,13 +10783,13 @@
         <f t="shared" si="2"/>
         <v>92408</v>
       </c>
-      <c r="J6" s="267" t="str">
+      <c r="J6" s="267">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K6" s="267" t="str">
+        <v>78761</v>
+      </c>
+      <c r="K6" s="267">
         <f t="shared" si="2"/>
-        <v/>
+        <v>65803</v>
       </c>
       <c r="L6" s="267" t="str">
         <f t="shared" si="2"/>
@@ -10796,13 +10838,13 @@
         <f t="shared" si="3"/>
         <v>-74064</v>
       </c>
-      <c r="J7" s="266" t="str">
+      <c r="J7" s="266">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K7" s="266" t="str">
+        <v>-70617</v>
+      </c>
+      <c r="K7" s="266">
         <f t="shared" si="3"/>
-        <v/>
+        <v>-55109</v>
       </c>
       <c r="L7" s="266" t="str">
         <f t="shared" si="3"/>
@@ -10853,13 +10895,13 @@
         <f t="shared" si="4"/>
         <v>18344</v>
       </c>
-      <c r="J8" s="267" t="str">
+      <c r="J8" s="267">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K8" s="267" t="str">
+        <v>8144</v>
+      </c>
+      <c r="K8" s="267">
         <f t="shared" si="4"/>
-        <v/>
+        <v>10694</v>
       </c>
       <c r="L8" s="267" t="str">
         <f t="shared" si="4"/>
@@ -10910,13 +10952,13 @@
         <f t="shared" si="5"/>
         <v>-2195</v>
       </c>
-      <c r="J9" s="270" t="str">
+      <c r="J9" s="270">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K9" s="270" t="str">
+        <v>-4918</v>
+      </c>
+      <c r="K9" s="270">
         <f t="shared" si="5"/>
-        <v/>
+        <v>4291</v>
       </c>
       <c r="L9" s="270" t="str">
         <f t="shared" si="5"/>
@@ -10965,13 +11007,13 @@
         <f t="shared" si="6"/>
         <v>-2106</v>
       </c>
-      <c r="J10" s="266" t="str">
+      <c r="J10" s="266">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="K10" s="266" t="str">
+        <v>-1213</v>
+      </c>
+      <c r="K10" s="266">
         <f t="shared" si="6"/>
-        <v/>
+        <v>-1125</v>
       </c>
       <c r="L10" s="266" t="str">
         <f t="shared" si="6"/>
@@ -11020,13 +11062,13 @@
         <f t="shared" si="7"/>
         <v>14043</v>
       </c>
-      <c r="J11" s="267" t="str">
+      <c r="J11" s="267">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K11" s="267" t="str">
+        <v>2013</v>
+      </c>
+      <c r="K11" s="267">
         <f t="shared" si="7"/>
-        <v/>
+        <v>13860</v>
       </c>
       <c r="L11" s="267" t="str">
         <f t="shared" si="7"/>
@@ -11075,13 +11117,13 @@
         <f>Data!E46</f>
         <v>-4176</v>
       </c>
-      <c r="J12" s="266" t="str">
+      <c r="J12" s="266">
         <f>Data!F46</f>
-        <v/>
-      </c>
-      <c r="K12" s="266" t="str">
+        <v>-1887</v>
+      </c>
+      <c r="K12" s="266">
         <f>Data!G46</f>
-        <v/>
+        <v>-1482</v>
       </c>
       <c r="L12" s="266" t="str">
         <f>Data!H46</f>
@@ -11132,13 +11174,13 @@
         <f>Data!E48</f>
         <v>0</v>
       </c>
-      <c r="J13" s="270" t="str">
+      <c r="J13" s="270">
         <f>Data!F48</f>
-        <v/>
-      </c>
-      <c r="K13" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="K13" s="270">
         <f>Data!G48</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L13" s="270" t="str">
         <f>Data!H48</f>
@@ -11189,13 +11231,13 @@
         <f t="shared" si="8"/>
         <v>9867</v>
       </c>
-      <c r="J14" s="267" t="str">
+      <c r="J14" s="267">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K14" s="267" t="str">
+        <v>126</v>
+      </c>
+      <c r="K14" s="267">
         <f t="shared" si="8"/>
-        <v/>
+        <v>12378</v>
       </c>
       <c r="L14" s="267" t="str">
         <f t="shared" si="8"/>
@@ -11244,13 +11286,13 @@
         <f>IF(Data!E61="","",-Data!E61)</f>
         <v>7236</v>
       </c>
-      <c r="J15" s="266" t="str">
+      <c r="J15" s="266">
         <f>IF(Data!F61="","",-Data!F61)</f>
-        <v/>
-      </c>
-      <c r="K15" s="266" t="str">
+        <v>0</v>
+      </c>
+      <c r="K15" s="266">
         <f>IF(Data!G61="","",-Data!G61)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L15" s="266" t="str">
         <f>IF(Data!H61="","",-Data!H61)</f>
@@ -11299,13 +11341,13 @@
         <f>Data!E62</f>
         <v>-7236</v>
       </c>
-      <c r="J16" s="266" t="str">
+      <c r="J16" s="266">
         <f>Data!F62</f>
-        <v/>
-      </c>
-      <c r="K16" s="266" t="str">
+        <v>0</v>
+      </c>
+      <c r="K16" s="266">
         <f>Data!G62</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L16" s="266" t="str">
         <f>Data!H62</f>
@@ -11407,13 +11449,13 @@
         <f t="shared" si="9"/>
         <v>9867</v>
       </c>
-      <c r="J19" s="271" t="str">
+      <c r="J19" s="271">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K19" s="271" t="str">
+        <v>126</v>
+      </c>
+      <c r="K19" s="271">
         <f t="shared" si="9"/>
-        <v/>
+        <v>12378</v>
       </c>
       <c r="L19" s="271" t="str">
         <f t="shared" si="9"/>
@@ -11527,13 +11569,13 @@
         <f>Data!E37</f>
         <v>-899163</v>
       </c>
-      <c r="J23" s="270" t="str">
+      <c r="J23" s="270">
         <f>Data!F37</f>
-        <v/>
-      </c>
-      <c r="K23" s="270" t="str">
+        <v>-822526</v>
+      </c>
+      <c r="K23" s="270">
         <f>Data!G37</f>
-        <v/>
+        <v>-636694</v>
       </c>
       <c r="L23" s="270" t="str">
         <f>Data!H37</f>
@@ -11584,13 +11626,13 @@
         <f>Data!E40</f>
         <v>-37772</v>
       </c>
-      <c r="J24" s="270" t="str">
+      <c r="J24" s="270">
         <f>Data!F40</f>
-        <v/>
-      </c>
-      <c r="K24" s="270" t="str">
+        <v>-38743</v>
+      </c>
+      <c r="K24" s="270">
         <f>Data!G40</f>
-        <v/>
+        <v>-27156</v>
       </c>
       <c r="L24" s="270" t="str">
         <f>Data!H40</f>
@@ -11641,13 +11683,13 @@
         <f>Data!E42</f>
         <v>-16893</v>
       </c>
-      <c r="J25" s="270" t="str">
+      <c r="J25" s="270">
         <f>Data!F42</f>
-        <v/>
-      </c>
-      <c r="K25" s="270" t="str">
+        <v>-11562</v>
+      </c>
+      <c r="K25" s="270">
         <f>Data!G42</f>
-        <v/>
+        <v>-16149</v>
       </c>
       <c r="L25" s="270" t="str">
         <f>Data!H42</f>
@@ -11698,13 +11740,13 @@
         <f t="shared" si="10"/>
         <v>-953828</v>
       </c>
-      <c r="J26" s="267" t="str">
+      <c r="J26" s="267">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="K26" s="267" t="str">
+        <v>-872831</v>
+      </c>
+      <c r="K26" s="267">
         <f t="shared" si="10"/>
-        <v/>
+        <v>-679999</v>
       </c>
       <c r="L26" s="267" t="str">
         <f t="shared" si="10"/>
@@ -11766,13 +11808,13 @@
         <f t="shared" si="11"/>
         <v>0.85942655385591782</v>
       </c>
-      <c r="J29" s="13" t="str">
+      <c r="J29" s="13">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K29" s="13" t="str">
+        <v>0.86436834273512175</v>
+      </c>
+      <c r="K29" s="13">
         <f t="shared" si="11"/>
-        <v/>
+        <v>0.85370379805900221</v>
       </c>
       <c r="L29" s="13" t="str">
         <f t="shared" si="11"/>
@@ -11824,13 +11866,13 @@
         <f t="shared" si="12"/>
         <v>3.6102753107329515E-2</v>
       </c>
-      <c r="J30" s="13" t="str">
+      <c r="J30" s="13">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K30" s="13" t="str">
+        <v>4.0713877376018295E-2</v>
+      </c>
+      <c r="K30" s="13">
         <f t="shared" si="12"/>
-        <v/>
+        <v>3.6411809032424157E-2</v>
       </c>
       <c r="L30" s="13" t="str">
         <f t="shared" si="12"/>
@@ -11882,13 +11924,13 @@
         <f t="shared" si="13"/>
         <v>1.614645261680921E-2</v>
       </c>
-      <c r="J31" s="13" t="str">
+      <c r="J31" s="13">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K31" s="13" t="str">
+        <v>1.2150165196849069E-2</v>
+      </c>
+      <c r="K31" s="13">
         <f t="shared" si="13"/>
-        <v/>
+        <v>2.1653200179136016E-2</v>
       </c>
       <c r="L31" s="13" t="str">
         <f t="shared" si="13"/>
@@ -11937,13 +11979,13 @@
         <f t="shared" si="14"/>
         <v>0.91167575958005653</v>
       </c>
-      <c r="J32" s="29" t="str">
+      <c r="J32" s="29">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="K32" s="29" t="str">
+        <v>0.91723238530798912</v>
+      </c>
+      <c r="K32" s="29">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0.91176880727056242</v>
       </c>
       <c r="L32" s="29" t="str">
         <f t="shared" si="14"/>
@@ -12005,13 +12047,13 @@
         <f>IF(I4="","",Data!E41)</f>
         <v>-74064</v>
       </c>
-      <c r="J35" s="267" t="str">
+      <c r="J35" s="267">
         <f>IF(J4="","",Data!F41)</f>
-        <v/>
-      </c>
-      <c r="K35" s="267" t="str">
+        <v>-70617</v>
+      </c>
+      <c r="K35" s="267">
         <f>IF(K4="","",Data!G41)</f>
-        <v/>
+        <v>-55109</v>
       </c>
       <c r="L35" s="267" t="str">
         <f>IF(L4="","",Data!H41)</f>
@@ -12071,13 +12113,13 @@
         <f t="shared" si="15"/>
         <v>7.0790911419603225E-2</v>
       </c>
-      <c r="J38" s="29" t="str">
+      <c r="J38" s="29">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K38" s="29" t="str">
+        <v>7.4209325004834001E-2</v>
+      </c>
+      <c r="K38" s="29">
         <f t="shared" si="15"/>
-        <v/>
+        <v>7.3892266311970198E-2</v>
       </c>
       <c r="L38" s="29" t="str">
         <f t="shared" si="15"/>
@@ -12140,13 +12182,13 @@
         <f t="shared" si="16"/>
         <v>0.29737235633411663</v>
       </c>
-      <c r="J41" s="6" t="str">
+      <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="K41" s="6" t="str">
+        <v>0.93740685543964231</v>
+      </c>
+      <c r="K41" s="6">
         <f t="shared" si="16"/>
-        <v/>
+        <v>0.10692640692640693</v>
       </c>
       <c r="L41" s="6" t="str">
         <f t="shared" si="16"/>
@@ -12228,13 +12270,13 @@
         <f>Data!E51</f>
         <v>-2106</v>
       </c>
-      <c r="J45" s="266" t="str">
+      <c r="J45" s="266">
         <f>Data!F51</f>
-        <v/>
-      </c>
-      <c r="K45" s="266" t="str">
+        <v>-1213</v>
+      </c>
+      <c r="K45" s="266">
         <f>Data!G51</f>
-        <v/>
+        <v>-1125</v>
       </c>
       <c r="L45" s="266" t="str">
         <f>Data!H51</f>
@@ -12283,13 +12325,13 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="J46" s="274" t="str">
+      <c r="J46" s="274">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="K46" s="274" t="str">
+        <v>0</v>
+      </c>
+      <c r="K46" s="274">
         <f t="shared" si="17"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L46" s="274" t="str">
         <f t="shared" si="17"/>
@@ -12340,13 +12382,13 @@
         <f>Data!E52</f>
         <v>0</v>
       </c>
-      <c r="J47" s="278" t="str">
+      <c r="J47" s="278">
         <f>Data!F52</f>
-        <v/>
-      </c>
-      <c r="K47" s="278" t="str">
+        <v>0</v>
+      </c>
+      <c r="K47" s="278">
         <f>Data!G52</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L47" s="278" t="str">
         <f>Data!H52</f>
@@ -12395,13 +12437,13 @@
         <f t="shared" si="18"/>
         <v>-2106</v>
       </c>
-      <c r="J48" s="267" t="str">
+      <c r="J48" s="267">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="K48" s="267" t="str">
+        <v>-1213</v>
+      </c>
+      <c r="K48" s="267">
         <f t="shared" si="18"/>
-        <v/>
+        <v>-1125</v>
       </c>
       <c r="L48" s="267" t="str">
         <f t="shared" si="18"/>
@@ -12512,13 +12554,13 @@
         <f t="shared" si="19"/>
         <v>8.7103513770180445</v>
       </c>
-      <c r="J53" s="40" t="str">
+      <c r="J53" s="40">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="K53" s="40" t="str">
+        <v>6.7139323990107176</v>
+      </c>
+      <c r="K53" s="40">
         <f t="shared" si="19"/>
-        <v/>
+        <v>9.5057777777777783</v>
       </c>
       <c r="L53" s="40" t="str">
         <f t="shared" si="19"/>
@@ -12581,13 +12623,13 @@
         <f>Data!E56</f>
         <v>0</v>
       </c>
-      <c r="J56" s="266" t="str">
+      <c r="J56" s="266">
         <f>Data!F56</f>
-        <v/>
-      </c>
-      <c r="K56" s="266" t="str">
+        <v>0</v>
+      </c>
+      <c r="K56" s="266">
         <f>Data!G56</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L56" s="266" t="str">
         <f>Data!H56</f>
@@ -12636,13 +12678,13 @@
         <f>Data!E55</f>
         <v>-2195</v>
       </c>
-      <c r="J57" s="266" t="str">
+      <c r="J57" s="266">
         <f>Data!F55</f>
-        <v/>
-      </c>
-      <c r="K57" s="266" t="str">
+        <v>-4918</v>
+      </c>
+      <c r="K57" s="266">
         <f>Data!G55</f>
-        <v/>
+        <v>4291</v>
       </c>
       <c r="L57" s="266" t="str">
         <f>Data!H55</f>
@@ -12691,13 +12733,13 @@
         <f>Data!E57</f>
         <v>0</v>
       </c>
-      <c r="J58" s="266" t="str">
+      <c r="J58" s="266">
         <f>Data!F57</f>
-        <v/>
-      </c>
-      <c r="K58" s="266" t="str">
+        <v>0</v>
+      </c>
+      <c r="K58" s="266">
         <f>Data!G57</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L58" s="266" t="str">
         <f>Data!H57</f>
@@ -12746,13 +12788,13 @@
         <f t="shared" si="20"/>
         <v>-2195</v>
       </c>
-      <c r="J59" s="267" t="str">
+      <c r="J59" s="267">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="K59" s="267" t="str">
+        <v>-4918</v>
+      </c>
+      <c r="K59" s="267">
         <f t="shared" si="20"/>
-        <v/>
+        <v>4291</v>
       </c>
       <c r="L59" s="267" t="str">
         <f t="shared" si="20"/>
@@ -12802,13 +12844,13 @@
         <f>Data!E58</f>
         <v>-176</v>
       </c>
-      <c r="J60" s="266" t="str">
+      <c r="J60" s="266">
         <f>Data!F58</f>
-        <v/>
-      </c>
-      <c r="K60" s="266" t="str">
+        <v>-4593</v>
+      </c>
+      <c r="K60" s="266">
         <f>Data!G58</f>
-        <v/>
+        <v>36959</v>
       </c>
       <c r="L60" s="266" t="str">
         <f>Data!H58</f>
@@ -12857,13 +12899,13 @@
         <f t="shared" si="21"/>
         <v>-2371</v>
       </c>
-      <c r="J61" s="267" t="str">
+      <c r="J61" s="267">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K61" s="267" t="str">
+        <v>-9511</v>
+      </c>
+      <c r="K61" s="267">
         <f t="shared" si="21"/>
-        <v/>
+        <v>41250</v>
       </c>
       <c r="L61" s="267" t="str">
         <f t="shared" si="21"/>
@@ -13077,13 +13119,13 @@
         <f t="shared" si="23"/>
         <v>0.91167575958005653</v>
       </c>
-      <c r="J71" s="6" t="str">
+      <c r="J71" s="6">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="K71" s="6" t="str">
+        <v>0.91723238530798912</v>
+      </c>
+      <c r="K71" s="6">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0.91176880727056242</v>
       </c>
       <c r="L71" s="6" t="str">
         <f t="shared" si="23"/>
@@ -13134,13 +13176,13 @@
         <f t="shared" si="24"/>
         <v>8.8324240419943495E-2</v>
       </c>
-      <c r="J72" s="62" t="str">
+      <c r="J72" s="62">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="K72" s="62" t="str">
+        <v>8.2767614692010869E-2</v>
+      </c>
+      <c r="K72" s="62">
         <f t="shared" si="24"/>
-        <v/>
+        <v>8.8231192729437566E-2</v>
       </c>
       <c r="L72" s="62" t="str">
         <f t="shared" si="24"/>
@@ -13191,13 +13233,13 @@
         <f t="shared" si="25"/>
         <v>7.0790911419603225E-2</v>
       </c>
-      <c r="J73" s="6" t="str">
+      <c r="J73" s="6">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="K73" s="6" t="str">
+        <v>7.4209325004834001E-2</v>
+      </c>
+      <c r="K73" s="6">
         <f t="shared" si="25"/>
-        <v/>
+        <v>7.3892266311970198E-2</v>
       </c>
       <c r="L73" s="6" t="str">
         <f t="shared" si="25"/>
@@ -13248,13 +13290,13 @@
         <f t="shared" si="26"/>
         <v>1.7533329000340266E-2</v>
       </c>
-      <c r="J74" s="62" t="str">
+      <c r="J74" s="62">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="K74" s="62" t="str">
+        <v>8.5582896871768573E-3</v>
+      </c>
+      <c r="K74" s="62">
         <f t="shared" si="26"/>
-        <v/>
+        <v>1.4338926417467372E-2</v>
       </c>
       <c r="L74" s="62" t="str">
         <f t="shared" si="26"/>
@@ -13305,13 +13347,13 @@
         <f t="shared" si="27"/>
         <v>-2.0979970102347847E-3</v>
       </c>
-      <c r="J75" s="6" t="str">
+      <c r="J75" s="6">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="K75" s="6" t="str">
+        <v>-5.168181321406653E-3</v>
+      </c>
+      <c r="K75" s="6">
         <f t="shared" si="27"/>
-        <v/>
+        <v>5.7535378022585083E-3</v>
       </c>
       <c r="L75" s="6" t="str">
         <f t="shared" si="27"/>
@@ -13362,13 +13404,13 @@
         <f t="shared" si="28"/>
         <v>2.0129301610726453E-3</v>
       </c>
-      <c r="J76" s="6" t="str">
+      <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="K76" s="6" t="str">
+        <v>1.2747059664225844E-3</v>
+      </c>
+      <c r="K76" s="6">
         <f t="shared" si="28"/>
-        <v/>
+        <v>1.5084432597391802E-3</v>
       </c>
       <c r="L76" s="6" t="str">
         <f t="shared" si="28"/>
@@ -13419,13 +13461,13 @@
         <f t="shared" si="29"/>
         <v>1.3422401829032838E-2</v>
       </c>
-      <c r="J77" s="62" t="str">
+      <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="K77" s="62" t="str">
+        <v>2.1154023993476194E-3</v>
+      </c>
+      <c r="K77" s="62">
         <f t="shared" si="29"/>
-        <v/>
+        <v>1.8584020959986697E-2</v>
       </c>
       <c r="L77" s="62" t="str">
         <f t="shared" si="29"/>
@@ -13476,13 +13518,13 @@
         <f t="shared" si="30"/>
         <v>3.9914512595628521E-3</v>
       </c>
-      <c r="J78" s="6" t="str">
+      <c r="J78" s="6">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K78" s="6" t="str">
+        <v>1.9829927111619265E-3</v>
+      </c>
+      <c r="K78" s="6">
         <f t="shared" si="30"/>
-        <v/>
+        <v>1.9871225874964131E-3</v>
       </c>
       <c r="L78" s="6" t="str">
         <f t="shared" si="30"/>
@@ -13534,13 +13576,13 @@
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="J79" s="6" t="str">
+      <c r="J79" s="6">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="K79" s="6" t="str">
+        <v>0</v>
+      </c>
+      <c r="K79" s="6">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L79" s="6" t="str">
         <f t="shared" si="31"/>
@@ -13591,13 +13633,13 @@
         <f t="shared" si="32"/>
         <v>9.4309505694699855E-3</v>
       </c>
-      <c r="J80" s="62" t="str">
+      <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="K80" s="62" t="str">
+        <v>1.3240968818569303E-4</v>
+      </c>
+      <c r="K80" s="62">
         <f t="shared" si="32"/>
-        <v/>
+        <v>1.6596898372490284E-2</v>
       </c>
       <c r="L80" s="62" t="str">
         <f t="shared" si="32"/>
@@ -13648,13 +13690,13 @@
         <f t="shared" si="33"/>
         <v>6.9162215790701141E-3</v>
       </c>
-      <c r="J81" s="6" t="str">
+      <c r="J81" s="6">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="K81" s="6" t="str">
+        <v>0</v>
+      </c>
+      <c r="K81" s="6">
         <f t="shared" si="33"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L81" s="6" t="str">
         <f t="shared" si="33"/>
@@ -13707,13 +13749,13 @@
         <f t="shared" si="34"/>
         <v>6.9162215790701141E-3</v>
       </c>
-      <c r="J82" s="6" t="str">
+      <c r="J82" s="6">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="K82" s="6" t="str">
+        <v>0</v>
+      </c>
+      <c r="K82" s="6">
         <f t="shared" si="34"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L82" s="6" t="str">
         <f t="shared" si="34"/>
@@ -13814,13 +13856,13 @@
         <f t="shared" si="35"/>
         <v>9.4309505694699855E-3</v>
       </c>
-      <c r="J85" s="62" t="str">
+      <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="K85" s="62" t="str">
+        <v>1.3240968818569303E-4</v>
+      </c>
+      <c r="K85" s="62">
         <f t="shared" si="35"/>
-        <v/>
+        <v>1.6596898372490284E-2</v>
       </c>
       <c r="L85" s="62" t="str">
         <f t="shared" si="35"/>
@@ -13881,13 +13923,13 @@
         <f>Data!E65</f>
         <v>2.4180000000000001</v>
       </c>
-      <c r="J88" s="109" t="str">
+      <c r="J88" s="109">
         <f>Data!F65</f>
-        <v/>
-      </c>
-      <c r="K88" s="109" t="str">
+        <v>0</v>
+      </c>
+      <c r="K88" s="109">
         <f>Data!G65</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L88" s="109" t="str">
         <f>Data!H65</f>
@@ -13937,13 +13979,13 @@
         <f t="shared" si="36"/>
         <v>7271.0574450503345</v>
       </c>
-      <c r="J89" s="71" t="str">
+      <c r="J89" s="71">
         <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="K89" s="71" t="str">
+        <v>0</v>
+      </c>
+      <c r="K89" s="71">
         <f t="shared" si="36"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L89" s="71" t="str">
         <f t="shared" si="36"/>
@@ -13992,13 +14034,13 @@
         <f t="shared" si="37"/>
         <v>0.73690660231583405</v>
       </c>
-      <c r="J90" s="152" t="str">
+      <c r="J90" s="152">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="K90" s="152" t="str">
+        <v>0</v>
+      </c>
+      <c r="K90" s="152">
         <f t="shared" si="37"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L90" s="152" t="str">
         <f t="shared" si="37"/>
@@ -14068,13 +14110,13 @@
         <f t="shared" si="38"/>
         <v>1.8956445993031361E-2</v>
       </c>
-      <c r="J92" s="22" t="str">
+      <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="K92" s="22" t="str">
+        <v>0</v>
+      </c>
+      <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -14146,13 +14188,13 @@
         <f t="shared" si="39"/>
         <v>3.6727851077577034E-2</v>
       </c>
-      <c r="I95" s="6" t="str">
+      <c r="I95" s="6">
         <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="J95" s="6" t="str">
+        <v>9.945859149719638E-2</v>
+      </c>
+      <c r="J95" s="6">
         <f t="shared" si="39"/>
-        <v/>
+        <v>0.27593114526375628</v>
       </c>
       <c r="K95" s="6" t="str">
         <f t="shared" si="39"/>
@@ -14203,13 +14245,13 @@
         <f t="shared" si="40"/>
         <v>0.92544328135013876</v>
       </c>
-      <c r="I96" s="6" t="str">
+      <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="J96" s="6" t="str">
+        <v>5.9761549925484347</v>
+      </c>
+      <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v/>
+        <v>-0.85476190476190472</v>
       </c>
       <c r="K96" s="6" t="str">
         <f t="shared" si="40"/>
@@ -14300,13 +14342,13 @@
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="J100" s="270" t="str">
+      <c r="J100" s="270">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="K100" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="K100" s="270">
         <f t="shared" si="41"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L100" s="270" t="str">
         <f t="shared" si="41"/>
@@ -14353,13 +14395,13 @@
         <f>IF(H$4="","",Data!E77)</f>
         <v>0</v>
       </c>
-      <c r="I101" s="282" t="str">
+      <c r="I101" s="282">
         <f>IF(I$4="","",Data!F77)</f>
-        <v/>
-      </c>
-      <c r="J101" s="282" t="str">
+        <v>0</v>
+      </c>
+      <c r="J101" s="282">
         <f>IF(J$4="","",Data!G77)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K101" s="282" t="str">
         <f>IF(K$4="","",Data!H77)</f>
@@ -14410,13 +14452,13 @@
         <f>IF(H$4="","",Data!E78)</f>
         <v>0</v>
       </c>
-      <c r="I102" s="282" t="str">
+      <c r="I102" s="282">
         <f>IF(I$4="","",Data!F78)</f>
-        <v/>
-      </c>
-      <c r="J102" s="282" t="str">
+        <v>0</v>
+      </c>
+      <c r="J102" s="282">
         <f>IF(J$4="","",Data!G78)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K102" s="282" t="str">
         <f>IF(K$4="","",Data!H78)</f>
@@ -14471,13 +14513,13 @@
         <f>Data!E79</f>
         <v>0</v>
       </c>
-      <c r="J103" s="270" t="str">
+      <c r="J103" s="270">
         <f>Data!F79</f>
-        <v/>
-      </c>
-      <c r="K103" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="K103" s="270">
         <f>Data!G79</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L103" s="270" t="str">
         <f>Data!H79</f>
@@ -14528,13 +14570,13 @@
         <f>Data!E80</f>
         <v>0</v>
       </c>
-      <c r="J104" s="270" t="str">
+      <c r="J104" s="270">
         <f>Data!F80</f>
-        <v/>
-      </c>
-      <c r="K104" s="270" t="str">
+        <v>0</v>
+      </c>
+      <c r="K104" s="270">
         <f>Data!G80</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L104" s="270" t="str">
         <f>Data!H80</f>
@@ -14608,17 +14650,17 @@
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="I107" s="91" t="e">
+      <c r="I107" s="91">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="J107" s="91">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="K107" s="91" t="e">
         <f t="shared" si="42"/>
         <v>#VALUE!</v>
-      </c>
-      <c r="J107" s="91" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="K107" s="91" t="str">
-        <f t="shared" si="42"/>
-        <v/>
       </c>
       <c r="L107" s="91" t="str">
         <f t="shared" si="42"/>
@@ -14665,17 +14707,17 @@
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="I108" s="91" t="e">
+      <c r="I108" s="91">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="J108" s="91">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="K108" s="91" t="e">
         <f t="shared" si="43"/>
         <v>#VALUE!</v>
-      </c>
-      <c r="J108" s="91" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="K108" s="91" t="str">
-        <f t="shared" si="43"/>
-        <v/>
       </c>
       <c r="L108" s="91" t="str">
         <f t="shared" si="43"/>
@@ -14761,13 +14803,13 @@
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>5.9662573521824376</v>
       </c>
-      <c r="J112" s="251" t="str">
+      <c r="J112" s="251">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
-        <v/>
-      </c>
-      <c r="K112" s="251" t="str">
+        <v>0</v>
+      </c>
+      <c r="K112" s="251">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L112" s="251" t="str">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
@@ -14816,13 +14858,13 @@
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>5.8598358163575552</v>
       </c>
-      <c r="J113" s="251" t="str">
+      <c r="J113" s="251">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v/>
-      </c>
-      <c r="K113" s="251" t="str">
+        <v>0</v>
+      </c>
+      <c r="K113" s="251">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L113" s="251" t="str">
         <f>IF(L$4="","",Data!H$22/L19)</f>
@@ -14937,13 +14979,13 @@
         <f t="shared" si="44"/>
         <v>1.3422401829032838E-2</v>
       </c>
-      <c r="J116" s="22" t="str">
+      <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v/>
-      </c>
-      <c r="K116" s="22" t="str">
+        <v>2.1154023993476194E-3</v>
+      </c>
+      <c r="K116" s="22">
         <f t="shared" si="44"/>
-        <v/>
+        <v>1.8584020959986697E-2</v>
       </c>
       <c r="L116" s="22" t="str">
         <f t="shared" si="44"/>
@@ -14994,13 +15036,13 @@
         <f t="shared" si="45"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J117" s="40" t="str">
+      <c r="J117" s="40" t="e">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="K117" s="40" t="str">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K117" s="40" t="e">
         <f t="shared" si="45"/>
-        <v/>
+        <v>#DIV/0!</v>
       </c>
       <c r="L117" s="40" t="str">
         <f t="shared" si="45"/>
@@ -15053,13 +15095,13 @@
         <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J118" s="15" t="str">
+      <c r="J118" s="15" t="e">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="K118" s="15" t="str">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K118" s="15" t="e">
         <f t="shared" si="46"/>
-        <v/>
+        <v>#DIV/0!</v>
       </c>
       <c r="L118" s="15" t="str">
         <f t="shared" si="46"/>
@@ -15112,13 +15154,13 @@
         <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J119" s="99" t="str">
+      <c r="J119" s="99" t="e">
         <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="K119" s="99" t="str">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K119" s="99" t="e">
         <f t="shared" si="47"/>
-        <v/>
+        <v>#DIV/0!</v>
       </c>
       <c r="L119" s="99" t="str">
         <f t="shared" si="47"/>
@@ -15233,13 +15275,13 @@
         <f t="shared" si="48"/>
         <v>3.6739910138475551</v>
       </c>
-      <c r="J123" s="159" t="str">
+      <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="K123" s="159" t="str">
+        <v>4.6916273208147556E-2</v>
+      </c>
+      <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v/>
+        <v>4.6089653156384962</v>
       </c>
       <c r="L123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15290,13 +15332,13 @@
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
         <v>3.2003406043968251E-2</v>
       </c>
-      <c r="J124" s="74" t="str">
+      <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="K124" s="74" t="str">
+        <v>4.0867833805006585E-4</v>
+      </c>
+      <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v/>
+        <v>4.014778149510885E-2</v>
       </c>
       <c r="L124" s="74" t="str">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
@@ -15340,13 +15382,13 @@
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>2.8072780259542379E-2</v>
       </c>
-      <c r="J125" s="22" t="str">
+      <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v/>
-      </c>
-      <c r="K125" s="22" t="str">
+        <v>-1.2939955569020308E-2</v>
+      </c>
+      <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v/>
+        <v>0.14291886901919743</v>
       </c>
       <c r="L125" s="22" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>

--- a/financial_models/opportunities/9618.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9618.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008D575C-DFE3-4047-9AEA-994BBDD9502C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAFB310-3F6D-4F67-91C4-EB2C99CC8623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>114.8</v>
+        <v>113.5</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5432,14 +5432,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>345209.84065003239</v>
+        <v>341300.66998065053</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.19986540491955213</v>
+        <v>0.20517568115776152</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5447,13 +5447,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5488,7 +5488,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1196808250427246</v>
+        <v>1.1215249683380129</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>185.53286313493385</v>
+        <v>185.83844056195898</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>91.921794301701311</v>
+        <v>92.062613392496303</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>114.55205061155499</v>
+        <v>114.72855742860922</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>141.45084486980141</v>
+        <v>141.66987066649239</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>159.56289465999788</v>
+        <v>159.81059657674808</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5631,22 +5631,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5658,13 +5658,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5684,13 +5684,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5719,13 +5719,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5811,13 +5811,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5833,7 +5833,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5855,22 +5855,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.881441067855093E-2</v>
+        <v>6.9717230628442983E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.0574912891986061E-2</v>
+        <v>3.0925110132158588E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6005,13 +6005,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-41.736493235143264</v>
+        <v>-41.805234319608559</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>11.552903475414809</v>
+        <v>11.571931406418704</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>36.688413943358988</v>
+        <v>36.748840710590464</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.5048241836305305</v>
+        <v>6.5155377974006097</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6205,31 +6205,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6279,22 +6279,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-64.613147314967009</v>
+        <v>-64.719566840731247</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>159.98848576107054</v>
+        <v>160.25199093749288</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6328,13 +6328,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>226.64 HKD</v>
+        <v>227.01 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.7960154682011633E-2</v>
+        <v>-4.7987375660487559E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>194.47 HKD</v>
+        <v>194.79 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.7761914692564695E-3</v>
+        <v>2.7460528879222597E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>180.19 HKD</v>
+        <v>180.48 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.9085969533860979E-2</v>
+        <v>2.9054240566849038E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>167 HKD</v>
+        <v>167.27 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.6020469089006444E-2</v>
+        <v>5.5987055893302717E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>154.82 HKD</v>
+        <v>155.07 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6465,17 +6465,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>8.3574386321419752E-2</v>
+        <v>8.3539190408932193E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>185.53286313493385</v>
+        <v>185.83844056195898</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6510,22 +6510,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6590,11 +6590,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>85.499015269554789</v>
+        <v>85.639834360349781</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>91.921794301701311</v>
+        <v>92.062613392496303</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6611,11 +6611,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>107.16699675664053</v>
+        <v>107.34350357369476</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>114.55205061155499</v>
+        <v>114.72855742860922</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6658,11 +6658,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>132.98260789775676</v>
+        <v>133.20163369444774</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>141.45084486980141</v>
+        <v>141.66987066649239</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6679,11 +6679,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>150.39345761262058</v>
+        <v>150.64115952937081</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>159.56289465999788</v>
+        <v>159.81059657674808</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6701,13 +6701,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6744,13 +6744,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6758,22 +6758,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6797,6 +6797,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6813,18 +6825,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10046,11 +10046,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>86.360571380835609</v>
+        <v>86.502809476842259</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-64.613147314967009</v>
+        <v>-64.719566840731247</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10456,11 +10456,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-125503.90399821395</v>
+        <v>-125710.61217603952</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-41.736493235143264</v>
+        <v>-41.805234319608559</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10473,11 +10473,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>34740.208778685992</v>
+        <v>34797.426801593261</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>11.552903475414809</v>
+        <v>11.571931406418704</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10490,11 +10490,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>110324.05514886223</v>
+        <v>110505.76172279057</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>36.688413943358988</v>
+        <v>36.748840710590464</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10507,11 +10507,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>19560.35992933427</v>
+        <v>19592.576348344315</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.5048241836305323</v>
+        <v>6.5155377974006115</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14095,20 +14095,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.0574912891986061E-2</v>
+        <v>3.0925110132158588E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.0574912891986061E-2</v>
+        <v>3.0925110132158588E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>2.323693379790941E-2</v>
+        <v>2.3503083700440529E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>1.8956445993031361E-2</v>
+        <v>1.9173568281938329E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
@@ -15258,30 +15258,30 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>7.8998943458976463</v>
+        <v>7.9129056763282781</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.731911320676419</v>
+        <v>10.749587056354843</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>6.9428637320565025</v>
+        <v>6.9542988082989519</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>3.6739910138475551</v>
+        <v>3.6800421721273064</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>4.6916273208147556E-2</v>
+        <v>4.6993545524276946E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.6089653156384962</v>
+        <v>4.6165564007896833</v>
       </c>
       <c r="L123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15315,30 +15315,30 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.881441067855093E-2</v>
+        <v>6.9717230628442983E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>9.3483548089515853E-2</v>
+        <v>9.4710018117663816E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.0477907073662913E-2</v>
+        <v>6.1271355139197813E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.2003406043968251E-2</v>
+        <v>3.2423279049579791E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>4.0867833805006585E-4</v>
+        <v>4.1404004867204357E-4</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>4.014778149510885E-2</v>
+        <v>4.0674505733829809E-2</v>
       </c>
       <c r="L124" s="74" t="str">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
@@ -15372,23 +15372,23 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12937058780220437</v>
+        <v>0.13085236545985077</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7370617118581888E-2</v>
+        <v>6.8142262953420268E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8072780259542379E-2</v>
+        <v>2.8394318711854317E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-1.2939955569020308E-2</v>
+        <v>-1.3088166513863712E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14291886901919743</v>
+        <v>0.14455582522822788</v>
       </c>
       <c r="L125" s="22" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16297,7 +16297,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.5048241836305305</v>
+        <v>6.5155377974006097</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1196808250427246</v>
+        <v>1.1215249683380129</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>481094.07382769289</v>
+        <v>481886.44821761636</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>159.98848576107054</v>
+        <v>160.25199093749288</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16492,7 +16492,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>185.56050774542021</v>
+        <v>185.86613070383422</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18680,23 +18680,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>159.98848576107054</v>
+        <v>160.25199093749288</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>159.98848576107054</v>
+        <v>160.25199093749288</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>159.98848576107054</v>
+        <v>160.25199093749288</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>159.98848576107054</v>
+        <v>160.25199093749288</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>159.98848576107054</v>
+        <v>160.25199093749288</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18711,23 +18711,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>165.0268547979984</v>
+        <v>165.29865829861353</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>166.61207510414206</v>
+        <v>166.88648950362563</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>168.19729541028579</v>
+        <v>168.47432070863783</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>169.78251571642949</v>
+        <v>170.06215191364996</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>172.95295632871685</v>
+        <v>173.23781432367423</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18742,23 +18742,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>164.82650155100126</v>
+        <v>165.0979750646336</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>167.93437199066022</v>
+        <v>168.21096424733588</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>171.07243359202178</v>
+        <v>171.3541943173654</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>174.24068635508604</v>
+        <v>174.52766527472227</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>180.66776536632261</v>
+        <v>180.96532985141798</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18773,23 +18773,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>164.63969199669154</v>
+        <v>164.91085783015345</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>169.17961194905948</v>
+        <v>169.45825514817241</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>173.80683074388256</v>
+        <v>174.0930950920993</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>178.52219288918053</v>
+        <v>178.81622356088036</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>188.22072526327929</v>
+        <v>188.53072966878952</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18804,23 +18804,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>164.46551059407173</v>
+        <v>164.73638954625582</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>170.35228547631661</v>
+        <v>170.63286009907679</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>176.40737628691102</v>
+        <v>176.69792380093716</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>182.63403599418487</v>
+        <v>182.93483897788985</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>195.61523145610406</v>
+        <v>195.93741480467776</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18835,23 +18835,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>161.15338432940104</v>
+        <v>161.41880812391204</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>168.24359266378866</v>
+        <v>168.52069421491532</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>175.60365437305867</v>
+        <v>175.89287813629304</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>183.24140165789214</v>
+        <v>183.54320498856339</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>199.38204255126666</v>
+        <v>199.71042993519617</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18866,23 +18866,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>161.00195598235243</v>
+        <v>161.26713037045701</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>169.28357333344812</v>
+        <v>169.56238775965159</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>177.95583249247059</v>
+        <v>178.2489303539401</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>187.0338212601323</v>
+        <v>187.34187080403322</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>206.4695442080403</v>
+        <v>206.80960489061738</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18898,23 +18898,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>157.92396278001246</v>
+        <v>158.18406763365678</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>167.23715978332504</v>
+        <v>167.51260371345194</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>177.07631202310134</v>
+        <v>177.36796129159652</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>187.46683645875532</v>
+        <v>187.77559918989445</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>210.00864244826721</v>
+        <v>210.35453211723498</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18929,23 +18929,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>157.79231529098678</v>
+        <v>158.05220331780976</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>168.15946234079402</v>
+        <v>168.43642532710149</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>179.203843271409</v>
+        <v>179.49899663892893</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>190.96464658238341</v>
+        <v>191.27917029731671</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>216.80188575956674</v>
+        <v>217.1589640760719</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18961,23 +18961,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>154.93129080671108</v>
+        <v>155.18646665216744</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>166.17855642427548</v>
+        <v>166.45225680727418</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>178.26323136530849</v>
+        <v>178.55683552067677</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>191.24189481019474</v>
+        <v>191.55687516013418</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>220.12422158962173</v>
+        <v>220.48677187921837</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18993,23 +18993,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>154.8168402318712</v>
+        <v>155.07182757426889</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>166.99649663444524</v>
+        <v>167.27154418613776</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>180.18757084248088</v>
+        <v>180.48434443476845</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>194.46798183224493</v>
+        <v>194.78827563099821</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>226.6354235506698</v>
+        <v>227.00869795840097</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19025,23 +19025,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>147.19728980748212</v>
+        <v>147.439727553143</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>162.83418560817415</v>
+        <v>163.10237772588911</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>180.43568232329363</v>
+        <v>180.73286456161102</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>200.24691116400436</v>
+        <v>200.57672300892114</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>247.62682751020935</v>
+        <v>248.03467530350264</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19057,23 +19057,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>142.86947809894883</v>
+        <v>143.10478782672547</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>161.02152521816939</v>
+        <v>161.28673183731183</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>182.16069911793903</v>
+        <v>182.46072250355925</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>206.79900226740807</v>
+        <v>207.13960557593501</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>269.06468637508107</v>
+        <v>269.50784287671934</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19089,23 +19089,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>137.59686789548579</v>
+        <v>137.82349349780637</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>157.28022100662108</v>
+        <v>157.53926560090511</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>180.92090033624558</v>
+        <v>181.21888174118735</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>209.38008097583409</v>
+        <v>209.72493538779008</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>285.17965351841104</v>
+        <v>285.64935178797691</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19121,23 +19121,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>134.61535228319676</v>
+        <v>134.83706725214469</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>155.44997219897922</v>
+        <v>155.7060023261117</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>181.14822821404141</v>
+        <v>181.44658403388101</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>212.98452200876883</v>
+        <v>213.33531302838611</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>301.97428813792379</v>
+        <v>302.47164760533963</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19184,7 +19184,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>226.6354235506698</v>
+        <v>227.00869795840097</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19212,7 +19212,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>194.46798183224493</v>
+        <v>194.78827563099821</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19240,7 +19240,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>180.18757084248088</v>
+        <v>180.48434443476845</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19268,7 +19268,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>166.99649663444524</v>
+        <v>167.27154418613776</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19296,7 +19296,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>154.8168402318712</v>
+        <v>155.07182757426889</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>194.46798183224493</v>
+        <v>194.78827563099821</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19680,7 +19680,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>180.18757084248088</v>
+        <v>180.48434443476845</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19703,7 +19703,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>166.99649663444524</v>
+        <v>167.27154418613776</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19719,7 +19719,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>179.74588448842476</v>
+        <v>180.04193061185671</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>226.6354235506698</v>
+        <v>227.00869795840097</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19789,7 +19789,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>154.8168402318712</v>
+        <v>155.07182757426889</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19834,7 +19834,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>114.8</v>
+        <v>113.5</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19845,7 +19845,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19986540491955213</v>
+        <v>0.20517568115776152</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>159.98848576107054</v>
+        <v>160.25199093749288</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19865,7 +19865,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>7.1528706990175162E-2</v>
+        <v>7.1494297926842101E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>185.53286313493385</v>
+        <v>185.83844056195898</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19977,7 +19977,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>185.56050774542021</v>
+        <v>185.86613070383422</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20122,11 +20122,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>85.499015269554789</v>
+        <v>85.639834360349781</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>91.921794301701311</v>
+        <v>92.062613392496303</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20134,7 +20134,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.50455249410532366</v>
+        <v>0.50460941711463403</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20147,11 +20147,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>107.16699675664053</v>
+        <v>107.34350357369476</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>114.55205061155499</v>
+        <v>114.72855742860922</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20159,7 +20159,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.38257811216849558</v>
+        <v>0.38264356350774231</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20193,11 +20193,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>132.98260789775676</v>
+        <v>133.20163369444774</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>141.45084486980141</v>
+        <v>141.66987066649239</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20205,7 +20205,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.2375968198856101</v>
+        <v>0.23767187112582711</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20218,11 +20218,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>150.39345761262058</v>
+        <v>150.64115952937081</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>159.56289465999788</v>
+        <v>159.81059657674808</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20230,7 +20230,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.13997503211088058</v>
+        <v>0.14005629786014673</v>
       </c>
     </row>
   </sheetData>
@@ -20341,7 +20341,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>114.8</v>
+        <v>113.5</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20359,14 +20359,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>345209.84065003239</v>
+        <v>341300.66998065053</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.19986540491955213</v>
+        <v>0.20517568115776152</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20374,13 +20374,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20418,7 +20418,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1196808250427246</v>
+        <v>1.1215249683380129</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20444,7 +20444,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>185.53286313493385</v>
+        <v>185.83844056195898</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>91.921794301701311</v>
+        <v>92.062613392496303</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20512,7 +20512,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>114.55205061155499</v>
+        <v>114.72855742860922</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>141.45084486980141</v>
+        <v>141.66987066649239</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20544,7 +20544,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>159.56289465999788</v>
+        <v>159.81059657674808</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20565,22 +20565,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20770,10 +20770,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20789,22 +20789,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20838,7 +20838,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.881441067855093E-2</v>
+        <v>6.9717230628442983E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20848,7 +20848,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.0574912891986061E-2</v>
+        <v>3.0925110132158588E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20939,22 +20939,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20962,13 +20962,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20989,7 +20989,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-41.736493235143264</v>
+        <v>-41.805234319608559</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21051,7 +21051,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>11.552903475414809</v>
+        <v>11.571931406418704</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21082,7 +21082,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>36.688413943358988</v>
+        <v>36.748840710590464</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21095,7 +21095,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>6.5048241836305305</v>
+        <v>6.5155377974006097</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21117,33 +21117,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21206,23 +21206,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21240,7 +21240,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-64.613147314967009</v>
+        <v>-64.719566840731247</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21254,7 +21254,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>159.98848576107054</v>
+        <v>160.25199093749288</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21266,13 +21266,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21317,7 +21317,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>226.64 HKD</v>
+        <v>227.01 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21340,7 +21340,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>194.47 HKD</v>
+        <v>194.79 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21362,7 +21362,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>180.19 HKD</v>
+        <v>180.48 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21384,7 +21384,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>167 HKD</v>
+        <v>167.27 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21406,7 +21406,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>154.82 HKD</v>
+        <v>155.07 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21428,7 +21428,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>185.53286313493385</v>
+        <v>185.83844056195898</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21436,13 +21436,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21455,22 +21455,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21535,11 +21535,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>85.499015269554789</v>
+        <v>85.639834360349781</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>91.921794301701311</v>
+        <v>92.062613392496303</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21556,11 +21556,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>107.16699675664053</v>
+        <v>107.34350357369476</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>114.55205061155499</v>
+        <v>114.72855742860922</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21596,11 +21596,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>132.98260789775676</v>
+        <v>133.20163369444774</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>141.45084486980141</v>
+        <v>141.66987066649239</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21617,11 +21617,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>150.39345761262058</v>
+        <v>150.64115952937081</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>159.56289465999788</v>
+        <v>159.81059657674808</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21639,13 +21639,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21653,13 +21653,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21696,22 +21696,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21735,12 +21735,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21755,15 +21758,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9618.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9618.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAFB310-3F6D-4F67-91C4-EB2C99CC8623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1425EF62-6C5F-42AD-B893-DC1BE9D9B79F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4019,7 +4019,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="478">
+  <cellXfs count="479">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,26 +5025,29 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5447,13 +5450,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5631,22 +5634,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5658,13 +5661,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5684,13 +5687,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5719,13 +5722,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5741,13 +5744,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5811,13 +5814,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5833,7 +5836,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5855,22 +5858,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -6005,13 +6008,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6030,13 +6033,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6205,31 +6208,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6279,22 +6282,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6328,13 +6331,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6469,13 +6472,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6510,22 +6513,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6701,13 +6704,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6744,13 +6747,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6758,22 +6761,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6797,18 +6800,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6825,6 +6816,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7319,7 +7322,9 @@
       <c r="E22" s="287">
         <v>57819</v>
       </c>
-      <c r="F22" s="287"/>
+      <c r="F22" s="287">
+        <v>42301</v>
+      </c>
       <c r="G22" s="287"/>
       <c r="H22" s="287"/>
       <c r="I22" s="287"/>
@@ -7341,7 +7346,9 @@
       <c r="E23" s="287">
         <v>-54026</v>
       </c>
-      <c r="F23" s="287"/>
+      <c r="F23" s="287">
+        <v>-74248</v>
+      </c>
       <c r="G23" s="287"/>
       <c r="H23" s="287"/>
       <c r="I23" s="287"/>
@@ -7363,7 +7370,9 @@
       <c r="E24" s="287">
         <v>1180</v>
       </c>
-      <c r="F24" s="287"/>
+      <c r="F24" s="287">
+        <v>19503</v>
+      </c>
       <c r="G24" s="287"/>
       <c r="H24" s="287"/>
       <c r="I24" s="287"/>
@@ -7389,7 +7398,9 @@
         <f>0.31*7.8</f>
         <v>2.4180000000000001</v>
       </c>
-      <c r="F25" s="37"/>
+      <c r="F25" s="37">
+        <v>0</v>
+      </c>
       <c r="G25" s="37"/>
       <c r="H25" s="37"/>
       <c r="I25" s="37"/>
@@ -7418,8 +7429,12 @@
         <f>20302+2114</f>
         <v>22416</v>
       </c>
-      <c r="E28" s="287"/>
-      <c r="F28" s="287"/>
+      <c r="E28" s="287">
+        <v>205760</v>
+      </c>
+      <c r="F28" s="287">
+        <v>11900</v>
+      </c>
       <c r="G28" s="287"/>
       <c r="H28" s="287"/>
       <c r="I28" s="287"/>
@@ -7439,8 +7454,12 @@
       <c r="D29" s="287">
         <v>68058</v>
       </c>
-      <c r="E29" s="287"/>
-      <c r="F29" s="287"/>
+      <c r="E29" s="287">
+        <v>77949</v>
+      </c>
+      <c r="F29" s="287">
+        <v>75601</v>
+      </c>
       <c r="G29" s="287"/>
       <c r="H29" s="287"/>
       <c r="I29" s="287"/>
@@ -7460,8 +7479,14 @@
       <c r="D30" s="289">
         <v>332578</v>
       </c>
-      <c r="E30" s="289"/>
-      <c r="F30" s="289"/>
+      <c r="E30" s="289">
+        <f>266561+54566</f>
+        <v>321127</v>
+      </c>
+      <c r="F30" s="289">
+        <f>221636+28087</f>
+        <v>249723</v>
+      </c>
       <c r="G30" s="289"/>
       <c r="H30" s="289"/>
       <c r="I30" s="289"/>
@@ -7481,8 +7506,12 @@
       <c r="D31" s="289">
         <v>295766</v>
       </c>
-      <c r="E31" s="289"/>
-      <c r="F31" s="289"/>
+      <c r="E31" s="289">
+        <v>274123</v>
+      </c>
+      <c r="F31" s="289">
+        <v>246784</v>
+      </c>
       <c r="G31" s="289"/>
       <c r="H31" s="289"/>
       <c r="I31" s="289"/>
@@ -7502,8 +7531,12 @@
       <c r="D32" s="287">
         <v>63908</v>
       </c>
-      <c r="E32" s="287"/>
-      <c r="F32" s="287"/>
+      <c r="E32" s="478">
+        <v>60167</v>
+      </c>
+      <c r="F32" s="287">
+        <v>36661</v>
+      </c>
       <c r="G32" s="287"/>
       <c r="H32" s="287"/>
       <c r="I32" s="287"/>
@@ -8645,7 +8678,7 @@
       </c>
       <c r="F64" s="270">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-12444</v>
       </c>
       <c r="G64" s="270">
         <f t="shared" si="32"/>
@@ -9014,11 +9047,11 @@
       </c>
       <c r="E76" s="285">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>595250</v>
       </c>
       <c r="F76" s="285">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>496507</v>
       </c>
       <c r="G76" s="285">
         <f t="shared" si="39"/>
@@ -9063,11 +9096,11 @@
       </c>
       <c r="E77" s="282">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>205760</v>
       </c>
       <c r="F77" s="282">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>11900</v>
       </c>
       <c r="G77" s="282">
         <f t="shared" si="40"/>
@@ -9097,11 +9130,11 @@
       </c>
       <c r="E78" s="282">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>77949</v>
       </c>
       <c r="F78" s="282">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>75601</v>
       </c>
       <c r="G78" s="282">
         <f t="shared" si="40"/>
@@ -9131,11 +9164,11 @@
       </c>
       <c r="E79" s="270">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>321127</v>
       </c>
       <c r="F79" s="270">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>249723</v>
       </c>
       <c r="G79" s="270">
         <f t="shared" si="41"/>
@@ -9180,11 +9213,11 @@
       </c>
       <c r="E80" s="270">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>274123</v>
       </c>
       <c r="F80" s="270">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>246784</v>
       </c>
       <c r="G80" s="270">
         <f t="shared" si="42"/>
@@ -14340,11 +14373,11 @@
       </c>
       <c r="I100" s="270">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>595250</v>
       </c>
       <c r="J100" s="270">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>496507</v>
       </c>
       <c r="K100" s="270">
         <f t="shared" si="41"/>
@@ -14393,11 +14426,11 @@
       </c>
       <c r="H101" s="282">
         <f>IF(H$4="","",Data!E77)</f>
-        <v>0</v>
+        <v>205760</v>
       </c>
       <c r="I101" s="282">
         <f>IF(I$4="","",Data!F77)</f>
-        <v>0</v>
+        <v>11900</v>
       </c>
       <c r="J101" s="282">
         <f>IF(J$4="","",Data!G77)</f>
@@ -14450,11 +14483,11 @@
       </c>
       <c r="H102" s="282">
         <f>IF(H$4="","",Data!E78)</f>
-        <v>0</v>
+        <v>77949</v>
       </c>
       <c r="I102" s="282">
         <f>IF(I$4="","",Data!F78)</f>
-        <v>0</v>
+        <v>75601</v>
       </c>
       <c r="J102" s="282">
         <f>IF(J$4="","",Data!G78)</f>
@@ -14511,11 +14544,11 @@
       </c>
       <c r="I103" s="270">
         <f>Data!E79</f>
-        <v>0</v>
+        <v>321127</v>
       </c>
       <c r="J103" s="270">
         <f>Data!F79</f>
-        <v>0</v>
+        <v>249723</v>
       </c>
       <c r="K103" s="270">
         <f>Data!G79</f>
@@ -14568,11 +14601,11 @@
       </c>
       <c r="I104" s="270">
         <f>Data!E80</f>
-        <v>0</v>
+        <v>274123</v>
       </c>
       <c r="J104" s="270">
         <f>Data!F80</f>
-        <v>0</v>
+        <v>246784</v>
       </c>
       <c r="K104" s="270">
         <f>Data!G80</f>
@@ -14648,11 +14681,11 @@
       </c>
       <c r="H107" s="91">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>0.18969964836972256</v>
       </c>
       <c r="I107" s="91">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>1.1374106798083797E-2</v>
       </c>
       <c r="J107" s="91">
         <f t="shared" si="42"/>
@@ -14705,11 +14738,11 @@
       </c>
       <c r="H108" s="91">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>7.1864783683765074E-2</v>
       </c>
       <c r="I108" s="91">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>7.2259987230414546E-2</v>
       </c>
       <c r="J108" s="91">
         <f t="shared" si="43"/>
@@ -14805,7 +14838,7 @@
       </c>
       <c r="J112" s="251">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
-        <v>0</v>
+        <v>-9.4696664428027759</v>
       </c>
       <c r="K112" s="251">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
@@ -14860,7 +14893,7 @@
       </c>
       <c r="J113" s="251">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>0</v>
+        <v>335.72222222222223</v>
       </c>
       <c r="K113" s="251">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -15032,13 +15065,13 @@
         <f t="shared" si="45"/>
         <v>1.7262232153088117</v>
       </c>
-      <c r="I117" s="40" t="e">
+      <c r="I117" s="40">
         <f t="shared" si="45"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J117" s="40" t="e">
+        <v>1.7576413271734566</v>
+      </c>
+      <c r="J117" s="40">
         <f t="shared" si="45"/>
-        <v>#DIV/0!</v>
+        <v>1.9165731802371366</v>
       </c>
       <c r="K117" s="40" t="e">
         <f t="shared" si="45"/>
@@ -15091,13 +15124,13 @@
         <f t="shared" si="46"/>
         <v>2.1244632581162133</v>
       </c>
-      <c r="I118" s="15" t="e">
+      <c r="I118" s="15">
         <f t="shared" si="46"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J118" s="15" t="e">
+        <v>2.1714704712847883</v>
+      </c>
+      <c r="J118" s="15">
         <f t="shared" si="46"/>
-        <v>#DIV/0!</v>
+        <v>2.0119091999481329</v>
       </c>
       <c r="K118" s="15" t="e">
         <f t="shared" si="46"/>
@@ -15150,13 +15183,13 @@
         <f t="shared" si="47"/>
         <v>9.1420244382383373E-2</v>
       </c>
-      <c r="I119" s="99" t="e">
+      <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J119" s="99" t="e">
+        <v>5.1228827934905137E-2</v>
+      </c>
+      <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>#DIV/0!</v>
+        <v>8.1569307572614113E-3</v>
       </c>
       <c r="K119" s="99" t="e">
         <f t="shared" si="47"/>
@@ -20374,13 +20407,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20565,22 +20598,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20770,10 +20803,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20789,22 +20822,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20939,22 +20972,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20962,13 +20995,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21117,33 +21150,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21206,23 +21239,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21266,13 +21299,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21436,13 +21469,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21455,22 +21488,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21639,13 +21672,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21653,13 +21686,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21696,22 +21729,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21735,15 +21768,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21758,12 +21788,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9618.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9618.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1425EF62-6C5F-42AD-B893-DC1BE9D9B79F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A98EB9-0275-4504-BC0E-A6EAEC316EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,30 +4992,33 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5028,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,20 +5046,8 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5416,7 +5416,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>113.5</v>
+        <v>115.2</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5435,14 +5435,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>341300.66998065053</v>
+        <v>346412.66239445761</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.20517568115776152</v>
+        <v>0.19966443414501156</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5450,13 +5450,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5491,7 +5491,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1215249683380129</v>
+        <v>1.1232618942260741</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>185.83844056195898</v>
+        <v>186.12625189699088</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>92.062613392496303</v>
+        <v>92.195245344123904</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>114.72855742860922</v>
+        <v>114.89480224306809</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>141.66987066649239</v>
+        <v>141.87616243210397</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>159.81059657674808</v>
+        <v>160.04389724965404</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5634,22 +5634,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="463" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="463"/>
+      <c r="D30" s="463"/>
+      <c r="E30" s="463"/>
+      <c r="F30" s="463"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5661,13 +5661,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5687,13 +5687,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5722,13 +5722,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5744,13 +5744,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5814,13 +5814,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C54" s="464"/>
-      <c r="D54" s="464"/>
-      <c r="E54" s="464"/>
-      <c r="F54" s="464"/>
+      <c r="C54" s="465"/>
+      <c r="D54" s="465"/>
+      <c r="E54" s="465"/>
+      <c r="F54" s="465"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
@@ -5858,22 +5858,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.9717230628442983E-2</v>
+        <v>6.8794796316454396E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.0925110132158588E-2</v>
+        <v>3.0468749999999996E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6008,13 +6008,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="461" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6033,13 +6033,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-41.805234319608559</v>
+        <v>-41.869978837828064</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>11.571931406418704</v>
+        <v>11.589853064698382</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>36.748840710590464</v>
+        <v>36.805754301093096</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.5155377974006097</v>
+        <v>6.5256285279634056</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6208,31 +6208,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="461" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="463" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="463"/>
+      <c r="D97" s="463"/>
+      <c r="E97" s="463"/>
+      <c r="F97" s="463"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="463" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="463"/>
+      <c r="D98" s="463"/>
+      <c r="E98" s="463"/>
+      <c r="F98" s="463"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6282,22 +6282,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-64.719566840731247</v>
+        <v>-64.819799197819449</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>160.25199093749288</v>
+        <v>160.50017607784261</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6331,13 +6331,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="461" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>227.01 HKD</v>
+        <v>227.36 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.7987375660487559E-2</v>
+        <v>-4.8012932352067272E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>194.79 HKD</v>
+        <v>195.09 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.7460528879222597E-3</v>
+        <v>2.7177570273617668E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>180.48 HKD</v>
+        <v>180.76 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.9054240566849038E-2</v>
+        <v>2.9024451588750323E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>167.27 HKD</v>
+        <v>167.53 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.5987055893302717E-2</v>
+        <v>5.5955685696976253E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>155.07 HKD</v>
+        <v>155.31 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6468,17 +6468,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>8.3539190408932193E-2</v>
+        <v>8.3506146533174286E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>185.83844056195898</v>
+        <v>186.12625189699088</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6494,13 +6494,13 @@
       </c>
     </row>
     <row r="127" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B127" s="465" t="s">
+      <c r="B127" s="466" t="s">
         <v>358</v>
       </c>
-      <c r="C127" s="465"/>
-      <c r="D127" s="465"/>
-      <c r="E127" s="465"/>
-      <c r="F127" s="465"/>
+      <c r="C127" s="466"/>
+      <c r="D127" s="466"/>
+      <c r="E127" s="466"/>
+      <c r="F127" s="466"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="200" t="s">
@@ -6513,22 +6513,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="464" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="464"/>
+      <c r="D131" s="464"/>
+      <c r="E131" s="464"/>
+      <c r="F131" s="464"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6593,11 +6593,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>85.639834360349781</v>
+        <v>85.772466311977382</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>92.062613392496303</v>
+        <v>92.195245344123904</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6614,11 +6614,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>107.34350357369476</v>
+        <v>107.50974838815362</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>114.72855742860922</v>
+        <v>114.89480224306809</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6661,11 +6661,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>133.20163369444774</v>
+        <v>133.40792546005932</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>141.66987066649239</v>
+        <v>141.87616243210397</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6682,11 +6682,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>150.64115952937081</v>
+        <v>150.87446020227677</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>159.81059657674808</v>
+        <v>160.04389724965404</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6704,13 +6704,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="468" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6718,13 +6718,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="464" t="s">
+      <c r="B152" s="465" t="s">
         <v>293</v>
       </c>
-      <c r="C152" s="464"/>
-      <c r="D152" s="464"/>
-      <c r="E152" s="464"/>
-      <c r="F152" s="464"/>
+      <c r="C152" s="465"/>
+      <c r="D152" s="465"/>
+      <c r="E152" s="465"/>
+      <c r="F152" s="465"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
@@ -6747,13 +6747,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="462" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6761,22 +6761,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="467" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="467" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6800,6 +6800,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6816,18 +6828,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7531,7 +7531,7 @@
       <c r="D32" s="287">
         <v>63908</v>
       </c>
-      <c r="E32" s="478">
+      <c r="E32" s="460">
         <v>60167</v>
       </c>
       <c r="F32" s="287">
@@ -10079,11 +10079,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>86.502809476842259</v>
+        <v>86.636777933552594</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-64.719566840731247</v>
+        <v>-64.819799197819449</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10489,11 +10489,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-125710.61217603952</v>
+        <v>-125905.30246190642</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-41.805234319608559</v>
+        <v>-41.869978837828064</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10506,11 +10506,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>34797.426801593261</v>
+        <v>34851.318202280643</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>11.571931406418704</v>
+        <v>11.58985306469838</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10523,11 +10523,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>110505.76172279057</v>
+        <v>110676.90398331526</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>36.748840710590464</v>
+        <v>36.805754301093096</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10540,11 +10540,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>19592.576348344315</v>
+        <v>19622.919723689483</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.5155377974006115</v>
+        <v>6.5256285279634128</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14128,20 +14128,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.0925110132158588E-2</v>
+        <v>3.0468749999999996E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.0925110132158588E-2</v>
+        <v>3.0468749999999996E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>2.3503083700440529E-2</v>
+        <v>2.315625E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>1.9173568281938329E-2</v>
+        <v>1.8890625000000001E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
@@ -15291,30 +15291,30 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>7.9129056763282781</v>
+        <v>7.9251605356555466</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.749587056354843</v>
+        <v>10.766235135150467</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>6.9542988082989519</v>
+        <v>6.9650690559300399</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>3.6800421721273064</v>
+        <v>3.6857415196214576</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>4.6993545524276946E-2</v>
+        <v>4.7066325273366141E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.6165564007896833</v>
+        <v>4.6237061447121119</v>
       </c>
       <c r="L123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15348,30 +15348,30 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.9717230628442983E-2</v>
+        <v>6.8794796316454396E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>9.4710018117663816E-2</v>
+        <v>9.3456902214847801E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.1271355139197813E-2</v>
+        <v>6.0460668888281596E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.2423279049579791E-2</v>
+        <v>3.1994284024491816E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>4.1404004867204357E-4</v>
+        <v>4.085618513313033E-4</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>4.0674505733829809E-2</v>
+        <v>4.0136338061737081E-2</v>
       </c>
       <c r="L124" s="74" t="str">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
@@ -15405,23 +15405,23 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13085236545985077</v>
+        <v>0.12892138437233561</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8142262953420268E-2</v>
+        <v>6.7136691364697923E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8394318711854317E-2</v>
+        <v>2.7975305328085631E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-1.3088166513863712E-2</v>
+        <v>-1.2895025167738987E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14455582522822788</v>
+        <v>0.14242262294621411</v>
       </c>
       <c r="L125" s="22" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16330,7 +16330,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.5155377974006097</v>
+        <v>6.5256285279634056</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1215249683380129</v>
+        <v>1.1232618942260741</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16380,7 +16380,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>481886.44821761636</v>
+        <v>482632.75442625606</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>160.25199093749288</v>
+        <v>160.50017607784261</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16525,7 +16525,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>185.86613070383422</v>
+        <v>186.15398492308685</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18174,10 +18174,10 @@
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
-      <c r="J52" s="468" t="s">
+      <c r="J52" s="469" t="s">
         <v>420</v>
       </c>
-      <c r="K52" s="468"/>
+      <c r="K52" s="469"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
         <v>480878.26645334472</v>
@@ -18713,23 +18713,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>160.25199093749288</v>
+        <v>160.50017607784261</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>160.25199093749288</v>
+        <v>160.50017607784261</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>160.25199093749288</v>
+        <v>160.50017607784261</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>160.25199093749288</v>
+        <v>160.50017607784261</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>160.25199093749288</v>
+        <v>160.50017607784261</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18744,23 +18744,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>165.29865829861353</v>
+        <v>165.55465930346509</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>166.88648950362563</v>
+        <v>167.14494961122008</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>168.47432070863783</v>
+        <v>168.73523991897517</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>170.06215191364996</v>
+        <v>170.32553022673019</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>173.23781432367423</v>
+        <v>173.50611084224022</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18775,23 +18775,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>165.0979750646336</v>
+        <v>165.35366526775161</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>168.21096424733588</v>
+        <v>168.47147559278537</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>171.3541943173654</v>
+        <v>171.61957363975245</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>174.52766527472227</v>
+        <v>174.79795940865296</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>180.96532985141798</v>
+        <v>181.24559411225408</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18806,23 +18806,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>164.91085783015345</v>
+        <v>165.16625824144526</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>169.45825514817241</v>
+        <v>169.72069819547144</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>174.0930950920993</v>
+        <v>174.36271619937281</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>178.81622356088036</v>
+        <v>179.0931594621546</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>188.53072966878952</v>
+        <v>188.82271060037957</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18837,23 +18837,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>164.73638954625582</v>
+        <v>164.99151975537873</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>170.63286009907679</v>
+        <v>170.89712227818745</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>176.69792380093716</v>
+        <v>176.97157905327748</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>182.93483897788985</v>
+        <v>183.21815345292993</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>195.93741480467776</v>
+        <v>196.24086660274017</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18868,23 +18868,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>161.41880812391204</v>
+        <v>161.66880033502252</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>168.52069421491532</v>
+        <v>168.78168524473583</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>175.89287813629304</v>
+        <v>176.16528659993452</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>183.54320498856339</v>
+        <v>183.8274616509851</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>199.71042993519617</v>
+        <v>200.0197250696454</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18899,23 +18899,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>161.26713037045701</v>
+        <v>161.51688767550294</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>169.56238775965159</v>
+        <v>169.82499207899872</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>178.2489303539401</v>
+        <v>178.52498767802251</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>187.34187080403322</v>
+        <v>187.63201052851886</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>206.80960489061738</v>
+        <v>207.12989464499222</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18931,23 +18931,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>158.18406763365678</v>
+        <v>158.42905014399616</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>167.51260371345194</v>
+        <v>167.77203349538323</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>177.36796129159652</v>
+        <v>177.64265424304864</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>187.77559918989445</v>
+        <v>188.0664106373315</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>210.35453211723498</v>
+        <v>210.68031196415794</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18962,23 +18962,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>158.05220331780976</v>
+        <v>158.29698160751173</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>168.43642532710149</v>
+        <v>168.69728584817994</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>179.49899663892893</v>
+        <v>179.77698996314817</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>191.27917029731671</v>
+        <v>191.57540778833629</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>217.1589640760719</v>
+        <v>217.49528206914098</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18994,23 +18994,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>155.18646665216744</v>
+        <v>155.42680672395767</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>166.45225680727418</v>
+        <v>166.71004441088252</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>178.55683552067677</v>
+        <v>178.8333697030283</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>191.55687516013418</v>
+        <v>191.8535427376691</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>220.48677187921837</v>
+        <v>220.82824370807973</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19026,23 +19026,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>155.07182757426889</v>
+        <v>155.31199010245754</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>167.27154418613776</v>
+        <v>167.53060063484386</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>180.48434443476845</v>
+        <v>180.76386378483969</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>194.78827563099821</v>
+        <v>195.08994773655613</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>227.00869795840097</v>
+        <v>227.36027041147202</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19058,23 +19058,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>147.439727553143</v>
+        <v>147.66807011077259</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>163.10237772588911</v>
+        <v>163.3549773115196</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>180.73286456161102</v>
+        <v>181.01276879927212</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>200.57672300892114</v>
+        <v>200.88735978703315</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>248.03467530350264</v>
+        <v>248.41881106582093</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19090,23 +19090,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>143.10478782672547</v>
+        <v>143.32641678524087</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>161.28673183731183</v>
+        <v>161.53651949950196</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>182.46072250355925</v>
+        <v>182.74330270588899</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>207.13960557593501</v>
+        <v>207.46040640830597</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>269.50784287671934</v>
+        <v>269.92523451983351</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19122,23 +19122,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>137.82349349780637</v>
+        <v>138.03694322081535</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>157.53926560090511</v>
+        <v>157.7832494947402</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>181.21888174118735</v>
+        <v>181.49953868239504</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>209.72493538779008</v>
+        <v>210.04974016693544</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>285.64935178797691</v>
+        <v>286.09174207623209</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19154,23 +19154,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>134.83706725214469</v>
+        <v>135.04589184311885</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>155.7060023261117</v>
+        <v>155.94714701214355</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>181.44658403388101</v>
+        <v>181.7275936217244</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>213.33531302838611</v>
+        <v>213.66570926431277</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>302.47164760533963</v>
+        <v>302.94009088566071</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>227.00869795840097</v>
+        <v>227.36027041147202</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19245,7 +19245,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>194.78827563099821</v>
+        <v>195.08994773655613</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19273,7 +19273,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>180.48434443476845</v>
+        <v>180.76386378483969</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>167.27154418613776</v>
+        <v>167.53060063484386</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>155.07182757426889</v>
+        <v>155.31199010245754</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19485,7 +19485,7 @@
       <c r="C4" s="449">
         <v>2</v>
       </c>
-      <c r="D4" s="469" t="str">
+      <c r="D4" s="470" t="str">
         <f>"DCF Model Inputs for " &amp; Thesis!C5 &amp; " – " &amp; Thesis!C4 &amp; ": Please develop Base, Pessimistic, and Optimistic scenarios under the following unified framework. " &amp;
 "Assume a consistent high-growth period across all cases, with each scenario using a single FCFE CAGR during this phase. " &amp;
 "Apply a two-stage model only if there is a material shift in FCFE margin or growth, and ensure this structure is used consistently across scenarios. " &amp;
@@ -19495,16 +19495,16 @@
 "For each scenario, specify the FCFE CAGR during the high-growth period. Accompany each with a concise business narrative and respective probability explaining the key drivers behind the scenario."</f>
         <v>DCF Model Inputs for 9618.HK – 京东集团: Please develop Base, Pessimistic, and Optimistic scenarios under the following unified framework. Assume a consistent high-growth period across all cases, with each scenario using a single FCFE CAGR during this phase. Apply a two-stage model only if there is a material shift in FCFE margin or growth, and ensure this structure is used consistently across scenarios. Margins should remain constant within each stage and be identical across all scenarios; any variation in outlook should be reflected through adjustments to the growth rate, not the margin. Terminal growth is fixed at 0%, so modify the high-growth duration or rate accordingly to reflect long-term expectations. Specify the FCFE margin (stage-specific if applicable) for all scenarios. For each scenario, specify the FCFE CAGR during the high-growth period. Accompany each with a concise business narrative and respective probability explaining the key drivers behind the scenario.</v>
       </c>
-      <c r="E4" s="469"/>
-      <c r="F4" s="469"/>
-      <c r="G4" s="469"/>
+      <c r="E4" s="470"/>
+      <c r="F4" s="470"/>
+      <c r="G4" s="470"/>
     </row>
     <row r="5" spans="2:7">
       <c r="C5" s="445"/>
-      <c r="D5" s="469"/>
-      <c r="E5" s="469"/>
-      <c r="F5" s="469"/>
-      <c r="G5" s="469"/>
+      <c r="D5" s="470"/>
+      <c r="E5" s="470"/>
+      <c r="F5" s="470"/>
+      <c r="G5" s="470"/>
     </row>
     <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="145" t="s">
@@ -19514,10 +19514,10 @@
         <f>DCF!C3&amp;" "&amp;Reporting_currency</f>
         <v>1000000 CNY</v>
       </c>
-      <c r="D6" s="469"/>
-      <c r="E6" s="469"/>
-      <c r="F6" s="469"/>
-      <c r="G6" s="469"/>
+      <c r="D6" s="470"/>
+      <c r="E6" s="470"/>
+      <c r="F6" s="470"/>
+      <c r="G6" s="470"/>
     </row>
     <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
@@ -19527,10 +19527,10 @@
         <f>Normalized_FCF!G8</f>
         <v>39570</v>
       </c>
-      <c r="D7" s="469"/>
-      <c r="E7" s="469"/>
-      <c r="F7" s="469"/>
-      <c r="G7" s="469"/>
+      <c r="D7" s="470"/>
+      <c r="E7" s="470"/>
+      <c r="F7" s="470"/>
+      <c r="G7" s="470"/>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
@@ -19540,10 +19540,10 @@
         <f>Normalized_FCF!G19</f>
         <v>28822</v>
       </c>
-      <c r="D8" s="469"/>
-      <c r="E8" s="469"/>
-      <c r="F8" s="469"/>
-      <c r="G8" s="469"/>
+      <c r="D8" s="470"/>
+      <c r="E8" s="470"/>
+      <c r="F8" s="470"/>
+      <c r="G8" s="470"/>
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
@@ -19553,27 +19553,27 @@
         <f>Normalized_FCF!C19</f>
         <v>21216.235210477949</v>
       </c>
-      <c r="D9" s="469"/>
-      <c r="E9" s="469"/>
-      <c r="F9" s="469"/>
-      <c r="G9" s="469"/>
+      <c r="D9" s="470"/>
+      <c r="E9" s="470"/>
+      <c r="F9" s="470"/>
+      <c r="G9" s="470"/>
     </row>
     <row r="10" spans="2:7">
       <c r="C10" s="448"/>
-      <c r="D10" s="469"/>
-      <c r="E10" s="469"/>
-      <c r="F10" s="469"/>
-      <c r="G10" s="469"/>
+      <c r="D10" s="470"/>
+      <c r="E10" s="470"/>
+      <c r="F10" s="470"/>
+      <c r="G10" s="470"/>
     </row>
     <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="145" t="s">
         <v>321</v>
       </c>
       <c r="C11" s="448"/>
-      <c r="D11" s="469"/>
-      <c r="E11" s="469"/>
-      <c r="F11" s="469"/>
-      <c r="G11" s="469"/>
+      <c r="D11" s="470"/>
+      <c r="E11" s="470"/>
+      <c r="F11" s="470"/>
+      <c r="G11" s="470"/>
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
@@ -19583,10 +19583,10 @@
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>5.2429405031766629E-2</v>
       </c>
-      <c r="D12" s="469"/>
-      <c r="E12" s="469"/>
-      <c r="F12" s="469"/>
-      <c r="G12" s="469"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
+      <c r="G12" s="470"/>
     </row>
     <row r="13" spans="2:7">
       <c r="B13" s="135" t="s">
@@ -19596,10 +19596,10 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.46870983906455255</v>
       </c>
-      <c r="D13" s="469"/>
-      <c r="E13" s="469"/>
-      <c r="F13" s="469"/>
-      <c r="G13" s="469"/>
+      <c r="D13" s="470"/>
+      <c r="E13" s="470"/>
+      <c r="F13" s="470"/>
+      <c r="G13" s="470"/>
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
@@ -19609,10 +19609,10 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.70910794408317734</v>
       </c>
-      <c r="D14" s="469"/>
-      <c r="E14" s="469"/>
-      <c r="F14" s="469"/>
-      <c r="G14" s="469"/>
+      <c r="D14" s="470"/>
+      <c r="E14" s="470"/>
+      <c r="F14" s="470"/>
+      <c r="G14" s="470"/>
     </row>
     <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
@@ -19689,7 +19689,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>194.78827563099821</v>
+        <v>195.08994773655613</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19713,7 +19713,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>180.48434443476845</v>
+        <v>180.76386378483969</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19736,7 +19736,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>167.27154418613776</v>
+        <v>167.53060063484386</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>180.04193061185671</v>
+        <v>180.32076478768403</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19799,7 +19799,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>227.00869795840097</v>
+        <v>227.36027041147202</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19822,7 +19822,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>155.07182757426889</v>
+        <v>155.31199010245754</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19867,7 +19867,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>113.5</v>
+        <v>115.2</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.20517568115776152</v>
+        <v>0.19966443414501156</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>160.25199093749288</v>
+        <v>160.50017607784261</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19898,7 +19898,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>7.1494297926842101E-2</v>
+        <v>7.1461992773322186E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19907,7 +19907,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>185.83844056195898</v>
+        <v>186.12625189699088</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20010,7 +20010,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>185.86613070383422</v>
+        <v>186.15398492308685</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>3.5060226386415011E-2</v>
+        <v>3.5060226386415046E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20155,11 +20155,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>85.639834360349781</v>
+        <v>85.772466311977382</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>92.062613392496303</v>
+        <v>92.195245344123904</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20167,7 +20167,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.50460941711463403</v>
+        <v>0.50466285972841618</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20180,11 +20180,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>107.34350357369476</v>
+        <v>107.50974838815362</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>114.72855742860922</v>
+        <v>114.89480224306809</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20192,7 +20192,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.38264356350774231</v>
+        <v>0.38270501301097981</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20226,11 +20226,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>133.20163369444774</v>
+        <v>133.40792546005932</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>141.66987066649239</v>
+        <v>141.87616243210397</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20238,7 +20238,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.23767187112582711</v>
+        <v>0.23774233357138974</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20251,11 +20251,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>150.64115952937081</v>
+        <v>150.87446020227677</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>159.81059657674808</v>
+        <v>160.04389724965404</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20263,7 +20263,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.14005629786014673</v>
+        <v>0.14013259484627549</v>
       </c>
     </row>
   </sheetData>
@@ -20374,7 +20374,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>113.5</v>
+        <v>115.2</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20392,14 +20392,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>341300.66998065053</v>
+        <v>346412.66239445761</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.20517568115776152</v>
+        <v>0.19966443414501156</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20407,13 +20407,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="472" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="472"/>
+      <c r="D12" s="472"/>
+      <c r="E12" s="472"/>
+      <c r="F12" s="472"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20451,7 +20451,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1215249683380129</v>
+        <v>1.1232618942260741</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>185.83844056195898</v>
+        <v>186.12625189699088</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>92.062613392496303</v>
+        <v>92.195245344123904</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>114.72855742860922</v>
+        <v>114.89480224306809</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20561,7 +20561,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>141.66987066649239</v>
+        <v>141.87616243210397</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>159.81059657674808</v>
+        <v>160.04389724965404</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20598,22 +20598,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="472"/>
+      <c r="D29" s="472"/>
+      <c r="E29" s="472"/>
+      <c r="F29" s="472"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="473" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20625,13 +20625,13 @@
       </c>
     </row>
     <row r="33" spans="2:6">
-      <c r="B33" s="470" t="s">
+      <c r="B33" s="471" t="s">
         <v>501</v>
       </c>
-      <c r="C33" s="470"/>
-      <c r="D33" s="470"/>
-      <c r="E33" s="470"/>
-      <c r="F33" s="470"/>
+      <c r="C33" s="471"/>
+      <c r="D33" s="471"/>
+      <c r="E33" s="471"/>
+      <c r="F33" s="471"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="372" t="s">
@@ -20651,13 +20651,13 @@
       <c r="C35" s="374"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="470" t="s">
+      <c r="B36" s="471" t="s">
         <v>502</v>
       </c>
-      <c r="C36" s="470"/>
-      <c r="D36" s="470"/>
-      <c r="E36" s="470"/>
-      <c r="F36" s="470"/>
+      <c r="C36" s="471"/>
+      <c r="D36" s="471"/>
+      <c r="E36" s="471"/>
+      <c r="F36" s="471"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="372" t="s">
@@ -20686,13 +20686,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="470" t="s">
+      <c r="B40" s="471" t="s">
         <v>503</v>
       </c>
-      <c r="C40" s="470"/>
-      <c r="D40" s="470"/>
-      <c r="E40" s="470"/>
-      <c r="F40" s="470"/>
+      <c r="C40" s="471"/>
+      <c r="D40" s="471"/>
+      <c r="E40" s="471"/>
+      <c r="F40" s="471"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="372" t="s">
@@ -20708,13 +20708,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="470" t="s">
+      <c r="B43" s="471" t="s">
         <v>504</v>
       </c>
-      <c r="C43" s="470"/>
-      <c r="D43" s="470"/>
-      <c r="E43" s="470"/>
-      <c r="F43" s="470"/>
+      <c r="C43" s="471"/>
+      <c r="D43" s="471"/>
+      <c r="E43" s="471"/>
+      <c r="F43" s="471"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="372" t="s">
@@ -20778,13 +20778,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="470" t="s">
+      <c r="B51" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C51" s="470"/>
-      <c r="D51" s="470"/>
-      <c r="E51" s="470"/>
-      <c r="F51" s="470"/>
+      <c r="C51" s="471"/>
+      <c r="D51" s="471"/>
+      <c r="E51" s="471"/>
+      <c r="F51" s="471"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="372" t="s">
@@ -20800,13 +20800,13 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="470" t="s">
+      <c r="B54" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="474"/>
+      <c r="D54" s="474"/>
+      <c r="E54" s="474"/>
+      <c r="F54" s="474"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20822,22 +20822,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="472" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="472"/>
+      <c r="D57" s="472"/>
+      <c r="E57" s="472"/>
+      <c r="F57" s="472"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="472" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="472"/>
+      <c r="D58" s="472"/>
+      <c r="E58" s="472"/>
+      <c r="F58" s="472"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20871,7 +20871,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.9717230628442983E-2</v>
+        <v>6.8794796316454396E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20881,7 +20881,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.0925110132158588E-2</v>
+        <v>3.0468749999999996E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20972,22 +20972,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="472" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="472"/>
+      <c r="D73" s="472"/>
+      <c r="E73" s="472"/>
+      <c r="F73" s="472"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="473" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20995,13 +20995,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="472" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="472"/>
+      <c r="D77" s="472"/>
+      <c r="E77" s="472"/>
+      <c r="F77" s="472"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21022,7 +21022,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-41.805234319608559</v>
+        <v>-41.869978837828064</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21084,7 +21084,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>11.571931406418704</v>
+        <v>11.589853064698382</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21115,7 +21115,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>36.748840710590464</v>
+        <v>36.805754301093096</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21128,7 +21128,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>6.5155377974006097</v>
+        <v>6.5256285279634056</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21150,33 +21150,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="472"/>
+      <c r="D96" s="472"/>
+      <c r="E96" s="472"/>
+      <c r="F96" s="472"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="473" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="473" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21239,23 +21239,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="472"/>
+      <c r="D107" s="472"/>
+      <c r="E107" s="472"/>
+      <c r="F107" s="472"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="472" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="472"/>
+      <c r="D108" s="472"/>
+      <c r="E108" s="472"/>
+      <c r="F108" s="472"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-64.719566840731247</v>
+        <v>-64.819799197819449</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21287,7 +21287,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>160.25199093749288</v>
+        <v>160.50017607784261</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21299,13 +21299,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="472" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="472"/>
+      <c r="D114" s="472"/>
+      <c r="E114" s="472"/>
+      <c r="F114" s="472"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,7 +21350,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>227.01 HKD</v>
+        <v>227.36 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21373,7 +21373,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>194.79 HKD</v>
+        <v>195.09 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21395,7 +21395,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>180.48 HKD</v>
+        <v>180.76 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>167.27 HKD</v>
+        <v>167.53 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>155.07 HKD</v>
+        <v>155.31 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21447,13 +21447,13 @@
       </c>
     </row>
     <row r="124" spans="1:6">
-      <c r="B124" s="470" t="s">
+      <c r="B124" s="471" t="s">
         <v>519</v>
       </c>
-      <c r="C124" s="470"/>
-      <c r="D124" s="470"/>
-      <c r="E124" s="470"/>
-      <c r="F124" s="470"/>
+      <c r="C124" s="471"/>
+      <c r="D124" s="471"/>
+      <c r="E124" s="471"/>
+      <c r="F124" s="471"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="372" t="s">
@@ -21461,7 +21461,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>185.83844056195898</v>
+        <v>186.12625189699088</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21469,13 +21469,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="476"/>
+      <c r="D127" s="476"/>
+      <c r="E127" s="476"/>
+      <c r="F127" s="476"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21488,22 +21488,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="477" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="477"/>
+      <c r="D131" s="477"/>
+      <c r="E131" s="477"/>
+      <c r="F131" s="477"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="472" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="472"/>
+      <c r="D132" s="472"/>
+      <c r="E132" s="472"/>
+      <c r="F132" s="472"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21568,11 +21568,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>85.639834360349781</v>
+        <v>85.772466311977382</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>92.062613392496303</v>
+        <v>92.195245344123904</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21589,11 +21589,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>107.34350357369476</v>
+        <v>107.50974838815362</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>114.72855742860922</v>
+        <v>114.89480224306809</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21629,11 +21629,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>133.20163369444774</v>
+        <v>133.40792546005932</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>141.66987066649239</v>
+        <v>141.87616243210397</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21650,11 +21650,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>150.64115952937081</v>
+        <v>150.87446020227677</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>159.81059657674808</v>
+        <v>160.04389724965404</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21672,13 +21672,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="478" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="472"/>
+      <c r="D149" s="472"/>
+      <c r="E149" s="472"/>
+      <c r="F149" s="472"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21686,13 +21686,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="474" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="474"/>
+      <c r="D152" s="474"/>
+      <c r="E152" s="474"/>
+      <c r="F152" s="474"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21715,13 +21715,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B158" s="470" t="s">
+      <c r="B158" s="471" t="s">
         <v>439</v>
       </c>
-      <c r="C158" s="470"/>
-      <c r="D158" s="470"/>
-      <c r="E158" s="470"/>
-      <c r="F158" s="470"/>
+      <c r="C158" s="471"/>
+      <c r="D158" s="471"/>
+      <c r="E158" s="471"/>
+      <c r="F158" s="471"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="343" t="s">
@@ -21729,22 +21729,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="475" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="475"/>
+      <c r="D161" s="475"/>
+      <c r="E161" s="475"/>
+      <c r="F161" s="475"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="475" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="475"/>
+      <c r="D162" s="475"/>
+      <c r="E162" s="475"/>
+      <c r="F162" s="475"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21768,12 +21768,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21788,15 +21791,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9618.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9618.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A98EB9-0275-4504-BC0E-A6EAEC316EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E49F50A-1C4F-4FB6-A4AA-903BCFBAE1CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.19966443414501156</v>
+        <v>0.20425434714922333</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>186.12625189699088</v>
+        <v>188.36311559430365</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>92.195245344123904</v>
+        <v>93.226058107862514</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>114.89480224306809</v>
+        <v>116.18685347617293</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>141.87616243210397</v>
+        <v>143.47945773491043</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>160.04389724965404</v>
+        <v>161.85710521703368</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="C45" s="286">
         <f>Normalized_FCF!C45</f>
-        <v>-6725.34</v>
+        <v>-4483.5600000000004</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="C46" s="285">
         <f>Normalized_FCF!C10</f>
-        <v>-6159.4913131261419</v>
+        <v>-3917.7113131261426</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="C52" s="285">
         <f>Normalized_FCF!C12</f>
-        <v>-8172.4117368259831</v>
+        <v>-8732.8567368259828</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="C61" s="285">
         <f>Normalized_FCF!C19</f>
-        <v>21216.235210477949</v>
+        <v>22897.570210477948</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.8794796316454396E-2</v>
+        <v>7.4246616477629909E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="F63" s="258">
         <f>Normalized_FCF!C90</f>
-        <v>0.55276121761479602</v>
+        <v>0.51217277206029399</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>160.50017607784261</v>
+        <v>172.70228419629535</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>227.36 HKD</v>
+        <v>229.74 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.8012932352067272E-2</v>
+        <v>-4.7718870553804284E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>195.09 HKD</v>
+        <v>197.36 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.7177570273617668E-3</v>
+        <v>2.624191101882751E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>180.76 HKD</v>
+        <v>182.98 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.9024451588750323E-2</v>
+        <v>2.8706233475927469E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>167.53 HKD</v>
+        <v>169.7 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.5955685696976253E-2</v>
+        <v>5.5390407552362853E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>155.31 HKD</v>
+        <v>157.43 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>8.3506146533174286E-2</v>
+        <v>8.2670005641726316E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>186.12625189699088</v>
+        <v>188.36311559430365</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6593,11 +6593,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>85.772466311977382</v>
+        <v>86.803279075715992</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>92.195245344123904</v>
+        <v>93.226058107862514</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6614,11 +6614,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>107.50974838815362</v>
+        <v>108.80179962125847</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>114.89480224306809</v>
+        <v>116.18685347617293</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6661,11 +6661,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>133.40792546005932</v>
+        <v>135.01122076286578</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>141.87616243210397</v>
+        <v>143.47945773491043</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6682,11 +6682,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>150.87446020227677</v>
+        <v>152.6876681696564</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>160.04389724965404</v>
+        <v>161.85710521703368</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C10" s="266">
         <f>C48</f>
-        <v>-6159.4913131261419</v>
+        <v>-3917.7113131261426</v>
       </c>
       <c r="E10" s="237"/>
       <c r="G10" s="266">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="C11" s="267">
         <f>SUM(C8:C10)</f>
-        <v>32689.646947303932</v>
+        <v>34931.426947303931</v>
       </c>
       <c r="E11" s="237"/>
       <c r="G11" s="267">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="C12" s="266">
         <f>-C11*C41</f>
-        <v>-8172.4117368259831</v>
+        <v>-8732.8567368259828</v>
       </c>
       <c r="E12" s="237"/>
       <c r="G12" s="266">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="C14" s="269">
         <f>SUM(C11:C13)</f>
-        <v>21216.235210477949</v>
+        <v>22897.570210477948</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="243"/>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="C19" s="267">
         <f>C14+C17</f>
-        <v>21216.235210477949</v>
+        <v>22897.570210477948</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="234"/>
@@ -12288,7 +12288,7 @@
       </c>
       <c r="C45" s="266">
         <f>-BS!G31*Normalized_FCF!C52</f>
-        <v>-6725.34</v>
+        <v>-4483.5600000000004</v>
       </c>
       <c r="E45" s="237"/>
       <c r="G45" s="266">
@@ -12455,7 +12455,7 @@
       </c>
       <c r="C48" s="267">
         <f>C45+C46</f>
-        <v>-6159.4913131261419</v>
+        <v>-3917.7113131261426</v>
       </c>
       <c r="E48" s="237"/>
       <c r="G48" s="267">
@@ -12547,7 +12547,7 @@
         <v>84</v>
       </c>
       <c r="C52" s="79">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="E52" s="234"/>
       <c r="G52" s="22">
@@ -12572,7 +12572,7 @@
       </c>
       <c r="C53" s="40">
         <f>-C8/C45</f>
-        <v>5.7765314854609686</v>
+        <v>8.6647972281914534</v>
       </c>
       <c r="E53" s="237"/>
       <c r="G53" s="40">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>5.3153178478486645E-3</v>
+        <v>3.3807793219874224E-3</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="234"/>
@@ -13477,7 +13477,7 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>2.8209450265575496E-2</v>
+        <v>3.0143988791436739E-2</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="234"/>
@@ -13534,7 +13534,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>7.052362566393874E-3</v>
+        <v>7.5359971978591848E-3</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="234"/>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>1.8308497884896562E-2</v>
+        <v>1.9759401779292494E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="234"/>
@@ -13872,7 +13872,7 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>1.8308497884896562E-2</v>
+        <v>1.9759401779292494E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="234"/>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.55276121761479602</v>
+        <v>0.51217277206029399</v>
       </c>
       <c r="E90" s="237"/>
       <c r="G90" s="152">
@@ -14265,7 +14265,7 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>-0.16182541608410217</v>
+        <v>-0.10434535147037427</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="234"/>
@@ -14994,7 +14994,7 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>2.8209450265575496E-2</v>
+        <v>3.0143988791436739E-2</v>
       </c>
       <c r="E116" s="22">
         <f>E119/E117/E118</f>
@@ -15168,7 +15168,7 @@
       </c>
       <c r="C119" s="62">
         <f>C11/C104</f>
-        <v>0.10738337476941046</v>
+        <v>0.11474747699659658</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="453">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>7.9251605356555466</v>
+        <v>8.5532102182229668</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
@@ -15348,7 +15348,7 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.8794796316454396E-2</v>
+        <v>7.4246616477629909E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
@@ -16196,7 +16196,7 @@
       </c>
       <c r="C4" s="275">
         <f>Normalized_FCF!C19</f>
-        <v>21216.235210477949</v>
+        <v>22897.570210477948</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="C6" s="283">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>412201.1412321431</v>
+        <v>444867.07837500022</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16278,7 +16278,7 @@
       </c>
       <c r="I6" s="305">
         <f>I7+I8</f>
-        <v>-6159.4913131261419</v>
+        <v>-3917.7113131261426</v>
       </c>
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
@@ -16319,7 +16319,7 @@
       </c>
       <c r="C8" s="283">
         <f>C6+C7</f>
-        <v>429670.72675316682</v>
+        <v>462336.66389602394</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16342,7 +16342,7 @@
       </c>
       <c r="I8" s="313">
         <f>Normalized_FCF!C10</f>
-        <v>-6159.4913131261419</v>
+        <v>-3917.7113131261426</v>
       </c>
       <c r="J8" s="313"/>
       <c r="N8" s="304"/>
@@ -16380,7 +16380,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>482632.75442625606</v>
+        <v>519325.15685801161</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>160.50017607784261</v>
+        <v>172.70228419629535</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16492,7 +16492,7 @@
       </c>
       <c r="C17" s="306">
         <f>Normalized_FCF!C77</f>
-        <v>2.8209450265575496E-2</v>
+        <v>3.0143988791436739E-2</v>
       </c>
       <c r="E17" s="308" t="s">
         <v>551</v>
@@ -16525,7 +16525,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>186.15398492308685</v>
+        <v>188.39395633948806</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16592,11 +16592,11 @@
       </c>
       <c r="E21" s="299">
         <f>$C$17</f>
-        <v>2.8209450265575496E-2</v>
+        <v>3.0143988791436739E-2</v>
       </c>
       <c r="F21" s="277">
         <f>C21*E21</f>
-        <v>33469.488456468323</v>
+        <v>35764.748174411827</v>
       </c>
       <c r="G21" s="299">
         <f t="shared" ref="G21:G50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16604,7 +16604,7 @@
       </c>
       <c r="H21" s="277">
         <f>(F21*(1-$I$10)+C21*(G21-$I$9))</f>
-        <v>21722.367959846488</v>
+        <v>23443.812748304117</v>
       </c>
       <c r="I21" s="299">
         <f>H21/C4-1</f>
@@ -16612,7 +16612,7 @@
       </c>
       <c r="J21" s="299">
         <f>H21/C21</f>
-        <v>1.8308497884896562E-2</v>
+        <v>1.9759401779292494E-2</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16620,7 +16620,7 @@
       </c>
       <c r="L21" s="277">
         <f t="shared" ref="L21:L51" si="4">H21*K21</f>
-        <v>20253.956139717004</v>
+        <v>21859.032865551624</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16641,11 +16641,11 @@
       </c>
       <c r="E22" s="299">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
-        <v>2.8209450265575496E-2</v>
+        <v>3.0143988791436739E-2</v>
       </c>
       <c r="F22" s="277">
         <f t="shared" ref="F22:F50" si="7">IF(A22="", 0,C22*E22)</f>
-        <v>34267.933800063722</v>
+        <v>36617.949043671077</v>
       </c>
       <c r="G22" s="299">
         <f t="shared" si="2"/>
@@ -16653,7 +16653,7 @@
       </c>
       <c r="H22" s="277">
         <f t="shared" ref="H22:H50" si="8">IF(A22="", 0,F22*(1-$I$10)+C22*(G22-$I$9))</f>
-        <v>22240.57497014973</v>
+        <v>24003.086402855246</v>
       </c>
       <c r="I22" s="299">
         <f t="shared" ref="I22:I50" si="9">IF(A22="", 0,H22/H21-1)</f>
@@ -16661,7 +16661,7 @@
       </c>
       <c r="J22" s="299">
         <f>IF(A22="", 0,H22/C22)</f>
-        <v>1.8308497884896562E-2</v>
+        <v>1.9759401779292494E-2</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16669,7 +16669,7 @@
       </c>
       <c r="L22" s="277">
         <f t="shared" si="4"/>
-        <v>19335.321994685732</v>
+        <v>20867.599200487064</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16690,11 +16690,11 @@
       </c>
       <c r="E23" s="299">
         <f t="shared" si="6"/>
-        <v>2.8209450265575496E-2</v>
+        <v>3.0143988791436739E-2</v>
       </c>
       <c r="F23" s="277">
         <f t="shared" si="7"/>
-        <v>35085.426789622943</v>
+        <v>37491.503802177765</v>
       </c>
       <c r="G23" s="299">
         <f t="shared" si="2"/>
@@ -16702,15 +16702,15 @@
       </c>
       <c r="H23" s="277">
         <f t="shared" si="8"/>
-        <v>22771.14428395615</v>
+        <v>24575.702043372272</v>
       </c>
       <c r="I23" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759254E-2</v>
+        <v>2.3855917147759476E-2</v>
       </c>
       <c r="J23" s="299">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,H23/C23)</f>
-        <v>1.8308497884896559E-2</v>
+        <v>1.9759401779292494E-2</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16718,7 +16718,7 @@
       </c>
       <c r="L23" s="277">
         <f t="shared" si="4"/>
-        <v>18458.353225376413</v>
+        <v>19921.132790756674</v>
       </c>
       <c r="N23" s="275"/>
       <c r="O23" s="275"/>
@@ -16747,11 +16747,11 @@
       </c>
       <c r="E24" s="299">
         <f t="shared" si="6"/>
-        <v>2.8209450265575496E-2</v>
+        <v>3.0143988791436739E-2</v>
       </c>
       <c r="F24" s="277">
         <f t="shared" si="7"/>
-        <v>35922.421824209967</v>
+        <v>38385.898010627432</v>
       </c>
       <c r="G24" s="299">
         <f t="shared" si="2"/>
@@ -16759,7 +16759,7 @@
       </c>
       <c r="H24" s="277">
         <f t="shared" si="8"/>
-        <v>23314.370815353883</v>
+        <v>25161.977955166985</v>
       </c>
       <c r="I24" s="299">
         <f t="shared" si="9"/>
@@ -16767,7 +16767,7 @@
       </c>
       <c r="J24" s="299">
         <f t="shared" si="10"/>
-        <v>1.8308497884896559E-2</v>
+        <v>1.9759401779292498E-2</v>
       </c>
       <c r="K24" s="119">
         <f t="shared" si="3"/>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="L24" s="277">
         <f t="shared" si="4"/>
-        <v>17621.160065832231</v>
+        <v>19017.594111051261</v>
       </c>
       <c r="N24" s="275"/>
       <c r="O24" s="275"/>
@@ -16820,7 +16820,7 @@
       </c>
       <c r="I25" s="299">
         <f t="shared" si="9"/>
-        <v>0.49340827256600162</v>
+        <v>0.38374949327745655</v>
       </c>
       <c r="J25" s="299">
         <f t="shared" si="10"/>
@@ -18180,7 +18180,7 @@
       <c r="K52" s="469"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
-        <v>480878.26645334472</v>
+        <v>486874.83399557997</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18204,7 +18204,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>480878.26645334472</v>
+        <v>486874.83399557997</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18239,19 +18239,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>425732.36302881944</v>
+        <v>427300.04135049781</v>
       </c>
       <c r="C56" s="118">
-        <v>429989.68665910763</v>
+        <v>431573.04176400276</v>
       </c>
       <c r="D56" s="118">
-        <v>434247.01028939598</v>
+        <v>435846.04217750789</v>
       </c>
       <c r="E56" s="118">
-        <v>438504.33391968417</v>
+        <v>440119.04259101284</v>
       </c>
       <c r="F56" s="118">
-        <v>447018.98118026054</v>
+        <v>448665.0434180228</v>
       </c>
       <c r="G56" s="295"/>
       <c r="H56" s="295"/>
@@ -18265,19 +18265,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>425194.28727396054</v>
+        <v>426761.9655956389</v>
       </c>
       <c r="C57" s="118">
-        <v>433540.89386949519</v>
+        <v>435124.24897439033</v>
       </c>
       <c r="D57" s="118">
-        <v>441968.58291498595</v>
+        <v>443567.61480309779</v>
       </c>
       <c r="E57" s="118">
-        <v>450477.35441043309</v>
+        <v>452092.06308176182</v>
       </c>
       <c r="F57" s="118">
-        <v>467738.14475119644</v>
+        <v>469384.2069889587</v>
       </c>
       <c r="G57" s="295"/>
       <c r="H57" s="295"/>
@@ -18291,19 +18291,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>424692.58493842767</v>
+        <v>426260.26326010597</v>
       </c>
       <c r="C58" s="118">
-        <v>436885.15427275037</v>
+        <v>438468.50937764545</v>
       </c>
       <c r="D58" s="118">
-        <v>449312.17646100163</v>
+        <v>450911.20834911353</v>
       </c>
       <c r="E58" s="118">
-        <v>461975.91954373999</v>
+        <v>463590.6282150686</v>
       </c>
       <c r="F58" s="118">
-        <v>488022.64055490994</v>
+        <v>489668.70279267221</v>
       </c>
       <c r="G58" s="295"/>
       <c r="H58" s="295"/>
@@ -18317,19 +18317,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>424224.79721298913</v>
+        <v>425792.47553466744</v>
       </c>
       <c r="C59" s="118">
-        <v>440034.52770611882</v>
+        <v>441617.88281101396</v>
       </c>
       <c r="D59" s="118">
-        <v>456296.29339986964</v>
+        <v>457895.32528798154</v>
       </c>
       <c r="E59" s="118">
-        <v>473018.83058085479</v>
+        <v>474633.53925218346</v>
       </c>
       <c r="F59" s="118">
-        <v>507881.58749560849</v>
+        <v>509527.64973337075</v>
       </c>
       <c r="G59" s="295"/>
       <c r="H59" s="295"/>
@@ -18343,19 +18343,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>415329.63396127464</v>
+        <v>418359.01701179054</v>
       </c>
       <c r="C60" s="118">
-        <v>434371.34782821708</v>
+        <v>437445.78792699939</v>
       </c>
       <c r="D60" s="118">
-        <v>454137.78944760328</v>
+        <v>457257.57893559779</v>
       </c>
       <c r="E60" s="118">
-        <v>474649.99325414718</v>
+        <v>477815.42447229964</v>
       </c>
       <c r="F60" s="118">
-        <v>517997.86838358123</v>
+        <v>521255.46008488693</v>
       </c>
       <c r="G60" s="295"/>
       <c r="H60" s="295"/>
@@ -18369,19 +18369,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>414922.95264531695</v>
+        <v>417952.33569583291</v>
       </c>
       <c r="C61" s="118">
-        <v>437164.35663767077</v>
+        <v>440238.79673645308</v>
       </c>
       <c r="D61" s="118">
-        <v>460454.88206344284</v>
+        <v>463574.67155143735</v>
       </c>
       <c r="E61" s="118">
-        <v>484835.04925299564</v>
+        <v>488000.4804711481</v>
       </c>
       <c r="F61" s="118">
-        <v>537032.3131015473</v>
+        <v>540289.90480285301</v>
       </c>
       <c r="G61" s="295"/>
       <c r="H61" s="295"/>
@@ -18395,19 +18395,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>406656.58541332866</v>
+        <v>411048.8633159076</v>
       </c>
       <c r="C62" s="118">
-        <v>431668.43614604214</v>
+        <v>436147.0681737999</v>
       </c>
       <c r="D62" s="118">
-        <v>458092.81083393865</v>
+        <v>462658.9152421013</v>
       </c>
       <c r="E62" s="118">
-        <v>485997.97016072512</v>
+        <v>490652.67338188784</v>
       </c>
       <c r="F62" s="118">
-        <v>546537.04030547943</v>
+        <v>551372.3531599046</v>
       </c>
       <c r="G62" s="295"/>
       <c r="H62" s="295"/>
@@ -18421,19 +18421,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>406303.02826816408</v>
+        <v>410695.30617074302</v>
       </c>
       <c r="C63" s="118">
-        <v>434145.40446203586</v>
+        <v>438624.03648979362</v>
       </c>
       <c r="D63" s="118">
-        <v>463806.58388017898</v>
+        <v>468372.68828834163</v>
       </c>
       <c r="E63" s="118">
-        <v>495391.81254078454</v>
+        <v>500046.51576194726</v>
       </c>
       <c r="F63" s="118">
-        <v>564781.21442021057</v>
+        <v>569616.52727463574</v>
       </c>
       <c r="G63" s="295"/>
       <c r="H63" s="295"/>
@@ -18447,19 +18447,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>398619.35988684569</v>
+        <v>404282.40222025261</v>
       </c>
       <c r="C64" s="118">
-        <v>428825.41358437197</v>
+        <v>434626.40817461465</v>
       </c>
       <c r="D64" s="118">
-        <v>461280.44333097438</v>
+        <v>467222.06402684934</v>
       </c>
       <c r="E64" s="118">
-        <v>496136.40017137572</v>
+        <v>502221.35995486996</v>
       </c>
       <c r="F64" s="118">
-        <v>573703.7968412335</v>
+        <v>580083.73180360778</v>
       </c>
       <c r="G64" s="295"/>
       <c r="H64" s="295"/>
@@ -18473,19 +18473,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>398311.987381663</v>
+        <v>403975.02971506992</v>
       </c>
       <c r="C65" s="118">
-        <v>431022.10269529419</v>
+        <v>436823.09728553693</v>
       </c>
       <c r="D65" s="118">
-        <v>466448.51738169871</v>
+        <v>472390.13807757368</v>
       </c>
       <c r="E65" s="118">
-        <v>504800.49339495535</v>
+        <v>510885.45317844965</v>
       </c>
       <c r="F65" s="118">
-        <v>591190.51074649696</v>
+        <v>597570.44570887124</v>
       </c>
       <c r="G65" s="295"/>
       <c r="H65" s="295"/>
@@ -18499,19 +18499,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>377848.65370608249</v>
+        <v>386831.40955815709</v>
       </c>
       <c r="C66" s="277">
-        <v>419843.65322674008</v>
+        <v>429167.0721551741</v>
       </c>
       <c r="D66" s="118">
-        <v>467114.8543356958</v>
+        <v>476792.04883739928</v>
       </c>
       <c r="E66" s="118">
-        <v>520320.59006954031</v>
+        <v>530365.15327993874</v>
       </c>
       <c r="F66" s="118">
-        <v>647565.76645292563</v>
+        <v>658387.84479172144</v>
       </c>
       <c r="G66" s="295"/>
       <c r="H66" s="295"/>
@@ -18534,19 +18534,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>366225.72976120922</v>
+        <v>377064.46472967777</v>
       </c>
       <c r="C67" s="277">
-        <v>414975.50847604114</v>
+        <v>426318.38410724991</v>
       </c>
       <c r="D67" s="118">
-        <v>471747.62035189278</v>
+        <v>483620.37524178997</v>
       </c>
       <c r="E67" s="118">
-        <v>537917.11729936081</v>
+        <v>550346.81211956847</v>
       </c>
       <c r="F67" s="118">
-        <v>705140.03721799445</v>
+        <v>718770.39704685635</v>
       </c>
       <c r="G67" s="295"/>
       <c r="H67" s="295"/>
@@ -18569,19 +18569,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>352065.42161633779</v>
+        <v>365243.60838978499</v>
       </c>
       <c r="C68" s="277">
-        <v>404927.72977538285</v>
+        <v>418879.53307044599</v>
       </c>
       <c r="D68" s="118">
-        <v>468417.97296493349</v>
+        <v>483197.23688072362</v>
       </c>
       <c r="E68" s="118">
-        <v>544848.95341982238</v>
+        <v>560513.47711203783</v>
       </c>
       <c r="F68" s="118">
-        <v>748418.96201773675</v>
+        <v>766044.65098794212</v>
       </c>
       <c r="G68" s="295"/>
       <c r="H68" s="295"/>
@@ -18604,19 +18604,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>344058.15800693462</v>
+        <v>358544.28104338603</v>
       </c>
       <c r="C69" s="277">
-        <v>400012.3489492088</v>
+        <v>415459.88812160527</v>
       </c>
       <c r="D69" s="118">
-        <v>469028.49274077325</v>
+        <v>485516.03935070307</v>
       </c>
       <c r="E69" s="118">
-        <v>554529.16753518628</v>
+        <v>572142.24308048002</v>
       </c>
       <c r="F69" s="118">
-        <v>793523.22579142265</v>
+        <v>813674.72447184823</v>
       </c>
       <c r="G69" s="295"/>
       <c r="H69" s="295"/>
@@ -18713,23 +18713,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>160.50017607784261</v>
+        <v>172.70228419629535</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>160.50017607784261</v>
+        <v>172.70228419629535</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>160.50017607784261</v>
+        <v>172.70228419629535</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>160.50017607784261</v>
+        <v>172.70228419629535</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>160.50017607784261</v>
+        <v>172.70228419629535</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18744,23 +18744,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>165.55465930346509</v>
+        <v>166.14025341308508</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>167.14494961122008</v>
+        <v>167.73639966193628</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>168.73523991897517</v>
+        <v>169.33254591078756</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>170.32553022673019</v>
+        <v>170.92869215963876</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>173.50611084224022</v>
+        <v>174.12098465734121</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18775,23 +18775,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>165.35366526775161</v>
+        <v>165.93925937737157</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>168.47147559278537</v>
+        <v>169.06292564350153</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>171.61957363975245</v>
+        <v>172.21687963156481</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>174.79795940865296</v>
+        <v>175.40112134156155</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>181.24559411225408</v>
+        <v>181.86046792735507</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18806,23 +18806,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>165.16625824144526</v>
+        <v>165.7518523510652</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>169.72069819547144</v>
+        <v>170.31214824618763</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>174.36271619937281</v>
+        <v>174.9600221911852</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>179.0931594621546</v>
+        <v>179.69632139506317</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>188.82271060037957</v>
+        <v>189.43758441548056</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18837,23 +18837,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>164.99151975537873</v>
+        <v>165.57711386499869</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>170.89712227818745</v>
+        <v>171.48857232890364</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>176.97157905327748</v>
+        <v>177.56888504508984</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>183.21815345292993</v>
+        <v>183.82131538583849</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>196.24086660274017</v>
+        <v>196.85574041784116</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18868,23 +18868,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>161.66880033502252</v>
+        <v>162.80040293846062</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>168.78168524473583</v>
+        <v>169.93011855999589</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>176.16528659993452</v>
+        <v>177.33065982871528</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>183.8274616509851</v>
+        <v>185.00988399498536</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>200.0197250696454</v>
+        <v>201.23657324918091</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18899,23 +18899,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>161.51688767550294</v>
+        <v>162.6484902789411</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>169.82499207899872</v>
+        <v>170.97342539425878</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>178.52498767802251</v>
+        <v>179.69036090680328</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>187.63201052851886</v>
+        <v>188.81443287251906</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>207.12989464499222</v>
+        <v>208.34674282452775</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18931,23 +18931,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>158.42905014399616</v>
+        <v>160.06975157616915</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>167.77203349538323</v>
+        <v>169.44499184298769</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>177.64265424304864</v>
+        <v>179.34828722167353</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>188.0664106373315</v>
+        <v>189.80513901715872</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>210.68031196415794</v>
+        <v>212.48650567530765</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18962,23 +18962,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>158.29698160751173</v>
+        <v>159.93768303968471</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>168.69728584817994</v>
+        <v>170.37024419578438</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>179.77698996314817</v>
+        <v>181.48262294177303</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>191.57540778833629</v>
+        <v>193.31413616816354</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>217.49528206914098</v>
+        <v>219.3014757802907</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18994,23 +18994,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>155.42680672395767</v>
+        <v>157.54219237872729</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>166.71004441088252</v>
+        <v>168.87696106400477</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>178.8333697030283</v>
+        <v>181.05281615003636</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>191.8535427376691</v>
+        <v>194.12653239199679</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>220.82824370807973</v>
+        <v>223.21141905857201</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19026,23 +19026,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>155.31199010245754</v>
+        <v>157.42737575722717</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>167.53060063484386</v>
+        <v>169.69751728796609</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>180.76386378483969</v>
+        <v>182.98331023184772</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>195.08994773655613</v>
+        <v>197.36293739088384</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>227.36027041147202</v>
+        <v>229.74344576196432</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19058,23 +19058,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>147.66807011077259</v>
+        <v>151.02350906938355</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>163.3549773115196</v>
+        <v>166.8376683269604</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>181.01276879927212</v>
+        <v>184.62760994332618</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>200.88735978703315</v>
+        <v>204.63942867028314</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>248.41881106582093</v>
+        <v>252.46131471048452</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19090,23 +19090,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>143.32641678524087</v>
+        <v>147.37514238506424</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>161.53651949950196</v>
+        <v>165.77356294389728</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>182.74330270588899</v>
+        <v>187.17827844826084</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>207.46040640830597</v>
+        <v>212.10342275319934</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>269.92523451983351</v>
+        <v>275.01674999045446</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19122,23 +19122,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>138.03694322081535</v>
+        <v>142.95955294456326</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>157.7832494947402</v>
+        <v>162.99483768549783</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>181.49953868239504</v>
+        <v>187.02021838685138</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>210.04974016693544</v>
+        <v>215.90110181257162</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>286.09174207623209</v>
+        <v>292.67568184003255</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19154,23 +19154,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>135.04589184311885</v>
+        <v>140.45707103981428</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>155.94714701214355</v>
+        <v>161.71745576897752</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>181.7275936217244</v>
+        <v>187.88638911142866</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>213.66570926431277</v>
+        <v>220.24493738081412</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>302.94009088566071</v>
+        <v>310.4675273272378</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>227.36027041147202</v>
+        <v>229.74344576196432</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19245,7 +19245,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>195.08994773655613</v>
+        <v>197.36293739088384</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19273,7 +19273,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>180.76386378483969</v>
+        <v>182.98331023184772</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>167.53060063484386</v>
+        <v>169.69751728796609</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>155.31199010245754</v>
+        <v>157.42737575722717</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19551,7 +19551,7 @@
       </c>
       <c r="C9" s="447">
         <f>Normalized_FCF!C19</f>
-        <v>21216.235210477949</v>
+        <v>22897.570210477948</v>
       </c>
       <c r="D9" s="470"/>
       <c r="E9" s="470"/>
@@ -19689,7 +19689,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>195.08994773655613</v>
+        <v>197.36293739088384</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19713,7 +19713,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>180.76386378483969</v>
+        <v>182.98331023184772</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19736,7 +19736,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>167.53060063484386</v>
+        <v>169.69751728796609</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>180.32076478768403</v>
+        <v>182.53778742768455</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19799,7 +19799,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>227.36027041147202</v>
+        <v>229.74344576196432</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19822,7 +19822,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>155.31199010245754</v>
+        <v>157.42737575722717</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19966443414501156</v>
+        <v>0.20425434714922333</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>160.50017607784261</v>
+        <v>172.70228419629535</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19898,7 +19898,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>7.1461992773322186E-2</v>
+        <v>4.9113890339692497E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19907,7 +19907,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>186.12625189699088</v>
+        <v>188.36311559430365</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20010,7 +20010,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>186.15398492308685</v>
+        <v>188.39395633948806</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>3.5060226386415046E-2</v>
+        <v>3.4643876575169347E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20155,11 +20155,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>85.772466311977382</v>
+        <v>86.803279075715992</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>92.195245344123904</v>
+        <v>93.226058107862514</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20167,7 +20167,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.50466285972841618</v>
+        <v>0.50507264750996828</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20180,11 +20180,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>107.50974838815362</v>
+        <v>108.80179962125847</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>114.89480224306809</v>
+        <v>116.18685347617293</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20192,7 +20192,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.38270501301097981</v>
+        <v>0.3831761960955451</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20226,11 +20226,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>133.40792546005932</v>
+        <v>135.01122076286578</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>141.87616243210397</v>
+        <v>143.47945773491043</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20238,7 +20238,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.23774233357138974</v>
+        <v>0.23828262618072005</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20251,11 +20251,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>150.87446020227677</v>
+        <v>152.6876681696564</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>160.04389724965404</v>
+        <v>161.85710521703368</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20263,7 +20263,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.14013259484627549</v>
+        <v>0.14071762560117451</v>
       </c>
     </row>
   </sheetData>
@@ -20399,7 +20399,7 @@
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.19966443414501156</v>
+        <v>0.20425434714922333</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>186.12625189699088</v>
+        <v>188.36311559430365</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>92.195245344123904</v>
+        <v>93.226058107862514</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>114.89480224306809</v>
+        <v>116.18685347617293</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20561,7 +20561,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>141.87616243210397</v>
+        <v>143.47945773491043</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>160.04389724965404</v>
+        <v>161.85710521703368</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20737,7 +20737,7 @@
       </c>
       <c r="C45" s="376">
         <f>Normalized_FCF!C45</f>
-        <v>-6725.34</v>
+        <v>-4483.5600000000004</v>
       </c>
       <c r="D45" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C46" s="373">
         <f>Normalized_FCF!C10</f>
-        <v>-6159.4913131261419</v>
+        <v>-3917.7113131261426</v>
       </c>
       <c r="D46" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20792,7 +20792,7 @@
       </c>
       <c r="C52" s="373">
         <f>Normalized_FCF!C12</f>
-        <v>-8172.4117368259831</v>
+        <v>-8732.8567368259828</v>
       </c>
       <c r="D52" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20858,7 +20858,7 @@
       </c>
       <c r="C61" s="373">
         <f>Normalized_FCF!C19</f>
-        <v>21216.235210477949</v>
+        <v>22897.570210477948</v>
       </c>
       <c r="D61" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20871,7 +20871,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.8794796316454396E-2</v>
+        <v>7.4246616477629909E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20888,7 +20888,7 @@
       </c>
       <c r="F63" s="380">
         <f>Normalized_FCF!C90</f>
-        <v>0.55276121761479602</v>
+        <v>0.51217277206029399</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -21287,7 +21287,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>160.50017607784261</v>
+        <v>172.70228419629535</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21350,7 +21350,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>227.36 HKD</v>
+        <v>229.74 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21373,7 +21373,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>195.09 HKD</v>
+        <v>197.36 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21395,7 +21395,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>180.76 HKD</v>
+        <v>182.98 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>167.53 HKD</v>
+        <v>169.7 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>155.31 HKD</v>
+        <v>157.43 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21461,7 +21461,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>186.12625189699088</v>
+        <v>188.36311559430365</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21568,11 +21568,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>85.772466311977382</v>
+        <v>86.803279075715992</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>92.195245344123904</v>
+        <v>93.226058107862514</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21589,11 +21589,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>107.50974838815362</v>
+        <v>108.80179962125847</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>114.89480224306809</v>
+        <v>116.18685347617293</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21629,11 +21629,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>133.40792546005932</v>
+        <v>135.01122076286578</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>141.87616243210397</v>
+        <v>143.47945773491043</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21650,11 +21650,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>150.87446020227677</v>
+        <v>152.6876681696564</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>160.04389724965404</v>
+        <v>161.85710521703368</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>

--- a/financial_models/opportunities/9618.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9618.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E49F50A-1C4F-4FB6-A4AA-903BCFBAE1CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F8AC17-229E-45EB-BC91-8BAD1014AC8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4995,30 +4995,30 @@
     <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5028,25 +5028,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5416,7 +5416,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>115.2</v>
+        <v>108.5</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5435,14 +5435,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>346412.66239445761</v>
+        <v>326265.39817533549</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.20425434714922333</v>
+        <v>0.23040202190361286</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5450,13 +5450,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+      <c r="B12" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="C12" s="463"/>
+      <c r="D12" s="463"/>
+      <c r="E12" s="463"/>
+      <c r="F12" s="463"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5491,7 +5491,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1232618942260741</v>
+        <v>1.1268191807746888</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>188.36311559430365</v>
+        <v>188.95964751691497</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>93.226058107862514</v>
+        <v>93.500957611370026</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>116.18685347617293</v>
+        <v>116.53142065168849</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>143.47945773491043</v>
+        <v>143.9070281902072</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>161.85710521703368</v>
+        <v>162.34065566142357</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5634,22 +5634,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+      <c r="B29" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="463"/>
+      <c r="D29" s="463"/>
+      <c r="E29" s="463"/>
+      <c r="F29" s="463"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="463" t="s">
+      <c r="B30" s="467" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="463"/>
-      <c r="D30" s="463"/>
-      <c r="E30" s="463"/>
-      <c r="F30" s="463"/>
+      <c r="C30" s="467"/>
+      <c r="D30" s="467"/>
+      <c r="E30" s="467"/>
+      <c r="F30" s="467"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5661,13 +5661,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+      <c r="B33" s="464" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="C33" s="464"/>
+      <c r="D33" s="464"/>
+      <c r="E33" s="464"/>
+      <c r="F33" s="464"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5687,13 +5687,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+      <c r="B36" s="464" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="C36" s="464"/>
+      <c r="D36" s="464"/>
+      <c r="E36" s="464"/>
+      <c r="F36" s="464"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5722,13 +5722,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+      <c r="B40" s="464" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="C40" s="464"/>
+      <c r="D40" s="464"/>
+      <c r="E40" s="464"/>
+      <c r="F40" s="464"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5744,13 +5744,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+      <c r="B43" s="464" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="C43" s="464"/>
+      <c r="D43" s="464"/>
+      <c r="E43" s="464"/>
+      <c r="F43" s="464"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5814,13 +5814,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+      <c r="B51" s="464" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="C51" s="464"/>
+      <c r="D51" s="464"/>
+      <c r="E51" s="464"/>
+      <c r="F51" s="464"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5836,7 +5836,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+      <c r="B54" s="464" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5858,22 +5858,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+      <c r="B57" s="463" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="C57" s="463"/>
+      <c r="D57" s="463"/>
+      <c r="E57" s="463"/>
+      <c r="F57" s="463"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="B58" s="463" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="C58" s="463"/>
+      <c r="D58" s="463"/>
+      <c r="E58" s="463"/>
+      <c r="F58" s="463"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.4246616477629909E-2</v>
+        <v>7.9081083837262922E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.0468749999999996E-2</v>
+        <v>3.2350230414746543E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6008,13 +6008,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
+      <c r="B73" s="463" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="C73" s="463"/>
+      <c r="D73" s="463"/>
+      <c r="E73" s="463"/>
+      <c r="F73" s="463"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6033,13 +6033,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="463" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="C77" s="463"/>
+      <c r="D77" s="463"/>
+      <c r="E77" s="463"/>
+      <c r="F77" s="463"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-41.869978837828064</v>
+        <v>-42.002577934509091</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>11.589853064698382</v>
+        <v>11.626557263976748</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>36.805754301093096</v>
+        <v>36.922315376795837</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.5256285279634056</v>
+        <v>6.5462947062635024</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6208,31 +6208,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
+      <c r="B96" s="463" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="C96" s="463"/>
+      <c r="D96" s="463"/>
+      <c r="E96" s="463"/>
+      <c r="F96" s="463"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="463" t="s">
+      <c r="B97" s="467" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="463"/>
-      <c r="D97" s="463"/>
-      <c r="E97" s="463"/>
-      <c r="F97" s="463"/>
+      <c r="C97" s="467"/>
+      <c r="D97" s="467"/>
+      <c r="E97" s="467"/>
+      <c r="F97" s="467"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="463" t="s">
+      <c r="B98" s="467" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="463"/>
-      <c r="D98" s="463"/>
-      <c r="E98" s="463"/>
-      <c r="F98" s="463"/>
+      <c r="C98" s="467"/>
+      <c r="D98" s="467"/>
+      <c r="E98" s="467"/>
+      <c r="F98" s="467"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6282,22 +6282,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="463" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
+      <c r="C107" s="463"/>
+      <c r="D107" s="463"/>
+      <c r="E107" s="463"/>
+      <c r="F107" s="463"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="B108" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="463"/>
+      <c r="D108" s="463"/>
+      <c r="E108" s="463"/>
+      <c r="F108" s="463"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-64.819799197819449</v>
+        <v>-65.025078661990335</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>172.70228419629535</v>
+        <v>173.24921943521377</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6331,13 +6331,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
+      <c r="B114" s="463" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="C114" s="463"/>
+      <c r="D114" s="463"/>
+      <c r="E114" s="463"/>
+      <c r="F114" s="463"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>229.74 HKD</v>
+        <v>230.47 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.7718870553804284E-2</v>
+        <v>-4.7770399690866813E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>197.36 HKD</v>
+        <v>197.99 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.624191101882751E-3</v>
+        <v>2.5671832081474487E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>182.98 HKD</v>
+        <v>183.56 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.8706233475927469E-2</v>
+        <v>2.8646242962904404E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>169.7 HKD</v>
+        <v>170.23 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.5390407552362853E-2</v>
+        <v>5.532726134963737E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>157.43 HKD</v>
+        <v>157.93 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6468,17 +6468,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>8.2670005641726316E-2</v>
+        <v>8.2603522450848801E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+      <c r="B124" s="464" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="C124" s="464"/>
+      <c r="D124" s="464"/>
+      <c r="E124" s="464"/>
+      <c r="F124" s="464"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>188.36311559430365</v>
+        <v>188.95964751691497</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6513,22 +6513,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="464" t="s">
+      <c r="B131" s="468" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="464"/>
-      <c r="D131" s="464"/>
-      <c r="E131" s="464"/>
-      <c r="F131" s="464"/>
+      <c r="C131" s="468"/>
+      <c r="D131" s="468"/>
+      <c r="E131" s="468"/>
+      <c r="F131" s="468"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="B132" s="463" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="C132" s="463"/>
+      <c r="D132" s="463"/>
+      <c r="E132" s="463"/>
+      <c r="F132" s="463"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6593,11 +6593,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>86.803279075715992</v>
+        <v>87.078178579223504</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>93.226058107862514</v>
+        <v>93.500957611370026</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6614,11 +6614,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>108.80179962125847</v>
+        <v>109.14636679677403</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>116.18685347617293</v>
+        <v>116.53142065168849</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6661,11 +6661,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>135.01122076286578</v>
+        <v>135.43879121816255</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>143.47945773491043</v>
+        <v>143.9070281902072</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6682,11 +6682,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>152.6876681696564</v>
+        <v>153.17121861404627</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>161.85710521703368</v>
+        <v>162.34065566142357</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6704,13 +6704,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="468" t="s">
+      <c r="B149" s="462" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="C149" s="463"/>
+      <c r="D149" s="463"/>
+      <c r="E149" s="463"/>
+      <c r="F149" s="463"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6747,13 +6747,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
+      <c r="B158" s="464" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="C158" s="464"/>
+      <c r="D158" s="464"/>
+      <c r="E158" s="464"/>
+      <c r="F158" s="464"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6761,22 +6761,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="461" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="461"/>
+      <c r="D161" s="461"/>
+      <c r="E161" s="461"/>
+      <c r="F161" s="461"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="461" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="461"/>
+      <c r="D162" s="461"/>
+      <c r="E162" s="461"/>
+      <c r="F162" s="461"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6800,18 +6800,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6828,6 +6816,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10079,11 +10079,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>86.636777933552594</v>
+        <v>86.911150140375028</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-64.819799197819449</v>
+        <v>-65.025078661990335</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10489,11 +10489,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-125905.30246190642</v>
+        <v>-126304.03515385409</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-41.869978837828064</v>
+        <v>-42.002577934509084</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10506,11 +10506,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>34851.318202280643</v>
+        <v>34961.689724789991</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>11.58985306469838</v>
+        <v>11.626557263976752</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10523,11 +10523,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>110676.90398331526</v>
+        <v>111027.4094743374</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>36.805754301093096</v>
+        <v>36.922315376795837</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10540,11 +10540,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>19622.919723689483</v>
+        <v>19685.064045273306</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.5256285279634128</v>
+        <v>6.5462947062635024</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14128,20 +14128,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.0468749999999996E-2</v>
+        <v>3.2350230414746543E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.0468749999999996E-2</v>
+        <v>3.2350230414746543E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>2.315625E-2</v>
+        <v>2.4586175115207377E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>1.8890625000000001E-2</v>
+        <v>2.0057142857142857E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
@@ -15291,30 +15291,30 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>8.5532102182229668</v>
+        <v>8.5802975963430281</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.766235135150467</v>
+        <v>10.800330997942893</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>6.9650690559300399</v>
+        <v>6.987126909570577</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>3.6857415196214576</v>
+        <v>3.6974139878114816</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>4.7066325273366141E-2</v>
+        <v>4.7215380811213813E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.6237061447121119</v>
+        <v>4.6383490768349569</v>
       </c>
       <c r="L123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15348,30 +15348,30 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.4246616477629909E-2</v>
+        <v>7.9081083837262922E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>9.3456902214847801E-2</v>
+        <v>9.9542221179197171E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.0460668888281596E-2</v>
+        <v>6.4397483037516842E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.1994284024491816E-2</v>
+        <v>3.40775482747602E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>4.085618513313033E-4</v>
+        <v>4.3516480010335313E-4</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>4.0136338061737081E-2</v>
+        <v>4.2749761076819881E-2</v>
       </c>
       <c r="L124" s="74" t="str">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
@@ -15405,23 +15405,23 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12892138437233561</v>
+        <v>0.13688242838426787</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7136691364697923E-2</v>
+        <v>7.1282459402886647E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7975305328085631E-2</v>
+        <v>2.9702812661709356E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-1.2895025167738987E-2</v>
+        <v>-1.3691307827866648E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14242262294621411</v>
+        <v>0.15121738399450568</v>
       </c>
       <c r="L125" s="22" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16330,7 +16330,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.5256285279634056</v>
+        <v>6.5462947062635024</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1232618942260741</v>
+        <v>1.1268191807746888</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16380,7 +16380,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>519325.15685801161</v>
+        <v>520969.8208534203</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>172.70228419629535</v>
+        <v>173.24921943521377</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16525,7 +16525,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>188.39395633948806</v>
+        <v>188.99058593243666</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18713,23 +18713,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>172.70228419629535</v>
+        <v>173.24921943521377</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>172.70228419629535</v>
+        <v>173.24921943521377</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>172.70228419629535</v>
+        <v>173.24921943521377</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>172.70228419629535</v>
+        <v>173.24921943521377</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>172.70228419629535</v>
+        <v>173.24921943521377</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18744,23 +18744,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>166.14025341308508</v>
+        <v>166.66640719047908</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>167.73639966193628</v>
+        <v>168.26760831532124</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>169.33254591078756</v>
+        <v>169.86880944016346</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>170.92869215963876</v>
+        <v>171.47001056500557</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>174.12098465734121</v>
+        <v>174.67241281468992</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18775,23 +18775,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>165.93925937737157</v>
+        <v>166.46477662166205</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>169.06292564350153</v>
+        <v>169.59833530562261</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>172.21687963156481</v>
+        <v>172.76227763047035</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>175.40112134156155</v>
+        <v>175.95660359620544</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>181.86046792735507</v>
+        <v>182.43640645033727</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18806,23 +18806,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>165.7518523510652</v>
+        <v>166.27677609129645</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>170.31214824618763</v>
+        <v>170.85151410301592</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>174.9600221911852</v>
+        <v>175.51410751775532</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>179.69632139506317</v>
+        <v>180.26540622756752</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>189.43758441548056</v>
+        <v>190.03751910062141</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18837,23 +18837,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>165.57711386499869</v>
+        <v>166.10148422149177</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>171.48857232890364</v>
+        <v>172.03166383296207</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>177.56888504508984</v>
+        <v>178.13123244552278</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>183.82131538583849</v>
+        <v>184.40346376631143</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>196.85574041784116</v>
+        <v>197.47916784915131</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18868,23 +18868,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>162.80040293846062</v>
+        <v>163.31597965877754</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>169.93011855999589</v>
+        <v>170.46827455733296</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>177.33065982871528</v>
+        <v>177.89225278767549</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>185.00988399498536</v>
+        <v>185.59579648349683</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>201.23657324918091</v>
+        <v>201.87387445096505</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18899,23 +18899,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>162.6484902789411</v>
+        <v>163.16358590320814</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>170.97342539425878</v>
+        <v>171.51488546643958</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>179.69036090680328</v>
+        <v>180.25942686288639</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>188.81443287251906</v>
+        <v>189.41239408325211</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>208.34674282452775</v>
+        <v>209.00656140246323</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18931,23 +18931,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>160.06975157616915</v>
+        <v>160.57668052751075</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>169.44499184298769</v>
+        <v>169.98161148023487</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>179.34828722167353</v>
+        <v>179.91626985593737</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>189.80513901715872</v>
+        <v>190.40623772027894</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>212.48650567530765</v>
+        <v>213.15943457308859</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18962,23 +18962,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>159.93768303968471</v>
+        <v>160.4441937398324</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>170.37024419578438</v>
+        <v>170.90979403814723</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>181.48262294177303</v>
+        <v>182.05736485789836</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>193.31413616816354</v>
+        <v>193.92634760325535</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>219.3014757802907</v>
+        <v>219.99598717954194</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18994,23 +18994,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>157.54219237872729</v>
+        <v>158.04111673881542</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>168.87696106400477</v>
+        <v>169.41178179018797</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>181.05281615003636</v>
+        <v>181.62619690014458</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>194.12653239199679</v>
+        <v>194.74131662527043</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>223.21141905857201</v>
+        <v>223.91831295624254</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19026,23 +19026,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>157.42737575722717</v>
+        <v>157.92593650164798</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>169.69751728796609</v>
+        <v>170.23493665444227</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>182.98331023184772</v>
+        <v>183.56280471256918</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>197.36293739088384</v>
+        <v>197.98797107713685</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>229.74344576196432</v>
+        <v>230.47102610047878</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19058,23 +19058,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>151.02350906938355</v>
+        <v>151.50178924616034</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>166.8376683269604</v>
+        <v>167.3660307653129</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>184.62760994332618</v>
+        <v>185.21231179845924</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>204.63942867028314</v>
+        <v>205.28750646110549</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>252.46131471048452</v>
+        <v>253.26084084368779</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19090,23 +19090,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>147.37514238506424</v>
+        <v>147.84186845696377</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>165.77356294389728</v>
+        <v>166.29855543995498</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>187.17827844826084</v>
+        <v>187.7710580800987</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>212.10342275319934</v>
+        <v>212.77513845596957</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>275.01674999045446</v>
+        <v>275.88770750304667</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19122,23 +19122,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>142.95955294456326</v>
+        <v>143.41229517440277</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>162.99483768549783</v>
+        <v>163.51103016614076</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>187.02021838685138</v>
+        <v>187.61249745427662</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>215.90110181257162</v>
+        <v>216.58484448136224</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>292.67568184003255</v>
+        <v>293.60256387125605</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19154,23 +19154,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>140.45707103981428</v>
+        <v>140.90188809631383</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>161.71745576897752</v>
+        <v>162.2296028764689</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>187.88638911142866</v>
+        <v>188.48141127686441</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>220.24493738081412</v>
+        <v>220.94243665250897</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>310.4675273272378</v>
+        <v>311.45075480465863</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>229.74344576196432</v>
+        <v>230.47102610047878</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19245,7 +19245,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>197.36293739088384</v>
+        <v>197.98797107713685</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19273,7 +19273,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>182.98331023184772</v>
+        <v>183.56280471256918</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>169.69751728796609</v>
+        <v>170.23493665444227</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>157.42737575722717</v>
+        <v>157.92593650164798</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19689,7 +19689,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>197.36293739088384</v>
+        <v>197.98797107713685</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19713,7 +19713,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>182.98331023184772</v>
+        <v>183.56280471256918</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19736,7 +19736,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>169.69751728796609</v>
+        <v>170.23493665444227</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>182.53778742768455</v>
+        <v>183.11587097095099</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19799,7 +19799,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>229.74344576196432</v>
+        <v>230.47102610047878</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19822,7 +19822,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>157.42737575722717</v>
+        <v>157.92593650164798</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19867,7 +19867,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>115.2</v>
+        <v>108.5</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.20425434714922333</v>
+        <v>0.23040202190361286</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>172.70228419629535</v>
+        <v>173.24921943521377</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19898,7 +19898,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>4.9113890339692497E-2</v>
+        <v>4.9051495980330033E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19907,7 +19907,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>188.36311559430365</v>
+        <v>188.95964751691497</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20010,7 +20010,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>188.39395633948806</v>
+        <v>188.99058593243666</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>3.4643876575169347E-2</v>
+        <v>3.4643876575169319E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20155,11 +20155,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>86.803279075715992</v>
+        <v>87.078178579223504</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>93.226058107862514</v>
+        <v>93.500957611370026</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20167,7 +20167,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.50507264750996828</v>
+        <v>0.50518029198270931</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20180,11 +20180,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>108.80179962125847</v>
+        <v>109.14636679677403</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>116.18685347617293</v>
+        <v>116.53142065168849</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20192,7 +20192,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.3831761960955451</v>
+        <v>0.38329996809897182</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20226,11 +20226,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>135.01122076286578</v>
+        <v>135.43879121816255</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>143.47945773491043</v>
+        <v>143.9070281902072</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20238,7 +20238,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.23828262618072005</v>
+        <v>0.23842455211330149</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20251,11 +20251,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>152.6876681696564</v>
+        <v>153.17121861404627</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>161.85710521703368</v>
+        <v>162.34065566142357</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20263,7 +20263,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.14071762560117451</v>
+        <v>0.14087130350467325</v>
       </c>
     </row>
   </sheetData>
@@ -20374,7 +20374,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>115.2</v>
+        <v>108.5</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20392,14 +20392,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>346412.66239445761</v>
+        <v>326265.39817533549</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.20425434714922333</v>
+        <v>0.23040202190361286</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20407,13 +20407,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="472" t="s">
+      <c r="B12" s="475" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="472"/>
-      <c r="D12" s="472"/>
-      <c r="E12" s="472"/>
-      <c r="F12" s="472"/>
+      <c r="C12" s="475"/>
+      <c r="D12" s="475"/>
+      <c r="E12" s="475"/>
+      <c r="F12" s="475"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20451,7 +20451,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1232618942260741</v>
+        <v>1.1268191807746888</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>188.36311559430365</v>
+        <v>188.95964751691497</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>93.226058107862514</v>
+        <v>93.500957611370026</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>116.18685347617293</v>
+        <v>116.53142065168849</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20561,7 +20561,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>143.47945773491043</v>
+        <v>143.9070281902072</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>161.85710521703368</v>
+        <v>162.34065566142357</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20598,22 +20598,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="472" t="s">
+      <c r="B29" s="475" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="472"/>
-      <c r="D29" s="472"/>
-      <c r="E29" s="472"/>
-      <c r="F29" s="472"/>
+      <c r="C29" s="475"/>
+      <c r="D29" s="475"/>
+      <c r="E29" s="475"/>
+      <c r="F29" s="475"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="478" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="478"/>
+      <c r="D30" s="478"/>
+      <c r="E30" s="478"/>
+      <c r="F30" s="478"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20803,10 +20803,10 @@
       <c r="B54" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="474"/>
-      <c r="D54" s="474"/>
-      <c r="E54" s="474"/>
-      <c r="F54" s="474"/>
+      <c r="C54" s="477"/>
+      <c r="D54" s="477"/>
+      <c r="E54" s="477"/>
+      <c r="F54" s="477"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20822,22 +20822,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="472" t="s">
+      <c r="B57" s="475" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="472"/>
-      <c r="D57" s="472"/>
-      <c r="E57" s="472"/>
-      <c r="F57" s="472"/>
+      <c r="C57" s="475"/>
+      <c r="D57" s="475"/>
+      <c r="E57" s="475"/>
+      <c r="F57" s="475"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="472" t="s">
+      <c r="B58" s="475" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="472"/>
-      <c r="D58" s="472"/>
-      <c r="E58" s="472"/>
-      <c r="F58" s="472"/>
+      <c r="C58" s="475"/>
+      <c r="D58" s="475"/>
+      <c r="E58" s="475"/>
+      <c r="F58" s="475"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20871,7 +20871,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.4246616477629909E-2</v>
+        <v>7.9081083837262922E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20881,7 +20881,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.0468749999999996E-2</v>
+        <v>3.2350230414746543E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20972,22 +20972,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="472" t="s">
+      <c r="B73" s="475" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="472"/>
-      <c r="D73" s="472"/>
-      <c r="E73" s="472"/>
-      <c r="F73" s="472"/>
+      <c r="C73" s="475"/>
+      <c r="D73" s="475"/>
+      <c r="E73" s="475"/>
+      <c r="F73" s="475"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="478" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="478"/>
+      <c r="D74" s="478"/>
+      <c r="E74" s="478"/>
+      <c r="F74" s="478"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20995,13 +20995,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="472" t="s">
+      <c r="B77" s="475" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="472"/>
-      <c r="D77" s="472"/>
-      <c r="E77" s="472"/>
-      <c r="F77" s="472"/>
+      <c r="C77" s="475"/>
+      <c r="D77" s="475"/>
+      <c r="E77" s="475"/>
+      <c r="F77" s="475"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21022,7 +21022,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-41.869978837828064</v>
+        <v>-42.002577934509091</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21084,7 +21084,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>11.589853064698382</v>
+        <v>11.626557263976748</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21115,7 +21115,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>36.805754301093096</v>
+        <v>36.922315376795837</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21128,7 +21128,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>6.5256285279634056</v>
+        <v>6.5462947062635024</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21150,33 +21150,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="472" t="s">
+      <c r="B96" s="475" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="472"/>
-      <c r="D96" s="472"/>
-      <c r="E96" s="472"/>
-      <c r="F96" s="472"/>
+      <c r="C96" s="475"/>
+      <c r="D96" s="475"/>
+      <c r="E96" s="475"/>
+      <c r="F96" s="475"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="478" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="478"/>
+      <c r="D97" s="478"/>
+      <c r="E97" s="478"/>
+      <c r="F97" s="478"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="478" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="478"/>
+      <c r="D98" s="478"/>
+      <c r="E98" s="478"/>
+      <c r="F98" s="478"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21239,23 +21239,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="472" t="s">
+      <c r="B107" s="475" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="472"/>
-      <c r="D107" s="472"/>
-      <c r="E107" s="472"/>
-      <c r="F107" s="472"/>
+      <c r="C107" s="475"/>
+      <c r="D107" s="475"/>
+      <c r="E107" s="475"/>
+      <c r="F107" s="475"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="472" t="s">
+      <c r="B108" s="475" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="472"/>
-      <c r="D108" s="472"/>
-      <c r="E108" s="472"/>
-      <c r="F108" s="472"/>
+      <c r="C108" s="475"/>
+      <c r="D108" s="475"/>
+      <c r="E108" s="475"/>
+      <c r="F108" s="475"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-64.819799197819449</v>
+        <v>-65.025078661990335</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21287,7 +21287,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>172.70228419629535</v>
+        <v>173.24921943521377</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21299,13 +21299,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="472" t="s">
+      <c r="B114" s="475" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="472"/>
-      <c r="D114" s="472"/>
-      <c r="E114" s="472"/>
-      <c r="F114" s="472"/>
+      <c r="C114" s="475"/>
+      <c r="D114" s="475"/>
+      <c r="E114" s="475"/>
+      <c r="F114" s="475"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,7 +21350,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>229.74 HKD</v>
+        <v>230.47 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21373,7 +21373,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>197.36 HKD</v>
+        <v>197.99 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21395,7 +21395,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>182.98 HKD</v>
+        <v>183.56 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>169.7 HKD</v>
+        <v>170.23 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>157.43 HKD</v>
+        <v>157.93 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21461,7 +21461,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>188.36311559430365</v>
+        <v>188.95964751691497</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21469,13 +21469,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="476" t="s">
+      <c r="B127" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="476"/>
-      <c r="D127" s="476"/>
-      <c r="E127" s="476"/>
-      <c r="F127" s="476"/>
+      <c r="C127" s="473"/>
+      <c r="D127" s="473"/>
+      <c r="E127" s="473"/>
+      <c r="F127" s="473"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21488,22 +21488,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="477" t="s">
+      <c r="B131" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="477"/>
-      <c r="D131" s="477"/>
-      <c r="E131" s="477"/>
-      <c r="F131" s="477"/>
+      <c r="C131" s="474"/>
+      <c r="D131" s="474"/>
+      <c r="E131" s="474"/>
+      <c r="F131" s="474"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="472" t="s">
+      <c r="B132" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="472"/>
-      <c r="D132" s="472"/>
-      <c r="E132" s="472"/>
-      <c r="F132" s="472"/>
+      <c r="C132" s="475"/>
+      <c r="D132" s="475"/>
+      <c r="E132" s="475"/>
+      <c r="F132" s="475"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21568,11 +21568,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>86.803279075715992</v>
+        <v>87.078178579223504</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>93.226058107862514</v>
+        <v>93.500957611370026</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21589,11 +21589,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>108.80179962125847</v>
+        <v>109.14636679677403</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>116.18685347617293</v>
+        <v>116.53142065168849</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21629,11 +21629,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>135.01122076286578</v>
+        <v>135.43879121816255</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>143.47945773491043</v>
+        <v>143.9070281902072</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21650,11 +21650,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>152.6876681696564</v>
+        <v>153.17121861404627</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>161.85710521703368</v>
+        <v>162.34065566142357</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21672,13 +21672,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="478" t="s">
+      <c r="B149" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="472"/>
-      <c r="D149" s="472"/>
-      <c r="E149" s="472"/>
-      <c r="F149" s="472"/>
+      <c r="C149" s="475"/>
+      <c r="D149" s="475"/>
+      <c r="E149" s="475"/>
+      <c r="F149" s="475"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21686,13 +21686,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="474" t="s">
+      <c r="B152" s="477" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="474"/>
-      <c r="D152" s="474"/>
-      <c r="E152" s="474"/>
-      <c r="F152" s="474"/>
+      <c r="C152" s="477"/>
+      <c r="D152" s="477"/>
+      <c r="E152" s="477"/>
+      <c r="F152" s="477"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21729,22 +21729,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="475" t="s">
+      <c r="B161" s="472" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="475"/>
-      <c r="D161" s="475"/>
-      <c r="E161" s="475"/>
-      <c r="F161" s="475"/>
+      <c r="C161" s="472"/>
+      <c r="D161" s="472"/>
+      <c r="E161" s="472"/>
+      <c r="F161" s="472"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="475" t="s">
+      <c r="B162" s="472" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="475"/>
-      <c r="D162" s="475"/>
-      <c r="E162" s="475"/>
-      <c r="F162" s="475"/>
+      <c r="C162" s="472"/>
+      <c r="D162" s="472"/>
+      <c r="E162" s="472"/>
+      <c r="F162" s="472"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21768,15 +21768,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21791,12 +21788,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9618.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9618.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F8AC17-229E-45EB-BC91-8BAD1014AC8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84DB05B6-4FFE-4775-A730-4E27DFE9D6E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4995,30 +4995,30 @@
     <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5028,6 +5028,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5037,16 +5046,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5416,7 +5416,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>108.5</v>
+        <v>108.8</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5435,14 +5435,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>326265.39817533549</v>
+        <v>327167.51448365441</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.23040202190361286</v>
+        <v>0.2287790804195324</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5450,13 +5450,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="463" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="463"/>
-      <c r="D12" s="463"/>
-      <c r="E12" s="463"/>
-      <c r="F12" s="463"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5491,7 +5491,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1268191807746888</v>
+        <v>1.1254930708885194</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>188.95964751691497</v>
+        <v>188.73726822045415</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>93.500957611370026</v>
+        <v>93.398478672908823</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>116.53142065168849</v>
+        <v>116.40297051654868</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>143.9070281902072</v>
+        <v>143.74763551827758</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>162.34065566142357</v>
+        <v>162.16039438193326</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5634,22 +5634,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="463" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="463"/>
-      <c r="D29" s="463"/>
-      <c r="E29" s="463"/>
-      <c r="F29" s="463"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="467" t="s">
+      <c r="B30" s="463" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="467"/>
-      <c r="D30" s="467"/>
-      <c r="E30" s="467"/>
-      <c r="F30" s="467"/>
+      <c r="C30" s="463"/>
+      <c r="D30" s="463"/>
+      <c r="E30" s="463"/>
+      <c r="F30" s="463"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5661,13 +5661,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="464" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="464"/>
-      <c r="D33" s="464"/>
-      <c r="E33" s="464"/>
-      <c r="F33" s="464"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5687,13 +5687,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="464" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="464"/>
-      <c r="D36" s="464"/>
-      <c r="E36" s="464"/>
-      <c r="F36" s="464"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5722,13 +5722,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="464" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="464"/>
-      <c r="D40" s="464"/>
-      <c r="E40" s="464"/>
-      <c r="F40" s="464"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5744,13 +5744,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="464" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="464"/>
-      <c r="D43" s="464"/>
-      <c r="E43" s="464"/>
-      <c r="F43" s="464"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5814,13 +5814,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="464" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="464"/>
-      <c r="D51" s="464"/>
-      <c r="E51" s="464"/>
-      <c r="F51" s="464"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5836,7 +5836,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="464" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5858,22 +5858,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="463" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="463"/>
-      <c r="D57" s="463"/>
-      <c r="E57" s="463"/>
-      <c r="F57" s="463"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="463" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="463"/>
-      <c r="D58" s="463"/>
-      <c r="E58" s="463"/>
-      <c r="F58" s="463"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.9081083837262922E-2</v>
+        <v>7.8770218530861663E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.2350230414746543E-2</v>
+        <v>3.2261029411764702E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6008,13 +6008,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="463" t="s">
+      <c r="B73" s="461" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="463"/>
-      <c r="D73" s="463"/>
-      <c r="E73" s="463"/>
-      <c r="F73" s="463"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6033,13 +6033,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="463" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="463"/>
-      <c r="D77" s="463"/>
-      <c r="E77" s="463"/>
-      <c r="F77" s="463"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-42.002577934509091</v>
+        <v>-41.953146726029601</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>11.626557263976748</v>
+        <v>11.612874418678294</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>36.922315376795837</v>
+        <v>36.87886293271535</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.5462947062635024</v>
+        <v>6.5385906253640389</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6208,31 +6208,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="463" t="s">
+      <c r="B96" s="461" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="463"/>
-      <c r="D96" s="463"/>
-      <c r="E96" s="463"/>
-      <c r="F96" s="463"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="467" t="s">
+      <c r="B97" s="463" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="467"/>
-      <c r="D97" s="467"/>
-      <c r="E97" s="467"/>
-      <c r="F97" s="467"/>
+      <c r="C97" s="463"/>
+      <c r="D97" s="463"/>
+      <c r="E97" s="463"/>
+      <c r="F97" s="463"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="467" t="s">
+      <c r="B98" s="463" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="467"/>
-      <c r="D98" s="467"/>
-      <c r="E98" s="467"/>
-      <c r="F98" s="467"/>
+      <c r="C98" s="463"/>
+      <c r="D98" s="463"/>
+      <c r="E98" s="463"/>
+      <c r="F98" s="463"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6282,22 +6282,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="463" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="463"/>
-      <c r="D107" s="463"/>
-      <c r="E107" s="463"/>
-      <c r="F107" s="463"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="463" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="463"/>
-      <c r="D108" s="463"/>
-      <c r="E108" s="463"/>
-      <c r="F108" s="463"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-65.025078661990335</v>
+        <v>-64.948553163371002</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>173.24921943521377</v>
+        <v>173.04532913357176</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6331,13 +6331,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="463" t="s">
+      <c r="B114" s="461" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="463"/>
-      <c r="D114" s="463"/>
-      <c r="E114" s="463"/>
-      <c r="F114" s="463"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>230.47 HKD</v>
+        <v>230.2 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.7770399690866813E-2</v>
+        <v>-4.7751228354903356E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>197.99 HKD</v>
+        <v>197.75 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.5671832081474487E-3</v>
+        <v>2.5883928833457955E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>183.56 HKD</v>
+        <v>183.35 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.8646242962904404E-2</v>
+        <v>2.8668562302364944E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>170.23 HKD</v>
+        <v>170.03 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.532726134963737E-2</v>
+        <v>5.5350754741792782E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>157.93 HKD</v>
+        <v>157.74 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6468,17 +6468,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>8.2603522450848801E-2</v>
+        <v>8.2628257345110617E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="464" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="464"/>
-      <c r="D124" s="464"/>
-      <c r="E124" s="464"/>
-      <c r="F124" s="464"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>188.95964751691497</v>
+        <v>188.73726822045415</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6513,22 +6513,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="468" t="s">
+      <c r="B131" s="464" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="468"/>
-      <c r="D131" s="468"/>
-      <c r="E131" s="468"/>
-      <c r="F131" s="468"/>
+      <c r="C131" s="464"/>
+      <c r="D131" s="464"/>
+      <c r="E131" s="464"/>
+      <c r="F131" s="464"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="463" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="463"/>
-      <c r="D132" s="463"/>
-      <c r="E132" s="463"/>
-      <c r="F132" s="463"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6593,11 +6593,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>87.078178579223504</v>
+        <v>86.975699640762301</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>93.500957611370026</v>
+        <v>93.398478672908823</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6614,11 +6614,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>109.14636679677403</v>
+        <v>109.01791666163422</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>116.53142065168849</v>
+        <v>116.40297051654868</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6661,11 +6661,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>135.43879121816255</v>
+        <v>135.27939854623293</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>143.9070281902072</v>
+        <v>143.74763551827758</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6682,11 +6682,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>153.17121861404627</v>
+        <v>152.99095733455596</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>162.34065566142357</v>
+        <v>162.16039438193326</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6704,13 +6704,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="462" t="s">
+      <c r="B149" s="468" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="463"/>
-      <c r="D149" s="463"/>
-      <c r="E149" s="463"/>
-      <c r="F149" s="463"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6747,13 +6747,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="464" t="s">
+      <c r="B158" s="462" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="464"/>
-      <c r="D158" s="464"/>
-      <c r="E158" s="464"/>
-      <c r="F158" s="464"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6761,22 +6761,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="461" t="s">
+      <c r="B161" s="467" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="461"/>
-      <c r="D161" s="461"/>
-      <c r="E161" s="461"/>
-      <c r="F161" s="461"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="461" t="s">
+      <c r="B162" s="467" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="461"/>
-      <c r="D162" s="461"/>
-      <c r="E162" s="461"/>
-      <c r="F162" s="461"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6800,6 +6800,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6816,18 +6828,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10079,11 +10079,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>86.911150140375028</v>
+        <v>86.808867771219511</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-65.025078661990335</v>
+        <v>-64.948553163371002</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10489,11 +10489,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-126304.03515385409</v>
+        <v>-126155.39282282324</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-42.002577934509084</v>
+        <v>-41.953146726029601</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10506,11 +10506,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>34961.689724789991</v>
+        <v>34920.544665163514</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>11.626557263976752</v>
+        <v>11.612874418678294</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10523,11 +10523,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>111027.4094743374</v>
+        <v>110896.74561286632</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>36.922315376795837</v>
+        <v>36.87886293271535</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10540,11 +10540,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>19685.064045273306</v>
+        <v>19661.897455206592</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.5462947062635024</v>
+        <v>6.5385906253640442</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14128,20 +14128,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.2350230414746543E-2</v>
+        <v>3.2261029411764702E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.2350230414746543E-2</v>
+        <v>3.2261029411764702E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>2.4586175115207377E-2</v>
+        <v>2.4518382352941178E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>2.0057142857142857E-2</v>
+        <v>2.0001838235294118E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
@@ -15291,30 +15291,30 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>8.5802975963430281</v>
+        <v>8.5701997761577484</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.800330997942893</v>
+        <v>10.787620506362135</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>6.987126909570577</v>
+        <v>6.9789040303111634</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>3.6974139878114816</v>
+        <v>3.6930626443784322</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>4.7215380811213813E-2</v>
+        <v>4.7159814856763196E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.6383490768349569</v>
+        <v>4.6328903833096424</v>
       </c>
       <c r="L123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15348,30 +15348,30 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.9081083837262922E-2</v>
+        <v>7.8770218530861663E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>9.9542221179197171E-2</v>
+        <v>9.9150923771710794E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.4397483037516842E-2</v>
+        <v>6.4144338513889371E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.40775482747602E-2</v>
+        <v>3.3943590481419414E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>4.3516480010335313E-4</v>
+        <v>4.3345418066877942E-4</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>4.2749761076819881E-2</v>
+        <v>4.2581713081890099E-2</v>
       </c>
       <c r="L124" s="74" t="str">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
@@ -15405,23 +15405,23 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13688242838426787</v>
+        <v>0.13650499521776713</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1282459402886647E-2</v>
+        <v>7.1085908503797798E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9702812661709356E-2</v>
+        <v>2.9620911523855376E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-1.3691307827866648E-2</v>
+        <v>-1.3653556059958927E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15121738399450568</v>
+        <v>0.15080042429599141</v>
       </c>
       <c r="L125" s="22" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16330,7 +16330,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.5462947062635024</v>
+        <v>6.5385906253640389</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1268191807746888</v>
+        <v>1.1254930708885194</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16380,7 +16380,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>520969.8208534203</v>
+        <v>520356.71163268923</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>173.24921943521377</v>
+        <v>173.04532913357176</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16525,7 +16525,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>188.99058593243666</v>
+        <v>188.7681702257519</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18713,23 +18713,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>173.24921943521377</v>
+        <v>173.04532913357176</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>173.24921943521377</v>
+        <v>173.04532913357176</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>173.24921943521377</v>
+        <v>173.04532913357176</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>173.24921943521377</v>
+        <v>173.04532913357176</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>173.24921943521377</v>
+        <v>173.04532913357176</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18744,23 +18744,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>166.66640719047908</v>
+        <v>166.47026394581431</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>168.26760831532124</v>
+        <v>168.06958067901883</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>169.86880944016346</v>
+        <v>169.66889741222337</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>171.47001056500557</v>
+        <v>171.26821414542786</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>174.67241281468992</v>
+        <v>174.4668476118369</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18775,23 +18775,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>166.46477662166205</v>
+        <v>166.26887066821067</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>169.59833530562261</v>
+        <v>169.3987415882242</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>172.76227763047035</v>
+        <v>172.55896039179379</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>175.95660359620544</v>
+        <v>175.74952707891958</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>182.43640645033727</v>
+        <v>182.2217041038395</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18806,23 +18806,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>166.27677609129645</v>
+        <v>166.08109138839367</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>170.85151410301592</v>
+        <v>170.65044556798864</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>175.51410751775532</v>
+        <v>175.30755175697968</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>180.26540622756752</v>
+        <v>180.05325884721466</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>190.03751910062141</v>
+        <v>189.8138712988071</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18837,23 +18837,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>166.10148422149177</v>
+        <v>165.9060058128068</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>172.03166383296207</v>
+        <v>171.82920642538917</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>178.13123244552278</v>
+        <v>177.92159669170189</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>184.40346376631143</v>
+        <v>184.18644646618324</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>197.47916784915131</v>
+        <v>197.24676225891525</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18868,23 +18868,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>163.31597965877754</v>
+        <v>163.12377940261393</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>170.46827455733296</v>
+        <v>170.26765704209569</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>177.89225278767549</v>
+        <v>177.68289827976542</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>185.59579648349683</v>
+        <v>185.37737597313682</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>201.87387445096505</v>
+        <v>201.63629690060358</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18899,23 +18899,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>163.16358590320814</v>
+        <v>162.97156499335787</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>171.51488546643958</v>
+        <v>171.31303623532699</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>180.25942686288639</v>
+        <v>180.04728651941639</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>189.41239408325211</v>
+        <v>189.18948196687853</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>209.00656140246323</v>
+        <v>208.76058966886217</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18931,23 +18931,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>160.57668052751075</v>
+        <v>160.3877040464844</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>169.98161148023487</v>
+        <v>169.78156669993928</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>179.91626985593737</v>
+        <v>179.70453336066876</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>190.40623772027894</v>
+        <v>190.18215598779051</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>213.15943457308859</v>
+        <v>212.9085754837684</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18962,23 +18962,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>160.4441937398324</v>
+        <v>160.25537317737925</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>170.90979403814723</v>
+        <v>170.70865691571967</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>182.05736485789836</v>
+        <v>181.8431085907819</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>193.92634760325535</v>
+        <v>193.6981231896732</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>219.99598717954194</v>
+        <v>219.73708241603248</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18994,23 +18994,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>158.04111673881542</v>
+        <v>157.85512426468614</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>169.41178179018797</v>
+        <v>169.21240762040227</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>181.62619690014458</v>
+        <v>181.41244805791149</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>194.74131662527043</v>
+        <v>194.51213310618542</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>223.91831295624254</v>
+        <v>223.65479215931973</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19026,23 +19026,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>157.92593650164798</v>
+        <v>157.74007957868238</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>170.23493665444227</v>
+        <v>170.03459374555277</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>183.56280471256918</v>
+        <v>183.34677675154799</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>197.98797107713685</v>
+        <v>197.75496669607236</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>230.47102610047878</v>
+        <v>230.19979366904525</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19058,23 +19058,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>151.50178924616034</v>
+        <v>151.32349265348648</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>167.3660307653129</v>
+        <v>167.1690641607382</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>185.21231179845924</v>
+        <v>184.99434259638429</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>205.28750646110549</v>
+        <v>205.04591153933822</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>253.26084084368779</v>
+        <v>252.9627879612444</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19090,23 +19090,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>147.84186845696377</v>
+        <v>147.66787908342849</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>166.29855543995498</v>
+        <v>166.10284510577964</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>187.7710580800987</v>
+        <v>187.55007758854785</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>212.77513845596957</v>
+        <v>212.52473162987741</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>275.88770750304667</v>
+        <v>275.56302593688724</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19122,23 +19122,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>143.41229517440277</v>
+        <v>143.24351879424009</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>163.51103016614076</v>
+        <v>163.31860036258348</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>187.61249745427662</v>
+        <v>187.39170356659002</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>216.58484448136224</v>
+        <v>216.32995415968372</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>293.60256387125605</v>
+        <v>293.25703437619836</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19154,23 +19154,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>140.90188809631383</v>
+        <v>140.73606611708908</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>162.2296028764689</v>
+        <v>162.03868113509782</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>188.48141127686441</v>
+        <v>188.25959479812681</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>220.94243665250897</v>
+        <v>220.68241804924219</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>311.45075480465863</v>
+        <v>311.08422046441302</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>230.47102610047878</v>
+        <v>230.19979366904525</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19245,7 +19245,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>197.98797107713685</v>
+        <v>197.75496669607236</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19273,7 +19273,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>183.56280471256918</v>
+        <v>183.34677675154799</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>170.23493665444227</v>
+        <v>170.03459374555277</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>157.92593650164798</v>
+        <v>157.74007957868238</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19689,7 +19689,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>197.98797107713685</v>
+        <v>197.75496669607236</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19713,7 +19713,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>183.56280471256918</v>
+        <v>183.34677675154799</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19736,7 +19736,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>170.23493665444227</v>
+        <v>170.03459374555277</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>183.11587097095099</v>
+        <v>182.90036898895406</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19799,7 +19799,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>230.47102610047878</v>
+        <v>230.19979366904525</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19822,7 +19822,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>157.92593650164798</v>
+        <v>157.74007957868238</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19867,7 +19867,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>108.5</v>
+        <v>108.8</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.23040202190361286</v>
+        <v>0.2287790804195324</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>173.24921943521377</v>
+        <v>173.04532913357176</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19898,7 +19898,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>4.9051495980330033E-2</v>
+        <v>4.9074709654442515E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19907,7 +19907,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>188.95964751691497</v>
+        <v>188.73726822045415</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20010,7 +20010,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>188.99058593243666</v>
+        <v>188.7681702257519</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>3.4643876575169319E-2</v>
+        <v>3.464387657516934E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20155,11 +20155,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>87.078178579223504</v>
+        <v>86.975699640762301</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>93.500957611370026</v>
+        <v>93.398478672908823</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20167,7 +20167,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.50518029198270931</v>
+        <v>0.50514024308217209</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20180,11 +20180,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>109.14636679677403</v>
+        <v>109.01791666163422</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>116.53142065168849</v>
+        <v>116.40297051654868</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20192,7 +20192,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.38329996809897182</v>
+        <v>0.38325391898443484</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20226,11 +20226,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>135.43879121816255</v>
+        <v>135.27939854623293</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>143.9070281902072</v>
+        <v>143.74763551827758</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20238,7 +20238,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.23842455211330149</v>
+        <v>0.23837174886746026</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20251,11 +20251,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>153.17121861404627</v>
+        <v>152.99095733455596</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>162.34065566142357</v>
+        <v>162.16039438193326</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20263,7 +20263,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.14087130350467325</v>
+        <v>0.14081412796267578</v>
       </c>
     </row>
   </sheetData>
@@ -20374,7 +20374,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>108.5</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20392,14 +20392,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>326265.39817533549</v>
+        <v>327167.51448365441</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.23040202190361286</v>
+        <v>0.2287790804195324</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20407,13 +20407,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="475" t="s">
+      <c r="B12" s="472" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="475"/>
-      <c r="D12" s="475"/>
-      <c r="E12" s="475"/>
-      <c r="F12" s="475"/>
+      <c r="C12" s="472"/>
+      <c r="D12" s="472"/>
+      <c r="E12" s="472"/>
+      <c r="F12" s="472"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20451,7 +20451,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1268191807746888</v>
+        <v>1.1254930708885194</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>188.95964751691497</v>
+        <v>188.73726822045415</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>93.500957611370026</v>
+        <v>93.398478672908823</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>116.53142065168849</v>
+        <v>116.40297051654868</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20561,7 +20561,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>143.9070281902072</v>
+        <v>143.74763551827758</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>162.34065566142357</v>
+        <v>162.16039438193326</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20598,22 +20598,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="475" t="s">
+      <c r="B29" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="475"/>
-      <c r="D29" s="475"/>
-      <c r="E29" s="475"/>
-      <c r="F29" s="475"/>
+      <c r="C29" s="472"/>
+      <c r="D29" s="472"/>
+      <c r="E29" s="472"/>
+      <c r="F29" s="472"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="478" t="s">
+      <c r="B30" s="473" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="478"/>
-      <c r="D30" s="478"/>
-      <c r="E30" s="478"/>
-      <c r="F30" s="478"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20803,10 +20803,10 @@
       <c r="B54" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="477"/>
-      <c r="D54" s="477"/>
-      <c r="E54" s="477"/>
-      <c r="F54" s="477"/>
+      <c r="C54" s="474"/>
+      <c r="D54" s="474"/>
+      <c r="E54" s="474"/>
+      <c r="F54" s="474"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20822,22 +20822,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="475" t="s">
+      <c r="B57" s="472" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="475"/>
-      <c r="D57" s="475"/>
-      <c r="E57" s="475"/>
-      <c r="F57" s="475"/>
+      <c r="C57" s="472"/>
+      <c r="D57" s="472"/>
+      <c r="E57" s="472"/>
+      <c r="F57" s="472"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="475" t="s">
+      <c r="B58" s="472" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="475"/>
-      <c r="D58" s="475"/>
-      <c r="E58" s="475"/>
-      <c r="F58" s="475"/>
+      <c r="C58" s="472"/>
+      <c r="D58" s="472"/>
+      <c r="E58" s="472"/>
+      <c r="F58" s="472"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20871,7 +20871,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.9081083837262922E-2</v>
+        <v>7.8770218530861663E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20881,7 +20881,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.2350230414746543E-2</v>
+        <v>3.2261029411764702E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20972,22 +20972,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="475" t="s">
+      <c r="B73" s="472" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="475"/>
-      <c r="D73" s="475"/>
-      <c r="E73" s="475"/>
-      <c r="F73" s="475"/>
+      <c r="C73" s="472"/>
+      <c r="D73" s="472"/>
+      <c r="E73" s="472"/>
+      <c r="F73" s="472"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="478" t="s">
+      <c r="B74" s="473" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="478"/>
-      <c r="D74" s="478"/>
-      <c r="E74" s="478"/>
-      <c r="F74" s="478"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20995,13 +20995,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="475" t="s">
+      <c r="B77" s="472" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="475"/>
-      <c r="D77" s="475"/>
-      <c r="E77" s="475"/>
-      <c r="F77" s="475"/>
+      <c r="C77" s="472"/>
+      <c r="D77" s="472"/>
+      <c r="E77" s="472"/>
+      <c r="F77" s="472"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21022,7 +21022,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-42.002577934509091</v>
+        <v>-41.953146726029601</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21084,7 +21084,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>11.626557263976748</v>
+        <v>11.612874418678294</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21115,7 +21115,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>36.922315376795837</v>
+        <v>36.87886293271535</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21128,7 +21128,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>6.5462947062635024</v>
+        <v>6.5385906253640389</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21150,33 +21150,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="475" t="s">
+      <c r="B96" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="475"/>
-      <c r="D96" s="475"/>
-      <c r="E96" s="475"/>
-      <c r="F96" s="475"/>
+      <c r="C96" s="472"/>
+      <c r="D96" s="472"/>
+      <c r="E96" s="472"/>
+      <c r="F96" s="472"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="478" t="s">
+      <c r="B97" s="473" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="478"/>
-      <c r="D97" s="478"/>
-      <c r="E97" s="478"/>
-      <c r="F97" s="478"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="478" t="s">
+      <c r="B98" s="473" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="478"/>
-      <c r="D98" s="478"/>
-      <c r="E98" s="478"/>
-      <c r="F98" s="478"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21239,23 +21239,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="475" t="s">
+      <c r="B107" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="475"/>
-      <c r="D107" s="475"/>
-      <c r="E107" s="475"/>
-      <c r="F107" s="475"/>
+      <c r="C107" s="472"/>
+      <c r="D107" s="472"/>
+      <c r="E107" s="472"/>
+      <c r="F107" s="472"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="475" t="s">
+      <c r="B108" s="472" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="475"/>
-      <c r="D108" s="475"/>
-      <c r="E108" s="475"/>
-      <c r="F108" s="475"/>
+      <c r="C108" s="472"/>
+      <c r="D108" s="472"/>
+      <c r="E108" s="472"/>
+      <c r="F108" s="472"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-65.025078661990335</v>
+        <v>-64.948553163371002</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21287,7 +21287,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>173.24921943521377</v>
+        <v>173.04532913357176</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21299,13 +21299,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="475" t="s">
+      <c r="B114" s="472" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="475"/>
-      <c r="D114" s="475"/>
-      <c r="E114" s="475"/>
-      <c r="F114" s="475"/>
+      <c r="C114" s="472"/>
+      <c r="D114" s="472"/>
+      <c r="E114" s="472"/>
+      <c r="F114" s="472"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,7 +21350,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>230.47 HKD</v>
+        <v>230.2 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21373,7 +21373,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>197.99 HKD</v>
+        <v>197.75 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21395,7 +21395,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>183.56 HKD</v>
+        <v>183.35 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>170.23 HKD</v>
+        <v>170.03 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>157.93 HKD</v>
+        <v>157.74 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21461,7 +21461,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>188.95964751691497</v>
+        <v>188.73726822045415</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21469,13 +21469,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="473" t="s">
+      <c r="B127" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="473"/>
-      <c r="D127" s="473"/>
-      <c r="E127" s="473"/>
-      <c r="F127" s="473"/>
+      <c r="C127" s="476"/>
+      <c r="D127" s="476"/>
+      <c r="E127" s="476"/>
+      <c r="F127" s="476"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21488,22 +21488,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="474" t="s">
+      <c r="B131" s="477" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="474"/>
-      <c r="D131" s="474"/>
-      <c r="E131" s="474"/>
-      <c r="F131" s="474"/>
+      <c r="C131" s="477"/>
+      <c r="D131" s="477"/>
+      <c r="E131" s="477"/>
+      <c r="F131" s="477"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="475" t="s">
+      <c r="B132" s="472" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="475"/>
-      <c r="D132" s="475"/>
-      <c r="E132" s="475"/>
-      <c r="F132" s="475"/>
+      <c r="C132" s="472"/>
+      <c r="D132" s="472"/>
+      <c r="E132" s="472"/>
+      <c r="F132" s="472"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21568,11 +21568,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>87.078178579223504</v>
+        <v>86.975699640762301</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>93.500957611370026</v>
+        <v>93.398478672908823</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21589,11 +21589,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>109.14636679677403</v>
+        <v>109.01791666163422</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>116.53142065168849</v>
+        <v>116.40297051654868</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21629,11 +21629,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>135.43879121816255</v>
+        <v>135.27939854623293</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>143.9070281902072</v>
+        <v>143.74763551827758</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21650,11 +21650,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>153.17121861404627</v>
+        <v>152.99095733455596</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>162.34065566142357</v>
+        <v>162.16039438193326</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21672,13 +21672,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="476" t="s">
+      <c r="B149" s="478" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="475"/>
-      <c r="D149" s="475"/>
-      <c r="E149" s="475"/>
-      <c r="F149" s="475"/>
+      <c r="C149" s="472"/>
+      <c r="D149" s="472"/>
+      <c r="E149" s="472"/>
+      <c r="F149" s="472"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21686,13 +21686,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="477" t="s">
+      <c r="B152" s="474" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="477"/>
-      <c r="D152" s="477"/>
-      <c r="E152" s="477"/>
-      <c r="F152" s="477"/>
+      <c r="C152" s="474"/>
+      <c r="D152" s="474"/>
+      <c r="E152" s="474"/>
+      <c r="F152" s="474"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21729,22 +21729,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="472" t="s">
+      <c r="B161" s="475" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="472"/>
-      <c r="D161" s="472"/>
-      <c r="E161" s="472"/>
-      <c r="F161" s="472"/>
+      <c r="C161" s="475"/>
+      <c r="D161" s="475"/>
+      <c r="E161" s="475"/>
+      <c r="F161" s="475"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="472" t="s">
+      <c r="B162" s="475" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="472"/>
-      <c r="D162" s="472"/>
-      <c r="E162" s="472"/>
-      <c r="F162" s="472"/>
+      <c r="C162" s="475"/>
+      <c r="D162" s="475"/>
+      <c r="E162" s="475"/>
+      <c r="F162" s="475"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21768,12 +21768,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21788,15 +21791,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9618.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9618.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84DB05B6-4FFE-4775-A730-4E27DFE9D6E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522EAEDE-62D3-4AA5-BB32-E90609B7F2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4995,30 +4995,30 @@
     <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5028,25 +5028,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5416,7 +5416,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>108.8</v>
+        <v>106.9</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5435,14 +5435,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>327167.51448365441</v>
+        <v>321454.11119763477</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.2287790804195324</v>
+        <v>0.23628140529661751</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5450,13 +5450,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+      <c r="B12" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="C12" s="463"/>
+      <c r="D12" s="463"/>
+      <c r="E12" s="463"/>
+      <c r="F12" s="463"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5491,7 +5491,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1254930708885194</v>
+        <v>1.1257236004352571</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>188.73726822045415</v>
+        <v>188.77592640327265</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>93.398478672908823</v>
+        <v>93.416293503700757</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>116.40297051654868</v>
+        <v>116.42530015283373</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>143.74763551827758</v>
+        <v>143.77534417258781</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>162.16039438193326</v>
+        <v>162.19173081301534</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5634,22 +5634,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+      <c r="B29" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="463"/>
+      <c r="D29" s="463"/>
+      <c r="E29" s="463"/>
+      <c r="F29" s="463"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="463" t="s">
+      <c r="B30" s="467" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="463"/>
-      <c r="D30" s="463"/>
-      <c r="E30" s="463"/>
-      <c r="F30" s="463"/>
+      <c r="C30" s="467"/>
+      <c r="D30" s="467"/>
+      <c r="E30" s="467"/>
+      <c r="F30" s="467"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5661,13 +5661,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+      <c r="B33" s="464" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="C33" s="464"/>
+      <c r="D33" s="464"/>
+      <c r="E33" s="464"/>
+      <c r="F33" s="464"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5687,13 +5687,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+      <c r="B36" s="464" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="C36" s="464"/>
+      <c r="D36" s="464"/>
+      <c r="E36" s="464"/>
+      <c r="F36" s="464"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5722,13 +5722,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+      <c r="B40" s="464" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="C40" s="464"/>
+      <c r="D40" s="464"/>
+      <c r="E40" s="464"/>
+      <c r="F40" s="464"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5744,13 +5744,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+      <c r="B43" s="464" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="C43" s="464"/>
+      <c r="D43" s="464"/>
+      <c r="E43" s="464"/>
+      <c r="F43" s="464"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5814,13 +5814,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+      <c r="B51" s="464" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="C51" s="464"/>
+      <c r="D51" s="464"/>
+      <c r="E51" s="464"/>
+      <c r="F51" s="464"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5836,7 +5836,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+      <c r="B54" s="464" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5858,22 +5858,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+      <c r="B57" s="463" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="C57" s="463"/>
+      <c r="D57" s="463"/>
+      <c r="E57" s="463"/>
+      <c r="F57" s="463"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="B58" s="463" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="C58" s="463"/>
+      <c r="D58" s="463"/>
+      <c r="E58" s="463"/>
+      <c r="F58" s="463"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.8770218530861663E-2</v>
+        <v>8.0186671380633401E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.2261029411764702E-2</v>
+        <v>3.2834424695977547E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6008,13 +6008,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
+      <c r="B73" s="463" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="C73" s="463"/>
+      <c r="D73" s="463"/>
+      <c r="E73" s="463"/>
+      <c r="F73" s="463"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6033,13 +6033,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="463" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="C77" s="463"/>
+      <c r="D77" s="463"/>
+      <c r="E77" s="463"/>
+      <c r="F77" s="463"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-41.953146726029601</v>
+        <v>-41.961739795279989</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>11.612874418678294</v>
+        <v>11.615253030102302</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>36.87886293271535</v>
+        <v>36.886416659855911</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.5385906253640389</v>
+        <v>6.5399298946782238</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6208,31 +6208,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
+      <c r="B96" s="463" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="C96" s="463"/>
+      <c r="D96" s="463"/>
+      <c r="E96" s="463"/>
+      <c r="F96" s="463"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="463" t="s">
+      <c r="B97" s="467" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="463"/>
-      <c r="D97" s="463"/>
-      <c r="E97" s="463"/>
-      <c r="F97" s="463"/>
+      <c r="C97" s="467"/>
+      <c r="D97" s="467"/>
+      <c r="E97" s="467"/>
+      <c r="F97" s="467"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="463" t="s">
+      <c r="B98" s="467" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="463"/>
-      <c r="D98" s="463"/>
-      <c r="E98" s="463"/>
-      <c r="F98" s="463"/>
+      <c r="C98" s="467"/>
+      <c r="D98" s="467"/>
+      <c r="E98" s="467"/>
+      <c r="F98" s="467"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6282,22 +6282,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="463" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
+      <c r="C107" s="463"/>
+      <c r="D107" s="463"/>
+      <c r="E107" s="463"/>
+      <c r="F107" s="463"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="B108" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="463"/>
+      <c r="D108" s="463"/>
+      <c r="E108" s="463"/>
+      <c r="F108" s="463"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-64.948553163371002</v>
+        <v>-64.961856275499628</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>173.04532913357176</v>
+        <v>173.08077320899264</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6331,13 +6331,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
+      <c r="B114" s="463" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="C114" s="463"/>
+      <c r="D114" s="463"/>
+      <c r="E114" s="463"/>
+      <c r="F114" s="463"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>230.2 HKD</v>
+        <v>230.25 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.7751228354903356E-2</v>
+        <v>-4.7754564320826712E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>197.75 HKD</v>
+        <v>197.8 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.5883928833457955E-3</v>
+        <v>2.5847022280579275E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>183.35 HKD</v>
+        <v>183.38 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.8668562302364944E-2</v>
+        <v>2.8664678555365398E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>170.03 HKD</v>
+        <v>170.07 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.5350754741792782E-2</v>
+        <v>5.5346666698796169E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>157.74 HKD</v>
+        <v>157.77 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6468,17 +6468,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>8.2628257345110617E-2</v>
+        <v>8.2623953269175293E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+      <c r="B124" s="464" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="C124" s="464"/>
+      <c r="D124" s="464"/>
+      <c r="E124" s="464"/>
+      <c r="F124" s="464"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>188.73726822045415</v>
+        <v>188.77592640327265</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6513,22 +6513,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="464" t="s">
+      <c r="B131" s="468" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="464"/>
-      <c r="D131" s="464"/>
-      <c r="E131" s="464"/>
-      <c r="F131" s="464"/>
+      <c r="C131" s="468"/>
+      <c r="D131" s="468"/>
+      <c r="E131" s="468"/>
+      <c r="F131" s="468"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="B132" s="463" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="C132" s="463"/>
+      <c r="D132" s="463"/>
+      <c r="E132" s="463"/>
+      <c r="F132" s="463"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6593,11 +6593,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>86.975699640762301</v>
+        <v>86.993514471554235</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>93.398478672908823</v>
+        <v>93.416293503700757</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6614,11 +6614,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>109.01791666163422</v>
+        <v>109.04024629791927</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>116.40297051654868</v>
+        <v>116.42530015283373</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6661,11 +6661,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>135.27939854623293</v>
+        <v>135.30710720054316</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>143.74763551827758</v>
+        <v>143.77534417258781</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6682,11 +6682,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>152.99095733455596</v>
+        <v>153.02229376563807</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>162.16039438193326</v>
+        <v>162.19173081301534</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6704,13 +6704,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="468" t="s">
+      <c r="B149" s="462" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="C149" s="463"/>
+      <c r="D149" s="463"/>
+      <c r="E149" s="463"/>
+      <c r="F149" s="463"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6747,13 +6747,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
+      <c r="B158" s="464" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="C158" s="464"/>
+      <c r="D158" s="464"/>
+      <c r="E158" s="464"/>
+      <c r="F158" s="464"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6761,22 +6761,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="461" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="461"/>
+      <c r="D161" s="461"/>
+      <c r="E161" s="461"/>
+      <c r="F161" s="461"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="461" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="461"/>
+      <c r="D162" s="461"/>
+      <c r="E162" s="461"/>
+      <c r="F162" s="461"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6800,18 +6800,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6828,6 +6816,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10079,11 +10079,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>86.808867771219511</v>
+        <v>86.826648430610263</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-64.948553163371002</v>
+        <v>-64.961856275499628</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10489,11 +10489,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-126155.39282282324</v>
+        <v>-126181.23264918753</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-41.953146726029601</v>
+        <v>-41.961739795279989</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10506,11 +10506,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>34920.544665163514</v>
+        <v>34927.697279019354</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>11.612874418678294</v>
+        <v>11.615253030102302</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10523,11 +10523,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>110896.74561286632</v>
+        <v>110919.46008100662</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>36.87886293271535</v>
+        <v>36.886416659855911</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10540,11 +10540,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>19661.897455206592</v>
+        <v>19665.924710838444</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.5385906253640442</v>
+        <v>6.5399298946782238</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14128,20 +14128,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.2261029411764702E-2</v>
+        <v>3.2834424695977547E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.2261029411764702E-2</v>
+        <v>3.2834424695977547E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>2.4518382352941178E-2</v>
+        <v>2.4954162768942939E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>2.0001838235294118E-2</v>
+        <v>2.0357343311506081E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
@@ -15291,30 +15291,30 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>8.5701997761577484</v>
+        <v>8.5719551705897103</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.787620506362135</v>
+        <v>10.789830084839368</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>6.9789040303111634</v>
+        <v>6.9803334869861509</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>3.6930626443784322</v>
+        <v>3.6938190773405744</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>4.7159814856763196E-2</v>
+        <v>4.716947438379572E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.6328903833096424</v>
+        <v>4.6338393168462177</v>
       </c>
       <c r="L123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15348,30 +15348,30 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.8770218530861663E-2</v>
+        <v>8.0186671380633401E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>9.9150923771710794E-2</v>
+        <v>0.10093386421739352</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.4144338513889371E-2</v>
+        <v>6.5297787530272683E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.3943590481419414E-2</v>
+        <v>3.4553967047152238E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>4.3345418066877942E-4</v>
+        <v>4.412485910551517E-4</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>4.2581713081890099E-2</v>
+        <v>4.3347421111751334E-2</v>
       </c>
       <c r="L124" s="74" t="str">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
@@ -15405,23 +15405,23 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13650499521776713</v>
+        <v>0.13893118315896222</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1085908503797798E-2</v>
+        <v>7.2349362443528534E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9620911523855376E-2</v>
+        <v>3.0147382355429977E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-1.3653556059958927E-2</v>
+        <v>-1.3896229179827232E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15080042429599141</v>
+        <v>0.15348069376430179</v>
       </c>
       <c r="L125" s="22" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16330,7 +16330,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.5385906253640389</v>
+        <v>6.5399298946782238</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1254930708885194</v>
+        <v>1.1257236004352571</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16380,7 +16380,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>520356.71163268923</v>
+        <v>520463.2938942574</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>173.04532913357176</v>
+        <v>173.08077320899264</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16525,7 +16525,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>188.7681702257519</v>
+        <v>188.8068347380854</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18713,23 +18713,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>173.04532913357176</v>
+        <v>173.08077320899264</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>173.04532913357176</v>
+        <v>173.08077320899264</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>173.04532913357176</v>
+        <v>173.08077320899264</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>173.04532913357176</v>
+        <v>173.08077320899264</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>173.04532913357176</v>
+        <v>173.08077320899264</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18744,23 +18744,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>166.47026394581431</v>
+        <v>166.50436128100486</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>168.06958067901883</v>
+        <v>168.10400559486814</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>169.66889741222337</v>
+        <v>169.70364990873148</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>171.26821414542786</v>
+        <v>171.3032942225947</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>174.4668476118369</v>
+        <v>174.50258285032126</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18775,23 +18775,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>166.26887066821067</v>
+        <v>166.30292675294646</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>169.3987415882242</v>
+        <v>169.43343874996279</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>172.55896039179379</v>
+        <v>172.59430484655195</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>175.74952707891958</v>
+        <v>175.78552504271414</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>182.2217041038395</v>
+        <v>182.25902773375725</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18806,23 +18806,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>166.08109138839367</v>
+        <v>166.11510901116699</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>170.65044556798864</v>
+        <v>170.68539911047142</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>175.30755175697968</v>
+        <v>175.34345919301066</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>180.05325884721466</v>
+        <v>180.09013832450717</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>189.8138712988071</v>
+        <v>189.85274999726101</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18837,23 +18837,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>165.9060058128068</v>
+        <v>165.93998757361044</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>171.82920642538917</v>
+        <v>171.86440140801335</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>177.92159669170189</v>
+        <v>177.95803955048183</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>184.18644646618324</v>
+        <v>184.22417252520339</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>197.24676225891525</v>
+        <v>197.2871634020899</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18868,23 +18868,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>163.12377940261393</v>
+        <v>163.15719129283389</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>170.26765704209569</v>
+        <v>170.30253217977292</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>177.68289827976542</v>
+        <v>177.71929224705227</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>185.37737597313682</v>
+        <v>185.41534596474662</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>201.63629690060358</v>
+        <v>201.67759713188238</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18899,23 +18899,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>162.97156499335787</v>
+        <v>163.00494570620347</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>171.31303623532699</v>
+        <v>171.34812549319548</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>180.04728651941639</v>
+        <v>180.08416477342459</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>189.18948196687853</v>
+        <v>189.22823277454984</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>208.76058966886217</v>
+        <v>208.80334913611955</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18931,23 +18931,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>160.3877040464844</v>
+        <v>160.42055551902786</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>169.78156669993928</v>
+        <v>169.81634227397711</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>179.70453336066876</v>
+        <v>179.74134141013073</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>190.18215598779051</v>
+        <v>190.22111012029606</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>212.9085754837684</v>
+        <v>212.95218456379953</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18962,23 +18962,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>160.25537317737925</v>
+        <v>160.28819754520205</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>170.70865691571967</v>
+        <v>170.74362238136393</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>181.8431085907819</v>
+        <v>181.88035467472955</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>193.6981231896732</v>
+        <v>193.73779748149948</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>219.73708241603248</v>
+        <v>219.78209014759574</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18994,23 +18994,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>157.85512426468614</v>
+        <v>157.88745700061159</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>169.21240762040227</v>
+        <v>169.24706661621497</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>181.41244805791149</v>
+        <v>181.44960593165155</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>194.51213310618542</v>
+        <v>194.55197412790275</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>223.65479215931973</v>
+        <v>223.70060233727267</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19026,23 +19026,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>157.74007957868238</v>
+        <v>157.77238875053624</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>170.03459374555277</v>
+        <v>170.06942114595154</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>183.34677675154799</v>
+        <v>183.38433082489914</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>197.75496669607236</v>
+        <v>197.7954719324143</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>230.19979366904525</v>
+        <v>230.24694442942422</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19058,23 +19058,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>151.32349265348648</v>
+        <v>151.35448754548048</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>167.1690641607382</v>
+        <v>167.20330462794882</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>184.99434259638429</v>
+        <v>185.03223413303684</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>205.04591153933822</v>
+        <v>205.08791014623347</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>252.9627879612444</v>
+        <v>253.0146011605955</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19090,23 +19090,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>147.66787908342849</v>
+        <v>147.69812521298124</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>166.10284510577964</v>
+        <v>166.13686718426641</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>187.55007758854785</v>
+        <v>187.58849260459323</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>212.52473162987741</v>
+        <v>212.56826208894503</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>275.56302593688724</v>
+        <v>275.61946823858597</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19122,23 +19122,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>143.24351879424009</v>
+        <v>143.2728587025122</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>163.31860036258348</v>
+        <v>163.35205215708072</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>187.39170356659002</v>
+        <v>187.43008614361605</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>216.32995415968372</v>
+        <v>216.3742640249047</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>293.25703437619836</v>
+        <v>293.31710085991205</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19154,23 +19154,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>140.73606611708908</v>
+        <v>140.76489243541198</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>162.03868113509782</v>
+        <v>162.07187076965201</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>188.25959479812681</v>
+        <v>188.29815514130476</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>220.68241804924219</v>
+        <v>220.7276194095364</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>311.08422046441302</v>
+        <v>311.1479384083043</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>230.19979366904525</v>
+        <v>230.24694442942422</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19245,7 +19245,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>197.75496669607236</v>
+        <v>197.7954719324143</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19273,7 +19273,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>183.34677675154799</v>
+        <v>183.38433082489914</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>170.03459374555277</v>
+        <v>170.06942114595154</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>157.74007957868238</v>
+        <v>157.77238875053624</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19689,7 +19689,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>197.75496669607236</v>
+        <v>197.7954719324143</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19713,7 +19713,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>183.34677675154799</v>
+        <v>183.38433082489914</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19736,7 +19736,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>170.03459374555277</v>
+        <v>170.06942114595154</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>182.90036898895406</v>
+        <v>182.93783162666529</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19799,7 +19799,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>230.19979366904525</v>
+        <v>230.24694442942422</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19822,7 +19822,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>157.74007957868238</v>
+        <v>157.77238875053624</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19867,7 +19867,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>108.8</v>
+        <v>106.9</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.2287790804195324</v>
+        <v>0.23628140529661751</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>173.04532913357176</v>
+        <v>173.08077320899264</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19898,7 +19898,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>4.9074709654442515E-2</v>
+        <v>4.9070670284975415E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19907,7 +19907,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>188.73726822045415</v>
+        <v>188.77592640327265</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20010,7 +20010,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>188.7681702257519</v>
+        <v>188.8068347380854</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>3.464387657516934E-2</v>
+        <v>3.4643876575169312E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20155,11 +20155,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>86.975699640762301</v>
+        <v>86.993514471554235</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>93.398478672908823</v>
+        <v>93.416293503700757</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20167,7 +20167,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.50514024308217209</v>
+        <v>0.50514721191652279</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20180,11 +20180,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>109.01791666163422</v>
+        <v>109.04024629791927</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>116.40297051654868</v>
+        <v>116.42530015283373</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20192,7 +20192,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.38325391898443484</v>
+        <v>0.38326193190481217</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20226,11 +20226,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>135.27939854623293</v>
+        <v>135.30710720054316</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>143.74763551827758</v>
+        <v>143.77534417258781</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20238,7 +20238,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.23837174886746026</v>
+        <v>0.23838093706160568</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20251,11 +20251,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>152.99095733455596</v>
+        <v>153.02229376563807</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>162.16039438193326</v>
+        <v>162.19173081301534</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20263,7 +20263,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.14081412796267578</v>
+        <v>0.14082407697190591</v>
       </c>
     </row>
   </sheetData>
@@ -20374,7 +20374,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>108.8</v>
+        <v>106.9</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20392,14 +20392,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>327167.51448365441</v>
+        <v>321454.11119763477</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.2287790804195324</v>
+        <v>0.23628140529661751</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20407,13 +20407,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="472" t="s">
+      <c r="B12" s="475" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="472"/>
-      <c r="D12" s="472"/>
-      <c r="E12" s="472"/>
-      <c r="F12" s="472"/>
+      <c r="C12" s="475"/>
+      <c r="D12" s="475"/>
+      <c r="E12" s="475"/>
+      <c r="F12" s="475"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20451,7 +20451,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1254930708885194</v>
+        <v>1.1257236004352571</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>188.73726822045415</v>
+        <v>188.77592640327265</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>93.398478672908823</v>
+        <v>93.416293503700757</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>116.40297051654868</v>
+        <v>116.42530015283373</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20561,7 +20561,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>143.74763551827758</v>
+        <v>143.77534417258781</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>162.16039438193326</v>
+        <v>162.19173081301534</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20598,22 +20598,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="472" t="s">
+      <c r="B29" s="475" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="472"/>
-      <c r="D29" s="472"/>
-      <c r="E29" s="472"/>
-      <c r="F29" s="472"/>
+      <c r="C29" s="475"/>
+      <c r="D29" s="475"/>
+      <c r="E29" s="475"/>
+      <c r="F29" s="475"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="478" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="478"/>
+      <c r="D30" s="478"/>
+      <c r="E30" s="478"/>
+      <c r="F30" s="478"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20803,10 +20803,10 @@
       <c r="B54" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="474"/>
-      <c r="D54" s="474"/>
-      <c r="E54" s="474"/>
-      <c r="F54" s="474"/>
+      <c r="C54" s="477"/>
+      <c r="D54" s="477"/>
+      <c r="E54" s="477"/>
+      <c r="F54" s="477"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20822,22 +20822,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="472" t="s">
+      <c r="B57" s="475" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="472"/>
-      <c r="D57" s="472"/>
-      <c r="E57" s="472"/>
-      <c r="F57" s="472"/>
+      <c r="C57" s="475"/>
+      <c r="D57" s="475"/>
+      <c r="E57" s="475"/>
+      <c r="F57" s="475"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="472" t="s">
+      <c r="B58" s="475" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="472"/>
-      <c r="D58" s="472"/>
-      <c r="E58" s="472"/>
-      <c r="F58" s="472"/>
+      <c r="C58" s="475"/>
+      <c r="D58" s="475"/>
+      <c r="E58" s="475"/>
+      <c r="F58" s="475"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20871,7 +20871,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.8770218530861663E-2</v>
+        <v>8.0186671380633401E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20881,7 +20881,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.2261029411764702E-2</v>
+        <v>3.2834424695977547E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20972,22 +20972,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="472" t="s">
+      <c r="B73" s="475" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="472"/>
-      <c r="D73" s="472"/>
-      <c r="E73" s="472"/>
-      <c r="F73" s="472"/>
+      <c r="C73" s="475"/>
+      <c r="D73" s="475"/>
+      <c r="E73" s="475"/>
+      <c r="F73" s="475"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="478" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="478"/>
+      <c r="D74" s="478"/>
+      <c r="E74" s="478"/>
+      <c r="F74" s="478"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20995,13 +20995,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="472" t="s">
+      <c r="B77" s="475" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="472"/>
-      <c r="D77" s="472"/>
-      <c r="E77" s="472"/>
-      <c r="F77" s="472"/>
+      <c r="C77" s="475"/>
+      <c r="D77" s="475"/>
+      <c r="E77" s="475"/>
+      <c r="F77" s="475"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21022,7 +21022,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-41.953146726029601</v>
+        <v>-41.961739795279989</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21084,7 +21084,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>11.612874418678294</v>
+        <v>11.615253030102302</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21115,7 +21115,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>36.87886293271535</v>
+        <v>36.886416659855911</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21128,7 +21128,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>6.5385906253640389</v>
+        <v>6.5399298946782238</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21150,33 +21150,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="472" t="s">
+      <c r="B96" s="475" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="472"/>
-      <c r="D96" s="472"/>
-      <c r="E96" s="472"/>
-      <c r="F96" s="472"/>
+      <c r="C96" s="475"/>
+      <c r="D96" s="475"/>
+      <c r="E96" s="475"/>
+      <c r="F96" s="475"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="478" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="478"/>
+      <c r="D97" s="478"/>
+      <c r="E97" s="478"/>
+      <c r="F97" s="478"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="478" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="478"/>
+      <c r="D98" s="478"/>
+      <c r="E98" s="478"/>
+      <c r="F98" s="478"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21239,23 +21239,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="472" t="s">
+      <c r="B107" s="475" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="472"/>
-      <c r="D107" s="472"/>
-      <c r="E107" s="472"/>
-      <c r="F107" s="472"/>
+      <c r="C107" s="475"/>
+      <c r="D107" s="475"/>
+      <c r="E107" s="475"/>
+      <c r="F107" s="475"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="472" t="s">
+      <c r="B108" s="475" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="472"/>
-      <c r="D108" s="472"/>
-      <c r="E108" s="472"/>
-      <c r="F108" s="472"/>
+      <c r="C108" s="475"/>
+      <c r="D108" s="475"/>
+      <c r="E108" s="475"/>
+      <c r="F108" s="475"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-64.948553163371002</v>
+        <v>-64.961856275499628</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21287,7 +21287,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>173.04532913357176</v>
+        <v>173.08077320899264</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21299,13 +21299,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="472" t="s">
+      <c r="B114" s="475" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="472"/>
-      <c r="D114" s="472"/>
-      <c r="E114" s="472"/>
-      <c r="F114" s="472"/>
+      <c r="C114" s="475"/>
+      <c r="D114" s="475"/>
+      <c r="E114" s="475"/>
+      <c r="F114" s="475"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,7 +21350,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>230.2 HKD</v>
+        <v>230.25 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21373,7 +21373,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>197.75 HKD</v>
+        <v>197.8 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21395,7 +21395,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>183.35 HKD</v>
+        <v>183.38 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>170.03 HKD</v>
+        <v>170.07 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>157.74 HKD</v>
+        <v>157.77 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21461,7 +21461,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>188.73726822045415</v>
+        <v>188.77592640327265</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21469,13 +21469,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="476" t="s">
+      <c r="B127" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="476"/>
-      <c r="D127" s="476"/>
-      <c r="E127" s="476"/>
-      <c r="F127" s="476"/>
+      <c r="C127" s="473"/>
+      <c r="D127" s="473"/>
+      <c r="E127" s="473"/>
+      <c r="F127" s="473"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21488,22 +21488,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="477" t="s">
+      <c r="B131" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="477"/>
-      <c r="D131" s="477"/>
-      <c r="E131" s="477"/>
-      <c r="F131" s="477"/>
+      <c r="C131" s="474"/>
+      <c r="D131" s="474"/>
+      <c r="E131" s="474"/>
+      <c r="F131" s="474"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="472" t="s">
+      <c r="B132" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="472"/>
-      <c r="D132" s="472"/>
-      <c r="E132" s="472"/>
-      <c r="F132" s="472"/>
+      <c r="C132" s="475"/>
+      <c r="D132" s="475"/>
+      <c r="E132" s="475"/>
+      <c r="F132" s="475"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21568,11 +21568,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>86.975699640762301</v>
+        <v>86.993514471554235</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>93.398478672908823</v>
+        <v>93.416293503700757</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21589,11 +21589,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>109.01791666163422</v>
+        <v>109.04024629791927</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>116.40297051654868</v>
+        <v>116.42530015283373</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21629,11 +21629,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>135.27939854623293</v>
+        <v>135.30710720054316</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>143.74763551827758</v>
+        <v>143.77534417258781</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21650,11 +21650,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>152.99095733455596</v>
+        <v>153.02229376563807</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>162.16039438193326</v>
+        <v>162.19173081301534</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21672,13 +21672,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="478" t="s">
+      <c r="B149" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="472"/>
-      <c r="D149" s="472"/>
-      <c r="E149" s="472"/>
-      <c r="F149" s="472"/>
+      <c r="C149" s="475"/>
+      <c r="D149" s="475"/>
+      <c r="E149" s="475"/>
+      <c r="F149" s="475"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21686,13 +21686,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="474" t="s">
+      <c r="B152" s="477" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="474"/>
-      <c r="D152" s="474"/>
-      <c r="E152" s="474"/>
-      <c r="F152" s="474"/>
+      <c r="C152" s="477"/>
+      <c r="D152" s="477"/>
+      <c r="E152" s="477"/>
+      <c r="F152" s="477"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21729,22 +21729,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="475" t="s">
+      <c r="B161" s="472" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="475"/>
-      <c r="D161" s="475"/>
-      <c r="E161" s="475"/>
-      <c r="F161" s="475"/>
+      <c r="C161" s="472"/>
+      <c r="D161" s="472"/>
+      <c r="E161" s="472"/>
+      <c r="F161" s="472"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="475" t="s">
+      <c r="B162" s="472" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="475"/>
-      <c r="D162" s="475"/>
-      <c r="E162" s="475"/>
-      <c r="F162" s="475"/>
+      <c r="C162" s="472"/>
+      <c r="D162" s="472"/>
+      <c r="E162" s="472"/>
+      <c r="F162" s="472"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21768,15 +21768,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21791,12 +21788,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9618.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9618.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522EAEDE-62D3-4AA5-BB32-E90609B7F2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{137B8877-0E79-4C07-B0B9-34184C7BBB2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4995,30 +4995,30 @@
     <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5028,6 +5028,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5037,16 +5046,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5416,7 +5416,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>106.9</v>
+        <v>110.2</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5435,14 +5435,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>321454.11119763477</v>
+        <v>331377.39058914263</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.23628140529661751</v>
+        <v>0.22528850426598107</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5450,13 +5450,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="463" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="463"/>
-      <c r="D12" s="463"/>
-      <c r="E12" s="463"/>
-      <c r="F12" s="463"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5491,7 +5491,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1257236004352571</v>
+        <v>1.1308739082336425</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>188.77592640327265</v>
+        <v>189.63959677984315</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>93.416293503700757</v>
+        <v>93.814298285530484</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>116.42530015283373</v>
+        <v>116.92417112847011</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>143.77534417258781</v>
+        <v>144.39438889113373</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>162.19173081301534</v>
+        <v>162.89182443511163</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5634,22 +5634,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="463" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="463"/>
-      <c r="D29" s="463"/>
-      <c r="E29" s="463"/>
-      <c r="F29" s="463"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="467" t="s">
+      <c r="B30" s="463" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="467"/>
-      <c r="D30" s="467"/>
-      <c r="E30" s="467"/>
-      <c r="F30" s="467"/>
+      <c r="C30" s="463"/>
+      <c r="D30" s="463"/>
+      <c r="E30" s="463"/>
+      <c r="F30" s="463"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5661,13 +5661,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="464" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="464"/>
-      <c r="D33" s="464"/>
-      <c r="E33" s="464"/>
-      <c r="F33" s="464"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5687,13 +5687,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="464" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="464"/>
-      <c r="D36" s="464"/>
-      <c r="E36" s="464"/>
-      <c r="F36" s="464"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5722,13 +5722,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="464" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="464"/>
-      <c r="D40" s="464"/>
-      <c r="E40" s="464"/>
-      <c r="F40" s="464"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5744,13 +5744,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="464" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="464"/>
-      <c r="D43" s="464"/>
-      <c r="E43" s="464"/>
-      <c r="F43" s="464"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5814,13 +5814,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="464" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="464"/>
-      <c r="D51" s="464"/>
-      <c r="E51" s="464"/>
-      <c r="F51" s="464"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5836,7 +5836,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="464" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5858,22 +5858,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="463" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="463"/>
-      <c r="D57" s="463"/>
-      <c r="E57" s="463"/>
-      <c r="F57" s="463"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="463" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="463"/>
-      <c r="D58" s="463"/>
-      <c r="E58" s="463"/>
-      <c r="F58" s="463"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.0186671380633401E-2</v>
+        <v>7.8141313947041005E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.2834424695977547E-2</v>
+        <v>3.1851179673321232E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6008,13 +6008,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="463" t="s">
+      <c r="B73" s="461" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="463"/>
-      <c r="D73" s="463"/>
-      <c r="E73" s="463"/>
-      <c r="F73" s="463"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6033,13 +6033,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="463" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="463"/>
-      <c r="D77" s="463"/>
-      <c r="E77" s="463"/>
-      <c r="F77" s="463"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-41.961739795279989</v>
+        <v>-42.153719314602398</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>11.615253030102302</v>
+        <v>11.668394074882768</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>36.886416659855911</v>
+        <v>37.055176024325391</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.5399298946782238</v>
+        <v>6.5698507846057623</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6208,31 +6208,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="463" t="s">
+      <c r="B96" s="461" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="463"/>
-      <c r="D96" s="463"/>
-      <c r="E96" s="463"/>
-      <c r="F96" s="463"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="467" t="s">
+      <c r="B97" s="463" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="467"/>
-      <c r="D97" s="467"/>
-      <c r="E97" s="467"/>
-      <c r="F97" s="467"/>
+      <c r="C97" s="463"/>
+      <c r="D97" s="463"/>
+      <c r="E97" s="463"/>
+      <c r="F97" s="463"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="467" t="s">
+      <c r="B98" s="463" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="467"/>
-      <c r="D98" s="467"/>
-      <c r="E98" s="467"/>
-      <c r="F98" s="467"/>
+      <c r="C98" s="463"/>
+      <c r="D98" s="463"/>
+      <c r="E98" s="463"/>
+      <c r="F98" s="463"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6282,22 +6282,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="463" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="463"/>
-      <c r="D107" s="463"/>
-      <c r="E107" s="463"/>
-      <c r="F107" s="463"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="463" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="463"/>
-      <c r="D108" s="463"/>
-      <c r="E108" s="463"/>
-      <c r="F108" s="463"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-64.961856275499628</v>
+        <v>-65.259063827019318</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>173.08077320899264</v>
+        <v>173.87263655419051</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6331,13 +6331,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="463" t="s">
+      <c r="B114" s="461" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="463"/>
-      <c r="D114" s="463"/>
-      <c r="E114" s="463"/>
-      <c r="F114" s="463"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>230.25 HKD</v>
+        <v>231.3 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.7754564320826712E-2</v>
+        <v>-4.7828739461975286E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>197.8 HKD</v>
+        <v>198.7 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.5847022280579275E-3</v>
+        <v>2.5026407953677421E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>183.38 HKD</v>
+        <v>184.22 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.8664678555365398E-2</v>
+        <v>2.857832386773301E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>170.07 HKD</v>
+        <v>170.85 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.5346666698796169E-2</v>
+        <v>5.5255769649046299E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>157.77 HKD</v>
+        <v>158.49 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6468,17 +6468,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>8.2623953269175293E-2</v>
+        <v>8.2528252908840846E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="464" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="464"/>
-      <c r="D124" s="464"/>
-      <c r="E124" s="464"/>
-      <c r="F124" s="464"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>188.77592640327265</v>
+        <v>189.63959677984315</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6513,22 +6513,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="468" t="s">
+      <c r="B131" s="464" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="468"/>
-      <c r="D131" s="468"/>
-      <c r="E131" s="468"/>
-      <c r="F131" s="468"/>
+      <c r="C131" s="464"/>
+      <c r="D131" s="464"/>
+      <c r="E131" s="464"/>
+      <c r="F131" s="464"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="463" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="463"/>
-      <c r="D132" s="463"/>
-      <c r="E132" s="463"/>
-      <c r="F132" s="463"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6593,11 +6593,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>86.993514471554235</v>
+        <v>87.391519253383962</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>93.416293503700757</v>
+        <v>93.814298285530484</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6614,11 +6614,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>109.04024629791927</v>
+        <v>109.53911727355565</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>116.42530015283373</v>
+        <v>116.92417112847011</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6661,11 +6661,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>135.30710720054316</v>
+        <v>135.92615191908908</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>143.77534417258781</v>
+        <v>144.39438889113373</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6682,11 +6682,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>153.02229376563807</v>
+        <v>153.72238738773436</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>162.19173081301534</v>
+        <v>162.89182443511163</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6704,13 +6704,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="462" t="s">
+      <c r="B149" s="468" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="463"/>
-      <c r="D149" s="463"/>
-      <c r="E149" s="463"/>
-      <c r="F149" s="463"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6747,13 +6747,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="464" t="s">
+      <c r="B158" s="462" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="464"/>
-      <c r="D158" s="464"/>
-      <c r="E158" s="464"/>
-      <c r="F158" s="464"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6761,22 +6761,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="461" t="s">
+      <c r="B161" s="467" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="461"/>
-      <c r="D161" s="461"/>
-      <c r="E161" s="461"/>
-      <c r="F161" s="461"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="461" t="s">
+      <c r="B162" s="467" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="461"/>
-      <c r="D162" s="461"/>
-      <c r="E162" s="461"/>
-      <c r="F162" s="461"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6800,6 +6800,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6816,18 +6828,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10079,11 +10079,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>86.826648430610263</v>
+        <v>87.223889782170218</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-64.961856275499628</v>
+        <v>-65.259063827019318</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10489,11 +10489,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-126181.23264918753</v>
+        <v>-126758.52550000076</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-41.961739795279989</v>
+        <v>-42.153719314602398</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10506,11 +10506,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>34927.697279019354</v>
+        <v>35087.495289477898</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>11.615253030102302</v>
+        <v>11.668394074882768</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10523,11 +10523,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>110919.46008100662</v>
+        <v>111426.92866390479</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>36.886416659855911</v>
+        <v>37.055176024325391</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10540,11 +10540,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>19665.924710838444</v>
+        <v>19755.898453381931</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.5399298946782238</v>
+        <v>6.5698507846057623</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14128,20 +14128,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.2834424695977547E-2</v>
+        <v>3.1851179673321232E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.2834424695977547E-2</v>
+        <v>3.1851179673321232E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>2.4954162768942939E-2</v>
+        <v>2.4206896551724141E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>2.0357343311506081E-2</v>
+        <v>1.9747731397459167E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
@@ -15291,30 +15291,30 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>8.5719551705897103</v>
+        <v>8.6111727969639187</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.789830084839368</v>
+        <v>10.839194729950934</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>6.9803334869861509</v>
+        <v>7.0122692712048131</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>3.6938190773405744</v>
+        <v>3.7107187010070732</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>4.716947438379572E-2</v>
+        <v>4.7385279854757399E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.6338393168462177</v>
+        <v>4.6550396352554531</v>
       </c>
       <c r="L123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15348,30 +15348,30 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.0186671380633401E-2</v>
+        <v>7.8141313947041005E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.10093386421739352</v>
+        <v>9.8359298819881438E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.5297787530272683E-2</v>
+        <v>6.36322075426934E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.4553967047152238E-2</v>
+        <v>3.3672583493712098E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>4.412485910551517E-4</v>
+        <v>4.2999346510669143E-4</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>4.3347421111751334E-2</v>
+        <v>4.2241738976909735E-2</v>
       </c>
       <c r="L124" s="74" t="str">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
@@ -15405,23 +15405,23 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13893118315896222</v>
+        <v>0.13477081197543614</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2349362443528534E-2</v>
+        <v>7.0182820736961887E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0147382355429977E-2</v>
+        <v>2.9244602303044143E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-1.3896229179827232E-2</v>
+        <v>-1.3480098904932226E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15348069376430179</v>
+        <v>0.148884629431977</v>
       </c>
       <c r="L125" s="22" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16330,7 +16330,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.5399298946782238</v>
+        <v>6.5698507846057623</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1257236004352571</v>
+        <v>1.1308739082336425</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16380,7 +16380,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>520463.2938942574</v>
+        <v>522844.47001980059</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>173.08077320899264</v>
+        <v>173.87263655419051</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16525,7 +16525,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>188.8068347380854</v>
+        <v>189.6706465236463</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18713,23 +18713,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>173.08077320899264</v>
+        <v>173.87263655419051</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>173.08077320899264</v>
+        <v>173.87263655419051</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>173.08077320899264</v>
+        <v>173.87263655419051</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>173.08077320899264</v>
+        <v>173.87263655419051</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>173.08077320899264</v>
+        <v>173.87263655419051</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18744,23 +18744,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>166.50436128100486</v>
+        <v>167.26613682700849</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>168.10400559486814</v>
+        <v>168.87309968743253</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>169.70364990873148</v>
+        <v>170.48006254785662</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>171.3032942225947</v>
+        <v>172.08702540828062</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>174.50258285032126</v>
+        <v>175.30095112912872</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18775,23 +18775,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>166.30292675294646</v>
+        <v>167.06378071409543</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>169.43343874996279</v>
+        <v>170.20861514367417</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>172.59430484655195</v>
+        <v>173.38394254612973</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>175.78552504271414</v>
+        <v>176.5897629214623</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>182.25902773375725</v>
+        <v>183.09288259075799</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18806,23 +18806,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>166.11510901116699</v>
+        <v>166.87510368573817</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>170.68539911047142</v>
+        <v>171.46630335887599</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>175.34345919301066</v>
+        <v>176.14567457245946</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>180.09013832450717</v>
+        <v>180.91407027677892</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>189.85274999726101</v>
+        <v>190.72134695878671</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18837,23 +18837,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>165.93998757361044</v>
+        <v>166.69918104857527</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>171.86440140801335</v>
+        <v>172.65069972004508</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>177.95803955048183</v>
+        <v>178.77221691917859</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>184.22417252520339</v>
+        <v>185.06701813316681</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>197.2871634020899</v>
+        <v>198.18977361280082</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18868,23 +18868,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>163.15719129283389</v>
+        <v>163.90365317242248</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>170.30253217977292</v>
+        <v>171.08168477036546</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>177.71929224705227</v>
+        <v>178.53237732089246</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>185.41534596474662</v>
+        <v>186.26364132063446</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>201.67759713188238</v>
+        <v>202.60029405399217</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18899,23 +18899,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>163.00494570620347</v>
+        <v>163.75071104568954</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>171.34812549319548</v>
+        <v>172.13206178681597</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>180.08416477342459</v>
+        <v>180.90806939605102</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>189.22823277454984</v>
+        <v>190.09397250191864</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>208.80334913611955</v>
+        <v>209.75864714796629</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18931,23 +18931,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>160.42055551902786</v>
+        <v>161.15449699257562</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>169.81634227397711</v>
+        <v>170.59327049291895</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>179.74134141013073</v>
+        <v>180.5636775786173</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>190.22111012029606</v>
+        <v>191.09139236941238</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>212.95218456379953</v>
+        <v>213.92646394855979</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18962,23 +18962,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>160.28819754520205</v>
+        <v>161.02153346663695</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>170.74362238136393</v>
+        <v>171.52479300755965</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>181.88035467472955</v>
+        <v>182.71247706133687</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>193.73779748149948</v>
+        <v>194.62416895743297</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>219.78209014759574</v>
+        <v>220.78761709257134</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18994,23 +18994,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>157.88745700061159</v>
+        <v>158.60980927317931</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>169.24706661621497</v>
+        <v>170.02139033716236</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>181.44960593165155</v>
+        <v>182.27975759595211</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>194.55197412790275</v>
+        <v>195.44207055046579</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>223.70060233727267</v>
+        <v>224.72405690131993</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19026,23 +19026,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>157.77238875053624</v>
+        <v>158.49421457335598</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>170.06942114595154</v>
+        <v>170.84750722823341</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>183.38433082489914</v>
+        <v>184.22333406582257</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>197.7954719324143</v>
+        <v>198.70040770988666</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>230.24694442942422</v>
+        <v>231.30034921989923</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19058,23 +19058,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>151.35448754548048</v>
+        <v>152.0469507728879</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>167.20330462794882</v>
+        <v>167.96827791571519</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>185.03223413303684</v>
+        <v>185.87877671066389</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>205.08791014623347</v>
+        <v>206.02620962096449</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>253.0146011605955</v>
+        <v>254.17217045465574</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19090,23 +19090,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>147.69812521298124</v>
+        <v>148.37386018540005</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>166.13686718426641</v>
+        <v>166.89696140484384</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>187.58849260459323</v>
+        <v>188.44673034250263</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>212.56826208894503</v>
+        <v>213.54078498666399</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>275.61946823858597</v>
+        <v>276.88045725587864</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19122,23 +19122,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>143.2728587025122</v>
+        <v>143.92834759977544</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>163.35205215708072</v>
+        <v>164.09940554629773</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>187.43008614361605</v>
+        <v>188.28759915475331</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>216.3742640249047</v>
+        <v>217.36419979505868</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>293.31710085991205</v>
+        <v>294.65905846955491</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19154,23 +19154,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>140.76489243541198</v>
+        <v>141.40890711447588</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>162.07187076965201</v>
+        <v>162.81336718991105</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>188.29815514130476</v>
+        <v>189.15963966243487</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>220.7276194095364</v>
+        <v>221.73747225363104</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>311.1479384083043</v>
+        <v>312.57147403731329</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>230.24694442942422</v>
+        <v>231.30034921989923</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19245,7 +19245,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>197.7954719324143</v>
+        <v>198.70040770988666</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19273,7 +19273,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>183.38433082489914</v>
+        <v>184.22333406582257</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>170.06942114595154</v>
+        <v>170.84750722823341</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>157.77238875053624</v>
+        <v>158.49421457335598</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19689,7 +19689,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>197.7954719324143</v>
+        <v>198.70040770988666</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19713,7 +19713,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>183.38433082489914</v>
+        <v>184.22333406582257</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19736,7 +19736,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>170.06942114595154</v>
+        <v>170.84750722823341</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>182.93783162666529</v>
+        <v>183.77479208523812</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19799,7 +19799,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>230.24694442942422</v>
+        <v>231.30034921989923</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19822,7 +19822,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>157.77238875053624</v>
+        <v>158.49421457335598</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19867,7 +19867,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>106.9</v>
+        <v>110.2</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.23628140529661751</v>
+        <v>0.22528850426598107</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>173.08077320899264</v>
+        <v>173.87263655419051</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19898,7 +19898,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>4.9070670284975415E-2</v>
+        <v>4.8980855452068192E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19907,7 +19907,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>188.77592640327265</v>
+        <v>189.63959677984315</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20010,7 +20010,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>188.8068347380854</v>
+        <v>189.6706465236463</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>3.4643876575169312E-2</v>
+        <v>3.4643876575169319E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20155,11 +20155,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>86.993514471554235</v>
+        <v>87.391519253383962</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>93.416293503700757</v>
+        <v>93.814298285530484</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20167,7 +20167,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.50514721191652279</v>
+        <v>0.50530216326898436</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20180,11 +20180,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>109.04024629791927</v>
+        <v>109.53911727355565</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>116.42530015283373</v>
+        <v>116.92417112847011</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20192,7 +20192,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.38326193190481217</v>
+        <v>0.38344009840829818</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20226,11 +20226,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>135.30710720054316</v>
+        <v>135.92615191908908</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>143.77534417258781</v>
+        <v>144.39438889113373</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20238,7 +20238,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.23838093706160568</v>
+        <v>0.23858523566275869</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20251,11 +20251,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>153.02229376563807</v>
+        <v>153.72238738773436</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>162.19173081301534</v>
+        <v>162.89182443511163</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20263,7 +20263,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.14082407697190591</v>
+        <v>0.14104529222229678</v>
       </c>
     </row>
   </sheetData>
@@ -20374,7 +20374,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>106.9</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20392,14 +20392,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>321454.11119763477</v>
+        <v>331377.39058914263</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.23628140529661751</v>
+        <v>0.22528850426598107</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20407,13 +20407,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="475" t="s">
+      <c r="B12" s="472" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="475"/>
-      <c r="D12" s="475"/>
-      <c r="E12" s="475"/>
-      <c r="F12" s="475"/>
+      <c r="C12" s="472"/>
+      <c r="D12" s="472"/>
+      <c r="E12" s="472"/>
+      <c r="F12" s="472"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20451,7 +20451,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1257236004352571</v>
+        <v>1.1308739082336425</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>188.77592640327265</v>
+        <v>189.63959677984315</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>93.416293503700757</v>
+        <v>93.814298285530484</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>116.42530015283373</v>
+        <v>116.92417112847011</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20561,7 +20561,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>143.77534417258781</v>
+        <v>144.39438889113373</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>162.19173081301534</v>
+        <v>162.89182443511163</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20598,22 +20598,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="475" t="s">
+      <c r="B29" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="475"/>
-      <c r="D29" s="475"/>
-      <c r="E29" s="475"/>
-      <c r="F29" s="475"/>
+      <c r="C29" s="472"/>
+      <c r="D29" s="472"/>
+      <c r="E29" s="472"/>
+      <c r="F29" s="472"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="478" t="s">
+      <c r="B30" s="473" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="478"/>
-      <c r="D30" s="478"/>
-      <c r="E30" s="478"/>
-      <c r="F30" s="478"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20803,10 +20803,10 @@
       <c r="B54" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="477"/>
-      <c r="D54" s="477"/>
-      <c r="E54" s="477"/>
-      <c r="F54" s="477"/>
+      <c r="C54" s="474"/>
+      <c r="D54" s="474"/>
+      <c r="E54" s="474"/>
+      <c r="F54" s="474"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20822,22 +20822,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="475" t="s">
+      <c r="B57" s="472" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="475"/>
-      <c r="D57" s="475"/>
-      <c r="E57" s="475"/>
-      <c r="F57" s="475"/>
+      <c r="C57" s="472"/>
+      <c r="D57" s="472"/>
+      <c r="E57" s="472"/>
+      <c r="F57" s="472"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="475" t="s">
+      <c r="B58" s="472" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="475"/>
-      <c r="D58" s="475"/>
-      <c r="E58" s="475"/>
-      <c r="F58" s="475"/>
+      <c r="C58" s="472"/>
+      <c r="D58" s="472"/>
+      <c r="E58" s="472"/>
+      <c r="F58" s="472"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20871,7 +20871,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.0186671380633401E-2</v>
+        <v>7.8141313947041005E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20881,7 +20881,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.2834424695977547E-2</v>
+        <v>3.1851179673321232E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20972,22 +20972,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="475" t="s">
+      <c r="B73" s="472" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="475"/>
-      <c r="D73" s="475"/>
-      <c r="E73" s="475"/>
-      <c r="F73" s="475"/>
+      <c r="C73" s="472"/>
+      <c r="D73" s="472"/>
+      <c r="E73" s="472"/>
+      <c r="F73" s="472"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="478" t="s">
+      <c r="B74" s="473" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="478"/>
-      <c r="D74" s="478"/>
-      <c r="E74" s="478"/>
-      <c r="F74" s="478"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20995,13 +20995,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="475" t="s">
+      <c r="B77" s="472" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="475"/>
-      <c r="D77" s="475"/>
-      <c r="E77" s="475"/>
-      <c r="F77" s="475"/>
+      <c r="C77" s="472"/>
+      <c r="D77" s="472"/>
+      <c r="E77" s="472"/>
+      <c r="F77" s="472"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21022,7 +21022,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-41.961739795279989</v>
+        <v>-42.153719314602398</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21084,7 +21084,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>11.615253030102302</v>
+        <v>11.668394074882768</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21115,7 +21115,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>36.886416659855911</v>
+        <v>37.055176024325391</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21128,7 +21128,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>6.5399298946782238</v>
+        <v>6.5698507846057623</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21150,33 +21150,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="475" t="s">
+      <c r="B96" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="475"/>
-      <c r="D96" s="475"/>
-      <c r="E96" s="475"/>
-      <c r="F96" s="475"/>
+      <c r="C96" s="472"/>
+      <c r="D96" s="472"/>
+      <c r="E96" s="472"/>
+      <c r="F96" s="472"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="478" t="s">
+      <c r="B97" s="473" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="478"/>
-      <c r="D97" s="478"/>
-      <c r="E97" s="478"/>
-      <c r="F97" s="478"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="478" t="s">
+      <c r="B98" s="473" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="478"/>
-      <c r="D98" s="478"/>
-      <c r="E98" s="478"/>
-      <c r="F98" s="478"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21239,23 +21239,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="475" t="s">
+      <c r="B107" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="475"/>
-      <c r="D107" s="475"/>
-      <c r="E107" s="475"/>
-      <c r="F107" s="475"/>
+      <c r="C107" s="472"/>
+      <c r="D107" s="472"/>
+      <c r="E107" s="472"/>
+      <c r="F107" s="472"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="475" t="s">
+      <c r="B108" s="472" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="475"/>
-      <c r="D108" s="475"/>
-      <c r="E108" s="475"/>
-      <c r="F108" s="475"/>
+      <c r="C108" s="472"/>
+      <c r="D108" s="472"/>
+      <c r="E108" s="472"/>
+      <c r="F108" s="472"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-64.961856275499628</v>
+        <v>-65.259063827019318</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21287,7 +21287,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>173.08077320899264</v>
+        <v>173.87263655419051</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21299,13 +21299,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="475" t="s">
+      <c r="B114" s="472" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="475"/>
-      <c r="D114" s="475"/>
-      <c r="E114" s="475"/>
-      <c r="F114" s="475"/>
+      <c r="C114" s="472"/>
+      <c r="D114" s="472"/>
+      <c r="E114" s="472"/>
+      <c r="F114" s="472"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,7 +21350,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>230.25 HKD</v>
+        <v>231.3 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21373,7 +21373,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>197.8 HKD</v>
+        <v>198.7 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21395,7 +21395,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>183.38 HKD</v>
+        <v>184.22 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>170.07 HKD</v>
+        <v>170.85 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>157.77 HKD</v>
+        <v>158.49 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21461,7 +21461,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>188.77592640327265</v>
+        <v>189.63959677984315</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21469,13 +21469,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="473" t="s">
+      <c r="B127" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="473"/>
-      <c r="D127" s="473"/>
-      <c r="E127" s="473"/>
-      <c r="F127" s="473"/>
+      <c r="C127" s="476"/>
+      <c r="D127" s="476"/>
+      <c r="E127" s="476"/>
+      <c r="F127" s="476"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21488,22 +21488,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="474" t="s">
+      <c r="B131" s="477" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="474"/>
-      <c r="D131" s="474"/>
-      <c r="E131" s="474"/>
-      <c r="F131" s="474"/>
+      <c r="C131" s="477"/>
+      <c r="D131" s="477"/>
+      <c r="E131" s="477"/>
+      <c r="F131" s="477"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="475" t="s">
+      <c r="B132" s="472" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="475"/>
-      <c r="D132" s="475"/>
-      <c r="E132" s="475"/>
-      <c r="F132" s="475"/>
+      <c r="C132" s="472"/>
+      <c r="D132" s="472"/>
+      <c r="E132" s="472"/>
+      <c r="F132" s="472"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21568,11 +21568,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>86.993514471554235</v>
+        <v>87.391519253383962</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>93.416293503700757</v>
+        <v>93.814298285530484</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21589,11 +21589,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>109.04024629791927</v>
+        <v>109.53911727355565</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>116.42530015283373</v>
+        <v>116.92417112847011</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21629,11 +21629,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>135.30710720054316</v>
+        <v>135.92615191908908</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>143.77534417258781</v>
+        <v>144.39438889113373</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21650,11 +21650,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>153.02229376563807</v>
+        <v>153.72238738773436</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>162.19173081301534</v>
+        <v>162.89182443511163</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21672,13 +21672,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="476" t="s">
+      <c r="B149" s="478" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="475"/>
-      <c r="D149" s="475"/>
-      <c r="E149" s="475"/>
-      <c r="F149" s="475"/>
+      <c r="C149" s="472"/>
+      <c r="D149" s="472"/>
+      <c r="E149" s="472"/>
+      <c r="F149" s="472"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21686,13 +21686,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="477" t="s">
+      <c r="B152" s="474" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="477"/>
-      <c r="D152" s="477"/>
-      <c r="E152" s="477"/>
-      <c r="F152" s="477"/>
+      <c r="C152" s="474"/>
+      <c r="D152" s="474"/>
+      <c r="E152" s="474"/>
+      <c r="F152" s="474"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21729,22 +21729,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="472" t="s">
+      <c r="B161" s="475" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="472"/>
-      <c r="D161" s="472"/>
-      <c r="E161" s="472"/>
-      <c r="F161" s="472"/>
+      <c r="C161" s="475"/>
+      <c r="D161" s="475"/>
+      <c r="E161" s="475"/>
+      <c r="F161" s="475"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="472" t="s">
+      <c r="B162" s="475" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="472"/>
-      <c r="D162" s="472"/>
-      <c r="E162" s="472"/>
-      <c r="F162" s="472"/>
+      <c r="C162" s="475"/>
+      <c r="D162" s="475"/>
+      <c r="E162" s="475"/>
+      <c r="F162" s="475"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21768,12 +21768,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21788,15 +21791,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9618.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9618.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{137B8877-0E79-4C07-B0B9-34184C7BBB2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB56BA0-F5B9-4226-B946-51A23EBBF180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4995,30 +4995,30 @@
     <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5028,25 +5028,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5416,7 +5416,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>110.2</v>
+        <v>108.4</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5435,14 +5435,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>331377.39058914263</v>
+        <v>325964.69273922924</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.22528850426598107</v>
+        <v>0.23276346821133451</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5450,13 +5450,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+      <c r="B12" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="C12" s="463"/>
+      <c r="D12" s="463"/>
+      <c r="E12" s="463"/>
+      <c r="F12" s="463"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5491,7 +5491,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1308739082336425</v>
+        <v>1.1324833301067352</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>189.63959677984315</v>
+        <v>189.90948550292694</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>93.814298285530484</v>
+        <v>93.938670968979238</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>116.92417112847011</v>
+        <v>117.08006353169542</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>144.39438889113373</v>
+        <v>144.58783443836151</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>162.89182443511163</v>
+        <v>163.11059698866035</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5634,22 +5634,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+      <c r="B29" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="463"/>
+      <c r="D29" s="463"/>
+      <c r="E29" s="463"/>
+      <c r="F29" s="463"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="463" t="s">
+      <c r="B30" s="467" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="463"/>
-      <c r="D30" s="463"/>
-      <c r="E30" s="463"/>
-      <c r="F30" s="463"/>
+      <c r="C30" s="467"/>
+      <c r="D30" s="467"/>
+      <c r="E30" s="467"/>
+      <c r="F30" s="467"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5661,13 +5661,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+      <c r="B33" s="464" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="C33" s="464"/>
+      <c r="D33" s="464"/>
+      <c r="E33" s="464"/>
+      <c r="F33" s="464"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5687,13 +5687,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+      <c r="B36" s="464" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="C36" s="464"/>
+      <c r="D36" s="464"/>
+      <c r="E36" s="464"/>
+      <c r="F36" s="464"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5722,13 +5722,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+      <c r="B40" s="464" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="C40" s="464"/>
+      <c r="D40" s="464"/>
+      <c r="E40" s="464"/>
+      <c r="F40" s="464"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5744,13 +5744,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+      <c r="B43" s="464" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="C43" s="464"/>
+      <c r="D43" s="464"/>
+      <c r="E43" s="464"/>
+      <c r="F43" s="464"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5814,13 +5814,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+      <c r="B51" s="464" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="C51" s="464"/>
+      <c r="D51" s="464"/>
+      <c r="E51" s="464"/>
+      <c r="F51" s="464"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5836,7 +5836,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+      <c r="B54" s="464" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5858,22 +5858,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+      <c r="B57" s="463" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="C57" s="463"/>
+      <c r="D57" s="463"/>
+      <c r="E57" s="463"/>
+      <c r="F57" s="463"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="B58" s="463" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="C58" s="463"/>
+      <c r="D58" s="463"/>
+      <c r="E58" s="463"/>
+      <c r="F58" s="463"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.8141313947041005E-2</v>
+        <v>7.9551918170658015E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.1851179673321232E-2</v>
+        <v>3.2380073800738006E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6008,13 +6008,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
+      <c r="B73" s="463" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="C73" s="463"/>
+      <c r="D73" s="463"/>
+      <c r="E73" s="463"/>
+      <c r="F73" s="463"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6033,13 +6033,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="463" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="C77" s="463"/>
+      <c r="D77" s="463"/>
+      <c r="E77" s="463"/>
+      <c r="F77" s="463"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-42.153719314602398</v>
+        <v>-42.213711076197725</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>11.668394074882768</v>
+        <v>11.685000142554197</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>37.055176024325391</v>
+        <v>37.107911709860836</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.5698507846057623</v>
+        <v>6.5792007762173075</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6208,31 +6208,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
+      <c r="B96" s="463" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="C96" s="463"/>
+      <c r="D96" s="463"/>
+      <c r="E96" s="463"/>
+      <c r="F96" s="463"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="463" t="s">
+      <c r="B97" s="467" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="463"/>
-      <c r="D97" s="463"/>
-      <c r="E97" s="463"/>
-      <c r="F97" s="463"/>
+      <c r="C97" s="467"/>
+      <c r="D97" s="467"/>
+      <c r="E97" s="467"/>
+      <c r="F97" s="467"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="463" t="s">
+      <c r="B98" s="467" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="463"/>
-      <c r="D98" s="463"/>
-      <c r="E98" s="463"/>
-      <c r="F98" s="463"/>
+      <c r="C98" s="467"/>
+      <c r="D98" s="467"/>
+      <c r="E98" s="467"/>
+      <c r="F98" s="467"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6282,22 +6282,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="463" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
+      <c r="C107" s="463"/>
+      <c r="D107" s="463"/>
+      <c r="E107" s="463"/>
+      <c r="F107" s="463"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="B108" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="463"/>
+      <c r="D108" s="463"/>
+      <c r="E108" s="463"/>
+      <c r="F108" s="463"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-65.259063827019318</v>
+        <v>-65.351938341123912</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>173.87263655419051</v>
+        <v>174.12008626751856</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6331,13 +6331,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
+      <c r="B114" s="463" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="C114" s="463"/>
+      <c r="D114" s="463"/>
+      <c r="E114" s="463"/>
+      <c r="F114" s="463"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>231.3 HKD</v>
+        <v>231.63 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.7828739461975286E-2</v>
+        <v>-4.7851780231952266E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>198.7 HKD</v>
+        <v>198.98 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.5026407953677421E-3</v>
+        <v>2.4771504193757663E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>184.22 HKD</v>
+        <v>184.49 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.857832386773301E-2</v>
+        <v>2.8551499945545622E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>170.85 HKD</v>
+        <v>171.09 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.5255769649046299E-2</v>
+        <v>5.5227534809112314E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>158.49 HKD</v>
+        <v>158.72 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6468,17 +6468,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>8.2528252908840846E-2</v>
+        <v>8.2498526102287431E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+      <c r="B124" s="464" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="C124" s="464"/>
+      <c r="D124" s="464"/>
+      <c r="E124" s="464"/>
+      <c r="F124" s="464"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>189.63959677984315</v>
+        <v>189.90948550292694</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6513,22 +6513,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="464" t="s">
+      <c r="B131" s="468" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="464"/>
-      <c r="D131" s="464"/>
-      <c r="E131" s="464"/>
-      <c r="F131" s="464"/>
+      <c r="C131" s="468"/>
+      <c r="D131" s="468"/>
+      <c r="E131" s="468"/>
+      <c r="F131" s="468"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="B132" s="463" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="C132" s="463"/>
+      <c r="D132" s="463"/>
+      <c r="E132" s="463"/>
+      <c r="F132" s="463"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6593,11 +6593,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>87.391519253383962</v>
+        <v>87.515891936832716</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>93.814298285530484</v>
+        <v>93.938670968979238</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6614,11 +6614,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>109.53911727355565</v>
+        <v>109.69500967678096</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>116.92417112847011</v>
+        <v>117.08006353169542</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6661,11 +6661,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>135.92615191908908</v>
+        <v>136.11959746631686</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>144.39438889113373</v>
+        <v>144.58783443836151</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6682,11 +6682,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>153.72238738773436</v>
+        <v>153.94115994128305</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>162.89182443511163</v>
+        <v>163.11059698866035</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6704,13 +6704,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="468" t="s">
+      <c r="B149" s="462" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="C149" s="463"/>
+      <c r="D149" s="463"/>
+      <c r="E149" s="463"/>
+      <c r="F149" s="463"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6747,13 +6747,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
+      <c r="B158" s="464" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="C158" s="464"/>
+      <c r="D158" s="464"/>
+      <c r="E158" s="464"/>
+      <c r="F158" s="464"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6761,22 +6761,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="461" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="461"/>
+      <c r="D161" s="461"/>
+      <c r="E161" s="461"/>
+      <c r="F161" s="461"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="461" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="461"/>
+      <c r="D162" s="461"/>
+      <c r="E162" s="461"/>
+      <c r="F162" s="461"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6800,18 +6800,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6828,6 +6816,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10079,11 +10079,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>87.223889782170218</v>
+        <v>87.348023900969466</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-65.259063827019318</v>
+        <v>-65.351938341123912</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10489,11 +10489,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-126758.52550000076</v>
+        <v>-126938.92398833385</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-42.153719314602398</v>
+        <v>-42.213711076197725</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10506,11 +10506,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>35087.495289477898</v>
+        <v>35137.430637689373</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>11.668394074882768</v>
+        <v>11.685000142554195</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10523,11 +10523,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>111426.92866390479</v>
+        <v>111585.5077370778</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>37.055176024325391</v>
+        <v>37.107911709860836</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10540,11 +10540,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>19755.898453381931</v>
+        <v>19784.014386433322</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.5698507846057623</v>
+        <v>6.5792007762173057</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14128,20 +14128,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.1851179673321232E-2</v>
+        <v>3.2380073800738006E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.1851179673321232E-2</v>
+        <v>3.2380073800738006E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>2.4206896551724141E-2</v>
+        <v>2.4608856088560886E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>1.9747731397459167E-2</v>
+        <v>2.0075645756457566E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
@@ -15291,30 +15291,30 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>8.6111727969639187</v>
+        <v>8.6234279296993286</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.839194729950934</v>
+        <v>10.854620708884644</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.0122692712048131</v>
+        <v>7.0222488979898365</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>3.7107187010070732</v>
+        <v>3.7159996715899237</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>4.7385279854757399E-2</v>
+        <v>4.7452716998107873E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.6550396352554531</v>
+        <v>4.661664531766502</v>
       </c>
       <c r="L123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15348,30 +15348,30 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.8141313947041005E-2</v>
+        <v>7.9551918170658015E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>9.8359298819881438E-2</v>
+        <v>0.10013487738823472</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.36322075426934E-2</v>
+        <v>6.4780893892895167E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.3672583493712098E-2</v>
+        <v>3.4280439774814792E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>4.2999346510669143E-4</v>
+        <v>4.3775569186446374E-4</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>4.2241738976909735E-2</v>
+        <v>4.3004285348399465E-2</v>
       </c>
       <c r="L124" s="74" t="str">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
@@ -15405,23 +15405,23 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13477081197543614</v>
+        <v>0.13700870368720536</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0182820736961887E-2</v>
+        <v>7.1348218129273069E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9244602303044143E-2</v>
+        <v>2.9730213780400964E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-1.3480098904932226E-2</v>
+        <v>-1.3703938185641432E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.148884629431977</v>
+        <v>0.15135688342623491</v>
       </c>
       <c r="L125" s="22" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16330,7 +16330,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.5698507846057623</v>
+        <v>6.5792007762173075</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1308739082336425</v>
+        <v>1.1324833301067352</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16380,7 +16380,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>522844.47001980059</v>
+        <v>523588.56475940754</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>173.87263655419051</v>
+        <v>174.12008626751856</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16525,7 +16525,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>189.6706465236463</v>
+        <v>189.94057943568561</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18713,23 +18713,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>173.87263655419051</v>
+        <v>174.12008626751856</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>173.87263655419051</v>
+        <v>174.12008626751856</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>173.87263655419051</v>
+        <v>174.12008626751856</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>173.87263655419051</v>
+        <v>174.12008626751856</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>173.87263655419051</v>
+        <v>174.12008626751856</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18744,23 +18744,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>167.26613682700849</v>
+        <v>167.50418439117732</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>168.87309968743253</v>
+        <v>169.11343422732693</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>170.48006254785662</v>
+        <v>170.72268406347661</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>172.08702540828062</v>
+        <v>172.33193389962616</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>175.30095112912872</v>
+        <v>175.5504335719254</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18775,23 +18775,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>167.06378071409543</v>
+        <v>167.30154029182128</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>170.20861514367417</v>
+        <v>170.45085034443932</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>173.38394254612973</v>
+        <v>173.63069676651196</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>176.5897629214623</v>
+        <v>176.84107955803935</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>183.09288259075799</v>
+        <v>183.35345424945814</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18806,23 +18806,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>166.87510368573817</v>
+        <v>167.11259474463608</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>171.46630335887599</v>
+        <v>171.71032845938888</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>176.14567457245946</v>
+        <v>176.3963591973708</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>180.91407027677892</v>
+        <v>181.17154112276251</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>190.72134695878671</v>
+        <v>190.99277519249722</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18837,23 +18837,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>166.69918104857527</v>
+        <v>166.93642174026763</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>172.65069972004508</v>
+        <v>172.8964104137936</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>178.77221691917859</v>
+        <v>179.02663955119456</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>185.06701813316681</v>
+        <v>185.33039931545687</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>198.18977361280082</v>
+        <v>198.47183066120681</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18868,23 +18868,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>163.90365317242248</v>
+        <v>164.13691536246407</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>171.08168477036546</v>
+        <v>171.32516249458411</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>178.53237732089246</v>
+        <v>178.7864586212244</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>186.26364132063446</v>
+        <v>186.52872549696986</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>202.60029405399217</v>
+        <v>202.88862800738121</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18899,23 +18899,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>163.75071104568954</v>
+        <v>163.98375557361842</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>172.13206178681597</v>
+        <v>172.37703437242718</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>180.90806939605102</v>
+        <v>181.16553170178213</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>190.09397250191864</v>
+        <v>190.364507877313</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>209.75864714796629</v>
+        <v>210.05716862974452</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18931,23 +18931,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>161.15449699257562</v>
+        <v>161.38384667561166</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>170.59327049291895</v>
+        <v>170.83605312229497</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>180.5636775786173</v>
+        <v>180.82064975744754</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>191.09139236941238</v>
+        <v>191.36334723935843</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>213.92646394855979</v>
+        <v>214.23091692762793</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18962,23 +18962,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>161.02153346663695</v>
+        <v>161.25069392043582</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>171.52479300755965</v>
+        <v>171.76890134858172</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>182.71247706133687</v>
+        <v>182.97250733962738</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>194.62416895743297</v>
+        <v>194.901151556706</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>220.78761709257134</v>
+        <v>221.1018346350132</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18994,23 +18994,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>158.60980927317931</v>
+        <v>158.83553744187498</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>170.02139033716236</v>
+        <v>170.26335908585307</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>182.27975759595211</v>
+        <v>182.5391720423913</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>195.44207055046579</v>
+        <v>195.72021715989436</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>224.72405690131993</v>
+        <v>225.04387665306575</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19026,23 +19026,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>158.49421457335598</v>
+        <v>158.71977823154614</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>170.84750722823341</v>
+        <v>171.0906516788167</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>184.22333406582257</v>
+        <v>184.48551454520307</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>198.70040770988666</v>
+        <v>198.98319147563842</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>231.30034921989923</v>
+        <v>231.62952813063202</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19058,23 +19058,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>152.0469507728879</v>
+        <v>152.26333890115691</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>167.96827791571519</v>
+        <v>168.20732474356666</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>185.87877671066389</v>
+        <v>186.14331316057556</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>206.02620962096449</v>
+        <v>206.31941922265409</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>254.17217045465574</v>
+        <v>254.53389977538976</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19090,23 +19090,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>148.37386018540005</v>
+        <v>148.5850208941572</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>166.89696140484384</v>
+        <v>167.13448357091556</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>188.44673034250263</v>
+        <v>188.71492141802204</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>213.54078498666399</v>
+        <v>213.84468908035004</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>276.88045725587864</v>
+        <v>277.27450424988484</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19122,23 +19122,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>143.92834759977544</v>
+        <v>144.13318160390148</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>164.09940554629773</v>
+        <v>164.33294632456207</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>188.28759915475331</v>
+        <v>188.55556376009562</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>217.36419979505868</v>
+        <v>217.67354524465338</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>294.65905846955491</v>
+        <v>295.07840737340086</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19154,23 +19154,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>141.40890711447588</v>
+        <v>141.61015553527963</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>162.81336718991105</v>
+        <v>163.04507772145615</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>189.15963966243487</v>
+        <v>189.42884532662299</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>221.73747225363104</v>
+        <v>222.05304159812732</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>312.57147403731329</v>
+        <v>313.01631529110631</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>231.30034921989923</v>
+        <v>231.62952813063202</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19245,7 +19245,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>198.70040770988666</v>
+        <v>198.98319147563842</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19273,7 +19273,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>184.22333406582257</v>
+        <v>184.48551454520307</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>170.84750722823341</v>
+        <v>171.0906516788167</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>158.49421457335598</v>
+        <v>158.71977823154614</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19689,7 +19689,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>198.70040770988666</v>
+        <v>198.98319147563842</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19713,7 +19713,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>184.22333406582257</v>
+        <v>184.48551454520307</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19736,7 +19736,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>170.84750722823341</v>
+        <v>171.0906516788167</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>183.77479208523812</v>
+        <v>184.03633421469354</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19799,7 +19799,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>231.30034921989923</v>
+        <v>231.62952813063202</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19822,7 +19822,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>158.49421457335598</v>
+        <v>158.71977823154614</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19867,7 +19867,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>110.2</v>
+        <v>108.4</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.22528850426598107</v>
+        <v>0.23276346821133451</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>173.87263655419051</v>
+        <v>174.12008626751856</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19898,7 +19898,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>4.8980855452068192E-2</v>
+        <v>4.8952956762563962E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19907,7 +19907,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>189.63959677984315</v>
+        <v>189.90948550292694</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20010,7 +20010,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>189.6706465236463</v>
+        <v>189.94057943568561</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>3.4643876575169319E-2</v>
+        <v>3.4643876575169305E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20155,11 +20155,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>87.391519253383962</v>
+        <v>87.515891936832716</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>93.814298285530484</v>
+        <v>93.938670968979238</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20167,7 +20167,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.50530216326898436</v>
+        <v>0.50535029506184714</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20180,11 +20180,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>109.53911727355565</v>
+        <v>109.69500967678096</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>116.92417112847011</v>
+        <v>117.08006353169542</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20192,7 +20192,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.38344009840829818</v>
+        <v>0.38349544141179326</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20226,11 +20226,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>135.92615191908908</v>
+        <v>136.11959746631686</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>144.39438889113373</v>
+        <v>144.58783443836151</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20238,7 +20238,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.23858523566275869</v>
+        <v>0.23864869595398341</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20251,11 +20251,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>153.72238738773436</v>
+        <v>153.94115994128305</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>162.89182443511163</v>
+        <v>163.11059698866035</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20263,7 +20263,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.14104529222229678</v>
+        <v>0.14111400725085721</v>
       </c>
     </row>
   </sheetData>
@@ -20374,7 +20374,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>110.2</v>
+        <v>108.4</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20392,14 +20392,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>331377.39058914263</v>
+        <v>325964.69273922924</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.22528850426598107</v>
+        <v>0.23276346821133451</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20407,13 +20407,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="472" t="s">
+      <c r="B12" s="475" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="472"/>
-      <c r="D12" s="472"/>
-      <c r="E12" s="472"/>
-      <c r="F12" s="472"/>
+      <c r="C12" s="475"/>
+      <c r="D12" s="475"/>
+      <c r="E12" s="475"/>
+      <c r="F12" s="475"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20451,7 +20451,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1308739082336425</v>
+        <v>1.1324833301067352</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>189.63959677984315</v>
+        <v>189.90948550292694</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>93.814298285530484</v>
+        <v>93.938670968979238</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>116.92417112847011</v>
+        <v>117.08006353169542</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20561,7 +20561,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>144.39438889113373</v>
+        <v>144.58783443836151</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>162.89182443511163</v>
+        <v>163.11059698866035</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20598,22 +20598,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="472" t="s">
+      <c r="B29" s="475" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="472"/>
-      <c r="D29" s="472"/>
-      <c r="E29" s="472"/>
-      <c r="F29" s="472"/>
+      <c r="C29" s="475"/>
+      <c r="D29" s="475"/>
+      <c r="E29" s="475"/>
+      <c r="F29" s="475"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="478" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="478"/>
+      <c r="D30" s="478"/>
+      <c r="E30" s="478"/>
+      <c r="F30" s="478"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20803,10 +20803,10 @@
       <c r="B54" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="474"/>
-      <c r="D54" s="474"/>
-      <c r="E54" s="474"/>
-      <c r="F54" s="474"/>
+      <c r="C54" s="477"/>
+      <c r="D54" s="477"/>
+      <c r="E54" s="477"/>
+      <c r="F54" s="477"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20822,22 +20822,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="472" t="s">
+      <c r="B57" s="475" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="472"/>
-      <c r="D57" s="472"/>
-      <c r="E57" s="472"/>
-      <c r="F57" s="472"/>
+      <c r="C57" s="475"/>
+      <c r="D57" s="475"/>
+      <c r="E57" s="475"/>
+      <c r="F57" s="475"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="472" t="s">
+      <c r="B58" s="475" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="472"/>
-      <c r="D58" s="472"/>
-      <c r="E58" s="472"/>
-      <c r="F58" s="472"/>
+      <c r="C58" s="475"/>
+      <c r="D58" s="475"/>
+      <c r="E58" s="475"/>
+      <c r="F58" s="475"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20871,7 +20871,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.8141313947041005E-2</v>
+        <v>7.9551918170658015E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20881,7 +20881,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.1851179673321232E-2</v>
+        <v>3.2380073800738006E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20972,22 +20972,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="472" t="s">
+      <c r="B73" s="475" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="472"/>
-      <c r="D73" s="472"/>
-      <c r="E73" s="472"/>
-      <c r="F73" s="472"/>
+      <c r="C73" s="475"/>
+      <c r="D73" s="475"/>
+      <c r="E73" s="475"/>
+      <c r="F73" s="475"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="478" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="478"/>
+      <c r="D74" s="478"/>
+      <c r="E74" s="478"/>
+      <c r="F74" s="478"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20995,13 +20995,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="472" t="s">
+      <c r="B77" s="475" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="472"/>
-      <c r="D77" s="472"/>
-      <c r="E77" s="472"/>
-      <c r="F77" s="472"/>
+      <c r="C77" s="475"/>
+      <c r="D77" s="475"/>
+      <c r="E77" s="475"/>
+      <c r="F77" s="475"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21022,7 +21022,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-42.153719314602398</v>
+        <v>-42.213711076197725</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21084,7 +21084,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>11.668394074882768</v>
+        <v>11.685000142554197</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21115,7 +21115,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>37.055176024325391</v>
+        <v>37.107911709860836</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21128,7 +21128,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>6.5698507846057623</v>
+        <v>6.5792007762173075</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21150,33 +21150,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="472" t="s">
+      <c r="B96" s="475" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="472"/>
-      <c r="D96" s="472"/>
-      <c r="E96" s="472"/>
-      <c r="F96" s="472"/>
+      <c r="C96" s="475"/>
+      <c r="D96" s="475"/>
+      <c r="E96" s="475"/>
+      <c r="F96" s="475"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="478" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="478"/>
+      <c r="D97" s="478"/>
+      <c r="E97" s="478"/>
+      <c r="F97" s="478"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="478" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="478"/>
+      <c r="D98" s="478"/>
+      <c r="E98" s="478"/>
+      <c r="F98" s="478"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21239,23 +21239,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="472" t="s">
+      <c r="B107" s="475" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="472"/>
-      <c r="D107" s="472"/>
-      <c r="E107" s="472"/>
-      <c r="F107" s="472"/>
+      <c r="C107" s="475"/>
+      <c r="D107" s="475"/>
+      <c r="E107" s="475"/>
+      <c r="F107" s="475"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="472" t="s">
+      <c r="B108" s="475" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="472"/>
-      <c r="D108" s="472"/>
-      <c r="E108" s="472"/>
-      <c r="F108" s="472"/>
+      <c r="C108" s="475"/>
+      <c r="D108" s="475"/>
+      <c r="E108" s="475"/>
+      <c r="F108" s="475"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-65.259063827019318</v>
+        <v>-65.351938341123912</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21287,7 +21287,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>173.87263655419051</v>
+        <v>174.12008626751856</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21299,13 +21299,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="472" t="s">
+      <c r="B114" s="475" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="472"/>
-      <c r="D114" s="472"/>
-      <c r="E114" s="472"/>
-      <c r="F114" s="472"/>
+      <c r="C114" s="475"/>
+      <c r="D114" s="475"/>
+      <c r="E114" s="475"/>
+      <c r="F114" s="475"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,7 +21350,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>231.3 HKD</v>
+        <v>231.63 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21373,7 +21373,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>198.7 HKD</v>
+        <v>198.98 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21395,7 +21395,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>184.22 HKD</v>
+        <v>184.49 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>170.85 HKD</v>
+        <v>171.09 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>158.49 HKD</v>
+        <v>158.72 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21461,7 +21461,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>189.63959677984315</v>
+        <v>189.90948550292694</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21469,13 +21469,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="476" t="s">
+      <c r="B127" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="476"/>
-      <c r="D127" s="476"/>
-      <c r="E127" s="476"/>
-      <c r="F127" s="476"/>
+      <c r="C127" s="473"/>
+      <c r="D127" s="473"/>
+      <c r="E127" s="473"/>
+      <c r="F127" s="473"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21488,22 +21488,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="477" t="s">
+      <c r="B131" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="477"/>
-      <c r="D131" s="477"/>
-      <c r="E131" s="477"/>
-      <c r="F131" s="477"/>
+      <c r="C131" s="474"/>
+      <c r="D131" s="474"/>
+      <c r="E131" s="474"/>
+      <c r="F131" s="474"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="472" t="s">
+      <c r="B132" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="472"/>
-      <c r="D132" s="472"/>
-      <c r="E132" s="472"/>
-      <c r="F132" s="472"/>
+      <c r="C132" s="475"/>
+      <c r="D132" s="475"/>
+      <c r="E132" s="475"/>
+      <c r="F132" s="475"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21568,11 +21568,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>87.391519253383962</v>
+        <v>87.515891936832716</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>93.814298285530484</v>
+        <v>93.938670968979238</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21589,11 +21589,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>109.53911727355565</v>
+        <v>109.69500967678096</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>116.92417112847011</v>
+        <v>117.08006353169542</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21629,11 +21629,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>135.92615191908908</v>
+        <v>136.11959746631686</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>144.39438889113373</v>
+        <v>144.58783443836151</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21650,11 +21650,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>153.72238738773436</v>
+        <v>153.94115994128305</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>162.89182443511163</v>
+        <v>163.11059698866035</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21672,13 +21672,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="478" t="s">
+      <c r="B149" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="472"/>
-      <c r="D149" s="472"/>
-      <c r="E149" s="472"/>
-      <c r="F149" s="472"/>
+      <c r="C149" s="475"/>
+      <c r="D149" s="475"/>
+      <c r="E149" s="475"/>
+      <c r="F149" s="475"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21686,13 +21686,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="474" t="s">
+      <c r="B152" s="477" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="474"/>
-      <c r="D152" s="474"/>
-      <c r="E152" s="474"/>
-      <c r="F152" s="474"/>
+      <c r="C152" s="477"/>
+      <c r="D152" s="477"/>
+      <c r="E152" s="477"/>
+      <c r="F152" s="477"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21729,22 +21729,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="475" t="s">
+      <c r="B161" s="472" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="475"/>
-      <c r="D161" s="475"/>
-      <c r="E161" s="475"/>
-      <c r="F161" s="475"/>
+      <c r="C161" s="472"/>
+      <c r="D161" s="472"/>
+      <c r="E161" s="472"/>
+      <c r="F161" s="472"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="475" t="s">
+      <c r="B162" s="472" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="475"/>
-      <c r="D162" s="475"/>
-      <c r="E162" s="475"/>
-      <c r="F162" s="475"/>
+      <c r="C162" s="472"/>
+      <c r="D162" s="472"/>
+      <c r="E162" s="472"/>
+      <c r="F162" s="472"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21768,15 +21768,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21791,12 +21788,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9618.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9618.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB56BA0-F5B9-4226-B946-51A23EBBF180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7DD97C-CF4D-457D-B68D-58980BFA67DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4995,30 +4995,30 @@
     <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5028,6 +5028,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5037,16 +5046,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5416,7 +5416,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>108.4</v>
+        <v>106.4</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5435,14 +5435,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>325964.69273922924</v>
+        <v>319950.58401710319</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.23276346821133451</v>
+        <v>0.24012210262343742</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5450,13 +5450,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="463" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="463"/>
-      <c r="D12" s="463"/>
-      <c r="E12" s="463"/>
-      <c r="F12" s="463"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5491,7 +5491,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1324833301067352</v>
+        <v>1.1310185977458953</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>189.90948550292694</v>
+        <v>189.66386019290991</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>93.938670968979238</v>
+        <v>93.825479581874617</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>117.08006353169542</v>
+        <v>116.93818609630651</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>144.58783443836151</v>
+        <v>144.41177994461933</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>163.11059698866035</v>
+        <v>162.91149242558481</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5634,22 +5634,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="463" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="463"/>
-      <c r="D29" s="463"/>
-      <c r="E29" s="463"/>
-      <c r="F29" s="463"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="467" t="s">
+      <c r="B30" s="463" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="467"/>
-      <c r="D30" s="467"/>
-      <c r="E30" s="467"/>
-      <c r="F30" s="467"/>
+      <c r="C30" s="463"/>
+      <c r="D30" s="463"/>
+      <c r="E30" s="463"/>
+      <c r="F30" s="463"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5661,13 +5661,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="464" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="464"/>
-      <c r="D33" s="464"/>
-      <c r="E33" s="464"/>
-      <c r="F33" s="464"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5687,13 +5687,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="464" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="464"/>
-      <c r="D36" s="464"/>
-      <c r="E36" s="464"/>
-      <c r="F36" s="464"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5722,13 +5722,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="464" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="464"/>
-      <c r="D40" s="464"/>
-      <c r="E40" s="464"/>
-      <c r="F40" s="464"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5744,13 +5744,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="464" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="464"/>
-      <c r="D43" s="464"/>
-      <c r="E43" s="464"/>
-      <c r="F43" s="464"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5814,13 +5814,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="464" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="464"/>
-      <c r="D51" s="464"/>
-      <c r="E51" s="464"/>
-      <c r="F51" s="464"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5836,7 +5836,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="464" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5858,22 +5858,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="463" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="463"/>
-      <c r="D57" s="463"/>
-      <c r="E57" s="463"/>
-      <c r="F57" s="463"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="463" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="463"/>
-      <c r="D58" s="463"/>
-      <c r="E58" s="463"/>
-      <c r="F58" s="463"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.9551918170658015E-2</v>
+        <v>8.0942430003061269E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.2380073800738006E-2</v>
+        <v>3.2988721804511276E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6008,13 +6008,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="463" t="s">
+      <c r="B73" s="461" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="463"/>
-      <c r="D73" s="463"/>
-      <c r="E73" s="463"/>
-      <c r="F73" s="463"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6033,13 +6033,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="463" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="463"/>
-      <c r="D77" s="463"/>
-      <c r="E77" s="463"/>
-      <c r="F77" s="463"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-42.213711076197725</v>
+        <v>-42.159112666631181</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>11.685000142554197</v>
+        <v>11.669886986015634</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>37.107911709860836</v>
+        <v>37.059917043908889</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.5792007762173075</v>
+        <v>6.5706913632933395</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6208,31 +6208,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="463" t="s">
+      <c r="B96" s="461" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="463"/>
-      <c r="D96" s="463"/>
-      <c r="E96" s="463"/>
-      <c r="F96" s="463"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="467" t="s">
+      <c r="B97" s="463" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="467"/>
-      <c r="D97" s="467"/>
-      <c r="E97" s="467"/>
-      <c r="F97" s="467"/>
+      <c r="C97" s="463"/>
+      <c r="D97" s="463"/>
+      <c r="E97" s="463"/>
+      <c r="F97" s="463"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="467" t="s">
+      <c r="B98" s="463" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="467"/>
-      <c r="D98" s="467"/>
-      <c r="E98" s="467"/>
-      <c r="F98" s="467"/>
+      <c r="C98" s="463"/>
+      <c r="D98" s="463"/>
+      <c r="E98" s="463"/>
+      <c r="F98" s="463"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6282,22 +6282,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="463" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="463"/>
-      <c r="D107" s="463"/>
-      <c r="E107" s="463"/>
-      <c r="F107" s="463"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="463" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="463"/>
-      <c r="D108" s="463"/>
-      <c r="E108" s="463"/>
-      <c r="F108" s="463"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-65.351938341123912</v>
+        <v>-65.267413389288336</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>174.12008626751856</v>
+        <v>173.89488266562165</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6331,13 +6331,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="463" t="s">
+      <c r="B114" s="461" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="463"/>
-      <c r="D114" s="463"/>
-      <c r="E114" s="463"/>
-      <c r="F114" s="463"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>231.63 HKD</v>
+        <v>231.33 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.7851780231952266E-2</v>
+        <v>-4.7830813543366824E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>198.98 HKD</v>
+        <v>198.73 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.4771504193757663E-3</v>
+        <v>2.500346203958686E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>184.49 HKD</v>
+        <v>184.25 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.8551499945545622E-2</v>
+        <v>2.8575909232288525E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>171.09 HKD</v>
+        <v>170.87 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.5227534809112314E-2</v>
+        <v>5.5253228004592488E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>158.72 HKD</v>
+        <v>158.51 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6468,17 +6468,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>8.2498526102287431E-2</v>
+        <v>8.2525576959361635E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="464" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="464"/>
-      <c r="D124" s="464"/>
-      <c r="E124" s="464"/>
-      <c r="F124" s="464"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>189.90948550292694</v>
+        <v>189.66386019290991</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6513,22 +6513,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="468" t="s">
+      <c r="B131" s="464" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="468"/>
-      <c r="D131" s="468"/>
-      <c r="E131" s="468"/>
-      <c r="F131" s="468"/>
+      <c r="C131" s="464"/>
+      <c r="D131" s="464"/>
+      <c r="E131" s="464"/>
+      <c r="F131" s="464"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="463" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="463"/>
-      <c r="D132" s="463"/>
-      <c r="E132" s="463"/>
-      <c r="F132" s="463"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6593,11 +6593,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>87.515891936832716</v>
+        <v>87.402700549728095</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>93.938670968979238</v>
+        <v>93.825479581874617</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6614,11 +6614,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>109.69500967678096</v>
+        <v>109.55313224139205</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>117.08006353169542</v>
+        <v>116.93818609630651</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6661,11 +6661,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>136.11959746631686</v>
+        <v>135.94354297257468</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>144.58783443836151</v>
+        <v>144.41177994461933</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6682,11 +6682,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>153.94115994128305</v>
+        <v>153.74205537820751</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>163.11059698866035</v>
+        <v>162.91149242558481</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6704,13 +6704,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="462" t="s">
+      <c r="B149" s="468" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="463"/>
-      <c r="D149" s="463"/>
-      <c r="E149" s="463"/>
-      <c r="F149" s="463"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6747,13 +6747,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="464" t="s">
+      <c r="B158" s="462" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="464"/>
-      <c r="D158" s="464"/>
-      <c r="E158" s="464"/>
-      <c r="F158" s="464"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6761,22 +6761,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="461" t="s">
+      <c r="B161" s="467" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="461"/>
-      <c r="D161" s="461"/>
-      <c r="E161" s="461"/>
-      <c r="F161" s="461"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="461" t="s">
+      <c r="B162" s="467" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="461"/>
-      <c r="D162" s="461"/>
-      <c r="E162" s="461"/>
-      <c r="F162" s="461"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6800,6 +6800,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6816,18 +6828,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10079,11 +10079,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>87.348023900969466</v>
+        <v>87.23504963118387</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-65.351938341123912</v>
+        <v>-65.267413389288336</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10489,11 +10489,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-126938.92398833385</v>
+        <v>-126774.74360273966</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-42.213711076197725</v>
+        <v>-42.159112666631181</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10506,11 +10506,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>35137.430637689373</v>
+        <v>35091.984554410657</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>11.685000142554195</v>
+        <v>11.669886986015634</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10523,11 +10523,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>111585.5077370778</v>
+        <v>111441.18516751923</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>37.107911709860836</v>
+        <v>37.059917043908889</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10540,11 +10540,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>19784.014386433322</v>
+        <v>19758.426119190233</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.5792007762173057</v>
+        <v>6.5706913632933421</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14128,20 +14128,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.2380073800738006E-2</v>
+        <v>3.2988721804511276E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.2380073800738006E-2</v>
+        <v>3.2988721804511276E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>2.4608856088560886E-2</v>
+        <v>2.5071428571428571E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>2.0075645756457566E-2</v>
+        <v>2.0453007518796994E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
@@ -15291,30 +15291,30 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>8.6234279296993286</v>
+        <v>8.6122745523257205</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.854620708884644</v>
+        <v>10.84058154928355</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.0222488979898365</v>
+        <v>7.0131664550670001</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>3.7159996715899237</v>
+        <v>3.7111934684192907</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>4.7452716998107873E-2</v>
+        <v>4.739134255810587E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.661664531766502</v>
+        <v>4.655635223684401</v>
       </c>
       <c r="L123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15348,30 +15348,30 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.9551918170658015E-2</v>
+        <v>8.0942430003061269E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.10013487738823472</v>
+        <v>0.10188516493687547</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.4780893892895167E-2</v>
+        <v>6.5913218562659776E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.4280439774814792E-2</v>
+        <v>3.4879637861083557E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>4.3775569186446374E-4</v>
+        <v>4.4540735486941607E-4</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>4.3004285348399465E-2</v>
+        <v>4.3755970147409784E-2</v>
       </c>
       <c r="L124" s="74" t="str">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
@@ -15405,23 +15405,23 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13700870368720536</v>
+        <v>0.13958405526027315</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1348218129273069E-2</v>
+        <v>7.2689350048996251E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9730213780400964E-2</v>
+        <v>3.0289052385295723E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-1.3703938185641432E-2</v>
+        <v>-1.3961531008679806E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15135688342623491</v>
+        <v>0.15420193762597617</v>
       </c>
       <c r="L125" s="22" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16330,7 +16330,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.5792007762173075</v>
+        <v>6.5706913632933395</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1324833301067352</v>
+        <v>1.1310185977458953</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16380,7 +16380,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>523588.56475940754</v>
+        <v>522911.36528619629</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>174.12008626751856</v>
+        <v>173.89488266562165</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16525,7 +16525,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>189.94057943568561</v>
+        <v>189.69491390936841</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18713,23 +18713,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>174.12008626751856</v>
+        <v>173.89488266562165</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>174.12008626751856</v>
+        <v>173.89488266562165</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>174.12008626751856</v>
+        <v>173.89488266562165</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>174.12008626751856</v>
+        <v>173.89488266562165</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>174.12008626751856</v>
+        <v>173.89488266562165</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18744,23 +18744,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>167.50418439117732</v>
+        <v>167.28753767070796</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>169.11343422732693</v>
+        <v>168.89470613378211</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>170.72268406347661</v>
+        <v>170.50187459685631</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>172.33193389962616</v>
+        <v>172.10904305993043</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>175.5504335719254</v>
+        <v>175.32337998607878</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18775,23 +18775,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>167.30154029182128</v>
+        <v>167.08515566736884</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>170.45085034443932</v>
+        <v>170.23039246237173</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>173.63069676651196</v>
+        <v>173.40612613167079</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>176.84107955803935</v>
+        <v>176.61235667526623</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>183.35345424945814</v>
+        <v>183.11630838534583</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18806,23 +18806,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>167.11259474463608</v>
+        <v>166.8964544987542</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>171.71032845938888</v>
+        <v>171.48824159232549</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>176.3963591973708</v>
+        <v>176.16821150743849</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>181.17154112276251</v>
+        <v>180.9372173035141</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>190.99277519249722</v>
+        <v>190.74574877623667</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18837,23 +18837,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>166.93642174026763</v>
+        <v>166.72050935319282</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>172.8964104137936</v>
+        <v>172.67278949092997</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>179.02663955119456</v>
+        <v>178.79508990676993</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>185.33039931545687</v>
+        <v>185.09069650826487</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>198.47183066120681</v>
+        <v>198.21513097710883</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18868,23 +18868,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>164.13691536246407</v>
+        <v>163.92462380359655</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>171.32516249458411</v>
+        <v>171.10357379384064</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>178.7864586212244</v>
+        <v>178.55521962223818</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>186.52872549696986</v>
+        <v>186.28747279752758</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>202.88862800738121</v>
+        <v>202.62621572175328</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18899,23 +18899,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>163.98375557361842</v>
+        <v>163.77166210870348</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>172.37703437242718</v>
+        <v>172.15408520063929</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>181.16553170178213</v>
+        <v>180.93121565500434</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>190.364507877313</v>
+        <v>190.11829405002692</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>210.05716862974452</v>
+        <v>209.78548469026492</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18931,23 +18931,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>161.38384667561166</v>
+        <v>161.17511588332678</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>170.83605312229497</v>
+        <v>170.61509702629417</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>180.82064975744754</v>
+        <v>180.58677977440519</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>191.36334723935843</v>
+        <v>191.11584153227335</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>214.23091692762793</v>
+        <v>213.95383474162637</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18962,23 +18962,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>161.25069392043582</v>
+        <v>161.04213534538741</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>171.76890134858172</v>
+        <v>171.54673872445952</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>182.97250733962738</v>
+        <v>182.73585418498968</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>194.901151556706</v>
+        <v>194.64907012092613</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>221.1018346350132</v>
+        <v>220.81586573496728</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18994,23 +18994,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>158.83553744187498</v>
+        <v>158.63010258419757</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>170.26335908585307</v>
+        <v>170.04314370140688</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>182.5391720423913</v>
+        <v>182.30307935537027</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>195.72021715989436</v>
+        <v>195.4670763602698</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>225.04387665306575</v>
+        <v>224.75280919098529</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19026,23 +19026,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>158.71977823154614</v>
+        <v>158.51449309462569</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>171.0906516788167</v>
+        <v>170.869366289894</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>184.48551454520307</v>
+        <v>184.2469044958745</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>198.98319147563842</v>
+        <v>198.72583040720653</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>231.62952813063202</v>
+        <v>231.32994291241337</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19058,23 +19058,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>152.26333890115691</v>
+        <v>152.06640439984551</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>168.20732474356666</v>
+        <v>167.98976859476315</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>186.14331316057556</v>
+        <v>185.90255894610553</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>206.31941922265409</v>
+        <v>206.05256961703861</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>254.53389977538976</v>
+        <v>254.20469047930533</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19090,23 +19090,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>148.5850208941572</v>
+        <v>148.39284385926942</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>167.13448357091556</v>
+        <v>166.91831501444284</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>188.71492141802204</v>
+        <v>188.47084113443123</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>213.84468908035004</v>
+        <v>213.56810643408696</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>277.27450424988484</v>
+        <v>276.91588268927222</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19122,23 +19122,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>144.13318160390148</v>
+        <v>143.94676249312644</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>164.33294632456207</v>
+        <v>164.12040122298333</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>188.55556376009562</v>
+        <v>188.31168958666316</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>217.67354524465338</v>
+        <v>217.39201042878236</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>295.07840737340086</v>
+        <v>294.69675858372358</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19154,23 +19154,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>141.61015553527963</v>
+        <v>141.42699965834805</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>163.04507772145615</v>
+        <v>162.83419832458966</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>189.42884532662299</v>
+        <v>189.18384166745187</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>222.05304159812732</v>
+        <v>221.76584242511959</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>313.01631529110631</v>
+        <v>312.61146595311686</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>231.62952813063202</v>
+        <v>231.32994291241337</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19245,7 +19245,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>198.98319147563842</v>
+        <v>198.72583040720653</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19273,7 +19273,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>184.48551454520307</v>
+        <v>184.2469044958745</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>171.0906516788167</v>
+        <v>170.869366289894</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>158.71977823154614</v>
+        <v>158.51449309462569</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19689,7 +19689,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>198.98319147563842</v>
+        <v>198.72583040720653</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19713,7 +19713,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>184.48551454520307</v>
+        <v>184.2469044958745</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19736,7 +19736,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>171.0906516788167</v>
+        <v>170.869366289894</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>184.03633421469354</v>
+        <v>183.7983051266458</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19799,7 +19799,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>231.62952813063202</v>
+        <v>231.32994291241337</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19822,7 +19822,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>158.71977823154614</v>
+        <v>158.51449309462569</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19867,7 +19867,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>108.4</v>
+        <v>106.4</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.23276346821133451</v>
+        <v>0.24012210262343742</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>174.12008626751856</v>
+        <v>173.89488266562165</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19898,7 +19898,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>4.8952956762563962E-2</v>
+        <v>4.8978344067454216E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19907,7 +19907,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>189.90948550292694</v>
+        <v>189.66386019290991</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20010,7 +20010,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>189.94057943568561</v>
+        <v>189.69491390936841</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>3.4643876575169305E-2</v>
+        <v>3.4643876575169326E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20155,11 +20155,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>87.515891936832716</v>
+        <v>87.402700549728095</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>93.938670968979238</v>
+        <v>93.825479581874617</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20167,7 +20167,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.50535029506184714</v>
+        <v>0.50530649599537125</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20180,11 +20180,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>109.69500967678096</v>
+        <v>109.55313224139205</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>117.08006353169542</v>
+        <v>116.93818609630651</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20192,7 +20192,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.38349544141179326</v>
+        <v>0.38344508027324253</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20226,11 +20226,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>136.11959746631686</v>
+        <v>135.94354297257468</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>144.58783443836151</v>
+        <v>144.41177994461933</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20238,7 +20238,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.23864869595398341</v>
+        <v>0.23859094822948357</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20251,11 +20251,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>153.94115994128305</v>
+        <v>153.74205537820751</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>163.11059698866035</v>
+        <v>162.91149242558481</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20263,7 +20263,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.14111400725085721</v>
+        <v>0.1410514778098203</v>
       </c>
     </row>
   </sheetData>
@@ -20374,7 +20374,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>108.4</v>
+        <v>106.4</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20392,14 +20392,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>325964.69273922924</v>
+        <v>319950.58401710319</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.23276346821133451</v>
+        <v>0.24012210262343742</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20407,13 +20407,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="475" t="s">
+      <c r="B12" s="472" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="475"/>
-      <c r="D12" s="475"/>
-      <c r="E12" s="475"/>
-      <c r="F12" s="475"/>
+      <c r="C12" s="472"/>
+      <c r="D12" s="472"/>
+      <c r="E12" s="472"/>
+      <c r="F12" s="472"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20451,7 +20451,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1324833301067352</v>
+        <v>1.1310185977458953</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>189.90948550292694</v>
+        <v>189.66386019290991</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>93.938670968979238</v>
+        <v>93.825479581874617</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>117.08006353169542</v>
+        <v>116.93818609630651</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20561,7 +20561,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>144.58783443836151</v>
+        <v>144.41177994461933</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>163.11059698866035</v>
+        <v>162.91149242558481</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20598,22 +20598,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="475" t="s">
+      <c r="B29" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="475"/>
-      <c r="D29" s="475"/>
-      <c r="E29" s="475"/>
-      <c r="F29" s="475"/>
+      <c r="C29" s="472"/>
+      <c r="D29" s="472"/>
+      <c r="E29" s="472"/>
+      <c r="F29" s="472"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="478" t="s">
+      <c r="B30" s="473" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="478"/>
-      <c r="D30" s="478"/>
-      <c r="E30" s="478"/>
-      <c r="F30" s="478"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20803,10 +20803,10 @@
       <c r="B54" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="477"/>
-      <c r="D54" s="477"/>
-      <c r="E54" s="477"/>
-      <c r="F54" s="477"/>
+      <c r="C54" s="474"/>
+      <c r="D54" s="474"/>
+      <c r="E54" s="474"/>
+      <c r="F54" s="474"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20822,22 +20822,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="475" t="s">
+      <c r="B57" s="472" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="475"/>
-      <c r="D57" s="475"/>
-      <c r="E57" s="475"/>
-      <c r="F57" s="475"/>
+      <c r="C57" s="472"/>
+      <c r="D57" s="472"/>
+      <c r="E57" s="472"/>
+      <c r="F57" s="472"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="475" t="s">
+      <c r="B58" s="472" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="475"/>
-      <c r="D58" s="475"/>
-      <c r="E58" s="475"/>
-      <c r="F58" s="475"/>
+      <c r="C58" s="472"/>
+      <c r="D58" s="472"/>
+      <c r="E58" s="472"/>
+      <c r="F58" s="472"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20871,7 +20871,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.9551918170658015E-2</v>
+        <v>8.0942430003061269E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20881,7 +20881,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.2380073800738006E-2</v>
+        <v>3.2988721804511276E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20972,22 +20972,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="475" t="s">
+      <c r="B73" s="472" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="475"/>
-      <c r="D73" s="475"/>
-      <c r="E73" s="475"/>
-      <c r="F73" s="475"/>
+      <c r="C73" s="472"/>
+      <c r="D73" s="472"/>
+      <c r="E73" s="472"/>
+      <c r="F73" s="472"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="478" t="s">
+      <c r="B74" s="473" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="478"/>
-      <c r="D74" s="478"/>
-      <c r="E74" s="478"/>
-      <c r="F74" s="478"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20995,13 +20995,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="475" t="s">
+      <c r="B77" s="472" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="475"/>
-      <c r="D77" s="475"/>
-      <c r="E77" s="475"/>
-      <c r="F77" s="475"/>
+      <c r="C77" s="472"/>
+      <c r="D77" s="472"/>
+      <c r="E77" s="472"/>
+      <c r="F77" s="472"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21022,7 +21022,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-42.213711076197725</v>
+        <v>-42.159112666631181</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21084,7 +21084,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>11.685000142554197</v>
+        <v>11.669886986015634</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21115,7 +21115,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>37.107911709860836</v>
+        <v>37.059917043908889</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21128,7 +21128,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>6.5792007762173075</v>
+        <v>6.5706913632933395</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21150,33 +21150,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="475" t="s">
+      <c r="B96" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="475"/>
-      <c r="D96" s="475"/>
-      <c r="E96" s="475"/>
-      <c r="F96" s="475"/>
+      <c r="C96" s="472"/>
+      <c r="D96" s="472"/>
+      <c r="E96" s="472"/>
+      <c r="F96" s="472"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="478" t="s">
+      <c r="B97" s="473" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="478"/>
-      <c r="D97" s="478"/>
-      <c r="E97" s="478"/>
-      <c r="F97" s="478"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="478" t="s">
+      <c r="B98" s="473" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="478"/>
-      <c r="D98" s="478"/>
-      <c r="E98" s="478"/>
-      <c r="F98" s="478"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21239,23 +21239,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="475" t="s">
+      <c r="B107" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="475"/>
-      <c r="D107" s="475"/>
-      <c r="E107" s="475"/>
-      <c r="F107" s="475"/>
+      <c r="C107" s="472"/>
+      <c r="D107" s="472"/>
+      <c r="E107" s="472"/>
+      <c r="F107" s="472"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="475" t="s">
+      <c r="B108" s="472" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="475"/>
-      <c r="D108" s="475"/>
-      <c r="E108" s="475"/>
-      <c r="F108" s="475"/>
+      <c r="C108" s="472"/>
+      <c r="D108" s="472"/>
+      <c r="E108" s="472"/>
+      <c r="F108" s="472"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-65.351938341123912</v>
+        <v>-65.267413389288336</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21287,7 +21287,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>174.12008626751856</v>
+        <v>173.89488266562165</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21299,13 +21299,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="475" t="s">
+      <c r="B114" s="472" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="475"/>
-      <c r="D114" s="475"/>
-      <c r="E114" s="475"/>
-      <c r="F114" s="475"/>
+      <c r="C114" s="472"/>
+      <c r="D114" s="472"/>
+      <c r="E114" s="472"/>
+      <c r="F114" s="472"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,7 +21350,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>231.63 HKD</v>
+        <v>231.33 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21373,7 +21373,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>198.98 HKD</v>
+        <v>198.73 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21395,7 +21395,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>184.49 HKD</v>
+        <v>184.25 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>171.09 HKD</v>
+        <v>170.87 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>158.72 HKD</v>
+        <v>158.51 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21461,7 +21461,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>189.90948550292694</v>
+        <v>189.66386019290991</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21469,13 +21469,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="473" t="s">
+      <c r="B127" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="473"/>
-      <c r="D127" s="473"/>
-      <c r="E127" s="473"/>
-      <c r="F127" s="473"/>
+      <c r="C127" s="476"/>
+      <c r="D127" s="476"/>
+      <c r="E127" s="476"/>
+      <c r="F127" s="476"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21488,22 +21488,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="474" t="s">
+      <c r="B131" s="477" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="474"/>
-      <c r="D131" s="474"/>
-      <c r="E131" s="474"/>
-      <c r="F131" s="474"/>
+      <c r="C131" s="477"/>
+      <c r="D131" s="477"/>
+      <c r="E131" s="477"/>
+      <c r="F131" s="477"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="475" t="s">
+      <c r="B132" s="472" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="475"/>
-      <c r="D132" s="475"/>
-      <c r="E132" s="475"/>
-      <c r="F132" s="475"/>
+      <c r="C132" s="472"/>
+      <c r="D132" s="472"/>
+      <c r="E132" s="472"/>
+      <c r="F132" s="472"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21568,11 +21568,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>87.515891936832716</v>
+        <v>87.402700549728095</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>93.938670968979238</v>
+        <v>93.825479581874617</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21589,11 +21589,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>109.69500967678096</v>
+        <v>109.55313224139205</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>117.08006353169542</v>
+        <v>116.93818609630651</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21629,11 +21629,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>136.11959746631686</v>
+        <v>135.94354297257468</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>144.58783443836151</v>
+        <v>144.41177994461933</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21650,11 +21650,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>153.94115994128305</v>
+        <v>153.74205537820751</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>163.11059698866035</v>
+        <v>162.91149242558481</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21672,13 +21672,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="476" t="s">
+      <c r="B149" s="478" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="475"/>
-      <c r="D149" s="475"/>
-      <c r="E149" s="475"/>
-      <c r="F149" s="475"/>
+      <c r="C149" s="472"/>
+      <c r="D149" s="472"/>
+      <c r="E149" s="472"/>
+      <c r="F149" s="472"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21686,13 +21686,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="477" t="s">
+      <c r="B152" s="474" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="477"/>
-      <c r="D152" s="477"/>
-      <c r="E152" s="477"/>
-      <c r="F152" s="477"/>
+      <c r="C152" s="474"/>
+      <c r="D152" s="474"/>
+      <c r="E152" s="474"/>
+      <c r="F152" s="474"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21729,22 +21729,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="472" t="s">
+      <c r="B161" s="475" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="472"/>
-      <c r="D161" s="472"/>
-      <c r="E161" s="472"/>
-      <c r="F161" s="472"/>
+      <c r="C161" s="475"/>
+      <c r="D161" s="475"/>
+      <c r="E161" s="475"/>
+      <c r="F161" s="475"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="472" t="s">
+      <c r="B162" s="475" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="472"/>
-      <c r="D162" s="472"/>
-      <c r="E162" s="472"/>
-      <c r="F162" s="472"/>
+      <c r="C162" s="475"/>
+      <c r="D162" s="475"/>
+      <c r="E162" s="475"/>
+      <c r="F162" s="475"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21768,12 +21768,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21788,15 +21791,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9618.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9618.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7DD97C-CF4D-457D-B68D-58980BFA67DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDAD5803-A1F2-AC45-9138-CE8962A0E39A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -39,6 +39,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -3275,27 +3286,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="19">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.00\x"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="170" formatCode="#,##0_ "/>
-    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="176" formatCode="0.000_ "/>
-    <numFmt numFmtId="177" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="178" formatCode="0.0\x"/>
-    <numFmt numFmtId="179" formatCode="0\x"/>
-    <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
-    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.00\x"/>
+    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="171" formatCode="#,##0_ "/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="173" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="174" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="175" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="177" formatCode="0.000_ "/>
+    <numFmt numFmtId="178" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="179" formatCode="0.0\x"/>
+    <numFmt numFmtId="180" formatCode="0\x"/>
+    <numFmt numFmtId="181" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="182" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="72">
+  <fonts count="72" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4047,7 +4058,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4089,17 +4100,17 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4108,7 +4119,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4182,10 +4193,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4196,7 +4207,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4234,7 +4245,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4244,7 +4255,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4255,19 +4266,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4275,8 +4286,8 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4299,29 +4310,29 @@
     </xf>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4338,15 +4349,15 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4357,11 +4368,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4422,14 +4433,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4442,7 +4453,7 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4479,7 +4490,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4496,7 +4507,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4542,7 +4553,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4557,13 +4568,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4579,53 +4590,53 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="182" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4642,7 +4653,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -4655,21 +4666,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="181" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4679,14 +4690,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="174" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4695,8 +4706,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4708,7 +4719,7 @@
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4716,7 +4727,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4755,7 +4766,7 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4769,39 +4780,39 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="173" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="180" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4812,7 +4823,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4823,10 +4834,10 @@
     <xf numFmtId="9" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4835,7 +4846,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4848,7 +4859,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4857,8 +4868,8 @@
     <xf numFmtId="40" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4866,10 +4877,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4878,10 +4889,10 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4898,16 +4909,16 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4928,7 +4939,7 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4946,7 +4957,7 @@
     <xf numFmtId="40" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4956,10 +4967,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4974,7 +4985,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="71" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4988,12 +4999,18 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -5001,24 +5018,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5028,30 +5039,30 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5333,7 +5344,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:I167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -5342,7 +5353,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="13.9">
+    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="200" t="s">
         <v>225</v>
       </c>
@@ -5355,7 +5366,7 @@
       <c r="H2" s="21"/>
       <c r="I2" s="21"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="E3" s="428" t="s">
         <v>538</v>
       </c>
@@ -5363,7 +5374,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="12.4">
+    <row r="4" spans="1:9" ht="14" x14ac:dyDescent="0.2">
       <c r="B4" s="421" t="s">
         <v>533</v>
       </c>
@@ -5377,7 +5388,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>349</v>
       </c>
@@ -5391,7 +5402,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
@@ -5401,7 +5412,7 @@
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>351</v>
       </c>
@@ -5411,16 +5422,16 @@
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B8" s="4" t="s">
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>106.4</v>
+        <v>103.8</v>
       </c>
       <c r="E8" s="32"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>346</v>
       </c>
@@ -5429,43 +5440,43 @@
         <v>3007054361.0630002</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>352</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>319950.58401710319</v>
+        <v>312132.24267833942</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.24012210262343742</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>0.25085546041516749</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+    <row r="12" spans="1:9" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B12" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="C12" s="463"/>
+      <c r="D12" s="463"/>
+      <c r="E12" s="463"/>
+      <c r="F12" s="463"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
         <v>2-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B15" s="1" t="s">
         <v>319</v>
       </c>
@@ -5480,7 +5491,7 @@
         <v>CNY/HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>320</v>
       </c>
@@ -5491,10 +5502,10 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1310185977458953</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>1.1315830089569092</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>532</v>
       </c>
@@ -5508,14 +5519,14 @@
         <v>558</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B18" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C7&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>189.66386019290991</v>
+        <v>189.75850798139936</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5524,7 +5535,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B19" s="2" t="s">
         <v>275</v>
       </c>
@@ -5540,11 +5551,11 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B21" s="42" t="s">
         <v>404</v>
       </c>
@@ -5559,13 +5570,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B22" s="1" t="s">
         <v>312</v>
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>93.825479581874617</v>
+        <v>93.869096074266068</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5574,13 +5585,13 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>313</v>
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>116.93818609630651</v>
+        <v>116.99285629904411</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5589,13 +5600,13 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>315</v>
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>144.41177994461933</v>
+        <v>144.47961973069502</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5604,13 +5615,13 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B25" s="1" t="s">
         <v>314</v>
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>162.91149242558481</v>
+        <v>162.9882141875724</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5619,11 +5630,11 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:6" ht="13.9">
+    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A27" s="200" t="s">
         <v>280</v>
       </c>
@@ -5633,25 +5644,25 @@
       <c r="E27" s="34"/>
       <c r="F27" s="34"/>
     </row>
-    <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B29" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="463" t="s">
+      <c r="C29" s="463"/>
+      <c r="D29" s="463"/>
+      <c r="E29" s="463"/>
+      <c r="F29" s="463"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="467" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="463"/>
-      <c r="D30" s="463"/>
-      <c r="E30" s="463"/>
-      <c r="F30" s="463"/>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="C30" s="467"/>
+      <c r="D30" s="467"/>
+      <c r="E30" s="467"/>
+      <c r="F30" s="467"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B32" s="192" t="s">
         <v>195</v>
       </c>
@@ -5660,16 +5671,16 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+    <row r="33" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="464" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
-    </row>
-    <row r="34" spans="2:6">
+      <c r="C33" s="464"/>
+      <c r="D33" s="464"/>
+      <c r="E33" s="464"/>
+      <c r="F33" s="464"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="44" t="s">
         <v>197</v>
       </c>
@@ -5682,20 +5693,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="35" spans="2:6">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B35" s="44"/>
       <c r="C35" s="73"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="464" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
-    </row>
-    <row r="37" spans="2:6">
+      <c r="C36" s="464"/>
+      <c r="D36" s="464"/>
+      <c r="E36" s="464"/>
+      <c r="F36" s="464"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B37" s="44" t="s">
         <v>199</v>
       </c>
@@ -5708,7 +5719,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B38" s="49" t="s">
         <v>200</v>
       </c>
@@ -5721,16 +5732,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B40" s="464" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
-    </row>
-    <row r="41" spans="2:6">
+      <c r="C40" s="464"/>
+      <c r="D40" s="464"/>
+      <c r="E40" s="464"/>
+      <c r="F40" s="464"/>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B41" s="44" t="s">
         <v>202</v>
       </c>
@@ -5743,16 +5754,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B43" s="464" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
-    </row>
-    <row r="44" spans="2:6">
+      <c r="C43" s="464"/>
+      <c r="D43" s="464"/>
+      <c r="E43" s="464"/>
+      <c r="F43" s="464"/>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B44" s="44" t="s">
         <v>267</v>
       </c>
@@ -5767,7 +5778,7 @@
       <c r="E44" s="244"/>
       <c r="F44" s="244"/>
     </row>
-    <row r="45" spans="2:6">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B45" s="44" t="s">
         <v>268</v>
       </c>
@@ -5782,7 +5793,7 @@
       <c r="E45" s="244"/>
       <c r="F45" s="244"/>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B46" s="44" t="s">
         <v>203</v>
       </c>
@@ -5795,12 +5806,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B48" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="49" spans="2:6">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B49" s="44" t="s">
         <v>223</v>
       </c>
@@ -5813,16 +5824,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B51" s="464" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
-    </row>
-    <row r="52" spans="2:6">
+      <c r="C51" s="464"/>
+      <c r="D51" s="464"/>
+      <c r="E51" s="464"/>
+      <c r="F51" s="464"/>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="44" t="s">
         <v>204</v>
       </c>
@@ -5835,8 +5846,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B54" s="464" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5844,7 +5855,7 @@
       <c r="E54" s="465"/>
       <c r="F54" s="465"/>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="44" t="s">
         <v>207</v>
       </c>
@@ -5857,25 +5868,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+    <row r="57" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B57" s="463" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
-    </row>
-    <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="C57" s="463"/>
+      <c r="D57" s="463"/>
+      <c r="E57" s="463"/>
+      <c r="F57" s="463"/>
+    </row>
+    <row r="58" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B58" s="463" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
-    </row>
-    <row r="60" spans="2:6">
+      <c r="C58" s="463"/>
+      <c r="D58" s="463"/>
+      <c r="E58" s="463"/>
+      <c r="F58" s="463"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="44" t="s">
         <v>227</v>
       </c>
@@ -5888,7 +5899,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B61" s="44" t="s">
         <v>213</v>
       </c>
@@ -5901,23 +5912,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="204" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.0942430003061269E-2</v>
+        <v>8.3011294104839359E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
-    <row r="63" spans="2:6">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B63" s="204" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.2988721804511276E-2</v>
+        <v>3.3815028901734101E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5927,7 +5938,7 @@
         <v>0.51217277206029399</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B65" s="192" t="s">
         <v>325</v>
       </c>
@@ -5938,7 +5949,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B66" s="44" t="s">
         <v>326</v>
       </c>
@@ -5951,7 +5962,7 @@
         <v>0.12811576111950596</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="229" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -5965,7 +5976,7 @@
         <v>3.3655816827304348E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="229" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -5979,7 +5990,7 @@
         <v>1.6240671367246462</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="229" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -5993,7 +6004,7 @@
         <v>2.3438965902371725</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="13.9">
+    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A71" s="200" t="s">
         <v>477</v>
       </c>
@@ -6003,45 +6014,45 @@
       <c r="E71" s="34"/>
       <c r="F71" s="34"/>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A72" s="191"/>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
+      <c r="B73" s="463" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
-    </row>
-    <row r="74" spans="1:6">
+      <c r="C73" s="463"/>
+      <c r="D73" s="463"/>
+      <c r="E73" s="463"/>
+      <c r="F73" s="463"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A75" s="191"/>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A76" s="191"/>
       <c r="B76" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="463" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="C77" s="463"/>
+      <c r="D77" s="463"/>
+      <c r="E77" s="463"/>
+      <c r="F77" s="463"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A78" s="191"/>
       <c r="B78" s="1" t="s">
         <v>215</v>
@@ -6055,21 +6066,21 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="191"/>
       <c r="B79" s="44" t="s">
         <v>234</v>
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-42.159112666631181</v>
+        <v>-42.180151291356594</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A80" s="191"/>
       <c r="B80" s="229" t="s">
         <v>309</v>
@@ -6079,7 +6090,7 @@
         <v>0.36820511135930623</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A81" s="191"/>
       <c r="B81" s="229" t="s">
         <v>311</v>
@@ -6089,16 +6100,16 @@
         <v>2.8852377432054559</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A82" s="191"/>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A84" s="191"/>
       <c r="B84" s="1" t="s">
         <v>224</v>
@@ -6112,7 +6123,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A85" s="191"/>
       <c r="B85" s="229" t="s">
         <v>222</v>
@@ -6126,30 +6137,30 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A86" s="191"/>
       <c r="B86" s="44" t="s">
         <v>235</v>
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>11.669886986015634</v>
+        <v>11.675710599402095</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A87" s="191"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A88" s="191"/>
       <c r="B88" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A89" s="191"/>
       <c r="B89" s="1" t="s">
         <v>217</v>
@@ -6163,38 +6174,38 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A90" s="191"/>
       <c r="B90" s="44" t="s">
         <v>236</v>
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>37.059917043908889</v>
+        <v>37.078411021550387</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A91" s="191"/>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
         <v>469</v>
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.5706913632933395</v>
+        <v>6.5739703295958796</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="13.9">
+    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A94" s="200" t="s">
         <v>470</v>
       </c>
@@ -6204,42 +6215,42 @@
       <c r="E94" s="34"/>
       <c r="F94" s="34"/>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A95" s="191"/>
     </row>
-    <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
+    <row r="96" spans="1:6" ht="11.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B96" s="463" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
-    </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="463" t="s">
+      <c r="C96" s="463"/>
+      <c r="D96" s="463"/>
+      <c r="E96" s="463"/>
+      <c r="F96" s="463"/>
+    </row>
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="467" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="463"/>
-      <c r="D97" s="463"/>
-      <c r="E97" s="463"/>
-      <c r="F97" s="463"/>
-    </row>
-    <row r="98" spans="2:6">
-      <c r="B98" s="463" t="s">
+      <c r="C97" s="467"/>
+      <c r="D97" s="467"/>
+      <c r="E97" s="467"/>
+      <c r="F97" s="467"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B98" s="467" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="463"/>
-      <c r="D98" s="463"/>
-      <c r="E98" s="463"/>
-      <c r="F98" s="463"/>
-    </row>
-    <row r="100" spans="2:6">
+      <c r="C98" s="467"/>
+      <c r="D98" s="467"/>
+      <c r="E98" s="467"/>
+      <c r="F98" s="467"/>
+    </row>
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="101" spans="2:6">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B101" s="49" t="s">
         <v>467</v>
       </c>
@@ -6248,7 +6259,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="2:6">
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="229" t="s">
         <v>318</v>
       </c>
@@ -6257,7 +6268,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="229" t="s">
         <v>317</v>
       </c>
@@ -6266,7 +6277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="44" t="s">
         <v>214</v>
       </c>
@@ -6275,76 +6286,76 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="106" spans="2:6">
+    <row r="106" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B106" s="250" t="s">
         <v>281</v>
       </c>
       <c r="C106" s="116"/>
     </row>
-    <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B107" s="463" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
-    </row>
-    <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="C107" s="463"/>
+      <c r="D107" s="463"/>
+      <c r="E107" s="463"/>
+      <c r="F107" s="463"/>
+    </row>
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B108" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
-    </row>
-    <row r="110" spans="2:6">
+      <c r="C108" s="463"/>
+      <c r="D108" s="463"/>
+      <c r="E108" s="463"/>
+      <c r="F108" s="463"/>
+    </row>
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="192" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="111" spans="2:6">
+    <row r="111" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B111" s="49" t="s">
         <v>468</v>
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-65.267413389288336</v>
+        <v>-65.299983728895668</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="44" t="s">
         <v>323</v>
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>173.89488266562165</v>
+        <v>173.98166127519536</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
+    <row r="114" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B114" s="463" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
-    </row>
-    <row r="116" spans="2:6">
+      <c r="C114" s="463"/>
+      <c r="D114" s="463"/>
+      <c r="E114" s="463"/>
+      <c r="F114" s="463"/>
+    </row>
+    <row r="116" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B116" s="192" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="117" spans="2:6" ht="12.4">
+    <row r="117" spans="2:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B117" s="342" t="s">
         <v>101</v>
       </c>
@@ -6361,7 +6372,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="118" spans="2:6">
+    <row r="118" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
         <v>Snowball Scenario (10yrs)</v>
@@ -6372,7 +6383,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>231.33 HKD</v>
+        <v>231.45 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6380,10 +6391,10 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.7830813543366824E-2</v>
-      </c>
-    </row>
-    <row r="119" spans="2:6">
+        <v>-4.7838899145048276E-2</v>
+      </c>
+    </row>
+    <row r="119" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
         <v>Optimistic (10yrs)</v>
@@ -6394,7 +6405,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>198.73 HKD</v>
+        <v>198.83 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6402,10 +6413,10 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.500346203958686E-3</v>
-      </c>
-    </row>
-    <row r="120" spans="2:6">
+        <v>2.4914009688719284E-3</v>
+      </c>
+    </row>
+    <row r="120" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
         <v>Base (10yrs)</v>
@@ -6416,7 +6427,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>184.25 HKD</v>
+        <v>184.34 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6424,10 +6435,10 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.8575909232288525E-2</v>
-      </c>
-    </row>
-    <row r="121" spans="2:6">
+        <v>2.8566496019313072E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
         <v>Pessimistic (10yrs)</v>
@@ -6438,7 +6449,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>170.87 HKD</v>
+        <v>170.95 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6446,10 +6457,10 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.5253228004592488E-2</v>
-      </c>
-    </row>
-    <row r="122" spans="2:6">
+        <v>5.5243319661748662E-2</v>
+      </c>
+    </row>
+    <row r="122" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
         <v>Devil's advocate (10yrs)</v>
@@ -6460,7 +6471,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>158.51 HKD</v>
+        <v>158.59 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6468,32 +6479,32 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>8.2525576959361635E-2</v>
-      </c>
-    </row>
-    <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+        <v>8.2515145044167307E-2</v>
+      </c>
+    </row>
+    <row r="124" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B124" s="464" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
-    </row>
-    <row r="125" spans="2:6">
+      <c r="C124" s="464"/>
+      <c r="D124" s="464"/>
+      <c r="E124" s="464"/>
+      <c r="F124" s="464"/>
+    </row>
+    <row r="125" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B125" s="193" t="s">
         <v>218</v>
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>189.66386019290991</v>
+        <v>189.75850798139936</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="2:6" ht="24.5" customHeight="1">
+    <row r="127" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B127" s="466" t="s">
         <v>358</v>
       </c>
@@ -6502,7 +6513,7 @@
       <c r="E127" s="466"/>
       <c r="F127" s="466"/>
     </row>
-    <row r="129" spans="1:6" ht="13.9">
+    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A129" s="200" t="s">
         <v>474</v>
       </c>
@@ -6512,30 +6523,30 @@
       <c r="E129" s="34"/>
       <c r="F129" s="34"/>
     </row>
-    <row r="131" spans="1:6">
-      <c r="B131" s="464" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B131" s="468" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="464"/>
-      <c r="D131" s="464"/>
-      <c r="E131" s="464"/>
-      <c r="F131" s="464"/>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="C131" s="468"/>
+      <c r="D131" s="468"/>
+      <c r="E131" s="468"/>
+      <c r="F131" s="468"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B132" s="463" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
-    </row>
-    <row r="134" spans="1:6">
+      <c r="C132" s="463"/>
+      <c r="D132" s="463"/>
+      <c r="E132" s="463"/>
+      <c r="F132" s="463"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B134" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B135" s="1" t="s">
         <v>221</v>
       </c>
@@ -6544,7 +6555,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B136" s="194" t="s">
         <v>220</v>
       </c>
@@ -6557,14 +6568,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B138" s="192" t="s">
         <v>494</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
-    <row r="139" spans="1:6" ht="12.4">
+    <row r="139" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -6583,7 +6594,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="336" t="s">
         <v>312</v>
       </c>
@@ -6593,18 +6604,18 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>87.402700549728095</v>
+        <v>87.446317042119546</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>93.825479581874617</v>
+        <v>93.869096074266068</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="336" t="s">
         <v>313</v>
       </c>
@@ -6614,25 +6625,25 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>109.55313224139205</v>
+        <v>109.60780244412965</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>116.93818609630651</v>
+        <v>116.99285629904411</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="194"/>
       <c r="C142" s="194"/>
       <c r="D142" s="194"/>
       <c r="E142" s="194"/>
       <c r="F142" s="194"/>
     </row>
-    <row r="143" spans="1:6" ht="12.4">
+    <row r="143" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -6651,7 +6662,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B144" s="336" t="s">
         <v>315</v>
       </c>
@@ -6661,18 +6672,18 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>135.94354297257468</v>
+        <v>136.01138275865037</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>144.41177994461933</v>
+        <v>144.47961973069502</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B145" s="336" t="s">
         <v>314</v>
       </c>
@@ -6682,18 +6693,18 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>153.74205537820751</v>
+        <v>153.81877714019512</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>162.91149242558481</v>
+        <v>162.9882141875724</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="13.9">
+    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A147" s="200" t="s">
         <v>475</v>
       </c>
@@ -6703,21 +6714,21 @@
       <c r="E147" s="34"/>
       <c r="F147" s="34"/>
     </row>
-    <row r="149" spans="1:6">
-      <c r="B149" s="468" t="s">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B149" s="462" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="C149" s="463"/>
+      <c r="D149" s="463"/>
+      <c r="E149" s="463"/>
+      <c r="F149" s="463"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B151" s="192" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B152" s="465" t="s">
         <v>293</v>
       </c>
@@ -6726,92 +6737,80 @@
       <c r="E152" s="465"/>
       <c r="F152" s="465"/>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B153" s="196" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B154" s="196" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B155" s="196" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B157" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
+    <row r="158" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B158" s="464" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
-    </row>
-    <row r="160" spans="1:6">
+      <c r="C158" s="464"/>
+      <c r="D158" s="464"/>
+      <c r="E158" s="464"/>
+      <c r="F158" s="464"/>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B160" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="467" t="s">
+    <row r="161" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B161" s="461" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
-    </row>
-    <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="467" t="s">
+      <c r="C161" s="461"/>
+      <c r="D161" s="461"/>
+      <c r="E161" s="461"/>
+      <c r="F161" s="461"/>
+    </row>
+    <row r="162" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B162" s="461" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
-    </row>
-    <row r="164" spans="2:6">
+      <c r="C162" s="461"/>
+      <c r="D162" s="461"/>
+      <c r="E162" s="461"/>
+      <c r="F162" s="461"/>
+    </row>
+    <row r="164" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B164" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="165" spans="2:6">
+    <row r="165" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B165" s="196" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
+    <row r="166" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B166" s="196" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
+    <row r="167" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B167" s="196" t="s">
         <v>300</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6828,6 +6827,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6855,15 +6866,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
         <v>CNY</v>
@@ -6912,7 +6923,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>93</v>
       </c>
@@ -6928,7 +6939,7 @@
       <c r="L2" s="35"/>
       <c r="M2" s="35"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>25</v>
       </c>
@@ -6936,7 +6947,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="31" t="s">
         <v>0</v>
       </c>
@@ -6962,7 +6973,7 @@
       <c r="L4" s="287"/>
       <c r="M4" s="287"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="38" t="s">
         <v>40</v>
       </c>
@@ -6988,7 +6999,7 @@
       <c r="L5" s="287"/>
       <c r="M5" s="287"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="38" t="s">
         <v>51</v>
       </c>
@@ -7019,7 +7030,7 @@
       <c r="L6" s="287"/>
       <c r="M6" s="287"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="66" t="s">
         <v>58</v>
       </c>
@@ -7045,7 +7056,7 @@
       <c r="L7" s="288"/>
       <c r="M7" s="288"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="38" t="s">
         <v>46</v>
       </c>
@@ -7071,7 +7082,7 @@
       <c r="L8" s="287"/>
       <c r="M8" s="287"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="38" t="s">
         <v>134</v>
       </c>
@@ -7097,7 +7108,7 @@
       <c r="L9" s="287"/>
       <c r="M9" s="287"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="38" t="s">
         <v>138</v>
       </c>
@@ -7113,7 +7124,7 @@
       <c r="L10" s="287"/>
       <c r="M10" s="287"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="38" t="s">
         <v>133</v>
       </c>
@@ -7129,7 +7140,7 @@
       <c r="L11" s="287"/>
       <c r="M11" s="287"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="38" t="s">
         <v>37</v>
       </c>
@@ -7155,7 +7166,7 @@
       <c r="L12" s="287"/>
       <c r="M12" s="287"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="38" t="s">
         <v>64</v>
       </c>
@@ -7171,7 +7182,7 @@
       <c r="L13" s="287"/>
       <c r="M13" s="287"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="38" t="s">
         <v>47</v>
       </c>
@@ -7197,7 +7208,7 @@
       <c r="L14" s="287"/>
       <c r="M14" s="287"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="41" t="s">
         <v>39</v>
       </c>
@@ -7223,7 +7234,7 @@
       <c r="L15" s="289"/>
       <c r="M15" s="289"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="27" t="s">
         <v>41</v>
       </c>
@@ -7249,13 +7260,13 @@
       <c r="L16" s="287"/>
       <c r="M16" s="287"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="26" t="s">
         <v>44</v>
       </c>
@@ -7277,7 +7288,7 @@
       <c r="L19" s="287"/>
       <c r="M19" s="287"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="26" t="s">
         <v>50</v>
       </c>
@@ -7293,7 +7304,7 @@
       <c r="L20" s="287"/>
       <c r="M20" s="287"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="26" t="s">
         <v>49</v>
       </c>
@@ -7309,7 +7320,7 @@
       <c r="L21" s="287"/>
       <c r="M21" s="287"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="26" t="s">
         <v>286</v>
       </c>
@@ -7333,7 +7344,7 @@
       <c r="L22" s="287"/>
       <c r="M22" s="287"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="26" t="s">
         <v>288</v>
       </c>
@@ -7357,7 +7368,7 @@
       <c r="L23" s="287"/>
       <c r="M23" s="287"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="26" t="s">
         <v>287</v>
       </c>
@@ -7381,7 +7392,7 @@
       <c r="L24" s="287"/>
       <c r="M24" s="287"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="23" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -7409,7 +7420,7 @@
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>26</v>
       </c>
@@ -7417,7 +7428,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="25" t="s">
         <v>22</v>
       </c>
@@ -7443,7 +7454,7 @@
       <c r="L28" s="287"/>
       <c r="M28" s="287"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="25" t="s">
         <v>30</v>
       </c>
@@ -7468,7 +7479,7 @@
       <c r="L29" s="287"/>
       <c r="M29" s="287"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="28" t="s">
         <v>38</v>
       </c>
@@ -7495,7 +7506,7 @@
       <c r="L30" s="289"/>
       <c r="M30" s="289"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="28" t="s">
         <v>28</v>
       </c>
@@ -7520,7 +7531,7 @@
       <c r="L31" s="289"/>
       <c r="M31" s="289"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="25" t="s">
         <v>143</v>
       </c>
@@ -7545,7 +7556,7 @@
       <c r="L32" s="287"/>
       <c r="M32" s="287"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="34" t="s">
         <v>78</v>
       </c>
@@ -7561,12 +7572,12 @@
       <c r="L34" s="35"/>
       <c r="M34" s="35"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="31" t="s">
         <v>0</v>
       </c>
@@ -7615,7 +7626,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="38" t="s">
         <v>40</v>
       </c>
@@ -7664,7 +7675,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="30" t="s">
         <v>55</v>
       </c>
@@ -7713,7 +7724,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="38" t="s">
         <v>51</v>
       </c>
@@ -7762,7 +7773,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="66" t="s">
         <v>58</v>
       </c>
@@ -7811,7 +7822,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="66" t="s">
         <v>61</v>
       </c>
@@ -7860,7 +7871,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="38" t="s">
         <v>46</v>
       </c>
@@ -7909,7 +7920,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="41" t="s">
         <v>127</v>
       </c>
@@ -7958,7 +7969,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="41" t="s">
         <v>139</v>
       </c>
@@ -8007,7 +8018,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="38" t="s">
         <v>65</v>
       </c>
@@ -8056,7 +8067,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="38" t="s">
         <v>47</v>
       </c>
@@ -8105,7 +8116,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="41" t="s">
         <v>39</v>
       </c>
@@ -8154,7 +8165,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="27" t="s">
         <v>41</v>
       </c>
@@ -8203,12 +8214,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="38" t="s">
         <v>37</v>
       </c>
@@ -8257,7 +8268,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="38" t="s">
         <v>64</v>
       </c>
@@ -8306,12 +8317,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="156" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="38" t="s">
         <v>134</v>
       </c>
@@ -8360,7 +8371,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="38" t="s">
         <v>138</v>
       </c>
@@ -8409,7 +8420,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="38" t="s">
         <v>133</v>
       </c>
@@ -8458,7 +8469,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="38" t="s">
         <v>135</v>
       </c>
@@ -8507,13 +8518,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="26" t="s">
         <v>44</v>
       </c>
@@ -8562,7 +8573,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="26" t="s">
         <v>50</v>
       </c>
@@ -8611,7 +8622,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="26" t="s">
         <v>49</v>
       </c>
@@ -8660,7 +8671,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="26" t="s">
         <v>305</v>
       </c>
@@ -8709,7 +8720,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="23" t="s">
         <v>34</v>
       </c>
@@ -8758,12 +8769,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="88" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8813,7 +8824,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="30" t="s">
         <v>55</v>
       </c>
@@ -8862,7 +8873,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="77" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8912,7 +8923,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="41" t="s">
         <v>139</v>
       </c>
@@ -8961,7 +8972,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="77" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -9011,7 +9022,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="34" t="s">
         <v>79</v>
       </c>
@@ -9027,13 +9038,13 @@
       <c r="L74" s="35"/>
       <c r="M74" s="35"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="25" t="s">
         <v>1</v>
       </c>
@@ -9082,7 +9093,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="90" t="s">
         <v>82</v>
       </c>
@@ -9116,7 +9127,7 @@
       <c r="L77" s="291"/>
       <c r="M77" s="291"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="90" t="s">
         <v>83</v>
       </c>
@@ -9150,7 +9161,7 @@
       <c r="L78" s="291"/>
       <c r="M78" s="291"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="25" t="s">
         <v>38</v>
       </c>
@@ -9199,7 +9210,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="25" t="s">
         <v>28</v>
       </c>
@@ -9280,7 +9291,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -9291,7 +9302,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="17" t="s">
         <v>35</v>
       </c>
@@ -9307,7 +9318,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="76" t="s">
         <v>131</v>
       </c>
@@ -9318,7 +9329,7 @@
       <c r="G2" s="35"/>
       <c r="H2" s="35"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>154</v>
       </c>
@@ -9338,7 +9349,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
@@ -9360,7 +9371,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
@@ -9381,7 +9392,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
@@ -9402,7 +9413,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>66</v>
       </c>
@@ -9423,7 +9434,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>144</v>
       </c>
@@ -9444,7 +9455,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
@@ -9466,7 +9477,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
@@ -9486,7 +9497,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
@@ -9498,7 +9509,7 @@
       </c>
       <c r="H11" s="232"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="77" t="s">
         <v>69</v>
       </c>
@@ -9522,12 +9533,12 @@
         <v>161854.1</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="77"/>
       <c r="G13" s="78"/>
       <c r="H13" s="19"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>153</v>
       </c>
@@ -9547,7 +9558,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>329</v>
       </c>
@@ -9567,7 +9578,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
@@ -9587,7 +9598,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>66</v>
       </c>
@@ -9608,7 +9619,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>144</v>
       </c>
@@ -9628,7 +9639,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>24</v>
       </c>
@@ -9650,7 +9661,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>16</v>
       </c>
@@ -9670,7 +9681,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>17</v>
       </c>
@@ -9690,7 +9701,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>18</v>
       </c>
@@ -9702,7 +9713,7 @@
       </c>
       <c r="H22" s="232"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>19</v>
       </c>
@@ -9715,7 +9726,7 @@
       </c>
       <c r="H23" s="232"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="77" t="s">
         <v>70</v>
       </c>
@@ -9739,7 +9750,7 @@
         <v>47409.899999999994</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>169</v>
       </c>
@@ -9756,7 +9767,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
@@ -9776,7 +9787,7 @@
         <v>-101040.34999999998</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>4</v>
       </c>
@@ -9791,7 +9802,7 @@
       </c>
       <c r="H28" s="170"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>5</v>
       </c>
@@ -9810,7 +9821,7 @@
         <v>-173527.34999999998</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>6</v>
       </c>
@@ -9826,7 +9837,7 @@
       </c>
       <c r="H30" s="170"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="77" t="s">
         <v>172</v>
       </c>
@@ -9843,7 +9854,7 @@
       </c>
       <c r="H31" s="170"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
@@ -9863,7 +9874,7 @@
         <v>308068.65000000002</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="80" t="s">
         <v>2</v>
       </c>
@@ -9874,7 +9885,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="177"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="80"/>
       <c r="C34" s="81"/>
       <c r="F34" s="178" t="s">
@@ -9887,7 +9898,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>170</v>
       </c>
@@ -9906,7 +9917,7 @@
         <v>98804.65</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>11</v>
       </c>
@@ -9923,7 +9934,7 @@
       </c>
       <c r="H36" s="177"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>12</v>
       </c>
@@ -9939,7 +9950,7 @@
       </c>
       <c r="H37" s="177"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>13</v>
       </c>
@@ -9955,7 +9966,7 @@
       </c>
       <c r="H38" s="177"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
@@ -9974,7 +9985,7 @@
         <v>16362.7</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="77" t="s">
         <v>173</v>
       </c>
@@ -9994,7 +10005,7 @@
         <v>209264</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>15</v>
       </c>
@@ -10014,7 +10025,7 @@
         <v>110732.3</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="80" t="s">
         <v>20</v>
       </c>
@@ -10033,7 +10044,7 @@
         <v>98531.7</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="76" t="s">
         <v>92</v>
       </c>
@@ -10044,7 +10055,7 @@
       <c r="G44" s="35"/>
       <c r="H44" s="35"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>228</v>
       </c>
@@ -10058,7 +10069,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>230</v>
       </c>
@@ -10072,25 +10083,25 @@
       </c>
       <c r="F46" s="223"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>87.23504963118387</v>
+        <v>87.27858246088563</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-65.267413389288336</v>
+        <v>-65.299983728895668</v>
       </c>
       <c r="F47" s="223"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="223"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="143" t="s">
         <v>120</v>
       </c>
@@ -10103,7 +10114,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="223"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>90</v>
       </c>
@@ -10117,7 +10128,7 @@
       </c>
       <c r="F50" s="223"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>146</v>
       </c>
@@ -10128,10 +10139,10 @@
       </c>
       <c r="F51" s="223"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="223"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="143" t="s">
         <v>119</v>
       </c>
@@ -10143,7 +10154,7 @@
       </c>
       <c r="F53" s="223"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>116</v>
       </c>
@@ -10157,7 +10168,7 @@
       </c>
       <c r="F54" s="223"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>118</v>
       </c>
@@ -10171,10 +10182,10 @@
       </c>
       <c r="F55" s="223"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="223"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="143" t="s">
         <v>145</v>
       </c>
@@ -10186,7 +10197,7 @@
       </c>
       <c r="F57" s="223"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>86</v>
       </c>
@@ -10197,7 +10208,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>89</v>
       </c>
@@ -10208,10 +10219,10 @@
       </c>
       <c r="F59" s="223"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="223"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="143" t="s">
         <v>231</v>
       </c>
@@ -10223,7 +10234,7 @@
       </c>
       <c r="F61" s="223"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>210</v>
       </c>
@@ -10239,7 +10250,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="76" t="s">
         <v>162</v>
       </c>
@@ -10250,7 +10261,7 @@
       <c r="G64" s="35"/>
       <c r="H64" s="35"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>158</v>
       </c>
@@ -10264,7 +10275,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="102" t="s">
         <v>157</v>
       </c>
@@ -10280,7 +10291,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="102" t="s">
         <v>147</v>
       </c>
@@ -10290,7 +10301,7 @@
       </c>
       <c r="F67" s="223"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="102" t="s">
         <v>151</v>
       </c>
@@ -10300,7 +10311,7 @@
       </c>
       <c r="F68" s="223"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="102" t="s">
         <v>149</v>
       </c>
@@ -10310,7 +10321,7 @@
       </c>
       <c r="F69" s="223"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="77" t="s">
         <v>158</v>
       </c>
@@ -10320,10 +10331,10 @@
       </c>
       <c r="F70" s="223"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="223"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="225" t="s">
         <v>256</v>
       </c>
@@ -10335,7 +10346,7 @@
       </c>
       <c r="F72" s="223"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="102" t="s">
         <v>255</v>
       </c>
@@ -10351,7 +10362,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="227" t="s">
         <v>259</v>
       </c>
@@ -10367,7 +10378,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="77" t="s">
         <v>258</v>
       </c>
@@ -10380,7 +10391,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="229" t="s">
         <v>260</v>
       </c>
@@ -10393,10 +10404,10 @@
         <v>261</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="223"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>159</v>
       </c>
@@ -10408,7 +10419,7 @@
       </c>
       <c r="F78" s="223"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="102" t="s">
         <v>148</v>
       </c>
@@ -10422,7 +10433,7 @@
       </c>
       <c r="F79" s="223"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="102" t="s">
         <v>152</v>
       </c>
@@ -10436,7 +10447,7 @@
       </c>
       <c r="F80" s="223"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="102" t="s">
         <v>150</v>
       </c>
@@ -10450,7 +10461,7 @@
       </c>
       <c r="F81" s="223"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="77" t="s">
         <v>159</v>
       </c>
@@ -10464,7 +10475,7 @@
       </c>
       <c r="F82" s="223"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="76" t="s">
         <v>241</v>
       </c>
@@ -10475,7 +10486,7 @@
       <c r="G84" s="35"/>
       <c r="H84" s="35"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>242</v>
       </c>
@@ -10483,68 +10494,68 @@
         <v>243</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="212" t="s">
         <v>239</v>
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-126774.74360273966</v>
+        <v>-126838.007890971</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-42.159112666631181</v>
+        <v>-42.180151291356594</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="212" t="s">
         <v>240</v>
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>35091.984554410657</v>
+        <v>35109.496476441571</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>11.669886986015634</v>
+        <v>11.675710599402098</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="213" t="s">
         <v>159</v>
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>111441.18516751923</v>
+        <v>111496.79756363948</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>37.059917043908889</v>
+        <v>37.07841102155038</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="77" t="s">
         <v>244</v>
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>19758.426119190233</v>
+        <v>19768.286149110048</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.5706913632933421</v>
+        <v>6.573970329595884</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -10570,19 +10581,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q807"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
@@ -10639,7 +10650,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="51" t="s">
         <v>95</v>
@@ -10662,7 +10673,7 @@
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>393</v>
@@ -10682,7 +10693,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -10739,7 +10750,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>43</v>
@@ -10794,7 +10805,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="30" t="s">
         <v>45</v>
@@ -10849,7 +10860,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>42</v>
@@ -10904,7 +10915,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="28" t="s">
         <v>127</v>
@@ -10961,7 +10972,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
         <v>415</v>
@@ -11018,7 +11029,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>65</v>
@@ -11073,7 +11084,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="67" t="s">
         <v>137</v>
@@ -11128,7 +11139,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>60</v>
@@ -11183,7 +11194,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="38" t="s">
         <v>208</v>
@@ -11240,7 +11251,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="39" t="s">
         <v>129</v>
@@ -11297,7 +11308,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="2" t="s">
         <v>62</v>
@@ -11352,7 +11363,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
         <v>398</v>
@@ -11407,7 +11418,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="26" t="s">
         <v>49</v>
@@ -11433,7 +11444,7 @@
       <c r="P17" s="272"/>
       <c r="Q17" s="272"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="26" t="s">
         <v>94</v>
@@ -11458,7 +11469,7 @@
       <c r="P18" s="273"/>
       <c r="Q18" s="273"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="30" t="s">
         <v>63</v>
@@ -11515,7 +11526,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="26"/>
       <c r="C20" s="59"/>
@@ -11534,7 +11545,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="51" t="s">
         <v>174</v>
@@ -11557,7 +11568,7 @@
       <c r="P21" s="35"/>
       <c r="Q21" s="35"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="61" t="s">
         <v>43</v>
@@ -11578,7 +11589,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="26" t="s">
         <v>40</v>
@@ -11635,7 +11646,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="65" t="s">
         <v>59</v>
@@ -11692,7 +11703,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="26" t="s">
         <v>46</v>
@@ -11749,7 +11760,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="B26" s="67" t="s">
         <v>43</v>
@@ -11806,18 +11817,18 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="E27" s="237"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="61" t="s">
         <v>175</v>
       </c>
       <c r="E28" s="237"/>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="10"/>
       <c r="B29" s="25" t="s">
         <v>40</v>
@@ -11874,7 +11885,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="10"/>
       <c r="B30" s="65" t="str">
         <f>B24</f>
@@ -11932,7 +11943,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="B31" s="26" t="str">
         <f>B25</f>
@@ -11990,7 +12001,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="67" t="s">
         <v>43</v>
@@ -12045,18 +12056,18 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="E33" s="237"/>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="61" t="s">
         <v>42</v>
       </c>
       <c r="E34" s="237"/>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="298" t="s">
         <v>396</v>
@@ -12113,18 +12124,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="237"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="61" t="s">
         <v>176</v>
       </c>
       <c r="E37" s="237"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="298" t="s">
         <v>396</v>
@@ -12179,18 +12190,18 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="E39" s="237"/>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="61" t="s">
         <v>177</v>
       </c>
       <c r="E40" s="237"/>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="B41" s="26" t="s">
         <v>142</v>
@@ -12248,10 +12259,10 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
       <c r="B43" s="51" t="s">
         <v>178</v>
@@ -12274,14 +12285,14 @@
       <c r="P43" s="35"/>
       <c r="Q43" s="35"/>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
       <c r="B44" s="61" t="s">
         <v>57</v>
       </c>
       <c r="E44" s="237"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="10"/>
       <c r="B45" s="2" t="s">
         <v>37</v>
@@ -12336,7 +12347,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
         <v>272</v>
@@ -12391,7 +12402,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="245" t="s">
         <v>269</v>
@@ -12448,7 +12459,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="67" t="s">
         <v>65</v>
@@ -12503,11 +12514,11 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="E49" s="237"/>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="69" t="s">
         <v>130</v>
@@ -12517,7 +12528,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="B51" s="8" t="s">
         <v>85</v>
@@ -12541,7 +12552,7 @@
       <c r="P51" s="151"/>
       <c r="Q51" s="151"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
         <v>84</v>
@@ -12565,7 +12576,7 @@
       <c r="P52" s="151"/>
       <c r="Q52" s="151"/>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="25" t="s">
         <v>87</v>
@@ -12620,11 +12631,11 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="E54" s="237"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="61" t="s">
         <v>139</v>
@@ -12634,7 +12645,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="B56" s="38" t="s">
         <v>138</v>
@@ -12689,7 +12700,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="38" t="s">
         <v>134</v>
@@ -12744,7 +12755,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="38" t="s">
         <v>133</v>
@@ -12799,7 +12810,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="30" t="s">
         <v>163</v>
@@ -12854,7 +12865,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="38" t="s">
         <v>135</v>
@@ -12910,7 +12921,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="30" t="s">
         <v>164</v>
@@ -12965,11 +12976,11 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="E62" s="237"/>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="93" t="s">
         <v>140</v>
@@ -12979,7 +12990,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="B64" s="38" t="s">
         <v>138</v>
@@ -13004,7 +13015,7 @@
       <c r="P64" s="157"/>
       <c r="Q64" s="157"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="102" t="s">
         <v>132</v>
@@ -13029,7 +13040,7 @@
       <c r="P65" s="157"/>
       <c r="Q65" s="157"/>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="102" t="s">
         <v>133</v>
@@ -13054,7 +13065,7 @@
       <c r="P66" s="157"/>
       <c r="Q66" s="157"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="30" t="s">
         <v>163</v>
@@ -13081,10 +13092,10 @@
       <c r="P67" s="157"/>
       <c r="Q67" s="157"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="10"/>
       <c r="B69" s="51" t="s">
         <v>181</v>
@@ -13107,7 +13118,7 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
       <c r="B70" s="69" t="s">
         <v>185</v>
@@ -13128,7 +13139,7 @@
       <c r="P70" s="12"/>
       <c r="Q70" s="12"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="10"/>
       <c r="B71" s="2" t="s">
         <v>43</v>
@@ -13185,7 +13196,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="30" t="s">
         <v>45</v>
@@ -13242,7 +13253,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="8" t="s">
         <v>42</v>
@@ -13299,7 +13310,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="28" t="s">
         <v>127</v>
@@ -13356,7 +13367,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="26" t="s">
         <v>128</v>
@@ -13413,7 +13424,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
         <v>65</v>
@@ -13470,7 +13481,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="67" t="s">
         <v>137</v>
@@ -13527,7 +13538,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>60</v>
@@ -13584,7 +13595,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="38" t="str">
         <f>B13</f>
@@ -13642,7 +13653,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="39" t="s">
         <v>129</v>
@@ -13699,7 +13710,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
         <v>62</v>
@@ -13756,7 +13767,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>77</v>
@@ -13815,7 +13826,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="26" t="s">
         <v>49</v>
@@ -13841,7 +13852,7 @@
       <c r="P83" s="203"/>
       <c r="Q83" s="203"/>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="8" t="s">
         <v>94</v>
@@ -13865,7 +13876,7 @@
       <c r="P84" s="151"/>
       <c r="Q84" s="151"/>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="30" t="s">
         <v>117</v>
@@ -13922,18 +13933,18 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="E86" s="237"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="61" t="s">
         <v>183</v>
       </c>
       <c r="E87" s="237"/>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="B88" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13989,7 +14000,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -14045,7 +14056,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="s">
         <v>182</v>
@@ -14100,7 +14111,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
         <v>331</v>
@@ -14121,27 +14132,27 @@
       <c r="P91" s="293"/>
       <c r="Q91" s="293"/>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>330</v>
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.2988721804511276E-2</v>
+        <v>3.3815028901734101E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.2988721804511276E-2</v>
+        <v>3.3815028901734101E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>2.5071428571428571E-2</v>
+        <v>2.5699421965317923E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>2.0453007518796994E-2</v>
+        <v>2.0965317919075147E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
@@ -14176,11 +14187,11 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="E93" s="237"/>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="B94" s="143" t="s">
         <v>81</v>
@@ -14201,7 +14212,7 @@
       <c r="P94" s="12"/>
       <c r="Q94" s="12"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="B95" s="26" t="s">
         <v>121</v>
@@ -14258,7 +14269,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="67" t="s">
         <v>137</v>
@@ -14315,10 +14326,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
       <c r="B98" s="51" t="s">
         <v>184</v>
@@ -14341,7 +14352,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="10"/>
       <c r="B99" s="61" t="s">
         <v>26</v>
@@ -14351,7 +14362,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="10"/>
       <c r="B100" s="25" t="s">
         <v>1</v>
@@ -14408,7 +14419,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="90" t="s">
         <v>179</v>
@@ -14465,7 +14476,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="90" t="s">
         <v>180</v>
@@ -14522,7 +14533,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="25" t="s">
         <v>38</v>
@@ -14579,7 +14590,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="25" t="s">
         <v>28</v>
@@ -14636,11 +14647,11 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="E105" s="237"/>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="B106" s="88" t="s">
         <v>189</v>
@@ -14663,7 +14674,7 @@
       <c r="P106" s="12"/>
       <c r="Q106" s="12"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="B107" s="25" t="s">
         <v>186</v>
@@ -14720,7 +14731,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="25" t="s">
         <v>187</v>
@@ -14777,7 +14788,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="25" t="s">
         <v>66</v>
@@ -14804,18 +14815,18 @@
       <c r="P109" s="186"/>
       <c r="Q109" s="186"/>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="E110" s="237"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="B111" s="61" t="s">
         <v>48</v>
       </c>
       <c r="E111" s="237"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
         <v>303</v>
@@ -14869,7 +14880,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>304</v>
@@ -14924,11 +14935,11 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="E114" s="237"/>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="B115" s="88" t="s">
         <v>36</v>
@@ -14987,7 +14998,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="B116" s="7" t="s">
         <v>190</v>
@@ -15045,7 +15056,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B117" s="7" t="s">
         <v>80</v>
       </c>
@@ -15102,7 +15113,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B118" s="7" t="s">
         <v>88</v>
       </c>
@@ -15161,7 +15172,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="10"/>
       <c r="B119" s="67" t="s">
         <v>191</v>
@@ -15220,7 +15231,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="10"/>
       <c r="B120" s="26"/>
       <c r="C120" s="59"/>
@@ -15239,7 +15250,7 @@
       <c r="P120" s="12"/>
       <c r="Q120" s="12"/>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="10"/>
       <c r="B121" s="51" t="s">
         <v>192</v>
@@ -15262,7 +15273,7 @@
       <c r="P121" s="35"/>
       <c r="Q121" s="35"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="10"/>
       <c r="B122" s="160" t="s">
         <v>141</v>
@@ -15283,7 +15294,7 @@
       <c r="P122" s="12"/>
       <c r="Q122" s="12"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="10"/>
       <c r="B123" s="26" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -15291,30 +15302,30 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>8.6122745523257205</v>
+        <v>8.6165723280823254</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.84058154928355</v>
+        <v>10.845991315111027</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.0131664550670001</v>
+        <v>7.016666229323441</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>3.7111934684192907</v>
+        <v>3.713045462015145</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>4.739134255810587E-2</v>
+        <v>4.7414992217888745E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.655635223684401</v>
+        <v>4.6579585212144998</v>
       </c>
       <c r="L123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15341,37 +15352,37 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="26" t="s">
         <v>226</v>
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.0942430003061269E-2</v>
+        <v>8.3011294104839359E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.10188516493687547</v>
+        <v>0.10448931902804458</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.5913218562659776E-2</v>
+        <v>6.759794055224895E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.4879637861083557E-2</v>
+        <v>3.577115088646575E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>4.4540735486941607E-4</v>
+        <v>4.5679183254228079E-4</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>4.3755970147409784E-2</v>
+        <v>4.4874359549272637E-2</v>
       </c>
       <c r="L124" s="74" t="str">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
@@ -15398,30 +15409,30 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B125" s="2" t="s">
         <v>306</v>
       </c>
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13958405526027315</v>
+        <v>0.14308038034386381</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2689350048996251E-2</v>
+        <v>7.4510085214000002E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0289052385295723E-2</v>
+        <v>3.1047737705158621E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-1.3961531008679806E-2</v>
+        <v>-1.4311241804658297E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15420193762597617</v>
+        <v>0.1580644139056249</v>
       </c>
       <c r="L125" s="22" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15448,688 +15459,688 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q11 G13:Q16 G23:Q25">
@@ -16151,16 +16162,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:U118"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
     <col min="2" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="11" width="11.1328125" customWidth="1"/>
+    <col min="10" max="11" width="11.1640625" customWidth="1"/>
     <col min="12" max="12" width="20.6640625" customWidth="1"/>
     <col min="13" max="13" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="13.9">
+    <row r="2" spans="2:15" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>52</v>
       </c>
@@ -16175,7 +16186,7 @@
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
     </row>
-    <row r="3" spans="2:15" ht="13.15">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B3" s="106" t="s">
         <v>136</v>
       </c>
@@ -16190,7 +16201,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="4" spans="2:15">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B4" s="97" t="s">
         <v>393</v>
       </c>
@@ -16222,7 +16233,7 @@
       </c>
       <c r="J4" s="305"/>
     </row>
-    <row r="5" spans="2:15">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B5" s="187" t="s">
         <v>105</v>
       </c>
@@ -16250,7 +16261,7 @@
       </c>
       <c r="J5" s="305"/>
     </row>
-    <row r="6" spans="2:15" ht="13.25" customHeight="1">
+    <row r="6" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="136" t="s">
         <v>194</v>
       </c>
@@ -16283,7 +16294,7 @@
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
     </row>
-    <row r="7" spans="2:15" ht="12.75" customHeight="1">
+    <row r="7" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="318" t="s">
         <v>430</v>
       </c>
@@ -16313,7 +16324,7 @@
       <c r="N7" s="304"/>
       <c r="O7" s="304"/>
     </row>
-    <row r="8" spans="2:15" ht="13.15">
+    <row r="8" spans="2:15" ht="14" x14ac:dyDescent="0.15">
       <c r="B8" s="136" t="s">
         <v>426</v>
       </c>
@@ -16330,7 +16341,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.5706913632933395</v>
+        <v>6.5739703295958796</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16348,14 +16359,14 @@
       <c r="N8" s="304"/>
       <c r="O8" s="304"/>
     </row>
-    <row r="9" spans="2:15" ht="13.15" thickBot="1">
+    <row r="9" spans="2:15" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B9" s="189" t="str">
         <f>"*"&amp;Thesis!E15</f>
         <v>*CNY/HKD</v>
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1310185977458953</v>
+        <v>1.1315830089569092</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16374,13 +16385,13 @@
       <c r="N9" s="304"/>
       <c r="O9" s="304"/>
     </row>
-    <row r="10" spans="2:15" ht="13.5" thickTop="1">
+    <row r="10" spans="2:15" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B10" s="107" t="s">
         <v>427</v>
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>522911.36528619629</v>
+        <v>523172.31328256195</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16396,13 +16407,13 @@
       <c r="N10" s="304"/>
       <c r="O10" s="304"/>
     </row>
-    <row r="11" spans="2:15" ht="13.15">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B11" s="136" t="s">
         <v>425</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>173.89488266562165</v>
+        <v>173.98166127519536</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16412,7 +16423,7 @@
       <c r="I11" s="307"/>
       <c r="J11" s="307"/>
     </row>
-    <row r="13" spans="2:15" ht="13.9">
+    <row r="13" spans="2:15" ht="16" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
         <v>428</v>
       </c>
@@ -16427,7 +16438,7 @@
       <c r="K13" s="35"/>
       <c r="L13" s="35"/>
     </row>
-    <row r="14" spans="2:15" ht="13.15">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B14" s="106" t="s">
         <v>399</v>
       </c>
@@ -16445,7 +16456,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="15" spans="2:15">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B15" s="139" t="s">
         <v>421</v>
       </c>
@@ -16470,7 +16481,7 @@
       </c>
       <c r="J15" s="126"/>
     </row>
-    <row r="16" spans="2:15" ht="13.25" customHeight="1">
+    <row r="16" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="114" t="s">
         <v>422</v>
       </c>
@@ -16486,7 +16497,7 @@
         <v>2.38559171477595E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="13.25" customHeight="1">
+    <row r="17" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="308" t="s">
         <v>550</v>
       </c>
@@ -16505,7 +16516,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="13.25" customHeight="1">
+    <row r="18" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="308" t="s">
         <v>423</v>
       </c>
@@ -16525,17 +16536,17 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>189.69491390936841</v>
+        <v>189.7895771945665</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.15">
       <c r="L19" s="275"/>
     </row>
-    <row r="20" spans="1:21" ht="13.15">
+    <row r="20" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A20" s="121" t="s">
         <v>399</v>
       </c>
@@ -16574,7 +16585,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A21" s="302" t="str">
         <f t="shared" ref="A21:A50" si="0">IF($C$15&lt;B21,"",IF(B21&gt;=$F$15,"II","I"))</f>
         <v>I</v>
@@ -16623,7 +16634,7 @@
         <v>21859.032865551624</v>
       </c>
     </row>
-    <row r="22" spans="1:21">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A22" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16672,7 +16683,7 @@
         <v>20867.599200487064</v>
       </c>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A23" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16729,7 +16740,7 @@
       <c r="T23" s="275"/>
       <c r="U23" s="275"/>
     </row>
-    <row r="24" spans="1:21">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A24" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16786,7 +16797,7 @@
       <c r="T24" s="275"/>
       <c r="U24" s="275"/>
     </row>
-    <row r="25" spans="1:21">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A25" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -16843,7 +16854,7 @@
       <c r="T25" s="275"/>
       <c r="U25" s="275"/>
     </row>
-    <row r="26" spans="1:21">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A26" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -16892,7 +16903,7 @@
         <v>23423.796792194709</v>
       </c>
     </row>
-    <row r="27" spans="1:21">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A27" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -16941,7 +16952,7 @@
         <v>22361.392025879035</v>
       </c>
     </row>
-    <row r="28" spans="1:21">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A28" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -16990,7 +17001,7 @@
         <v>21347.173465134711</v>
       </c>
     </row>
-    <row r="29" spans="1:21">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A29" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17039,7 +17050,7 @@
         <v>20378.955586627329</v>
       </c>
     </row>
-    <row r="30" spans="1:21">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A30" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17088,7 +17099,7 @@
         <v>19454.651993155978</v>
       </c>
     </row>
-    <row r="31" spans="1:21">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A31" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17137,7 +17148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:21">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A32" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17186,7 +17197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:21">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A33" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17243,7 +17254,7 @@
       <c r="T33" s="275"/>
       <c r="U33" s="275"/>
     </row>
-    <row r="34" spans="1:21">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A34" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17300,7 +17311,7 @@
       <c r="T34" s="275"/>
       <c r="U34" s="275"/>
     </row>
-    <row r="35" spans="1:21">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17357,7 +17368,7 @@
       <c r="T35" s="275"/>
       <c r="U35" s="275"/>
     </row>
-    <row r="36" spans="1:21">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A36" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17406,7 +17417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:21">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A37" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17455,7 +17466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:21">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A38" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17504,7 +17515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:21">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A39" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17553,7 +17564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A40" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17602,7 +17613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:21">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A41" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17651,7 +17662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A42" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17700,7 +17711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:21">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A43" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17749,7 +17760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:21">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A44" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17798,7 +17809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:21">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A45" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17847,7 +17858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:21">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A46" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17896,7 +17907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:21">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A47" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17953,7 +17964,7 @@
       <c r="T47" s="275"/>
       <c r="U47" s="275"/>
     </row>
-    <row r="48" spans="1:21">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A48" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18010,7 +18021,7 @@
       <c r="T48" s="275"/>
       <c r="U48" s="275"/>
     </row>
-    <row r="49" spans="1:21">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A49" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18067,7 +18078,7 @@
       <c r="T49" s="275"/>
       <c r="U49" s="275"/>
     </row>
-    <row r="50" spans="1:21">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A50" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18124,7 +18135,7 @@
       <c r="T50" s="275"/>
       <c r="U50" s="275"/>
     </row>
-    <row r="51" spans="1:21">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A51" s="315" t="s">
         <v>418</v>
       </c>
@@ -18170,7 +18181,7 @@
         <v>273706.82804164273</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="13.15">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.15">
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
@@ -18183,10 +18194,10 @@
         <v>486874.83399557997</v>
       </c>
     </row>
-    <row r="53" spans="1:21">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.15">
       <c r="C53" s="111"/>
     </row>
-    <row r="54" spans="1:21" ht="13.15">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B54" s="115" t="s">
         <v>108</v>
       </c>
@@ -18201,7 +18212,7 @@
       <c r="K54" s="113"/>
       <c r="L54" s="113"/>
     </row>
-    <row r="55" spans="1:21" ht="13.15">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A55" s="125">
         <f>L52</f>
         <v>486874.83399557997</v>
@@ -18233,7 +18244,7 @@
       <c r="K55" s="123"/>
       <c r="L55" s="123"/>
     </row>
-    <row r="56" spans="1:21" ht="13.15">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A56" s="131">
         <v>1</v>
       </c>
@@ -18260,7 +18271,7 @@
       <c r="K56" s="295"/>
       <c r="L56" s="295"/>
     </row>
-    <row r="57" spans="1:21" ht="13.15">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A57" s="131">
         <v>2</v>
       </c>
@@ -18286,7 +18297,7 @@
       <c r="K57" s="295"/>
       <c r="L57" s="295"/>
     </row>
-    <row r="58" spans="1:21" ht="13.15">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A58" s="131">
         <v>3</v>
       </c>
@@ -18312,7 +18323,7 @@
       <c r="K58" s="295"/>
       <c r="L58" s="295"/>
     </row>
-    <row r="59" spans="1:21" ht="13.15">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A59" s="131">
         <v>4</v>
       </c>
@@ -18338,7 +18349,7 @@
       <c r="K59" s="295"/>
       <c r="L59" s="295"/>
     </row>
-    <row r="60" spans="1:21" ht="13.15">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A60" s="131">
         <v>5</v>
       </c>
@@ -18364,7 +18375,7 @@
       <c r="K60" s="295"/>
       <c r="L60" s="295"/>
     </row>
-    <row r="61" spans="1:21" ht="13.15">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A61" s="131">
         <v>6</v>
       </c>
@@ -18390,7 +18401,7 @@
       <c r="K61" s="295"/>
       <c r="L61" s="295"/>
     </row>
-    <row r="62" spans="1:21" ht="13.15">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A62" s="131">
         <v>7</v>
       </c>
@@ -18416,7 +18427,7 @@
       <c r="K62" s="295"/>
       <c r="L62" s="295"/>
     </row>
-    <row r="63" spans="1:21" ht="13.15">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A63" s="131">
         <v>8</v>
       </c>
@@ -18442,7 +18453,7 @@
       <c r="K63" s="295"/>
       <c r="L63" s="295"/>
     </row>
-    <row r="64" spans="1:21" ht="13.15">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A64" s="131">
         <v>9</v>
       </c>
@@ -18468,7 +18479,7 @@
       <c r="K64" s="295"/>
       <c r="L64" s="295"/>
     </row>
-    <row r="65" spans="1:21" ht="13.15">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A65" s="131">
         <v>10</v>
       </c>
@@ -18494,7 +18505,7 @@
       <c r="K65" s="295"/>
       <c r="L65" s="295"/>
     </row>
-    <row r="66" spans="1:21" ht="13.15">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A66" s="131">
         <v>15</v>
       </c>
@@ -18529,7 +18540,7 @@
       <c r="T66" s="275"/>
       <c r="U66" s="275"/>
     </row>
-    <row r="67" spans="1:21" ht="13.15">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A67" s="132">
         <v>20</v>
       </c>
@@ -18564,7 +18575,7 @@
       <c r="T67" s="275"/>
       <c r="U67" s="275"/>
     </row>
-    <row r="68" spans="1:21" ht="13.15">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A68" s="132">
         <v>25</v>
       </c>
@@ -18599,7 +18610,7 @@
       <c r="T68" s="275"/>
       <c r="U68" s="275"/>
     </row>
-    <row r="69" spans="1:21" ht="13.15">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A69" s="132">
         <v>30</v>
       </c>
@@ -18634,7 +18645,7 @@
       <c r="T69" s="275"/>
       <c r="U69" s="275"/>
     </row>
-    <row r="70" spans="1:21">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.15">
       <c r="C70" s="275"/>
       <c r="D70" s="111"/>
       <c r="E70" s="111"/>
@@ -18655,7 +18666,7 @@
       <c r="T70" s="275"/>
       <c r="U70" s="275"/>
     </row>
-    <row r="71" spans="1:21" ht="13.15">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B71" s="115" t="s">
         <v>109</v>
       </c>
@@ -18679,7 +18690,7 @@
       <c r="T71" s="275"/>
       <c r="U71" s="275"/>
     </row>
-    <row r="72" spans="1:21" ht="13.15">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B72" s="124">
         <f>B55</f>
         <v>0</v>
@@ -18707,29 +18718,29 @@
       <c r="K72" s="124"/>
       <c r="L72" s="124"/>
     </row>
-    <row r="73" spans="1:21" ht="13.15">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A73" s="131">
         <v>0</v>
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>173.89488266562165</v>
+        <v>173.98166127519536</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>173.89488266562165</v>
+        <v>173.98166127519536</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>173.89488266562165</v>
+        <v>173.98166127519536</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>173.89488266562165</v>
+        <v>173.98166127519536</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>173.89488266562165</v>
+        <v>173.98166127519536</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18738,29 +18749,29 @@
       <c r="K73" s="296"/>
       <c r="L73" s="296"/>
     </row>
-    <row r="74" spans="1:21" ht="13.15">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A74" s="131">
         <v>1</v>
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>167.28753767070796</v>
+        <v>167.37101902274978</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>168.89470613378211</v>
+        <v>168.97898950968133</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>170.50187459685631</v>
+        <v>170.58695999661293</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>172.10904305993043</v>
+        <v>172.19493048354443</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>175.32337998607878</v>
+        <v>175.41087145740755</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18769,29 +18780,29 @@
       <c r="K74" s="296"/>
       <c r="L74" s="296"/>
     </row>
-    <row r="75" spans="1:21" ht="13.15">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A75" s="131">
         <v>2</v>
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>167.08515566736884</v>
+        <v>167.16853602489843</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>170.23039246237173</v>
+        <v>170.31534238463874</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>173.40612613167079</v>
+        <v>173.49266083750345</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>176.61235667526623</v>
+        <v>176.70049138349276</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>183.11630838534583</v>
+        <v>183.20768875484475</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18800,29 +18811,29 @@
       <c r="K75" s="296"/>
       <c r="L75" s="296"/>
     </row>
-    <row r="76" spans="1:21" ht="13.15">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A76" s="131">
         <v>3</v>
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>166.8964544987542</v>
+        <v>166.97974068890642</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>171.48824159232549</v>
+        <v>171.57381921793188</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>176.16821150743849</v>
+        <v>176.25612457429452</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>180.9372173035141</v>
+        <v>181.02751024311678</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>190.74574877623667</v>
+        <v>190.84093645862944</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18831,29 +18842,29 @@
       <c r="K76" s="296"/>
       <c r="L76" s="296"/>
     </row>
-    <row r="77" spans="1:21" ht="13.15">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A77" s="131">
         <v>4</v>
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>166.72050935319282</v>
+        <v>166.80370774159459</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>172.67278949092997</v>
+        <v>172.75895824042709</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>178.79508990676993</v>
+        <v>178.88431386243141</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>185.09069650826487</v>
+        <v>185.18306215492342</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>198.21513097710883</v>
+        <v>198.31404609869838</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18862,29 +18873,29 @@
       <c r="K77" s="296"/>
       <c r="L77" s="296"/>
     </row>
-    <row r="78" spans="1:21" ht="13.15">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A78" s="131">
         <v>5</v>
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>163.92462380359655</v>
+        <v>164.00642696370409</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>171.10357379384064</v>
+        <v>171.18895945901562</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>178.55521962223818</v>
+        <v>178.64432387564364</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>186.28747279752758</v>
+        <v>186.38043567039981</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>202.62621572175328</v>
+        <v>202.72733210306356</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18893,29 +18904,29 @@
       <c r="K78" s="296"/>
       <c r="L78" s="296"/>
     </row>
-    <row r="79" spans="1:21" ht="13.15">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A79" s="131">
         <v>6</v>
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>163.77166210870348</v>
+        <v>163.85338893647162</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>172.15408520063929</v>
+        <v>172.23999510159291</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>180.93121565500434</v>
+        <v>181.02150559960964</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>190.11829405002692</v>
+        <v>190.21316861424233</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>209.78548469026492</v>
+        <v>209.89017375523974</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18924,30 +18935,30 @@
       <c r="K79" s="296"/>
       <c r="L79" s="296"/>
     </row>
-    <row r="80" spans="1:21" ht="13.15">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A80" s="131">
         <f t="shared" ref="A80" si="12">A62</f>
         <v>7</v>
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>161.17511588332678</v>
+        <v>161.2555469589274</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>170.61509702629417</v>
+        <v>170.70023892733963</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>180.58677977440519</v>
+        <v>180.67689783547749</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>191.11584153227335</v>
+        <v>191.21121390172701</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>213.95383474162637</v>
+        <v>214.06060393464253</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18956,29 +18967,29 @@
       <c r="K80" s="296"/>
       <c r="L80" s="296"/>
     </row>
-    <row r="81" spans="1:12" ht="13.15">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A81" s="131">
         <v>8</v>
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>161.04213534538741</v>
+        <v>161.12250005982773</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>171.54673872445952</v>
+        <v>171.63234554183805</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>182.73585418498968</v>
+        <v>182.82704469676531</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>194.64907012092613</v>
+        <v>194.74620567431901</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>220.81586573496728</v>
+        <v>220.92605928124399</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18987,30 +18998,30 @@
       <c r="K81" s="296"/>
       <c r="L81" s="296"/>
     </row>
-    <row r="82" spans="1:12" ht="13.15">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A82" s="131">
         <f t="shared" ref="A82" si="13">A64</f>
         <v>9</v>
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>158.63010258419757</v>
+        <v>158.70926362406132</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>170.04314370140688</v>
+        <v>170.12800018109024</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>182.30307935537027</v>
+        <v>182.39405389990526</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>195.4670763602698</v>
+        <v>195.5646201225932</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>224.75280919098529</v>
+        <v>224.86496738667461</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19019,30 +19030,30 @@
       <c r="K82" s="296"/>
       <c r="L82" s="296"/>
     </row>
-    <row r="83" spans="1:12" ht="13.15">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A83" s="131">
         <f t="shared" ref="A83:A87" si="14">A65</f>
         <v>10</v>
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>158.51449309462569</v>
+        <v>158.59359644198807</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>170.869366289894</v>
+        <v>170.95463507870531</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>184.2469044958745</v>
+        <v>184.33884906575102</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>198.72583040720653</v>
+        <v>198.82500038268122</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>231.32994291241337</v>
+        <v>231.44538328932953</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19051,30 +19062,30 @@
       <c r="K83" s="296"/>
       <c r="L83" s="296"/>
     </row>
-    <row r="84" spans="1:12" ht="13.15">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A84" s="131">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>152.06640439984551</v>
+        <v>152.14228996320662</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>167.98976859476315</v>
+        <v>168.07360038048222</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>185.90255894610553</v>
+        <v>185.99532973575873</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>206.05256961703861</v>
+        <v>206.15539584870433</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>254.20469047930533</v>
+        <v>254.33154602127854</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19083,30 +19094,30 @@
       <c r="K84" s="296"/>
       <c r="L84" s="296"/>
     </row>
-    <row r="85" spans="1:12" ht="13.15">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A85" s="132">
         <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>148.39284385926942</v>
+        <v>148.4668962089614</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>166.91831501444284</v>
+        <v>167.00161211362888</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>188.47084113443123</v>
+        <v>188.56489357167453</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>213.56810643408696</v>
+        <v>213.67468313744678</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>276.91588268927222</v>
+        <v>277.05407177741728</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19115,30 +19126,30 @@
       <c r="K85" s="296"/>
       <c r="L85" s="296"/>
     </row>
-    <row r="86" spans="1:12" ht="13.15">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A86" s="132">
         <f t="shared" si="14"/>
         <v>25</v>
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>143.94676249312644</v>
+        <v>144.01859611876461</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>164.12040122298333</v>
+        <v>164.20230208172339</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>188.31168958666316</v>
+        <v>188.40566260265027</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>217.39201042878236</v>
+        <v>217.50049537157233</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>294.69675858372358</v>
+        <v>294.84382084664804</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19147,30 +19158,30 @@
       <c r="K86" s="296"/>
       <c r="L86" s="296"/>
     </row>
-    <row r="87" spans="1:12" ht="13.15">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A87" s="132">
         <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>141.42699965834805</v>
+        <v>141.49757584896622</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>162.83419832458966</v>
+        <v>162.91545733063433</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>189.18384166745187</v>
+        <v>189.27824991272087</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>221.76584242511959</v>
+        <v>221.87651003742425</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>312.61146595311686</v>
+        <v>312.76746817662325</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19179,7 +19190,7 @@
       <c r="K87" s="296"/>
       <c r="L87" s="296"/>
     </row>
-    <row r="89" spans="1:12" ht="13.15">
+    <row r="89" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="B89" s="153" t="s">
         <v>101</v>
       </c>
@@ -19202,7 +19213,7 @@
       <c r="K89" s="323"/>
       <c r="L89" s="323"/>
     </row>
-    <row r="90" spans="1:12">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B90" s="120" t="str">
         <f>Scenarios!B29</f>
         <v>Snowball Scenario</v>
@@ -19217,7 +19228,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>231.32994291241337</v>
+        <v>231.44538328932953</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19230,7 +19241,7 @@
       <c r="K90" s="297"/>
       <c r="L90" s="297"/>
     </row>
-    <row r="91" spans="1:12">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B91" s="120" t="str">
         <f>Scenarios!B22</f>
         <v>Optimistic</v>
@@ -19245,7 +19256,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>198.72583040720653</v>
+        <v>198.82500038268122</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19258,7 +19269,7 @@
       <c r="K91" s="297"/>
       <c r="L91" s="297"/>
     </row>
-    <row r="92" spans="1:12">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B92" s="120" t="str">
         <f>Scenarios!B23</f>
         <v>Base</v>
@@ -19273,7 +19284,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>184.2469044958745</v>
+        <v>184.33884906575102</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19286,7 +19297,7 @@
       <c r="K92" s="297"/>
       <c r="L92" s="297"/>
     </row>
-    <row r="93" spans="1:12">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B93" s="120" t="str">
         <f>Scenarios!B24</f>
         <v>Pessimistic</v>
@@ -19301,7 +19312,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>170.869366289894</v>
+        <v>170.95463507870531</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19314,7 +19325,7 @@
       <c r="K93" s="297"/>
       <c r="L93" s="297"/>
     </row>
-    <row r="94" spans="1:12">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B94" s="120" t="str">
         <f>Scenarios!B30</f>
         <v>Devil's advocate</v>
@@ -19329,7 +19340,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>158.51449309462569</v>
+        <v>158.59359644198807</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19342,7 +19353,7 @@
       <c r="K94" s="297"/>
       <c r="L94" s="297"/>
     </row>
-    <row r="95" spans="1:12">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B95" s="141"/>
       <c r="C95" s="141"/>
       <c r="D95" s="141"/>
@@ -19355,16 +19366,16 @@
       <c r="K95" s="142"/>
       <c r="L95" s="142"/>
     </row>
-    <row r="105" spans="3:3">
+    <row r="105" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C105" s="112"/>
     </row>
-    <row r="106" spans="3:3">
+    <row r="106" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C106" s="112"/>
     </row>
-    <row r="107" spans="3:3">
+    <row r="107" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C107" s="112"/>
     </row>
-    <row r="114" spans="3:21">
+    <row r="114" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C114" s="275"/>
       <c r="M114" s="275"/>
       <c r="N114" s="275"/>
@@ -19376,7 +19387,7 @@
       <c r="T114" s="275"/>
       <c r="U114" s="275"/>
     </row>
-    <row r="115" spans="3:21">
+    <row r="115" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C115" s="275"/>
       <c r="M115" s="275"/>
       <c r="N115" s="275"/>
@@ -19388,7 +19399,7 @@
       <c r="T115" s="275"/>
       <c r="U115" s="275"/>
     </row>
-    <row r="116" spans="3:21">
+    <row r="116" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C116" s="275"/>
       <c r="M116" s="275"/>
       <c r="N116" s="275"/>
@@ -19400,7 +19411,7 @@
       <c r="T116" s="275"/>
       <c r="U116" s="275"/>
     </row>
-    <row r="117" spans="3:21">
+    <row r="117" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C117" s="275"/>
       <c r="M117" s="275"/>
       <c r="N117" s="275"/>
@@ -19412,7 +19423,7 @@
       <c r="T117" s="275"/>
       <c r="U117" s="275"/>
     </row>
-    <row r="118" spans="3:21">
+    <row r="118" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C118" s="275"/>
       <c r="M118" s="275"/>
       <c r="N118" s="275"/>
@@ -19452,14 +19463,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:G67"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="13.9">
+    <row r="2" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>122</v>
       </c>
@@ -19469,7 +19480,7 @@
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
     </row>
-    <row r="3" spans="2:7" ht="13.15">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B3" s="145" t="s">
         <v>125</v>
       </c>
@@ -19478,7 +19489,7 @@
       </c>
       <c r="E3" s="97"/>
     </row>
-    <row r="4" spans="2:7" ht="12.75" customHeight="1">
+    <row r="4" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="139" t="s">
         <v>123</v>
       </c>
@@ -19499,14 +19510,14 @@
       <c r="F4" s="470"/>
       <c r="G4" s="470"/>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.15">
       <c r="C5" s="445"/>
       <c r="D5" s="470"/>
       <c r="E5" s="470"/>
       <c r="F5" s="470"/>
       <c r="G5" s="470"/>
     </row>
-    <row r="6" spans="2:7" ht="13.15">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B6" s="145" t="s">
         <v>91</v>
       </c>
@@ -19519,7 +19530,7 @@
       <c r="F6" s="470"/>
       <c r="G6" s="470"/>
     </row>
-    <row r="7" spans="2:7" ht="12.75" customHeight="1">
+    <row r="7" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="97" t="s">
         <v>232</v>
       </c>
@@ -19532,7 +19543,7 @@
       <c r="F7" s="470"/>
       <c r="G7" s="470"/>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B8" s="97" t="s">
         <v>63</v>
       </c>
@@ -19545,7 +19556,7 @@
       <c r="F8" s="470"/>
       <c r="G8" s="470"/>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B9" s="97" t="s">
         <v>54</v>
       </c>
@@ -19558,14 +19569,14 @@
       <c r="F9" s="470"/>
       <c r="G9" s="470"/>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.15">
       <c r="C10" s="448"/>
       <c r="D10" s="470"/>
       <c r="E10" s="470"/>
       <c r="F10" s="470"/>
       <c r="G10" s="470"/>
     </row>
-    <row r="11" spans="2:7" ht="13.15">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B11" s="145" t="s">
         <v>321</v>
       </c>
@@ -19575,7 +19586,7 @@
       <c r="F11" s="470"/>
       <c r="G11" s="470"/>
     </row>
-    <row r="12" spans="2:7">
+    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B12" s="114" t="s">
         <v>121</v>
       </c>
@@ -19588,7 +19599,7 @@
       <c r="F12" s="470"/>
       <c r="G12" s="470"/>
     </row>
-    <row r="13" spans="2:7">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B13" s="135" t="s">
         <v>127</v>
       </c>
@@ -19601,7 +19612,7 @@
       <c r="F13" s="470"/>
       <c r="G13" s="470"/>
     </row>
-    <row r="14" spans="2:7">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B14" s="97" t="s">
         <v>63</v>
       </c>
@@ -19614,7 +19625,7 @@
       <c r="F14" s="470"/>
       <c r="G14" s="470"/>
     </row>
-    <row r="16" spans="2:7" ht="13.9">
+    <row r="16" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
         <v>453</v>
       </c>
@@ -19624,7 +19635,7 @@
       <c r="F16" s="35"/>
       <c r="G16" s="35"/>
     </row>
-    <row r="17" spans="2:7" ht="13.15">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B17" s="106" t="s">
         <v>126</v>
       </c>
@@ -19632,7 +19643,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="12.75" customHeight="1">
+    <row r="18" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="139" t="s">
         <v>111</v>
       </c>
@@ -19644,18 +19655,18 @@
       </c>
       <c r="F18" s="319"/>
     </row>
-    <row r="19" spans="2:7">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.15">
       <c r="E19" s="319"/>
       <c r="F19" s="319"/>
     </row>
-    <row r="20" spans="2:7" ht="13.15">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B20" s="106" t="s">
         <v>450</v>
       </c>
       <c r="E20" s="319"/>
       <c r="F20" s="319"/>
     </row>
-    <row r="21" spans="2:7" ht="13.15">
+    <row r="21" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B21" s="153" t="s">
         <v>436</v>
       </c>
@@ -19676,7 +19687,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B22" s="302" t="s">
         <v>445</v>
       </c>
@@ -19689,7 +19700,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>198.72583040720653</v>
+        <v>198.82500038268122</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19700,7 +19711,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B23" s="302" t="s">
         <v>437</v>
       </c>
@@ -19713,7 +19724,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>184.2469044958745</v>
+        <v>184.33884906575102</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19723,7 +19734,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B24" s="302" t="s">
         <v>446</v>
       </c>
@@ -19736,7 +19747,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>170.869366289894</v>
+        <v>170.95463507870531</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19746,13 +19757,13 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="2:7">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B25" s="141" t="s">
         <v>451</v>
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>183.7983051266458</v>
+        <v>183.89002583237564</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19760,12 +19771,12 @@
       </c>
       <c r="G25" s="149"/>
     </row>
-    <row r="27" spans="2:7" ht="13.15">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B27" s="106" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="13.15">
+    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B28" s="153" t="s">
         <v>436</v>
       </c>
@@ -19786,7 +19797,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="29" spans="2:7">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B29" s="302" t="s">
         <v>444</v>
       </c>
@@ -19799,7 +19810,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>231.32994291241337</v>
+        <v>231.44538328932953</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19809,7 +19820,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="2:7">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B30" s="315" t="s">
         <v>447</v>
       </c>
@@ -19822,7 +19833,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>158.51449309462569</v>
+        <v>158.59359644198807</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19832,16 +19843,16 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="31" spans="2:7">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.15">
       <c r="E31" s="329"/>
       <c r="F31" s="329"/>
     </row>
-    <row r="32" spans="2:7" ht="13.15">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B32" s="145" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="33" spans="2:7">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B33" s="97" t="s">
         <v>458</v>
       </c>
@@ -19861,13 +19872,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:7">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B34" s="97" t="s">
         <v>233</v>
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>106.4</v>
+        <v>103.8</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19878,16 +19889,16 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.24012210262343742</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7">
+        <v>0.25085546041516749</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B35" s="97" t="s">
         <v>434</v>
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>173.89488266562165</v>
+        <v>173.98166127519536</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19898,16 +19909,16 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>4.8978344067454216E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7">
+        <v>4.896855368906447E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B36" s="97" t="s">
         <v>435</v>
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>189.66386019290991</v>
+        <v>189.75850798139936</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19920,7 +19931,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="13.9">
+    <row r="38" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B38" s="34" t="s">
         <v>411</v>
       </c>
@@ -19930,7 +19941,7 @@
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
     </row>
-    <row r="39" spans="2:7" ht="13.15">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B39" s="414" t="str">
         <f>IF(DCF!F14="II","2","1")&amp;"-stage DCF"</f>
         <v>2-stage DCF</v>
@@ -19939,7 +19950,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="40" spans="2:7">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B40" t="s">
         <v>551</v>
       </c>
@@ -19951,7 +19962,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="41" spans="2:7">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B41" s="97" t="s">
         <v>400</v>
       </c>
@@ -19961,7 +19972,7 @@
       </c>
       <c r="E41" s="97"/>
     </row>
-    <row r="43" spans="2:7" ht="13.9">
+    <row r="43" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B43" s="34" t="s">
         <v>276</v>
       </c>
@@ -19971,7 +19982,7 @@
       <c r="F43" s="35"/>
       <c r="G43" s="35"/>
     </row>
-    <row r="44" spans="2:7" ht="13.15">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B44" s="106" t="s">
         <v>249</v>
       </c>
@@ -19979,7 +19990,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="2:7">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B45" s="139" t="s">
         <v>111</v>
       </c>
@@ -19992,7 +20003,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="46" spans="2:7">
+    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B46" s="114" t="s">
         <v>112</v>
       </c>
@@ -20004,13 +20015,13 @@
         <v>252</v>
       </c>
     </row>
-    <row r="47" spans="2:7">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B47" s="97" t="s">
         <v>96</v>
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>189.69491390936841</v>
+        <v>189.7895771945665</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20020,7 +20031,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="49" spans="2:7" ht="13.15">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B49" s="106" t="s">
         <v>277</v>
       </c>
@@ -20032,7 +20043,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="2:7">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B50" s="97" t="s">
         <v>250</v>
       </c>
@@ -20042,7 +20053,7 @@
       </c>
       <c r="E50" s="126"/>
     </row>
-    <row r="51" spans="2:7">
+    <row r="51" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B51" s="97" t="s">
         <v>246</v>
       </c>
@@ -20054,7 +20065,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="2:7">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B52" s="97" t="s">
         <v>245</v>
       </c>
@@ -20064,7 +20075,7 @@
       </c>
       <c r="E52" s="221"/>
     </row>
-    <row r="53" spans="2:7">
+    <row r="53" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B53" s="97" t="s">
         <v>237</v>
       </c>
@@ -20077,10 +20088,10 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>3.4643876575169326E-2</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7" ht="13.9">
+        <v>3.4643876575169333E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B55" s="34" t="s">
         <v>107</v>
       </c>
@@ -20090,12 +20101,12 @@
       <c r="F55" s="35"/>
       <c r="G55" s="35"/>
     </row>
-    <row r="56" spans="2:7" ht="13.15">
+    <row r="56" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B56" s="106" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="57" spans="2:7">
+    <row r="57" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B57" s="220" t="s">
         <v>248</v>
       </c>
@@ -20105,7 +20116,7 @@
       </c>
       <c r="D57" s="126"/>
     </row>
-    <row r="58" spans="2:7">
+    <row r="58" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B58" s="97" t="s">
         <v>333</v>
       </c>
@@ -20118,13 +20129,13 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="60" spans="2:7" ht="13.15">
+    <row r="60" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B60" s="106" t="s">
         <v>473</v>
       </c>
       <c r="E60" s="413"/>
     </row>
-    <row r="61" spans="2:7" ht="13.15">
+    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B61" s="153" t="s">
         <v>462</v>
       </c>
@@ -20145,7 +20156,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="62" spans="2:7" ht="13.15">
+    <row r="62" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B62" s="302" t="s">
         <v>312</v>
       </c>
@@ -20155,11 +20166,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>87.402700549728095</v>
+        <v>87.446317042119546</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>93.825479581874617</v>
+        <v>93.869096074266068</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20167,10 +20178,10 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.50530649599537125</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7" ht="13.15">
+        <v>0.50532338669385313</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B63" s="302" t="s">
         <v>313</v>
       </c>
@@ -20180,11 +20191,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>109.55313224139205</v>
+        <v>109.60780244412965</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>116.93818609630651</v>
+        <v>116.99285629904411</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20192,10 +20203,10 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.38344508027324253</v>
-      </c>
-    </row>
-    <row r="65" spans="2:7" ht="13.15">
+        <v>0.38346450157316758</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B65" s="153" t="s">
         <v>463</v>
       </c>
@@ -20216,7 +20227,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="66" spans="2:7" ht="13.15">
+    <row r="66" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B66" s="302" t="s">
         <v>315</v>
       </c>
@@ -20226,11 +20237,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>135.94354297257468</v>
+        <v>136.01138275865037</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>144.41177994461933</v>
+        <v>144.47961973069502</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20238,10 +20249,10 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.23859094822948357</v>
-      </c>
-    </row>
-    <row r="67" spans="2:7" ht="13.15">
+        <v>0.23861321809688074</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B67" s="302" t="s">
         <v>314</v>
       </c>
@@ -20251,11 +20262,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>153.74205537820751</v>
+        <v>153.81877714019512</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>162.91149242558481</v>
+        <v>162.9882141875724</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20263,7 +20274,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.1410514778098203</v>
+        <v>0.14107559170127471</v>
       </c>
     </row>
   </sheetData>
@@ -20282,7 +20293,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:J167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="343" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="343" customWidth="1"/>
@@ -20291,7 +20302,7 @@
     <col min="7" max="16384" width="9" style="343"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="345" t="s">
         <v>334</v>
       </c>
@@ -20305,7 +20316,7 @@
       <c r="I2" s="346"/>
       <c r="J2" s="346"/>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="E3" s="435" t="s">
         <v>542</v>
       </c>
@@ -20314,7 +20325,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B4" s="422" t="s">
         <v>534</v>
       </c>
@@ -20331,7 +20342,7 @@
         <v>INT</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B5" s="343" t="s">
         <v>364</v>
       </c>
@@ -20347,7 +20358,7 @@
         <v>Y</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B6" s="350" t="s">
         <v>336</v>
       </c>
@@ -20357,7 +20368,7 @@
       </c>
       <c r="E6" s="354"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B7" s="343" t="s">
         <v>366</v>
       </c>
@@ -20368,16 +20379,16 @@
       <c r="D7" s="354"/>
       <c r="E7" s="354"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B8" s="351" t="s">
         <v>365</v>
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>106.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>103.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B9" s="351" t="s">
         <v>361</v>
       </c>
@@ -20386,43 +20397,43 @@
         <v>3007054361.0630002</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B10" s="351" t="s">
         <v>367</v>
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>319950.58401710319</v>
+        <v>312132.24267833942</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.24012210262343742</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>0.25085546041516749</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="D11" s="349"/>
       <c r="E11" s="349"/>
     </row>
-    <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="472" t="s">
+    <row r="12" spans="1:10" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="475" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="472"/>
-      <c r="D12" s="472"/>
-      <c r="E12" s="472"/>
-      <c r="F12" s="472"/>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="C12" s="475"/>
+      <c r="D12" s="475"/>
+      <c r="E12" s="475"/>
+      <c r="F12" s="475"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B14" s="347" t="s">
         <v>370</v>
       </c>
       <c r="C14" s="348"/>
       <c r="D14" s="349"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B15" s="343" t="s">
         <v>337</v>
       </c>
@@ -20438,7 +20449,7 @@
         <v>CNY/HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B16" s="343" t="s">
         <v>338</v>
       </c>
@@ -20451,10 +20462,10 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1310185977458953</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>1.1315830089569092</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B17" s="343" t="s">
         <v>535</v>
       </c>
@@ -20470,14 +20481,14 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B18" s="343" t="str">
         <f>"预期股权价值 ("&amp;C7&amp;") :"</f>
         <v>预期股权价值 (HKD) :</v>
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>189.66386019290991</v>
+        <v>189.75850798139936</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20487,7 +20498,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B19" s="350" t="s">
         <v>335</v>
       </c>
@@ -20503,11 +20514,11 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="D20" s="349"/>
       <c r="E20" s="349"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B21" s="347" t="s">
         <v>493</v>
       </c>
@@ -20523,13 +20534,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B22" s="343" t="s">
         <v>340</v>
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>93.825479581874617</v>
+        <v>93.869096074266068</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20539,13 +20550,13 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B23" s="343" t="s">
         <v>341</v>
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>116.93818609630651</v>
+        <v>116.99285629904411</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20555,13 +20566,13 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B24" s="343" t="s">
         <v>343</v>
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>144.41177994461933</v>
+        <v>144.47961973069502</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20571,13 +20582,13 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B25" s="343" t="s">
         <v>342</v>
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>162.91149242558481</v>
+        <v>162.9882141875724</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20587,7 +20598,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="13.9">
+    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A27" s="345" t="s">
         <v>345</v>
       </c>
@@ -20597,25 +20608,25 @@
       <c r="E27" s="345"/>
       <c r="F27" s="345"/>
     </row>
-    <row r="29" spans="1:6">
-      <c r="B29" s="472" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B29" s="475" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="472"/>
-      <c r="D29" s="472"/>
-      <c r="E29" s="472"/>
-      <c r="F29" s="472"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="C29" s="475"/>
+      <c r="D29" s="475"/>
+      <c r="E29" s="475"/>
+      <c r="F29" s="475"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="478" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="C30" s="478"/>
+      <c r="D30" s="478"/>
+      <c r="E30" s="478"/>
+      <c r="F30" s="478"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B32" s="369" t="s">
         <v>371</v>
       </c>
@@ -20624,7 +20635,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" s="471" t="s">
         <v>501</v>
       </c>
@@ -20633,7 +20644,7 @@
       <c r="E33" s="471"/>
       <c r="F33" s="471"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34" s="372" t="s">
         <v>197</v>
       </c>
@@ -20646,11 +20657,11 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="35" spans="2:6">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" s="372"/>
       <c r="C35" s="374"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="471" t="s">
         <v>502</v>
       </c>
@@ -20659,7 +20670,7 @@
       <c r="E36" s="471"/>
       <c r="F36" s="471"/>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37" s="372" t="s">
         <v>199</v>
       </c>
@@ -20672,7 +20683,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="375" t="s">
         <v>200</v>
       </c>
@@ -20685,7 +20696,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40" s="471" t="s">
         <v>503</v>
       </c>
@@ -20694,7 +20705,7 @@
       <c r="E40" s="471"/>
       <c r="F40" s="471"/>
     </row>
-    <row r="41" spans="2:6">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" s="372" t="s">
         <v>202</v>
       </c>
@@ -20707,7 +20718,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B43" s="471" t="s">
         <v>504</v>
       </c>
@@ -20716,7 +20727,7 @@
       <c r="E43" s="471"/>
       <c r="F43" s="471"/>
     </row>
-    <row r="44" spans="2:6">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B44" s="372" t="s">
         <v>267</v>
       </c>
@@ -20731,7 +20742,7 @@
       <c r="E44" s="371"/>
       <c r="F44" s="371"/>
     </row>
-    <row r="45" spans="2:6">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B45" s="372" t="s">
         <v>268</v>
       </c>
@@ -20746,7 +20757,7 @@
       <c r="E45" s="371"/>
       <c r="F45" s="371"/>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="372" t="s">
         <v>203</v>
       </c>
@@ -20759,12 +20770,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B48" s="343" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="49" spans="2:6">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B49" s="372" t="s">
         <v>223</v>
       </c>
@@ -20777,7 +20788,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B51" s="471" t="s">
         <v>506</v>
       </c>
@@ -20786,7 +20797,7 @@
       <c r="E51" s="471"/>
       <c r="F51" s="471"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="372" t="s">
         <v>496</v>
       </c>
@@ -20799,16 +20810,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B54" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="474"/>
-      <c r="D54" s="474"/>
-      <c r="E54" s="474"/>
-      <c r="F54" s="474"/>
-    </row>
-    <row r="55" spans="2:6">
+      <c r="C54" s="477"/>
+      <c r="D54" s="477"/>
+      <c r="E54" s="477"/>
+      <c r="F54" s="477"/>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B55" s="372" t="s">
         <v>207</v>
       </c>
@@ -20821,25 +20832,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="2:6">
-      <c r="B57" s="472" t="s">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="475" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="472"/>
-      <c r="D57" s="472"/>
-      <c r="E57" s="472"/>
-      <c r="F57" s="472"/>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="472" t="s">
+      <c r="C57" s="475"/>
+      <c r="D57" s="475"/>
+      <c r="E57" s="475"/>
+      <c r="F57" s="475"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="475" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="472"/>
-      <c r="D58" s="472"/>
-      <c r="E58" s="472"/>
-      <c r="F58" s="472"/>
-    </row>
-    <row r="60" spans="2:6">
+      <c r="C58" s="475"/>
+      <c r="D58" s="475"/>
+      <c r="E58" s="475"/>
+      <c r="F58" s="475"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B60" s="372" t="s">
         <v>372</v>
       </c>
@@ -20852,7 +20863,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B61" s="372" t="s">
         <v>213</v>
       </c>
@@ -20865,23 +20876,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B62" s="377" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.0942430003061269E-2</v>
+        <v>8.3011294104839359E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
-    <row r="63" spans="2:6">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B63" s="377" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.2988721804511276E-2</v>
+        <v>3.3815028901734101E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20891,7 +20902,7 @@
         <v>0.51217277206029399</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B65" s="369" t="s">
         <v>376</v>
       </c>
@@ -20902,7 +20913,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B66" s="372" t="s">
         <v>326</v>
       </c>
@@ -20915,7 +20926,7 @@
         <v>0.12811576111950596</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B67" s="382" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -20929,7 +20940,7 @@
         <v>3.3655816827304348E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B68" s="382" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -20943,7 +20954,7 @@
         <v>1.6240671367246462</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B69" s="382" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -20957,7 +20968,7 @@
         <v>2.3438965902371725</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="13.9">
+    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A71" s="345" t="s">
         <v>476</v>
       </c>
@@ -20967,43 +20978,43 @@
       <c r="E71" s="345"/>
       <c r="F71" s="345"/>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="385"/>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="386"/>
-      <c r="B73" s="472" t="s">
+      <c r="B73" s="475" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="472"/>
-      <c r="D73" s="472"/>
-      <c r="E73" s="472"/>
-      <c r="F73" s="472"/>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="C73" s="475"/>
+      <c r="D73" s="475"/>
+      <c r="E73" s="475"/>
+      <c r="F73" s="475"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B74" s="478" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
-    </row>
-    <row r="76" spans="1:6">
+      <c r="C74" s="478"/>
+      <c r="D74" s="478"/>
+      <c r="E74" s="478"/>
+      <c r="F74" s="478"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B76" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="472" t="s">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B77" s="475" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="472"/>
-      <c r="D77" s="472"/>
-      <c r="E77" s="472"/>
-      <c r="F77" s="472"/>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="C77" s="475"/>
+      <c r="D77" s="475"/>
+      <c r="E77" s="475"/>
+      <c r="F77" s="475"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B78" s="343" t="s">
         <v>215</v>
       </c>
@@ -21016,20 +21027,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B79" s="372" t="s">
         <v>234</v>
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-42.159112666631181</v>
+        <v>-42.180151291356594</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B80" s="382" t="s">
         <v>309</v>
       </c>
@@ -21038,7 +21049,7 @@
         <v>0.36820511135930623</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B81" s="382" t="s">
         <v>311</v>
       </c>
@@ -21047,12 +21058,12 @@
         <v>2.8852377432054559</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B83" s="343" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B84" s="343" t="s">
         <v>224</v>
       </c>
@@ -21065,7 +21076,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B85" s="382" t="s">
         <v>481</v>
       </c>
@@ -21078,25 +21089,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B86" s="372" t="s">
         <v>235</v>
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>11.669886986015634</v>
+        <v>11.675710599402095</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B88" s="343" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B89" s="343" t="s">
         <v>217</v>
       </c>
@@ -21109,33 +21120,33 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B90" s="372" t="s">
         <v>236</v>
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>37.059917043908889</v>
+        <v>37.078411021550387</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B92" s="372" t="s">
         <v>480</v>
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>6.5706913632933395</v>
+        <v>6.5739703295958796</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="13.9">
+    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A94" s="345" t="s">
         <v>482</v>
       </c>
@@ -21145,49 +21156,49 @@
       <c r="E94" s="345"/>
       <c r="F94" s="345"/>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="385"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="385"/>
-      <c r="B96" s="472" t="s">
+      <c r="B96" s="475" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="472"/>
-      <c r="D96" s="472"/>
-      <c r="E96" s="472"/>
-      <c r="F96" s="472"/>
-    </row>
-    <row r="97" spans="1:6">
+      <c r="C96" s="475"/>
+      <c r="D96" s="475"/>
+      <c r="E96" s="475"/>
+      <c r="F96" s="475"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="385"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="478" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
-    </row>
-    <row r="98" spans="1:6">
+      <c r="C97" s="478"/>
+      <c r="D97" s="478"/>
+      <c r="E97" s="478"/>
+      <c r="F97" s="478"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="385"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="478" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
-    </row>
-    <row r="99" spans="1:6">
+      <c r="C98" s="478"/>
+      <c r="D98" s="478"/>
+      <c r="E98" s="478"/>
+      <c r="F98" s="478"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="385"/>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="385"/>
       <c r="B100" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="385"/>
       <c r="B101" s="372" t="s">
         <v>212</v>
@@ -21197,7 +21208,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="385"/>
       <c r="B102" s="382" t="s">
         <v>318</v>
@@ -21207,7 +21218,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="385"/>
       <c r="B103" s="382" t="s">
         <v>317</v>
@@ -21217,7 +21228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="385"/>
       <c r="B104" s="372" t="s">
         <v>535</v>
@@ -21226,97 +21237,97 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="385"/>
       <c r="C105" s="392"/>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="385"/>
       <c r="B106" s="393" t="s">
         <v>375</v>
       </c>
       <c r="C106" s="392"/>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="385"/>
-      <c r="B107" s="472" t="s">
+      <c r="B107" s="475" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="472"/>
-      <c r="D107" s="472"/>
-      <c r="E107" s="472"/>
-      <c r="F107" s="472"/>
-    </row>
-    <row r="108" spans="1:6">
+      <c r="C107" s="475"/>
+      <c r="D107" s="475"/>
+      <c r="E107" s="475"/>
+      <c r="F107" s="475"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="385"/>
-      <c r="B108" s="472" t="s">
+      <c r="B108" s="475" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="472"/>
-      <c r="D108" s="472"/>
-      <c r="E108" s="472"/>
-      <c r="F108" s="472"/>
-    </row>
-    <row r="109" spans="1:6">
+      <c r="C108" s="475"/>
+      <c r="D108" s="475"/>
+      <c r="E108" s="475"/>
+      <c r="F108" s="475"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="385"/>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="385"/>
       <c r="B110" s="369" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="385"/>
       <c r="B111" s="375" t="s">
         <v>486</v>
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-65.267413389288336</v>
+        <v>-65.299983728895668</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="385"/>
       <c r="B112" s="372" t="s">
         <v>377</v>
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>173.89488266562165</v>
+        <v>173.98166127519536</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="385"/>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="385"/>
-      <c r="B114" s="472" t="s">
+      <c r="B114" s="475" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="472"/>
-      <c r="D114" s="472"/>
-      <c r="E114" s="472"/>
-      <c r="F114" s="472"/>
-    </row>
-    <row r="115" spans="1:6">
+      <c r="C114" s="475"/>
+      <c r="D114" s="475"/>
+      <c r="E114" s="475"/>
+      <c r="F114" s="475"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="385"/>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="385"/>
       <c r="B116" s="369" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="385"/>
       <c r="B117" s="342" t="s">
         <v>378</v>
@@ -21334,7 +21345,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="385"/>
       <c r="B118" s="395" t="str">
         <f>DCF!B90</f>
@@ -21350,14 +21361,14 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>231.33 HKD</v>
+        <v>231.45 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="385"/>
       <c r="B119" s="400" t="str">
         <f>DCF!B91</f>
@@ -21373,14 +21384,14 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>198.73 HKD</v>
+        <v>198.83 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B120" s="400" t="str">
         <f>DCF!B92</f>
         <v>Base</v>
@@ -21395,14 +21406,14 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>184.25 HKD</v>
+        <v>184.34 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
         <v>0.44</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B121" s="400" t="str">
         <f>DCF!B93</f>
         <v>Pessimistic</v>
@@ -21417,14 +21428,14 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>170.87 HKD</v>
+        <v>170.95 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B122" s="400" t="str">
         <f>DCF!B94</f>
         <v>Devil's advocate</v>
@@ -21439,14 +21450,14 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>158.51 HKD</v>
+        <v>158.59 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B124" s="471" t="s">
         <v>519</v>
       </c>
@@ -21455,29 +21466,29 @@
       <c r="E124" s="471"/>
       <c r="F124" s="471"/>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B125" s="372" t="s">
         <v>218</v>
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>189.66386019290991</v>
+        <v>189.75850798139936</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="476" t="s">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B127" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="476"/>
-      <c r="D127" s="476"/>
-      <c r="E127" s="476"/>
-      <c r="F127" s="476"/>
-    </row>
-    <row r="129" spans="1:6" ht="13.9">
+      <c r="C127" s="473"/>
+      <c r="D127" s="473"/>
+      <c r="E127" s="473"/>
+      <c r="F127" s="473"/>
+    </row>
+    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A129" s="345" t="s">
         <v>492</v>
       </c>
@@ -21487,30 +21498,30 @@
       <c r="E129" s="345"/>
       <c r="F129" s="345"/>
     </row>
-    <row r="131" spans="1:6">
-      <c r="B131" s="477" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B131" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="477"/>
-      <c r="D131" s="477"/>
-      <c r="E131" s="477"/>
-      <c r="F131" s="477"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="472" t="s">
+      <c r="C131" s="474"/>
+      <c r="D131" s="474"/>
+      <c r="E131" s="474"/>
+      <c r="F131" s="474"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B132" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="472"/>
-      <c r="D132" s="472"/>
-      <c r="E132" s="472"/>
-      <c r="F132" s="472"/>
-    </row>
-    <row r="134" spans="1:6">
+      <c r="C132" s="475"/>
+      <c r="D132" s="475"/>
+      <c r="E132" s="475"/>
+      <c r="F132" s="475"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B134" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B135" s="343" t="s">
         <v>382</v>
       </c>
@@ -21519,7 +21530,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B136" s="343" t="s">
         <v>383</v>
       </c>
@@ -21532,14 +21543,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B138" s="369" t="s">
         <v>493</v>
       </c>
       <c r="C138" s="407"/>
       <c r="D138" s="407"/>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -21558,7 +21569,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B140" s="408" t="s">
         <v>312</v>
       </c>
@@ -21568,18 +21579,18 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>87.402700549728095</v>
+        <v>87.446317042119546</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>93.825479581874617</v>
+        <v>93.869096074266068</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B141" s="408" t="s">
         <v>313</v>
       </c>
@@ -21589,18 +21600,18 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>109.55313224139205</v>
+        <v>109.60780244412965</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>116.93818609630651</v>
+        <v>116.99285629904411</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -21619,7 +21630,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B144" s="408" t="s">
         <v>315</v>
       </c>
@@ -21629,18 +21640,18 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>135.94354297257468</v>
+        <v>136.01138275865037</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>144.41177994461933</v>
+        <v>144.47961973069502</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B145" s="408" t="s">
         <v>314</v>
       </c>
@@ -21650,18 +21661,18 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>153.74205537820751</v>
+        <v>153.81877714019512</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>162.91149242558481</v>
+        <v>162.9882141875724</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="13.9">
+    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A147" s="345" t="s">
         <v>475</v>
       </c>
@@ -21671,50 +21682,50 @@
       <c r="E147" s="345"/>
       <c r="F147" s="345"/>
     </row>
-    <row r="149" spans="1:6">
-      <c r="B149" s="478" t="s">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B149" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="472"/>
-      <c r="D149" s="472"/>
-      <c r="E149" s="472"/>
-      <c r="F149" s="472"/>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="C149" s="475"/>
+      <c r="D149" s="475"/>
+      <c r="E149" s="475"/>
+      <c r="F149" s="475"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B151" s="369" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
-      <c r="B152" s="474" t="s">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B152" s="477" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="474"/>
-      <c r="D152" s="474"/>
-      <c r="E152" s="474"/>
-      <c r="F152" s="474"/>
-    </row>
-    <row r="153" spans="1:6">
+      <c r="C152" s="477"/>
+      <c r="D152" s="477"/>
+      <c r="E152" s="477"/>
+      <c r="F152" s="477"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B153" s="412" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B154" s="412" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B155" s="412" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B157" s="343" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="24.5" customHeight="1">
+    <row r="158" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B158" s="471" t="s">
         <v>439</v>
       </c>
@@ -21723,60 +21734,57 @@
       <c r="E158" s="471"/>
       <c r="F158" s="471"/>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B160" s="343" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="475" t="s">
+    <row r="161" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B161" s="472" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="475"/>
-      <c r="D161" s="475"/>
-      <c r="E161" s="475"/>
-      <c r="F161" s="475"/>
-    </row>
-    <row r="162" spans="2:6">
-      <c r="B162" s="475" t="s">
+      <c r="C161" s="472"/>
+      <c r="D161" s="472"/>
+      <c r="E161" s="472"/>
+      <c r="F161" s="472"/>
+    </row>
+    <row r="162" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B162" s="472" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="475"/>
-      <c r="D162" s="475"/>
-      <c r="E162" s="475"/>
-      <c r="F162" s="475"/>
-    </row>
-    <row r="164" spans="2:6">
+      <c r="C162" s="472"/>
+      <c r="D162" s="472"/>
+      <c r="E162" s="472"/>
+      <c r="F162" s="472"/>
+    </row>
+    <row r="164" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B164" s="343" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="165" spans="2:6">
+    <row r="165" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B165" s="412" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
+    <row r="166" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B166" s="412" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
+    <row r="167" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B167" s="412" t="s">
         <v>392</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21791,12 +21799,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9618.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9618.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDAD5803-A1F2-AC45-9138-CE8962A0E39A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58A4D64-7A47-4F9B-AA60-CD40BA3367DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -39,17 +39,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -3286,27 +3275,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="19">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.00\x"/>
-    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="171" formatCode="#,##0_ "/>
-    <numFmt numFmtId="172" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="173" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="174" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="175" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="176" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="177" formatCode="0.000_ "/>
-    <numFmt numFmtId="178" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="179" formatCode="0.0\x"/>
-    <numFmt numFmtId="180" formatCode="0\x"/>
-    <numFmt numFmtId="181" formatCode="0.000000000000000%"/>
-    <numFmt numFmtId="182" formatCode="#,##0_);\(#,##0\);0;@"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00\x"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="170" formatCode="#,##0_ "/>
+    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="178" formatCode="0.0\x"/>
+    <numFmt numFmtId="179" formatCode="0\x"/>
+    <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="72" x14ac:knownFonts="1">
+  <fonts count="72">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4058,7 +4047,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4100,17 +4089,17 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4119,7 +4108,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4193,10 +4182,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4207,7 +4196,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4245,7 +4234,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4255,7 +4244,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4266,19 +4255,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4286,8 +4275,8 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4310,29 +4299,29 @@
     </xf>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4349,15 +4338,15 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4368,11 +4357,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4433,14 +4422,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4453,7 +4442,7 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4490,7 +4479,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4507,7 +4496,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4553,7 +4542,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4568,13 +4557,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4590,53 +4579,53 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="182" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4653,7 +4642,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -4666,21 +4655,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="182" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4690,14 +4679,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4706,8 +4695,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4719,7 +4708,7 @@
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4727,7 +4716,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4766,7 +4755,7 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4780,39 +4769,39 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="174" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4823,7 +4812,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4834,10 +4823,10 @@
     <xf numFmtId="9" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4846,7 +4835,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4859,7 +4848,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4868,8 +4857,8 @@
     <xf numFmtId="40" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4877,10 +4866,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4889,10 +4878,10 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4909,16 +4898,16 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4939,7 +4928,7 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4957,7 +4946,7 @@
     <xf numFmtId="40" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4967,10 +4956,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4985,7 +4974,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="71" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4999,12 +4988,30 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -5012,24 +5019,6 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5039,6 +5028,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5048,21 +5046,12 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5344,7 +5333,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:I167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -5353,7 +5342,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="13.9">
       <c r="A2" s="200" t="s">
         <v>225</v>
       </c>
@@ -5366,7 +5355,7 @@
       <c r="H2" s="21"/>
       <c r="I2" s="21"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9">
       <c r="E3" s="428" t="s">
         <v>538</v>
       </c>
@@ -5374,7 +5363,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="421" t="s">
         <v>533</v>
       </c>
@@ -5388,7 +5377,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
         <v>349</v>
       </c>
@@ -5402,7 +5391,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9">
       <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
@@ -5412,7 +5401,7 @@
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9">
       <c r="B7" s="1" t="s">
         <v>351</v>
       </c>
@@ -5422,16 +5411,16 @@
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9">
       <c r="B8" s="4" t="s">
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>103.8</v>
+        <v>104.4</v>
       </c>
       <c r="E8" s="32"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9">
       <c r="B9" s="4" t="s">
         <v>346</v>
       </c>
@@ -5440,43 +5429,43 @@
         <v>3007054361.0630002</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
         <v>352</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>312132.24267833942</v>
+        <v>313936.47529497725</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.25085546041516749</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+        <v>0.25152402246872663</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:9" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="463" t="s">
+    <row r="12" spans="1:9" ht="24.5" customHeight="1">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="463"/>
-      <c r="D12" s="463"/>
-      <c r="E12" s="463"/>
-      <c r="F12" s="463"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
         <v>2-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:9">
       <c r="B15" s="1" t="s">
         <v>319</v>
       </c>
@@ -5491,7 +5480,7 @@
         <v>CNY/HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:9">
       <c r="B16" s="1" t="s">
         <v>320</v>
       </c>
@@ -5502,10 +5491,10 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1315830089569092</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+        <v>1.1404913400000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
         <v>532</v>
       </c>
@@ -5519,14 +5508,14 @@
         <v>558</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:6">
       <c r="B18" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C7&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>189.75850798139936</v>
+        <v>191.25237241198982</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5535,7 +5524,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
         <v>275</v>
       </c>
@@ -5551,11 +5540,11 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:6">
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
         <v>404</v>
       </c>
@@ -5570,13 +5559,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:6">
       <c r="B22" s="1" t="s">
         <v>312</v>
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>93.869096074266068</v>
+        <v>94.557512862556607</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5585,13 +5574,13 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:6">
       <c r="B23" s="1" t="s">
         <v>313</v>
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>116.99285629904411</v>
+        <v>117.8557382806126</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5600,13 +5589,13 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:6">
       <c r="B24" s="1" t="s">
         <v>315</v>
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>144.47961973069502</v>
+        <v>145.55036258707588</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5615,13 +5604,13 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:6">
       <c r="B25" s="1" t="s">
         <v>314</v>
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>162.9882141875724</v>
+        <v>164.19914487189874</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5630,11 +5619,11 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:6">
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="200" t="s">
         <v>280</v>
       </c>
@@ -5644,25 +5633,25 @@
       <c r="E27" s="34"/>
       <c r="F27" s="34"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B29" s="463" t="s">
+    <row r="29" spans="1:6">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="463"/>
-      <c r="D29" s="463"/>
-      <c r="E29" s="463"/>
-      <c r="F29" s="463"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="467" t="s">
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="463" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="467"/>
-      <c r="D30" s="467"/>
-      <c r="E30" s="467"/>
-      <c r="F30" s="467"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C30" s="463"/>
+      <c r="D30" s="463"/>
+      <c r="E30" s="463"/>
+      <c r="F30" s="463"/>
+    </row>
+    <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
         <v>195</v>
       </c>
@@ -5671,16 +5660,16 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="464" t="s">
+    <row r="33" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="464"/>
-      <c r="D33" s="464"/>
-      <c r="E33" s="464"/>
-      <c r="F33" s="464"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
+    </row>
+    <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
         <v>197</v>
       </c>
@@ -5693,20 +5682,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:6">
       <c r="B35" s="44"/>
       <c r="C35" s="73"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="464" t="s">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="464"/>
-      <c r="D36" s="464"/>
-      <c r="E36" s="464"/>
-      <c r="F36" s="464"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
+    </row>
+    <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
         <v>199</v>
       </c>
@@ -5719,7 +5708,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="49" t="s">
         <v>200</v>
       </c>
@@ -5732,16 +5721,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B40" s="464" t="s">
+    <row r="40" spans="2:6">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="464"/>
-      <c r="D40" s="464"/>
-      <c r="E40" s="464"/>
-      <c r="F40" s="464"/>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
+    </row>
+    <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
         <v>202</v>
       </c>
@@ -5754,16 +5743,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B43" s="464" t="s">
+    <row r="43" spans="2:6">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="464"/>
-      <c r="D43" s="464"/>
-      <c r="E43" s="464"/>
-      <c r="F43" s="464"/>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
+    </row>
+    <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
         <v>267</v>
       </c>
@@ -5778,7 +5767,7 @@
       <c r="E44" s="244"/>
       <c r="F44" s="244"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6">
       <c r="B45" s="44" t="s">
         <v>268</v>
       </c>
@@ -5793,7 +5782,7 @@
       <c r="E45" s="244"/>
       <c r="F45" s="244"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="44" t="s">
         <v>203</v>
       </c>
@@ -5806,12 +5795,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6">
       <c r="B48" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6">
       <c r="B49" s="44" t="s">
         <v>223</v>
       </c>
@@ -5824,16 +5813,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B51" s="464" t="s">
+    <row r="51" spans="2:6">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="464"/>
-      <c r="D51" s="464"/>
-      <c r="E51" s="464"/>
-      <c r="F51" s="464"/>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
+    </row>
+    <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
         <v>204</v>
       </c>
@@ -5846,8 +5835,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B54" s="464" t="s">
+    <row r="54" spans="2:6">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5855,7 +5844,7 @@
       <c r="E54" s="465"/>
       <c r="F54" s="465"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
         <v>207</v>
       </c>
@@ -5868,25 +5857,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B57" s="463" t="s">
+    <row r="57" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="463"/>
-      <c r="D57" s="463"/>
-      <c r="E57" s="463"/>
-      <c r="F57" s="463"/>
-    </row>
-    <row r="58" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B58" s="463" t="s">
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
+    </row>
+    <row r="58" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="463"/>
-      <c r="D58" s="463"/>
-      <c r="E58" s="463"/>
-      <c r="F58" s="463"/>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
         <v>227</v>
       </c>
@@ -5899,7 +5888,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:6">
       <c r="B61" s="44" t="s">
         <v>213</v>
       </c>
@@ -5912,23 +5901,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="204" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.3011294104839359E-2</v>
+        <v>8.3183964232110025E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6">
       <c r="B63" s="204" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.3815028901734101E-2</v>
+        <v>3.3620689655172412E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5938,7 +5927,7 @@
         <v>0.51217277206029399</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6">
       <c r="B65" s="192" t="s">
         <v>325</v>
       </c>
@@ -5949,7 +5938,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:6">
       <c r="B66" s="44" t="s">
         <v>326</v>
       </c>
@@ -5962,7 +5951,7 @@
         <v>0.12811576111950596</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6">
       <c r="B67" s="229" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -5976,7 +5965,7 @@
         <v>3.3655816827304348E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="229" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -5990,7 +5979,7 @@
         <v>1.6240671367246462</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="229" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -6004,7 +5993,7 @@
         <v>2.3438965902371725</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="200" t="s">
         <v>477</v>
       </c>
@@ -6014,45 +6003,45 @@
       <c r="E71" s="34"/>
       <c r="F71" s="34"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="A72" s="191"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="463" t="s">
+      <c r="B73" s="461" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="463"/>
-      <c r="D73" s="463"/>
-      <c r="E73" s="463"/>
-      <c r="F73" s="463"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="A75" s="191"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="A76" s="191"/>
       <c r="B76" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="463" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="463"/>
-      <c r="D77" s="463"/>
-      <c r="E77" s="463"/>
-      <c r="F77" s="463"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" s="191"/>
       <c r="B78" s="1" t="s">
         <v>215</v>
@@ -6066,21 +6055,21 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="191"/>
       <c r="B79" s="44" t="s">
         <v>234</v>
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-42.180151291356594</v>
+        <v>-42.512212437712471</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="A80" s="191"/>
       <c r="B80" s="229" t="s">
         <v>309</v>
@@ -6090,7 +6079,7 @@
         <v>0.36820511135930623</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:6">
       <c r="A81" s="191"/>
       <c r="B81" s="229" t="s">
         <v>311</v>
@@ -6100,16 +6089,16 @@
         <v>2.8852377432054559</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="A82" s="191"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="A84" s="191"/>
       <c r="B84" s="1" t="s">
         <v>224</v>
@@ -6123,7 +6112,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="A85" s="191"/>
       <c r="B85" s="229" t="s">
         <v>222</v>
@@ -6137,30 +6126,30 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="A86" s="191"/>
       <c r="B86" s="44" t="s">
         <v>235</v>
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>11.675710599402095</v>
+        <v>11.767627051274838</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="A87" s="191"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="A88" s="191"/>
       <c r="B88" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:6">
       <c r="A89" s="191"/>
       <c r="B89" s="1" t="s">
         <v>217</v>
@@ -6174,38 +6163,38 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="191"/>
       <c r="B90" s="44" t="s">
         <v>236</v>
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>37.078411021550387</v>
+        <v>37.370308970986933</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6">
       <c r="A91" s="191"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
         <v>469</v>
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.5739703295958796</v>
+        <v>6.6257235845492923</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="200" t="s">
         <v>470</v>
       </c>
@@ -6215,42 +6204,42 @@
       <c r="E94" s="34"/>
       <c r="F94" s="34"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6">
       <c r="A95" s="191"/>
     </row>
-    <row r="96" spans="1:6" ht="11.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B96" s="463" t="s">
+    <row r="96" spans="1:6" ht="11.75" customHeight="1">
+      <c r="B96" s="461" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="463"/>
-      <c r="D96" s="463"/>
-      <c r="E96" s="463"/>
-      <c r="F96" s="463"/>
-    </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B97" s="467" t="s">
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="463" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="467"/>
-      <c r="D97" s="467"/>
-      <c r="E97" s="467"/>
-      <c r="F97" s="467"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B98" s="467" t="s">
+      <c r="C97" s="463"/>
+      <c r="D97" s="463"/>
+      <c r="E97" s="463"/>
+      <c r="F97" s="463"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="463" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="467"/>
-      <c r="D98" s="467"/>
-      <c r="E98" s="467"/>
-      <c r="F98" s="467"/>
-    </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C98" s="463"/>
+      <c r="D98" s="463"/>
+      <c r="E98" s="463"/>
+      <c r="F98" s="463"/>
+    </row>
+    <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
         <v>467</v>
       </c>
@@ -6259,7 +6248,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:6">
       <c r="B102" s="229" t="s">
         <v>318</v>
       </c>
@@ -6268,7 +6257,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="229" t="s">
         <v>317</v>
       </c>
@@ -6277,7 +6266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="44" t="s">
         <v>214</v>
       </c>
@@ -6286,76 +6275,76 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:6">
       <c r="B106" s="250" t="s">
         <v>281</v>
       </c>
       <c r="C106" s="116"/>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B107" s="463" t="s">
+    <row r="107" spans="2:6">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="463"/>
-      <c r="D107" s="463"/>
-      <c r="E107" s="463"/>
-      <c r="F107" s="463"/>
-    </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B108" s="463" t="s">
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="463"/>
-      <c r="D108" s="463"/>
-      <c r="E108" s="463"/>
-      <c r="F108" s="463"/>
-    </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
+    </row>
+    <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="111" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
         <v>468</v>
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-65.299983728895668</v>
+        <v>-65.814054607974768</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:6">
       <c r="B112" s="44" t="s">
         <v>323</v>
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>173.98166127519536</v>
+        <v>175.3513232635766</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B114" s="463" t="s">
+    <row r="114" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B114" s="461" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="463"/>
-      <c r="D114" s="463"/>
-      <c r="E114" s="463"/>
-      <c r="F114" s="463"/>
-    </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
+    </row>
+    <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="117" spans="2:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:6" ht="12.4">
       <c r="B117" s="342" t="s">
         <v>101</v>
       </c>
@@ -6372,7 +6361,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="118" spans="2:6">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
         <v>Snowball Scenario (10yrs)</v>
@@ -6383,7 +6372,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>231.45 HKD</v>
+        <v>233.27 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6391,10 +6380,10 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-4.7838899145048276E-2</v>
-      </c>
-    </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.15">
+        <v>-4.7965458280397603E-2</v>
+      </c>
+    </row>
+    <row r="119" spans="2:6">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
         <v>Optimistic (10yrs)</v>
@@ -6405,7 +6394,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>198.83 HKD</v>
+        <v>200.39 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6413,10 +6402,10 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.4914009688719284E-3</v>
-      </c>
-    </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.15">
+        <v>2.3513871529537845E-3</v>
+      </c>
+    </row>
+    <row r="120" spans="2:6">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
         <v>Base (10yrs)</v>
@@ -6427,7 +6416,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>184.34 HKD</v>
+        <v>185.79 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6435,10 +6424,10 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.8566496019313072E-2</v>
-      </c>
-    </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.15">
+        <v>2.8419157624928283E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="2:6">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
         <v>Pessimistic (10yrs)</v>
@@ -6449,7 +6438,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>170.95 HKD</v>
+        <v>172.3 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6457,10 +6446,10 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.5243319661748662E-2</v>
-      </c>
-    </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.15">
+        <v>5.5088231754056388E-2</v>
+      </c>
+    </row>
+    <row r="122" spans="2:6">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
         <v>Devil's advocate (10yrs)</v>
@@ -6471,7 +6460,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>158.59 HKD</v>
+        <v>159.84 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6479,32 +6468,32 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>8.2515145044167307E-2</v>
-      </c>
-    </row>
-    <row r="124" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B124" s="464" t="s">
+        <v>8.2351862495692874E-2</v>
+      </c>
+    </row>
+    <row r="124" spans="2:6">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="464"/>
-      <c r="D124" s="464"/>
-      <c r="E124" s="464"/>
-      <c r="F124" s="464"/>
-    </row>
-    <row r="125" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
+    </row>
+    <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
         <v>218</v>
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>189.75850798139936</v>
+        <v>191.25237241198982</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="2:6" ht="24.5" customHeight="1">
       <c r="B127" s="466" t="s">
         <v>358</v>
       </c>
@@ -6513,7 +6502,7 @@
       <c r="E127" s="466"/>
       <c r="F127" s="466"/>
     </row>
-    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="200" t="s">
         <v>474</v>
       </c>
@@ -6523,30 +6512,30 @@
       <c r="E129" s="34"/>
       <c r="F129" s="34"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B131" s="468" t="s">
+    <row r="131" spans="1:6">
+      <c r="B131" s="464" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="468"/>
-      <c r="D131" s="468"/>
-      <c r="E131" s="468"/>
-      <c r="F131" s="468"/>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B132" s="463" t="s">
+      <c r="C131" s="464"/>
+      <c r="D131" s="464"/>
+      <c r="E131" s="464"/>
+      <c r="F131" s="464"/>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="463"/>
-      <c r="D132" s="463"/>
-      <c r="E132" s="463"/>
-      <c r="F132" s="463"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
+    </row>
+    <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:6">
       <c r="B135" s="1" t="s">
         <v>221</v>
       </c>
@@ -6555,7 +6544,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="B136" s="194" t="s">
         <v>220</v>
       </c>
@@ -6568,14 +6557,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:6">
       <c r="B138" s="192" t="s">
         <v>494</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
-    <row r="139" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -6594,7 +6583,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="B140" s="336" t="s">
         <v>312</v>
       </c>
@@ -6604,18 +6593,18 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>87.446317042119546</v>
+        <v>88.134733830410084</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>93.869096074266068</v>
+        <v>94.557512862556607</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="336" t="s">
         <v>313</v>
       </c>
@@ -6625,25 +6614,25 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>109.60780244412965</v>
+        <v>110.47068442569814</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>116.99285629904411</v>
+        <v>117.8557382806126</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6">
       <c r="B142" s="194"/>
       <c r="C142" s="194"/>
       <c r="D142" s="194"/>
       <c r="E142" s="194"/>
       <c r="F142" s="194"/>
     </row>
-    <row r="143" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -6662,7 +6651,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:6">
       <c r="B144" s="336" t="s">
         <v>315</v>
       </c>
@@ -6672,18 +6661,18 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>136.01138275865037</v>
+        <v>137.08212561503123</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>144.47961973069502</v>
+        <v>145.55036258707588</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:6">
       <c r="B145" s="336" t="s">
         <v>314</v>
       </c>
@@ -6693,18 +6682,18 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>153.81877714019512</v>
+        <v>155.02970782452144</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>162.9882141875724</v>
+        <v>164.19914487189874</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="200" t="s">
         <v>475</v>
       </c>
@@ -6714,21 +6703,21 @@
       <c r="E147" s="34"/>
       <c r="F147" s="34"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B149" s="462" t="s">
+    <row r="149" spans="1:6">
+      <c r="B149" s="468" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="463"/>
-      <c r="D149" s="463"/>
-      <c r="E149" s="463"/>
-      <c r="F149" s="463"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
+    </row>
+    <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:6">
       <c r="B152" s="465" t="s">
         <v>293</v>
       </c>
@@ -6737,80 +6726,92 @@
       <c r="E152" s="465"/>
       <c r="F152" s="465"/>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:6">
       <c r="B154" s="196" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:6">
       <c r="B155" s="196" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:6">
       <c r="B157" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B158" s="464" t="s">
+    <row r="158" spans="1:6" ht="34.25" customHeight="1">
+      <c r="B158" s="462" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="464"/>
-      <c r="D158" s="464"/>
-      <c r="E158" s="464"/>
-      <c r="F158" s="464"/>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
+    </row>
+    <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="161" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B161" s="461" t="s">
+    <row r="161" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B161" s="467" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="461"/>
-      <c r="D161" s="461"/>
-      <c r="E161" s="461"/>
-      <c r="F161" s="461"/>
-    </row>
-    <row r="162" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B162" s="461" t="s">
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
+    </row>
+    <row r="162" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B162" s="467" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="461"/>
-      <c r="D162" s="461"/>
-      <c r="E162" s="461"/>
-      <c r="F162" s="461"/>
-    </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
+    </row>
+    <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:6">
       <c r="B165" s="196" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:6">
       <c r="B166" s="196" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:6">
       <c r="B167" s="196" t="s">
         <v>300</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6827,18 +6828,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6866,15 +6855,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
         <v>CNY</v>
@@ -6923,7 +6912,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>93</v>
       </c>
@@ -6939,7 +6928,7 @@
       <c r="L2" s="35"/>
       <c r="M2" s="35"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>25</v>
       </c>
@@ -6947,7 +6936,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="31" t="s">
         <v>0</v>
       </c>
@@ -6973,7 +6962,7 @@
       <c r="L4" s="287"/>
       <c r="M4" s="287"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="38" t="s">
         <v>40</v>
       </c>
@@ -6999,7 +6988,7 @@
       <c r="L5" s="287"/>
       <c r="M5" s="287"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="38" t="s">
         <v>51</v>
       </c>
@@ -7030,7 +7019,7 @@
       <c r="L6" s="287"/>
       <c r="M6" s="287"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="66" t="s">
         <v>58</v>
       </c>
@@ -7056,7 +7045,7 @@
       <c r="L7" s="288"/>
       <c r="M7" s="288"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="38" t="s">
         <v>46</v>
       </c>
@@ -7082,7 +7071,7 @@
       <c r="L8" s="287"/>
       <c r="M8" s="287"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="38" t="s">
         <v>134</v>
       </c>
@@ -7108,7 +7097,7 @@
       <c r="L9" s="287"/>
       <c r="M9" s="287"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="38" t="s">
         <v>138</v>
       </c>
@@ -7124,7 +7113,7 @@
       <c r="L10" s="287"/>
       <c r="M10" s="287"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="38" t="s">
         <v>133</v>
       </c>
@@ -7140,7 +7129,7 @@
       <c r="L11" s="287"/>
       <c r="M11" s="287"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="38" t="s">
         <v>37</v>
       </c>
@@ -7166,7 +7155,7 @@
       <c r="L12" s="287"/>
       <c r="M12" s="287"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="38" t="s">
         <v>64</v>
       </c>
@@ -7182,7 +7171,7 @@
       <c r="L13" s="287"/>
       <c r="M13" s="287"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="38" t="s">
         <v>47</v>
       </c>
@@ -7208,7 +7197,7 @@
       <c r="L14" s="287"/>
       <c r="M14" s="287"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="41" t="s">
         <v>39</v>
       </c>
@@ -7234,7 +7223,7 @@
       <c r="L15" s="289"/>
       <c r="M15" s="289"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="27" t="s">
         <v>41</v>
       </c>
@@ -7260,13 +7249,13 @@
       <c r="L16" s="287"/>
       <c r="M16" s="287"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
         <v>44</v>
       </c>
@@ -7288,7 +7277,7 @@
       <c r="L19" s="287"/>
       <c r="M19" s="287"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="26" t="s">
         <v>50</v>
       </c>
@@ -7304,7 +7293,7 @@
       <c r="L20" s="287"/>
       <c r="M20" s="287"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="26" t="s">
         <v>49</v>
       </c>
@@ -7320,7 +7309,7 @@
       <c r="L21" s="287"/>
       <c r="M21" s="287"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="26" t="s">
         <v>286</v>
       </c>
@@ -7344,7 +7333,7 @@
       <c r="L22" s="287"/>
       <c r="M22" s="287"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
         <v>288</v>
       </c>
@@ -7368,7 +7357,7 @@
       <c r="L23" s="287"/>
       <c r="M23" s="287"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="26" t="s">
         <v>287</v>
       </c>
@@ -7392,7 +7381,7 @@
       <c r="L24" s="287"/>
       <c r="M24" s="287"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="23" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -7420,7 +7409,7 @@
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>26</v>
       </c>
@@ -7428,7 +7417,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="25" t="s">
         <v>22</v>
       </c>
@@ -7454,7 +7443,7 @@
       <c r="L28" s="287"/>
       <c r="M28" s="287"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="25" t="s">
         <v>30</v>
       </c>
@@ -7479,7 +7468,7 @@
       <c r="L29" s="287"/>
       <c r="M29" s="287"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
         <v>38</v>
       </c>
@@ -7506,7 +7495,7 @@
       <c r="L30" s="289"/>
       <c r="M30" s="289"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="28" t="s">
         <v>28</v>
       </c>
@@ -7531,7 +7520,7 @@
       <c r="L31" s="289"/>
       <c r="M31" s="289"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="25" t="s">
         <v>143</v>
       </c>
@@ -7556,7 +7545,7 @@
       <c r="L32" s="287"/>
       <c r="M32" s="287"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="34" t="s">
         <v>78</v>
       </c>
@@ -7572,12 +7561,12 @@
       <c r="L34" s="35"/>
       <c r="M34" s="35"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="31" t="s">
         <v>0</v>
       </c>
@@ -7626,7 +7615,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="38" t="s">
         <v>40</v>
       </c>
@@ -7675,7 +7664,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="30" t="s">
         <v>55</v>
       </c>
@@ -7724,7 +7713,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="38" t="s">
         <v>51</v>
       </c>
@@ -7773,7 +7762,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="66" t="s">
         <v>58</v>
       </c>
@@ -7822,7 +7811,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="66" t="s">
         <v>61</v>
       </c>
@@ -7871,7 +7860,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="38" t="s">
         <v>46</v>
       </c>
@@ -7920,7 +7909,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="41" t="s">
         <v>127</v>
       </c>
@@ -7969,7 +7958,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="41" t="s">
         <v>139</v>
       </c>
@@ -8018,7 +8007,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="38" t="s">
         <v>65</v>
       </c>
@@ -8067,7 +8056,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="38" t="s">
         <v>47</v>
       </c>
@@ -8116,7 +8105,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="41" t="s">
         <v>39</v>
       </c>
@@ -8165,7 +8154,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="27" t="s">
         <v>41</v>
       </c>
@@ -8214,12 +8203,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="38" t="s">
         <v>37</v>
       </c>
@@ -8268,7 +8257,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="38" t="s">
         <v>64</v>
       </c>
@@ -8317,12 +8306,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="156" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="38" t="s">
         <v>134</v>
       </c>
@@ -8371,7 +8360,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="38" t="s">
         <v>138</v>
       </c>
@@ -8420,7 +8409,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="38" t="s">
         <v>133</v>
       </c>
@@ -8469,7 +8458,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="38" t="s">
         <v>135</v>
       </c>
@@ -8518,13 +8507,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="26" t="s">
         <v>44</v>
       </c>
@@ -8573,7 +8562,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="26" t="s">
         <v>50</v>
       </c>
@@ -8622,7 +8611,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="26" t="s">
         <v>49</v>
       </c>
@@ -8671,7 +8660,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="26" t="s">
         <v>305</v>
       </c>
@@ -8720,7 +8709,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="23" t="s">
         <v>34</v>
       </c>
@@ -8769,12 +8758,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="88" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8824,7 +8813,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="30" t="s">
         <v>55</v>
       </c>
@@ -8873,7 +8862,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="77" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8923,7 +8912,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="41" t="s">
         <v>139</v>
       </c>
@@ -8972,7 +8961,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="77" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -9022,7 +9011,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="34" t="s">
         <v>79</v>
       </c>
@@ -9038,13 +9027,13 @@
       <c r="L74" s="35"/>
       <c r="M74" s="35"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="25" t="s">
         <v>1</v>
       </c>
@@ -9093,7 +9082,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="90" t="s">
         <v>82</v>
       </c>
@@ -9127,7 +9116,7 @@
       <c r="L77" s="291"/>
       <c r="M77" s="291"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="90" t="s">
         <v>83</v>
       </c>
@@ -9161,7 +9150,7 @@
       <c r="L78" s="291"/>
       <c r="M78" s="291"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="25" t="s">
         <v>38</v>
       </c>
@@ -9210,7 +9199,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="25" t="s">
         <v>28</v>
       </c>
@@ -9291,7 +9280,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -9302,7 +9291,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="17" t="s">
         <v>35</v>
       </c>
@@ -9318,7 +9307,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="76" t="s">
         <v>131</v>
       </c>
@@ -9329,7 +9318,7 @@
       <c r="G2" s="35"/>
       <c r="H2" s="35"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>154</v>
       </c>
@@ -9349,7 +9338,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
@@ -9371,7 +9360,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
@@ -9392,7 +9381,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
@@ -9413,7 +9402,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>66</v>
       </c>
@@ -9434,7 +9423,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>144</v>
       </c>
@@ -9455,7 +9444,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
@@ -9477,7 +9466,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
@@ -9497,7 +9486,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
@@ -9509,7 +9498,7 @@
       </c>
       <c r="H11" s="232"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="77" t="s">
         <v>69</v>
       </c>
@@ -9533,12 +9522,12 @@
         <v>161854.1</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="77"/>
       <c r="G13" s="78"/>
       <c r="H13" s="19"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>153</v>
       </c>
@@ -9558,7 +9547,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>329</v>
       </c>
@@ -9578,7 +9567,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
@@ -9598,7 +9587,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>66</v>
       </c>
@@ -9619,7 +9608,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>144</v>
       </c>
@@ -9639,7 +9628,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>24</v>
       </c>
@@ -9661,7 +9650,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>16</v>
       </c>
@@ -9681,7 +9670,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>17</v>
       </c>
@@ -9701,7 +9690,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>18</v>
       </c>
@@ -9713,7 +9702,7 @@
       </c>
       <c r="H22" s="232"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>19</v>
       </c>
@@ -9726,7 +9715,7 @@
       </c>
       <c r="H23" s="232"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="77" t="s">
         <v>70</v>
       </c>
@@ -9750,7 +9739,7 @@
         <v>47409.899999999994</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>169</v>
       </c>
@@ -9767,7 +9756,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
@@ -9787,7 +9776,7 @@
         <v>-101040.34999999998</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>4</v>
       </c>
@@ -9802,7 +9791,7 @@
       </c>
       <c r="H28" s="170"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>5</v>
       </c>
@@ -9821,7 +9810,7 @@
         <v>-173527.34999999998</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>6</v>
       </c>
@@ -9837,7 +9826,7 @@
       </c>
       <c r="H30" s="170"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="77" t="s">
         <v>172</v>
       </c>
@@ -9854,7 +9843,7 @@
       </c>
       <c r="H31" s="170"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
@@ -9874,7 +9863,7 @@
         <v>308068.65000000002</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="80" t="s">
         <v>2</v>
       </c>
@@ -9885,7 +9874,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="177"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="80"/>
       <c r="C34" s="81"/>
       <c r="F34" s="178" t="s">
@@ -9898,7 +9887,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>170</v>
       </c>
@@ -9917,7 +9906,7 @@
         <v>98804.65</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>11</v>
       </c>
@@ -9934,7 +9923,7 @@
       </c>
       <c r="H36" s="177"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>12</v>
       </c>
@@ -9950,7 +9939,7 @@
       </c>
       <c r="H37" s="177"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>13</v>
       </c>
@@ -9966,7 +9955,7 @@
       </c>
       <c r="H38" s="177"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
@@ -9985,7 +9974,7 @@
         <v>16362.7</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="77" t="s">
         <v>173</v>
       </c>
@@ -10005,7 +9994,7 @@
         <v>209264</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>15</v>
       </c>
@@ -10025,7 +10014,7 @@
         <v>110732.3</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="80" t="s">
         <v>20</v>
       </c>
@@ -10044,7 +10033,7 @@
         <v>98531.7</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="76" t="s">
         <v>92</v>
       </c>
@@ -10055,7 +10044,7 @@
       <c r="G44" s="35"/>
       <c r="H44" s="35"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>228</v>
       </c>
@@ -10069,7 +10058,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>230</v>
       </c>
@@ -10083,25 +10072,25 @@
       </c>
       <c r="F46" s="223"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>87.27858246088563</v>
+        <v>87.965678767015206</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-65.299983728895668</v>
+        <v>-65.814054607974768</v>
       </c>
       <c r="F47" s="223"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="223"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="143" t="s">
         <v>120</v>
       </c>
@@ -10114,7 +10103,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="223"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>90</v>
       </c>
@@ -10128,7 +10117,7 @@
       </c>
       <c r="F50" s="223"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>146</v>
       </c>
@@ -10139,10 +10128,10 @@
       </c>
       <c r="F51" s="223"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="223"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="143" t="s">
         <v>119</v>
       </c>
@@ -10154,7 +10143,7 @@
       </c>
       <c r="F53" s="223"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>116</v>
       </c>
@@ -10168,7 +10157,7 @@
       </c>
       <c r="F54" s="223"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>118</v>
       </c>
@@ -10182,10 +10171,10 @@
       </c>
       <c r="F55" s="223"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="223"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="143" t="s">
         <v>145</v>
       </c>
@@ -10197,7 +10186,7 @@
       </c>
       <c r="F57" s="223"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>86</v>
       </c>
@@ -10208,7 +10197,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>89</v>
       </c>
@@ -10219,10 +10208,10 @@
       </c>
       <c r="F59" s="223"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="223"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="143" t="s">
         <v>231</v>
       </c>
@@ -10234,7 +10223,7 @@
       </c>
       <c r="F61" s="223"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>210</v>
       </c>
@@ -10250,7 +10239,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="76" t="s">
         <v>162</v>
       </c>
@@ -10261,7 +10250,7 @@
       <c r="G64" s="35"/>
       <c r="H64" s="35"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>158</v>
       </c>
@@ -10275,7 +10264,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="102" t="s">
         <v>157</v>
       </c>
@@ -10291,7 +10280,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="102" t="s">
         <v>147</v>
       </c>
@@ -10301,7 +10290,7 @@
       </c>
       <c r="F67" s="223"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="102" t="s">
         <v>151</v>
       </c>
@@ -10311,7 +10300,7 @@
       </c>
       <c r="F68" s="223"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="102" t="s">
         <v>149</v>
       </c>
@@ -10321,7 +10310,7 @@
       </c>
       <c r="F69" s="223"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="77" t="s">
         <v>158</v>
       </c>
@@ -10331,10 +10320,10 @@
       </c>
       <c r="F70" s="223"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="223"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="225" t="s">
         <v>256</v>
       </c>
@@ -10346,7 +10335,7 @@
       </c>
       <c r="F72" s="223"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="102" t="s">
         <v>255</v>
       </c>
@@ -10362,7 +10351,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="227" t="s">
         <v>259</v>
       </c>
@@ -10378,7 +10367,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="77" t="s">
         <v>258</v>
       </c>
@@ -10391,7 +10380,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="229" t="s">
         <v>260</v>
       </c>
@@ -10404,10 +10393,10 @@
         <v>261</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="223"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>159</v>
       </c>
@@ -10419,7 +10408,7 @@
       </c>
       <c r="F78" s="223"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="102" t="s">
         <v>148</v>
       </c>
@@ -10433,7 +10422,7 @@
       </c>
       <c r="F79" s="223"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="102" t="s">
         <v>152</v>
       </c>
@@ -10447,7 +10436,7 @@
       </c>
       <c r="F80" s="223"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="102" t="s">
         <v>150</v>
       </c>
@@ -10461,7 +10450,7 @@
       </c>
       <c r="F81" s="223"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="77" t="s">
         <v>159</v>
       </c>
@@ -10475,7 +10464,7 @@
       </c>
       <c r="F82" s="223"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="76" t="s">
         <v>241</v>
       </c>
@@ -10486,7 +10475,7 @@
       <c r="G84" s="35"/>
       <c r="H84" s="35"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>242</v>
       </c>
@@ -10494,68 +10483,68 @@
         <v>243</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="212" t="s">
         <v>239</v>
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-126838.007890971</v>
+        <v>-127836.53380926001</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-42.180151291356594</v>
+        <v>-42.512212437712471</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="212" t="s">
         <v>240</v>
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>35109.496476441571</v>
+        <v>35385.894243898932</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>11.675710599402098</v>
+        <v>11.767627051274838</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="213" t="s">
         <v>159</v>
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>111496.79756363948</v>
+        <v>112374.550565478</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>37.07841102155038</v>
+        <v>37.370308970986926</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="77" t="s">
         <v>244</v>
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>19768.286149110048</v>
+        <v>19923.911000116917</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.573970329595884</v>
+        <v>6.6257235845492914</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -10581,19 +10570,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q807"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
@@ -10650,7 +10639,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="51" t="s">
         <v>95</v>
@@ -10673,7 +10662,7 @@
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>393</v>
@@ -10693,7 +10682,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -10750,7 +10739,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>43</v>
@@ -10805,7 +10794,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="30" t="s">
         <v>45</v>
@@ -10860,7 +10849,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>42</v>
@@ -10915,7 +10904,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="28" t="s">
         <v>127</v>
@@ -10972,7 +10961,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
         <v>415</v>
@@ -11029,7 +11018,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>65</v>
@@ -11084,7 +11073,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="67" t="s">
         <v>137</v>
@@ -11139,7 +11128,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>60</v>
@@ -11194,7 +11183,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="38" t="s">
         <v>208</v>
@@ -11251,7 +11240,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="39" t="s">
         <v>129</v>
@@ -11308,7 +11297,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="2" t="s">
         <v>62</v>
@@ -11363,7 +11352,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
         <v>398</v>
@@ -11418,7 +11407,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="26" t="s">
         <v>49</v>
@@ -11444,7 +11433,7 @@
       <c r="P17" s="272"/>
       <c r="Q17" s="272"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="26" t="s">
         <v>94</v>
@@ -11469,7 +11458,7 @@
       <c r="P18" s="273"/>
       <c r="Q18" s="273"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="30" t="s">
         <v>63</v>
@@ -11526,7 +11515,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="26"/>
       <c r="C20" s="59"/>
@@ -11545,7 +11534,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="51" t="s">
         <v>174</v>
@@ -11568,7 +11557,7 @@
       <c r="P21" s="35"/>
       <c r="Q21" s="35"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="61" t="s">
         <v>43</v>
@@ -11589,7 +11578,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="26" t="s">
         <v>40</v>
@@ -11646,7 +11635,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="65" t="s">
         <v>59</v>
@@ -11703,7 +11692,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="26" t="s">
         <v>46</v>
@@ -11760,7 +11749,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="B26" s="67" t="s">
         <v>43</v>
@@ -11817,18 +11806,18 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="E27" s="237"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="61" t="s">
         <v>175</v>
       </c>
       <c r="E28" s="237"/>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="25" t="s">
         <v>40</v>
@@ -11885,7 +11874,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="65" t="str">
         <f>B24</f>
@@ -11943,7 +11932,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="B31" s="26" t="str">
         <f>B25</f>
@@ -12001,7 +11990,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="67" t="s">
         <v>43</v>
@@ -12056,18 +12045,18 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="E33" s="237"/>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="61" t="s">
         <v>42</v>
       </c>
       <c r="E34" s="237"/>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="298" t="s">
         <v>396</v>
@@ -12124,18 +12113,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="237"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="61" t="s">
         <v>176</v>
       </c>
       <c r="E37" s="237"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="298" t="s">
         <v>396</v>
@@ -12190,18 +12179,18 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="E39" s="237"/>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="61" t="s">
         <v>177</v>
       </c>
       <c r="E40" s="237"/>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="B41" s="26" t="s">
         <v>142</v>
@@ -12259,10 +12248,10 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="51" t="s">
         <v>178</v>
@@ -12285,14 +12274,14 @@
       <c r="P43" s="35"/>
       <c r="Q43" s="35"/>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
       <c r="B44" s="61" t="s">
         <v>57</v>
       </c>
       <c r="E44" s="237"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="2" t="s">
         <v>37</v>
@@ -12347,7 +12336,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
         <v>272</v>
@@ -12402,7 +12391,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="245" t="s">
         <v>269</v>
@@ -12459,7 +12448,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="67" t="s">
         <v>65</v>
@@ -12514,11 +12503,11 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="E49" s="237"/>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="69" t="s">
         <v>130</v>
@@ -12528,7 +12517,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="B51" s="8" t="s">
         <v>85</v>
@@ -12552,7 +12541,7 @@
       <c r="P51" s="151"/>
       <c r="Q51" s="151"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
         <v>84</v>
@@ -12576,7 +12565,7 @@
       <c r="P52" s="151"/>
       <c r="Q52" s="151"/>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="25" t="s">
         <v>87</v>
@@ -12631,11 +12620,11 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="E54" s="237"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="61" t="s">
         <v>139</v>
@@ -12645,7 +12634,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="B56" s="38" t="s">
         <v>138</v>
@@ -12700,7 +12689,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="38" t="s">
         <v>134</v>
@@ -12755,7 +12744,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="38" t="s">
         <v>133</v>
@@ -12810,7 +12799,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="30" t="s">
         <v>163</v>
@@ -12865,7 +12854,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="38" t="s">
         <v>135</v>
@@ -12921,7 +12910,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="30" t="s">
         <v>164</v>
@@ -12976,11 +12965,11 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="E62" s="237"/>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="93" t="s">
         <v>140</v>
@@ -12990,7 +12979,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="B64" s="38" t="s">
         <v>138</v>
@@ -13015,7 +13004,7 @@
       <c r="P64" s="157"/>
       <c r="Q64" s="157"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="102" t="s">
         <v>132</v>
@@ -13040,7 +13029,7 @@
       <c r="P65" s="157"/>
       <c r="Q65" s="157"/>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="102" t="s">
         <v>133</v>
@@ -13065,7 +13054,7 @@
       <c r="P66" s="157"/>
       <c r="Q66" s="157"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="30" t="s">
         <v>163</v>
@@ -13092,10 +13081,10 @@
       <c r="P67" s="157"/>
       <c r="Q67" s="157"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="51" t="s">
         <v>181</v>
@@ -13118,7 +13107,7 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
       <c r="B70" s="69" t="s">
         <v>185</v>
@@ -13139,7 +13128,7 @@
       <c r="P70" s="12"/>
       <c r="Q70" s="12"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="2" t="s">
         <v>43</v>
@@ -13196,7 +13185,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="30" t="s">
         <v>45</v>
@@ -13253,7 +13242,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="8" t="s">
         <v>42</v>
@@ -13310,7 +13299,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="28" t="s">
         <v>127</v>
@@ -13367,7 +13356,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="26" t="s">
         <v>128</v>
@@ -13424,7 +13413,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
         <v>65</v>
@@ -13481,7 +13470,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="67" t="s">
         <v>137</v>
@@ -13538,7 +13527,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>60</v>
@@ -13595,7 +13584,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="38" t="str">
         <f>B13</f>
@@ -13653,7 +13642,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="39" t="s">
         <v>129</v>
@@ -13710,7 +13699,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
         <v>62</v>
@@ -13767,7 +13756,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>77</v>
@@ -13826,7 +13815,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="26" t="s">
         <v>49</v>
@@ -13852,7 +13841,7 @@
       <c r="P83" s="203"/>
       <c r="Q83" s="203"/>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="8" t="s">
         <v>94</v>
@@ -13876,7 +13865,7 @@
       <c r="P84" s="151"/>
       <c r="Q84" s="151"/>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="30" t="s">
         <v>117</v>
@@ -13933,18 +13922,18 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="E86" s="237"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="61" t="s">
         <v>183</v>
       </c>
       <c r="E87" s="237"/>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="B88" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -14000,7 +13989,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -14056,7 +14045,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="s">
         <v>182</v>
@@ -14111,7 +14100,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
         <v>331</v>
@@ -14132,27 +14121,27 @@
       <c r="P91" s="293"/>
       <c r="Q91" s="293"/>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>330</v>
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.3815028901734101E-2</v>
+        <v>3.3620689655172412E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.3815028901734101E-2</v>
+        <v>3.3620689655172412E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>2.5699421965317923E-2</v>
+        <v>2.5551724137931036E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>2.0965317919075147E-2</v>
+        <v>2.0844827586206895E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
@@ -14187,11 +14176,11 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="E93" s="237"/>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="143" t="s">
         <v>81</v>
@@ -14212,7 +14201,7 @@
       <c r="P94" s="12"/>
       <c r="Q94" s="12"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="26" t="s">
         <v>121</v>
@@ -14269,7 +14258,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="67" t="s">
         <v>137</v>
@@ -14326,10 +14315,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="3"/>
       <c r="B98" s="51" t="s">
         <v>184</v>
@@ -14352,7 +14341,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="10"/>
       <c r="B99" s="61" t="s">
         <v>26</v>
@@ -14362,7 +14351,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="25" t="s">
         <v>1</v>
@@ -14419,7 +14408,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="90" t="s">
         <v>179</v>
@@ -14476,7 +14465,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="90" t="s">
         <v>180</v>
@@ -14533,7 +14522,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="25" t="s">
         <v>38</v>
@@ -14590,7 +14579,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="25" t="s">
         <v>28</v>
@@ -14647,11 +14636,11 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="E105" s="237"/>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="B106" s="88" t="s">
         <v>189</v>
@@ -14674,7 +14663,7 @@
       <c r="P106" s="12"/>
       <c r="Q106" s="12"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="25" t="s">
         <v>186</v>
@@ -14731,7 +14720,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="25" t="s">
         <v>187</v>
@@ -14788,7 +14777,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="25" t="s">
         <v>66</v>
@@ -14815,18 +14804,18 @@
       <c r="P109" s="186"/>
       <c r="Q109" s="186"/>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="E110" s="237"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="B111" s="61" t="s">
         <v>48</v>
       </c>
       <c r="E111" s="237"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
         <v>303</v>
@@ -14880,7 +14869,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>304</v>
@@ -14935,11 +14924,11 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="E114" s="237"/>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="88" t="s">
         <v>36</v>
@@ -14998,7 +14987,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="7" t="s">
         <v>190</v>
@@ -15056,7 +15045,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="B117" s="7" t="s">
         <v>80</v>
       </c>
@@ -15113,7 +15102,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>88</v>
       </c>
@@ -15172,7 +15161,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="A119" s="10"/>
       <c r="B119" s="67" t="s">
         <v>191</v>
@@ -15231,7 +15220,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="26"/>
       <c r="C120" s="59"/>
@@ -15250,7 +15239,7 @@
       <c r="P120" s="12"/>
       <c r="Q120" s="12"/>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="51" t="s">
         <v>192</v>
@@ -15273,7 +15262,7 @@
       <c r="P121" s="35"/>
       <c r="Q121" s="35"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="160" t="s">
         <v>141</v>
@@ -15294,7 +15283,7 @@
       <c r="P122" s="12"/>
       <c r="Q122" s="12"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="26" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -15302,30 +15291,30 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>8.6165723280823254</v>
+        <v>8.6844058658322876</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.845991315111027</v>
+        <v>10.931375843122421</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.016666229323441</v>
+        <v>7.0719045857629812</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>3.713045462015145</v>
+        <v>3.7422762280233473</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>4.7414992217888745E-2</v>
+        <v>4.7788264389474186E-2</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>4.6579585212144998</v>
+        <v>4.6946280683564403</v>
       </c>
       <c r="L123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15352,37 +15341,37 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="26" t="s">
         <v>226</v>
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.3011294104839359E-2</v>
+        <v>8.3183964232110025E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.10448931902804458</v>
+        <v>0.10470666516400785</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.759794055224895E-2</v>
+        <v>6.7738549672059209E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.577115088646575E-2</v>
+        <v>3.5845557739687235E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>4.5679183254228079E-4</v>
+        <v>4.577419960677604E-4</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>4.4874359549272637E-2</v>
+        <v>4.4967701804180457E-2</v>
       </c>
       <c r="L124" s="74" t="str">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
@@ -15409,30 +15398,30 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="B125" s="2" t="s">
         <v>306</v>
       </c>
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14308038034386381</v>
+        <v>0.14225807930740481</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4510085214000002E-2</v>
+        <v>7.408186633345977E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1047737705158621E-2</v>
+        <v>3.0869302430991043E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-1.4311241804658297E-2</v>
+        <v>-1.4228993288539571E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1580644139056249</v>
+        <v>0.15715599773375349</v>
       </c>
       <c r="L125" s="22" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15459,688 +15448,688 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q11 G13:Q16 G23:Q25">
@@ -16162,16 +16151,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:U118"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="11" width="11.1640625" customWidth="1"/>
+    <col min="10" max="11" width="11.1328125" customWidth="1"/>
     <col min="12" max="12" width="20.6640625" customWidth="1"/>
     <col min="13" max="13" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>52</v>
       </c>
@@ -16186,7 +16175,7 @@
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:15" ht="13.15">
       <c r="B3" s="106" t="s">
         <v>136</v>
       </c>
@@ -16201,7 +16190,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:15">
       <c r="B4" s="97" t="s">
         <v>393</v>
       </c>
@@ -16233,7 +16222,7 @@
       </c>
       <c r="J4" s="305"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:15">
       <c r="B5" s="187" t="s">
         <v>105</v>
       </c>
@@ -16261,7 +16250,7 @@
       </c>
       <c r="J5" s="305"/>
     </row>
-    <row r="6" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:15" ht="13.25" customHeight="1">
       <c r="B6" s="136" t="s">
         <v>194</v>
       </c>
@@ -16294,7 +16283,7 @@
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
     </row>
-    <row r="7" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="318" t="s">
         <v>430</v>
       </c>
@@ -16324,7 +16313,7 @@
       <c r="N7" s="304"/>
       <c r="O7" s="304"/>
     </row>
-    <row r="8" spans="2:15" ht="14" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="136" t="s">
         <v>426</v>
       </c>
@@ -16341,7 +16330,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.5739703295958796</v>
+        <v>6.6257235845492923</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16359,14 +16348,14 @@
       <c r="N8" s="304"/>
       <c r="O8" s="304"/>
     </row>
-    <row r="9" spans="2:15" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:15" ht="13.15" thickBot="1">
       <c r="B9" s="189" t="str">
         <f>"*"&amp;Thesis!E15</f>
         <v>*CNY/HKD</v>
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1315830089569092</v>
+        <v>1.1404913400000001</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16385,13 +16374,13 @@
       <c r="N9" s="304"/>
       <c r="O9" s="304"/>
     </row>
-    <row r="10" spans="2:15" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
         <v>427</v>
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>523172.31328256195</v>
+        <v>527290.96133790596</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16407,13 +16396,13 @@
       <c r="N10" s="304"/>
       <c r="O10" s="304"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="136" t="s">
         <v>425</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>173.98166127519536</v>
+        <v>175.3513232635766</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16423,7 +16412,7 @@
       <c r="I11" s="307"/>
       <c r="J11" s="307"/>
     </row>
-    <row r="13" spans="2:15" ht="16" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
         <v>428</v>
       </c>
@@ -16438,7 +16427,7 @@
       <c r="K13" s="35"/>
       <c r="L13" s="35"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:15" ht="13.15">
       <c r="B14" s="106" t="s">
         <v>399</v>
       </c>
@@ -16456,7 +16445,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:15">
       <c r="B15" s="139" t="s">
         <v>421</v>
       </c>
@@ -16481,7 +16470,7 @@
       </c>
       <c r="J15" s="126"/>
     </row>
-    <row r="16" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
         <v>422</v>
       </c>
@@ -16497,7 +16486,7 @@
         <v>2.38559171477595E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="308" t="s">
         <v>550</v>
       </c>
@@ -16516,7 +16505,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="308" t="s">
         <v>423</v>
       </c>
@@ -16536,17 +16525,17 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>189.7895771945665</v>
+        <v>191.28368621599475</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:21">
       <c r="L19" s="275"/>
     </row>
-    <row r="20" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" ht="13.15">
       <c r="A20" s="121" t="s">
         <v>399</v>
       </c>
@@ -16585,7 +16574,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:21">
       <c r="A21" s="302" t="str">
         <f t="shared" ref="A21:A50" si="0">IF($C$15&lt;B21,"",IF(B21&gt;=$F$15,"II","I"))</f>
         <v>I</v>
@@ -16634,7 +16623,7 @@
         <v>21859.032865551624</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:21">
       <c r="A22" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16683,7 +16672,7 @@
         <v>20867.599200487064</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:21">
       <c r="A23" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16740,7 +16729,7 @@
       <c r="T23" s="275"/>
       <c r="U23" s="275"/>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:21">
       <c r="A24" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16797,7 +16786,7 @@
       <c r="T24" s="275"/>
       <c r="U24" s="275"/>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:21">
       <c r="A25" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -16854,7 +16843,7 @@
       <c r="T25" s="275"/>
       <c r="U25" s="275"/>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:21">
       <c r="A26" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -16903,7 +16892,7 @@
         <v>23423.796792194709</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:21">
       <c r="A27" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -16952,7 +16941,7 @@
         <v>22361.392025879035</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:21">
       <c r="A28" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17001,7 +16990,7 @@
         <v>21347.173465134711</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:21">
       <c r="A29" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17050,7 +17039,7 @@
         <v>20378.955586627329</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:21">
       <c r="A30" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17099,7 +17088,7 @@
         <v>19454.651993155978</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:21">
       <c r="A31" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17148,7 +17137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:21">
       <c r="A32" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17197,7 +17186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:21">
       <c r="A33" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17254,7 +17243,7 @@
       <c r="T33" s="275"/>
       <c r="U33" s="275"/>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:21">
       <c r="A34" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17311,7 +17300,7 @@
       <c r="T34" s="275"/>
       <c r="U34" s="275"/>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:21">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17368,7 +17357,7 @@
       <c r="T35" s="275"/>
       <c r="U35" s="275"/>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:21">
       <c r="A36" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17417,7 +17406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:21">
       <c r="A37" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17466,7 +17455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:21">
       <c r="A38" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17515,7 +17504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:21">
       <c r="A39" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17564,7 +17553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:21">
       <c r="A40" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17613,7 +17602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:21">
       <c r="A41" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17662,7 +17651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:21">
       <c r="A42" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17711,7 +17700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:21">
       <c r="A43" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17760,7 +17749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:21">
       <c r="A44" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17809,7 +17798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:21">
       <c r="A45" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17858,7 +17847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:21">
       <c r="A46" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17907,7 +17896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:21">
       <c r="A47" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17964,7 +17953,7 @@
       <c r="T47" s="275"/>
       <c r="U47" s="275"/>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:21">
       <c r="A48" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18021,7 +18010,7 @@
       <c r="T48" s="275"/>
       <c r="U48" s="275"/>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:21">
       <c r="A49" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18078,7 +18067,7 @@
       <c r="T49" s="275"/>
       <c r="U49" s="275"/>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:21">
       <c r="A50" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18135,7 +18124,7 @@
       <c r="T50" s="275"/>
       <c r="U50" s="275"/>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:21">
       <c r="A51" s="315" t="s">
         <v>418</v>
       </c>
@@ -18181,7 +18170,7 @@
         <v>273706.82804164273</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:21" ht="13.15">
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
@@ -18194,10 +18183,10 @@
         <v>486874.83399557997</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:21">
       <c r="C53" s="111"/>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:21" ht="13.15">
       <c r="B54" s="115" t="s">
         <v>108</v>
       </c>
@@ -18212,7 +18201,7 @@
       <c r="K54" s="113"/>
       <c r="L54" s="113"/>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
         <v>486874.83399557997</v>
@@ -18244,7 +18233,7 @@
       <c r="K55" s="123"/>
       <c r="L55" s="123"/>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:21" ht="13.15">
       <c r="A56" s="131">
         <v>1</v>
       </c>
@@ -18271,7 +18260,7 @@
       <c r="K56" s="295"/>
       <c r="L56" s="295"/>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:21" ht="13.15">
       <c r="A57" s="131">
         <v>2</v>
       </c>
@@ -18297,7 +18286,7 @@
       <c r="K57" s="295"/>
       <c r="L57" s="295"/>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:21" ht="13.15">
       <c r="A58" s="131">
         <v>3</v>
       </c>
@@ -18323,7 +18312,7 @@
       <c r="K58" s="295"/>
       <c r="L58" s="295"/>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:21" ht="13.15">
       <c r="A59" s="131">
         <v>4</v>
       </c>
@@ -18349,7 +18338,7 @@
       <c r="K59" s="295"/>
       <c r="L59" s="295"/>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:21" ht="13.15">
       <c r="A60" s="131">
         <v>5</v>
       </c>
@@ -18375,7 +18364,7 @@
       <c r="K60" s="295"/>
       <c r="L60" s="295"/>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:21" ht="13.15">
       <c r="A61" s="131">
         <v>6</v>
       </c>
@@ -18401,7 +18390,7 @@
       <c r="K61" s="295"/>
       <c r="L61" s="295"/>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:21" ht="13.15">
       <c r="A62" s="131">
         <v>7</v>
       </c>
@@ -18427,7 +18416,7 @@
       <c r="K62" s="295"/>
       <c r="L62" s="295"/>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:21" ht="13.15">
       <c r="A63" s="131">
         <v>8</v>
       </c>
@@ -18453,7 +18442,7 @@
       <c r="K63" s="295"/>
       <c r="L63" s="295"/>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:21" ht="13.15">
       <c r="A64" s="131">
         <v>9</v>
       </c>
@@ -18479,7 +18468,7 @@
       <c r="K64" s="295"/>
       <c r="L64" s="295"/>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:21" ht="13.15">
       <c r="A65" s="131">
         <v>10</v>
       </c>
@@ -18505,7 +18494,7 @@
       <c r="K65" s="295"/>
       <c r="L65" s="295"/>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:21" ht="13.15">
       <c r="A66" s="131">
         <v>15</v>
       </c>
@@ -18540,7 +18529,7 @@
       <c r="T66" s="275"/>
       <c r="U66" s="275"/>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:21" ht="13.15">
       <c r="A67" s="132">
         <v>20</v>
       </c>
@@ -18575,7 +18564,7 @@
       <c r="T67" s="275"/>
       <c r="U67" s="275"/>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:21" ht="13.15">
       <c r="A68" s="132">
         <v>25</v>
       </c>
@@ -18610,7 +18599,7 @@
       <c r="T68" s="275"/>
       <c r="U68" s="275"/>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:21" ht="13.15">
       <c r="A69" s="132">
         <v>30</v>
       </c>
@@ -18645,7 +18634,7 @@
       <c r="T69" s="275"/>
       <c r="U69" s="275"/>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:21">
       <c r="C70" s="275"/>
       <c r="D70" s="111"/>
       <c r="E70" s="111"/>
@@ -18666,7 +18655,7 @@
       <c r="T70" s="275"/>
       <c r="U70" s="275"/>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:21" ht="13.15">
       <c r="B71" s="115" t="s">
         <v>109</v>
       </c>
@@ -18690,7 +18679,7 @@
       <c r="T71" s="275"/>
       <c r="U71" s="275"/>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:21" ht="13.15">
       <c r="B72" s="124">
         <f>B55</f>
         <v>0</v>
@@ -18718,29 +18707,29 @@
       <c r="K72" s="124"/>
       <c r="L72" s="124"/>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:21" ht="13.15">
       <c r="A73" s="131">
         <v>0</v>
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>173.98166127519536</v>
+        <v>175.3513232635766</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>173.98166127519536</v>
+        <v>175.3513232635766</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>173.98166127519536</v>
+        <v>175.3513232635766</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>173.98166127519536</v>
+        <v>175.3513232635766</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>173.98166127519536</v>
+        <v>175.3513232635766</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18749,29 +18738,29 @@
       <c r="K73" s="296"/>
       <c r="L73" s="296"/>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:21" ht="13.15">
       <c r="A74" s="131">
         <v>1</v>
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>167.37101902274978</v>
+        <v>168.6886390582861</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>168.97898950968133</v>
+        <v>170.30926821302347</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>170.58695999661293</v>
+        <v>171.9298973677609</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>172.19493048354443</v>
+        <v>173.55052652249825</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>175.41087145740755</v>
+        <v>176.79178483197302</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18780,29 +18769,29 @@
       <c r="K74" s="296"/>
       <c r="L74" s="296"/>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:21" ht="13.15">
       <c r="A75" s="131">
         <v>2</v>
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>167.16853602489843</v>
+        <v>168.48456202308958</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>170.31534238463874</v>
+        <v>171.6561414596251</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>173.49266083750345</v>
+        <v>174.85847319422294</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>176.70049138349276</v>
+        <v>178.09155722688322</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>183.20768875484475</v>
+        <v>184.64998218639084</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18811,29 +18800,29 @@
       <c r="K75" s="296"/>
       <c r="L75" s="296"/>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:21" ht="13.15">
       <c r="A76" s="131">
         <v>3</v>
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>166.97974068890642</v>
+        <v>168.29428040519065</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>171.57381921793188</v>
+        <v>172.92452558929185</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>176.25612457429452</v>
+        <v>177.64369216204705</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>181.02751024311678</v>
+        <v>182.45264032759792</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>190.84093645862944</v>
+        <v>192.34332225365307</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18842,29 +18831,29 @@
       <c r="K76" s="296"/>
       <c r="L76" s="296"/>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:21" ht="13.15">
       <c r="A77" s="131">
         <v>4</v>
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>166.80370774159459</v>
+        <v>168.11686164724296</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>172.75895824042709</v>
+        <v>174.11899455988708</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>178.88431386243141</v>
+        <v>180.29257173983774</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>185.18306215492342</v>
+        <v>186.64090661546371</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>198.31404609869838</v>
+        <v>199.87526357824544</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18873,29 +18862,29 @@
       <c r="K77" s="296"/>
       <c r="L77" s="296"/>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:21" ht="13.15">
       <c r="A78" s="131">
         <v>5</v>
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>164.00642696370409</v>
+        <v>165.29755941534273</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>171.18895945901562</v>
+        <v>172.53663604103579</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>178.64432387564364</v>
+        <v>180.05069244379698</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>186.38043567039981</v>
+        <v>187.84770639447856</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>202.72733210306356</v>
+        <v>204.32329295751421</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18904,29 +18893,29 @@
       <c r="K78" s="296"/>
       <c r="L78" s="296"/>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:21" ht="13.15">
       <c r="A79" s="131">
         <v>6</v>
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>163.85338893647162</v>
+        <v>165.14331660384082</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>172.23999510159291</v>
+        <v>173.5959459095144</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>181.02150559960964</v>
+        <v>182.44658841283299</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>190.21316861424233</v>
+        <v>191.71061233808626</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>209.89017375523974</v>
+        <v>211.54252372488722</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18935,30 +18924,30 @@
       <c r="K79" s="296"/>
       <c r="L79" s="296"/>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:21" ht="13.15">
       <c r="A80" s="131">
         <f t="shared" ref="A80" si="12">A62</f>
         <v>7</v>
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>161.2555469589274</v>
+        <v>162.5250232443384</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>170.70023892733963</v>
+        <v>172.04406808124429</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>180.67689783547749</v>
+        <v>182.09926774119108</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>191.21121390172701</v>
+        <v>192.71651468753325</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>214.06060393464253</v>
+        <v>215.74578540877189</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18967,29 +18956,29 @@
       <c r="K80" s="296"/>
       <c r="L80" s="296"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:12" ht="13.15">
       <c r="A81" s="131">
         <v>8</v>
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>161.12250005982773</v>
+        <v>162.39092894013274</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>171.63234554183805</v>
+        <v>172.9835126587765</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>182.82704469676531</v>
+        <v>184.26634152686714</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>194.74620567431901</v>
+        <v>196.27933550730569</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>220.92605928124399</v>
+        <v>222.66528871164789</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18998,30 +18987,30 @@
       <c r="K81" s="296"/>
       <c r="L81" s="296"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:12" ht="13.15">
       <c r="A82" s="131">
         <f t="shared" ref="A82" si="13">A64</f>
         <v>9</v>
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>158.70926362406132</v>
+        <v>159.95869442036818</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>170.12800018109024</v>
+        <v>171.46732441388269</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>182.39405389990526</v>
+        <v>183.82994203146131</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>195.5646201225932</v>
+        <v>197.1041928826811</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>224.86496738667461</v>
+        <v>226.63520567553056</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19030,30 +19019,30 @@
       <c r="K82" s="296"/>
       <c r="L82" s="296"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:12" ht="13.15">
       <c r="A83" s="131">
         <f t="shared" ref="A83:A87" si="14">A65</f>
         <v>10</v>
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>158.59359644198807</v>
+        <v>159.84211665414813</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>170.95463507870531</v>
+        <v>172.30046695367818</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>184.33884906575102</v>
+        <v>185.79004750067077</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>198.82500038268122</v>
+        <v>200.39024032445471</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>231.44538328932953</v>
+        <v>233.26742557559268</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19062,30 +19051,30 @@
       <c r="K83" s="296"/>
       <c r="L83" s="296"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:12" ht="13.15">
       <c r="A84" s="131">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>152.14228996320662</v>
+        <v>153.34002258548725</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>168.07360038048222</v>
+        <v>169.39675145286679</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>185.99532973575873</v>
+        <v>187.45956873249156</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>206.15539584870433</v>
+        <v>207.77834396475336</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>254.33154602127854</v>
+        <v>256.33375848711182</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19094,30 +19083,30 @@
       <c r="K84" s="296"/>
       <c r="L84" s="296"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:12" ht="13.15">
       <c r="A85" s="132">
         <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>148.4668962089614</v>
+        <v>149.63569447643343</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>167.00161211362888</v>
+        <v>168.31632401161809</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>188.56489357167453</v>
+        <v>190.04936133209989</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>213.67468313744678</v>
+        <v>215.35682646926523</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>277.05407177741728</v>
+        <v>279.23516619885493</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19126,30 +19115,30 @@
       <c r="K85" s="296"/>
       <c r="L85" s="296"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:12" ht="13.15">
       <c r="A86" s="132">
         <f t="shared" si="14"/>
         <v>25</v>
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>144.01859611876461</v>
+        <v>145.15237536468118</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>164.20230208172339</v>
+        <v>165.49497655050141</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>188.40566260265027</v>
+        <v>189.88887682517949</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>217.50049537157233</v>
+        <v>219.21275722021238</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>294.84382084664804</v>
+        <v>297.1649641841862</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19158,30 +19147,30 @@
       <c r="K86" s="296"/>
       <c r="L86" s="296"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:12" ht="13.15">
       <c r="A87" s="132">
         <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>141.49757584896622</v>
+        <v>142.61150848800381</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>162.91545733063433</v>
+        <v>164.19800117801466</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>189.27824991272087</v>
+        <v>190.76833353551555</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>221.87651003742425</v>
+        <v>223.62322184420634</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>312.76746817662325</v>
+        <v>315.22971453767025</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19190,7 +19179,7 @@
       <c r="K87" s="296"/>
       <c r="L87" s="296"/>
     </row>
-    <row r="89" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="13.15">
       <c r="B89" s="153" t="s">
         <v>101</v>
       </c>
@@ -19213,7 +19202,7 @@
       <c r="K89" s="323"/>
       <c r="L89" s="323"/>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:12">
       <c r="B90" s="120" t="str">
         <f>Scenarios!B29</f>
         <v>Snowball Scenario</v>
@@ -19228,7 +19217,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>231.44538328932953</v>
+        <v>233.26742557559268</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19241,7 +19230,7 @@
       <c r="K90" s="297"/>
       <c r="L90" s="297"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:12">
       <c r="B91" s="120" t="str">
         <f>Scenarios!B22</f>
         <v>Optimistic</v>
@@ -19256,7 +19245,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>198.82500038268122</v>
+        <v>200.39024032445471</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19269,7 +19258,7 @@
       <c r="K91" s="297"/>
       <c r="L91" s="297"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:12">
       <c r="B92" s="120" t="str">
         <f>Scenarios!B23</f>
         <v>Base</v>
@@ -19284,7 +19273,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>184.33884906575102</v>
+        <v>185.79004750067077</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19297,7 +19286,7 @@
       <c r="K92" s="297"/>
       <c r="L92" s="297"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:12">
       <c r="B93" s="120" t="str">
         <f>Scenarios!B24</f>
         <v>Pessimistic</v>
@@ -19312,7 +19301,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>170.95463507870531</v>
+        <v>172.30046695367818</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19325,7 +19314,7 @@
       <c r="K93" s="297"/>
       <c r="L93" s="297"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:12">
       <c r="B94" s="120" t="str">
         <f>Scenarios!B30</f>
         <v>Devil's advocate</v>
@@ -19340,7 +19329,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>158.59359644198807</v>
+        <v>159.84211665414813</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19353,7 +19342,7 @@
       <c r="K94" s="297"/>
       <c r="L94" s="297"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:12">
       <c r="B95" s="141"/>
       <c r="C95" s="141"/>
       <c r="D95" s="141"/>
@@ -19366,16 +19355,16 @@
       <c r="K95" s="142"/>
       <c r="L95" s="142"/>
     </row>
-    <row r="105" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:3">
       <c r="C105" s="112"/>
     </row>
-    <row r="106" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="106" spans="3:3">
       <c r="C106" s="112"/>
     </row>
-    <row r="107" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="107" spans="3:3">
       <c r="C107" s="112"/>
     </row>
-    <row r="114" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="114" spans="3:21">
       <c r="C114" s="275"/>
       <c r="M114" s="275"/>
       <c r="N114" s="275"/>
@@ -19387,7 +19376,7 @@
       <c r="T114" s="275"/>
       <c r="U114" s="275"/>
     </row>
-    <row r="115" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="115" spans="3:21">
       <c r="C115" s="275"/>
       <c r="M115" s="275"/>
       <c r="N115" s="275"/>
@@ -19399,7 +19388,7 @@
       <c r="T115" s="275"/>
       <c r="U115" s="275"/>
     </row>
-    <row r="116" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="116" spans="3:21">
       <c r="C116" s="275"/>
       <c r="M116" s="275"/>
       <c r="N116" s="275"/>
@@ -19411,7 +19400,7 @@
       <c r="T116" s="275"/>
       <c r="U116" s="275"/>
     </row>
-    <row r="117" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="117" spans="3:21">
       <c r="C117" s="275"/>
       <c r="M117" s="275"/>
       <c r="N117" s="275"/>
@@ -19423,7 +19412,7 @@
       <c r="T117" s="275"/>
       <c r="U117" s="275"/>
     </row>
-    <row r="118" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="118" spans="3:21">
       <c r="C118" s="275"/>
       <c r="M118" s="275"/>
       <c r="N118" s="275"/>
@@ -19463,14 +19452,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:G67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>122</v>
       </c>
@@ -19480,7 +19469,7 @@
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:7" ht="13.15">
       <c r="B3" s="145" t="s">
         <v>125</v>
       </c>
@@ -19489,7 +19478,7 @@
       </c>
       <c r="E3" s="97"/>
     </row>
-    <row r="4" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:7" ht="12.75" customHeight="1">
       <c r="B4" s="139" t="s">
         <v>123</v>
       </c>
@@ -19510,14 +19499,14 @@
       <c r="F4" s="470"/>
       <c r="G4" s="470"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:7">
       <c r="C5" s="445"/>
       <c r="D5" s="470"/>
       <c r="E5" s="470"/>
       <c r="F5" s="470"/>
       <c r="G5" s="470"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="145" t="s">
         <v>91</v>
       </c>
@@ -19530,7 +19519,7 @@
       <c r="F6" s="470"/>
       <c r="G6" s="470"/>
     </row>
-    <row r="7" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
         <v>232</v>
       </c>
@@ -19543,7 +19532,7 @@
       <c r="F7" s="470"/>
       <c r="G7" s="470"/>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
         <v>63</v>
       </c>
@@ -19556,7 +19545,7 @@
       <c r="F8" s="470"/>
       <c r="G8" s="470"/>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
         <v>54</v>
       </c>
@@ -19569,14 +19558,14 @@
       <c r="F9" s="470"/>
       <c r="G9" s="470"/>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:7">
       <c r="C10" s="448"/>
       <c r="D10" s="470"/>
       <c r="E10" s="470"/>
       <c r="F10" s="470"/>
       <c r="G10" s="470"/>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="145" t="s">
         <v>321</v>
       </c>
@@ -19586,7 +19575,7 @@
       <c r="F11" s="470"/>
       <c r="G11" s="470"/>
     </row>
-    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
         <v>121</v>
       </c>
@@ -19599,7 +19588,7 @@
       <c r="F12" s="470"/>
       <c r="G12" s="470"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:7">
       <c r="B13" s="135" t="s">
         <v>127</v>
       </c>
@@ -19612,7 +19601,7 @@
       <c r="F13" s="470"/>
       <c r="G13" s="470"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
         <v>63</v>
       </c>
@@ -19625,7 +19614,7 @@
       <c r="F14" s="470"/>
       <c r="G14" s="470"/>
     </row>
-    <row r="16" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
         <v>453</v>
       </c>
@@ -19635,7 +19624,7 @@
       <c r="F16" s="35"/>
       <c r="G16" s="35"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:7" ht="13.15">
       <c r="B17" s="106" t="s">
         <v>126</v>
       </c>
@@ -19643,7 +19632,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:7" ht="12.75" customHeight="1">
       <c r="B18" s="139" t="s">
         <v>111</v>
       </c>
@@ -19655,18 +19644,18 @@
       </c>
       <c r="F18" s="319"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:7">
       <c r="E19" s="319"/>
       <c r="F19" s="319"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
         <v>450</v>
       </c>
       <c r="E20" s="319"/>
       <c r="F20" s="319"/>
     </row>
-    <row r="21" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="153" t="s">
         <v>436</v>
       </c>
@@ -19687,7 +19676,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:7">
       <c r="B22" s="302" t="s">
         <v>445</v>
       </c>
@@ -19700,7 +19689,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>198.82500038268122</v>
+        <v>200.39024032445471</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19711,7 +19700,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:7">
       <c r="B23" s="302" t="s">
         <v>437</v>
       </c>
@@ -19724,7 +19713,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>184.33884906575102</v>
+        <v>185.79004750067077</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19734,7 +19723,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:7">
       <c r="B24" s="302" t="s">
         <v>446</v>
       </c>
@@ -19747,7 +19736,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>170.95463507870531</v>
+        <v>172.30046695367818</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19757,13 +19746,13 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:7">
       <c r="B25" s="141" t="s">
         <v>451</v>
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>183.89002583237564</v>
+        <v>185.33769092867942</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19771,12 +19760,12 @@
       </c>
       <c r="G25" s="149"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="153" t="s">
         <v>436</v>
       </c>
@@ -19797,7 +19786,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:7">
       <c r="B29" s="302" t="s">
         <v>444</v>
       </c>
@@ -19810,7 +19799,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>231.44538328932953</v>
+        <v>233.26742557559268</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19820,7 +19809,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:7">
       <c r="B30" s="315" t="s">
         <v>447</v>
       </c>
@@ -19833,7 +19822,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>158.59359644198807</v>
+        <v>159.84211665414813</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19843,16 +19832,16 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:7">
       <c r="E31" s="329"/>
       <c r="F31" s="329"/>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="145" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
         <v>458</v>
       </c>
@@ -19872,13 +19861,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:7">
       <c r="B34" s="97" t="s">
         <v>233</v>
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>103.8</v>
+        <v>104.4</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19889,16 +19878,16 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.25085546041516749</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.15">
+        <v>0.25152402246872663</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
         <v>434</v>
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>173.98166127519536</v>
+        <v>175.3513232635766</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19909,16 +19898,16 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>4.896855368906447E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.15">
+        <v>4.8815312095907192E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
         <v>435</v>
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>189.75850798139936</v>
+        <v>191.25237241198982</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19931,7 +19920,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
         <v>411</v>
       </c>
@@ -19941,7 +19930,7 @@
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:7" ht="13.15">
       <c r="B39" s="414" t="str">
         <f>IF(DCF!F14="II","2","1")&amp;"-stage DCF"</f>
         <v>2-stage DCF</v>
@@ -19950,7 +19939,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:7">
       <c r="B40" t="s">
         <v>551</v>
       </c>
@@ -19962,7 +19951,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:7">
       <c r="B41" s="97" t="s">
         <v>400</v>
       </c>
@@ -19972,7 +19961,7 @@
       </c>
       <c r="E41" s="97"/>
     </row>
-    <row r="43" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:7" ht="13.9">
       <c r="B43" s="34" t="s">
         <v>276</v>
       </c>
@@ -19982,7 +19971,7 @@
       <c r="F43" s="35"/>
       <c r="G43" s="35"/>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:7" ht="13.15">
       <c r="B44" s="106" t="s">
         <v>249</v>
       </c>
@@ -19990,7 +19979,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:7">
       <c r="B45" s="139" t="s">
         <v>111</v>
       </c>
@@ -20003,7 +19992,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:7">
       <c r="B46" s="114" t="s">
         <v>112</v>
       </c>
@@ -20015,13 +20004,13 @@
         <v>252</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:7">
       <c r="B47" s="97" t="s">
         <v>96</v>
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>189.7895771945665</v>
+        <v>191.28368621599475</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20031,7 +20020,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:7" ht="13.15">
       <c r="B49" s="106" t="s">
         <v>277</v>
       </c>
@@ -20043,7 +20032,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:7">
       <c r="B50" s="97" t="s">
         <v>250</v>
       </c>
@@ -20053,7 +20042,7 @@
       </c>
       <c r="E50" s="126"/>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:7">
       <c r="B51" s="97" t="s">
         <v>246</v>
       </c>
@@ -20065,7 +20054,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:7">
       <c r="B52" s="97" t="s">
         <v>245</v>
       </c>
@@ -20075,7 +20064,7 @@
       </c>
       <c r="E52" s="221"/>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:7">
       <c r="B53" s="97" t="s">
         <v>237</v>
       </c>
@@ -20088,10 +20077,10 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>3.4643876575169333E-2</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+        <v>3.4643876575169312E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" ht="13.9">
       <c r="B55" s="34" t="s">
         <v>107</v>
       </c>
@@ -20101,12 +20090,12 @@
       <c r="F55" s="35"/>
       <c r="G55" s="35"/>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:7" ht="13.15">
       <c r="B56" s="106" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:7">
       <c r="B57" s="220" t="s">
         <v>248</v>
       </c>
@@ -20116,7 +20105,7 @@
       </c>
       <c r="D57" s="126"/>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:7">
       <c r="B58" s="97" t="s">
         <v>333</v>
       </c>
@@ -20129,13 +20118,13 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
         <v>473</v>
       </c>
       <c r="E60" s="413"/>
     </row>
-    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="153" t="s">
         <v>462</v>
       </c>
@@ -20156,7 +20145,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:7" ht="13.15">
       <c r="B62" s="302" t="s">
         <v>312</v>
       </c>
@@ -20166,11 +20155,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>87.446317042119546</v>
+        <v>88.134733830410084</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>93.869096074266068</v>
+        <v>94.557512862556607</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20178,10 +20167,10 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.50532338669385313</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.15">
+        <v>0.5055877651605607</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" ht="13.15">
       <c r="B63" s="302" t="s">
         <v>313</v>
       </c>
@@ -20191,11 +20180,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>109.60780244412965</v>
+        <v>110.47068442569814</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>116.99285629904411</v>
+        <v>117.8557382806126</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20203,10 +20192,10 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.38346450157316758</v>
-      </c>
-    </row>
-    <row r="65" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+        <v>0.38376848980084033</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="153" t="s">
         <v>463</v>
       </c>
@@ -20227,7 +20216,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:7" ht="13.15">
       <c r="B66" s="302" t="s">
         <v>315</v>
       </c>
@@ -20237,11 +20226,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>136.01138275865037</v>
+        <v>137.08212561503123</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>144.47961973069502</v>
+        <v>145.55036258707588</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20249,10 +20238,10 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.23861321809688074</v>
-      </c>
-    </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.15">
+        <v>0.2389617929887119</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" ht="13.15">
       <c r="B67" s="302" t="s">
         <v>314</v>
       </c>
@@ -20262,11 +20251,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>153.81877714019512</v>
+        <v>155.02970782452144</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>162.9882141875724</v>
+        <v>164.19914487189874</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20274,7 +20263,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.14107559170127471</v>
+        <v>0.14145302983125285</v>
       </c>
     </row>
   </sheetData>
@@ -20293,7 +20282,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:J167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="343" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="343" customWidth="1"/>
@@ -20302,7 +20291,7 @@
     <col min="7" max="16384" width="9" style="343"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="345" t="s">
         <v>334</v>
       </c>
@@ -20316,7 +20305,7 @@
       <c r="I2" s="346"/>
       <c r="J2" s="346"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="E3" s="435" t="s">
         <v>542</v>
       </c>
@@ -20325,7 +20314,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="B4" s="422" t="s">
         <v>534</v>
       </c>
@@ -20342,7 +20331,7 @@
         <v>INT</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="B5" s="343" t="s">
         <v>364</v>
       </c>
@@ -20358,7 +20347,7 @@
         <v>Y</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="B6" s="350" t="s">
         <v>336</v>
       </c>
@@ -20368,7 +20357,7 @@
       </c>
       <c r="E6" s="354"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="B7" s="343" t="s">
         <v>366</v>
       </c>
@@ -20379,16 +20368,16 @@
       <c r="D7" s="354"/>
       <c r="E7" s="354"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="B8" s="351" t="s">
         <v>365</v>
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>103.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>104.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9" s="351" t="s">
         <v>361</v>
       </c>
@@ -20397,43 +20386,43 @@
         <v>3007054361.0630002</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="B10" s="351" t="s">
         <v>367</v>
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>312132.24267833942</v>
+        <v>313936.47529497725</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.25085546041516749</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.25152402246872663</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="D11" s="349"/>
       <c r="E11" s="349"/>
     </row>
-    <row r="12" spans="1:10" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="475" t="s">
+    <row r="12" spans="1:10" ht="24.5" customHeight="1">
+      <c r="B12" s="472" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="475"/>
-      <c r="D12" s="475"/>
-      <c r="E12" s="475"/>
-      <c r="F12" s="475"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C12" s="472"/>
+      <c r="D12" s="472"/>
+      <c r="E12" s="472"/>
+      <c r="F12" s="472"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
         <v>370</v>
       </c>
       <c r="C14" s="348"/>
       <c r="D14" s="349"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="B15" s="343" t="s">
         <v>337</v>
       </c>
@@ -20449,7 +20438,7 @@
         <v>CNY/HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="B16" s="343" t="s">
         <v>338</v>
       </c>
@@ -20462,10 +20451,10 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1315830089569092</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+        <v>1.1404913400000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="B17" s="343" t="s">
         <v>535</v>
       </c>
@@ -20481,14 +20470,14 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="B18" s="343" t="str">
         <f>"预期股权价值 ("&amp;C7&amp;") :"</f>
         <v>预期股权价值 (HKD) :</v>
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>189.75850798139936</v>
+        <v>191.25237241198982</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20498,7 +20487,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="B19" s="350" t="s">
         <v>335</v>
       </c>
@@ -20514,11 +20503,11 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="D20" s="349"/>
       <c r="E20" s="349"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="B21" s="347" t="s">
         <v>493</v>
       </c>
@@ -20534,13 +20523,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="B22" s="343" t="s">
         <v>340</v>
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>93.869096074266068</v>
+        <v>94.557512862556607</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20550,13 +20539,13 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="B23" s="343" t="s">
         <v>341</v>
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>116.99285629904411</v>
+        <v>117.8557382806126</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20566,13 +20555,13 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="B24" s="343" t="s">
         <v>343</v>
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>144.47961973069502</v>
+        <v>145.55036258707588</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20582,13 +20571,13 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="B25" s="343" t="s">
         <v>342</v>
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>162.9882141875724</v>
+        <v>164.19914487189874</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20598,7 +20587,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="345" t="s">
         <v>345</v>
       </c>
@@ -20608,25 +20597,25 @@
       <c r="E27" s="345"/>
       <c r="F27" s="345"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="475" t="s">
+    <row r="29" spans="1:6">
+      <c r="B29" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="475"/>
-      <c r="D29" s="475"/>
-      <c r="E29" s="475"/>
-      <c r="F29" s="475"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="478" t="s">
+      <c r="C29" s="472"/>
+      <c r="D29" s="472"/>
+      <c r="E29" s="472"/>
+      <c r="F29" s="472"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="473" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="478"/>
-      <c r="D30" s="478"/>
-      <c r="E30" s="478"/>
-      <c r="F30" s="478"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
+    </row>
+    <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
         <v>371</v>
       </c>
@@ -20635,7 +20624,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:6">
       <c r="B33" s="471" t="s">
         <v>501</v>
       </c>
@@ -20644,7 +20633,7 @@
       <c r="E33" s="471"/>
       <c r="F33" s="471"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:6">
       <c r="B34" s="372" t="s">
         <v>197</v>
       </c>
@@ -20657,11 +20646,11 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:6">
       <c r="B35" s="372"/>
       <c r="C35" s="374"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="471" t="s">
         <v>502</v>
       </c>
@@ -20670,7 +20659,7 @@
       <c r="E36" s="471"/>
       <c r="F36" s="471"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:6">
       <c r="B37" s="372" t="s">
         <v>199</v>
       </c>
@@ -20683,7 +20672,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:6">
       <c r="B38" s="375" t="s">
         <v>200</v>
       </c>
@@ -20696,7 +20685,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:6">
       <c r="B40" s="471" t="s">
         <v>503</v>
       </c>
@@ -20705,7 +20694,7 @@
       <c r="E40" s="471"/>
       <c r="F40" s="471"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:6">
       <c r="B41" s="372" t="s">
         <v>202</v>
       </c>
@@ -20718,7 +20707,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:6">
       <c r="B43" s="471" t="s">
         <v>504</v>
       </c>
@@ -20727,7 +20716,7 @@
       <c r="E43" s="471"/>
       <c r="F43" s="471"/>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:6">
       <c r="B44" s="372" t="s">
         <v>267</v>
       </c>
@@ -20742,7 +20731,7 @@
       <c r="E44" s="371"/>
       <c r="F44" s="371"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:6">
       <c r="B45" s="372" t="s">
         <v>268</v>
       </c>
@@ -20757,7 +20746,7 @@
       <c r="E45" s="371"/>
       <c r="F45" s="371"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:6">
       <c r="B46" s="372" t="s">
         <v>203</v>
       </c>
@@ -20770,12 +20759,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:6">
       <c r="B48" s="343" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:6">
       <c r="B49" s="372" t="s">
         <v>223</v>
       </c>
@@ -20788,7 +20777,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:6">
       <c r="B51" s="471" t="s">
         <v>506</v>
       </c>
@@ -20797,7 +20786,7 @@
       <c r="E51" s="471"/>
       <c r="F51" s="471"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:6">
       <c r="B52" s="372" t="s">
         <v>496</v>
       </c>
@@ -20810,16 +20799,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:6">
       <c r="B54" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="477"/>
-      <c r="D54" s="477"/>
-      <c r="E54" s="477"/>
-      <c r="F54" s="477"/>
-    </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C54" s="474"/>
+      <c r="D54" s="474"/>
+      <c r="E54" s="474"/>
+      <c r="F54" s="474"/>
+    </row>
+    <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
         <v>207</v>
       </c>
@@ -20832,25 +20821,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B57" s="475" t="s">
+    <row r="57" spans="2:6">
+      <c r="B57" s="472" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="475"/>
-      <c r="D57" s="475"/>
-      <c r="E57" s="475"/>
-      <c r="F57" s="475"/>
-    </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B58" s="475" t="s">
+      <c r="C57" s="472"/>
+      <c r="D57" s="472"/>
+      <c r="E57" s="472"/>
+      <c r="F57" s="472"/>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="472" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="475"/>
-      <c r="D58" s="475"/>
-      <c r="E58" s="475"/>
-      <c r="F58" s="475"/>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C58" s="472"/>
+      <c r="D58" s="472"/>
+      <c r="E58" s="472"/>
+      <c r="F58" s="472"/>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
         <v>372</v>
       </c>
@@ -20863,7 +20852,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:6">
       <c r="B61" s="372" t="s">
         <v>213</v>
       </c>
@@ -20876,23 +20865,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:6">
       <c r="B62" s="377" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.3011294104839359E-2</v>
+        <v>8.3183964232110025E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:6">
       <c r="B63" s="377" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.3815028901734101E-2</v>
+        <v>3.3620689655172412E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20902,7 +20891,7 @@
         <v>0.51217277206029399</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6">
       <c r="B65" s="369" t="s">
         <v>376</v>
       </c>
@@ -20913,7 +20902,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6">
       <c r="B66" s="372" t="s">
         <v>326</v>
       </c>
@@ -20926,7 +20915,7 @@
         <v>0.12811576111950596</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6">
       <c r="B67" s="382" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -20940,7 +20929,7 @@
         <v>3.3655816827304348E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6">
       <c r="B68" s="382" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -20954,7 +20943,7 @@
         <v>1.6240671367246462</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6">
       <c r="B69" s="382" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -20968,7 +20957,7 @@
         <v>2.3438965902371725</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="345" t="s">
         <v>476</v>
       </c>
@@ -20978,43 +20967,43 @@
       <c r="E71" s="345"/>
       <c r="F71" s="345"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6">
       <c r="A72" s="385"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="475" t="s">
+      <c r="B73" s="472" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="475"/>
-      <c r="D73" s="475"/>
-      <c r="E73" s="475"/>
-      <c r="F73" s="475"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B74" s="478" t="s">
+      <c r="C73" s="472"/>
+      <c r="D73" s="472"/>
+      <c r="E73" s="472"/>
+      <c r="F73" s="472"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="473" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="478"/>
-      <c r="D74" s="478"/>
-      <c r="E74" s="478"/>
-      <c r="F74" s="478"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
+    </row>
+    <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B77" s="475" t="s">
+    <row r="77" spans="1:6">
+      <c r="B77" s="472" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="475"/>
-      <c r="D77" s="475"/>
-      <c r="E77" s="475"/>
-      <c r="F77" s="475"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C77" s="472"/>
+      <c r="D77" s="472"/>
+      <c r="E77" s="472"/>
+      <c r="F77" s="472"/>
+    </row>
+    <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
         <v>215</v>
       </c>
@@ -21027,20 +21016,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6">
       <c r="B79" s="372" t="s">
         <v>234</v>
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-42.180151291356594</v>
+        <v>-42.512212437712471</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6">
       <c r="B80" s="382" t="s">
         <v>309</v>
       </c>
@@ -21049,7 +21038,7 @@
         <v>0.36820511135930623</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6">
       <c r="B81" s="382" t="s">
         <v>311</v>
       </c>
@@ -21058,12 +21047,12 @@
         <v>2.8852377432054559</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6">
       <c r="B83" s="343" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6">
       <c r="B84" s="343" t="s">
         <v>224</v>
       </c>
@@ -21076,7 +21065,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6">
       <c r="B85" s="382" t="s">
         <v>481</v>
       </c>
@@ -21089,25 +21078,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6">
       <c r="B86" s="372" t="s">
         <v>235</v>
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>11.675710599402095</v>
+        <v>11.767627051274838</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6">
       <c r="B88" s="343" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6">
       <c r="B89" s="343" t="s">
         <v>217</v>
       </c>
@@ -21120,33 +21109,33 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6">
       <c r="B90" s="372" t="s">
         <v>236</v>
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>37.078411021550387</v>
+        <v>37.370308970986933</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6">
       <c r="B92" s="372" t="s">
         <v>480</v>
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>6.5739703295958796</v>
+        <v>6.6257235845492923</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="345" t="s">
         <v>482</v>
       </c>
@@ -21156,49 +21145,49 @@
       <c r="E94" s="345"/>
       <c r="F94" s="345"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6">
       <c r="A95" s="385"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="475" t="s">
+      <c r="B96" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="475"/>
-      <c r="D96" s="475"/>
-      <c r="E96" s="475"/>
-      <c r="F96" s="475"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C96" s="472"/>
+      <c r="D96" s="472"/>
+      <c r="E96" s="472"/>
+      <c r="F96" s="472"/>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="478" t="s">
+      <c r="B97" s="473" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="478"/>
-      <c r="D97" s="478"/>
-      <c r="E97" s="478"/>
-      <c r="F97" s="478"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="478" t="s">
+      <c r="B98" s="473" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="478"/>
-      <c r="D98" s="478"/>
-      <c r="E98" s="478"/>
-      <c r="F98" s="478"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99" s="385"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6">
       <c r="A100" s="385"/>
       <c r="B100" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6">
       <c r="A101" s="385"/>
       <c r="B101" s="372" t="s">
         <v>212</v>
@@ -21208,7 +21197,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6">
       <c r="A102" s="385"/>
       <c r="B102" s="382" t="s">
         <v>318</v>
@@ -21218,7 +21207,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6">
       <c r="A103" s="385"/>
       <c r="B103" s="382" t="s">
         <v>317</v>
@@ -21228,7 +21217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6">
       <c r="A104" s="385"/>
       <c r="B104" s="372" t="s">
         <v>535</v>
@@ -21237,97 +21226,97 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6">
       <c r="A105" s="385"/>
       <c r="C105" s="392"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6">
       <c r="A106" s="385"/>
       <c r="B106" s="393" t="s">
         <v>375</v>
       </c>
       <c r="C106" s="392"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="475" t="s">
+      <c r="B107" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="475"/>
-      <c r="D107" s="475"/>
-      <c r="E107" s="475"/>
-      <c r="F107" s="475"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C107" s="472"/>
+      <c r="D107" s="472"/>
+      <c r="E107" s="472"/>
+      <c r="F107" s="472"/>
+    </row>
+    <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="475" t="s">
+      <c r="B108" s="472" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="475"/>
-      <c r="D108" s="475"/>
-      <c r="E108" s="475"/>
-      <c r="F108" s="475"/>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C108" s="472"/>
+      <c r="D108" s="472"/>
+      <c r="E108" s="472"/>
+      <c r="F108" s="472"/>
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109" s="385"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6">
       <c r="A110" s="385"/>
       <c r="B110" s="369" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6">
       <c r="A111" s="385"/>
       <c r="B111" s="375" t="s">
         <v>486</v>
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-65.299983728895668</v>
+        <v>-65.814054607974768</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6">
       <c r="A112" s="385"/>
       <c r="B112" s="372" t="s">
         <v>377</v>
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>173.98166127519536</v>
+        <v>175.3513232635766</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6">
       <c r="A113" s="385"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="475" t="s">
+      <c r="B114" s="472" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="475"/>
-      <c r="D114" s="475"/>
-      <c r="E114" s="475"/>
-      <c r="F114" s="475"/>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C114" s="472"/>
+      <c r="D114" s="472"/>
+      <c r="E114" s="472"/>
+      <c r="F114" s="472"/>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" s="385"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6">
       <c r="A116" s="385"/>
       <c r="B116" s="369" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6">
       <c r="A117" s="385"/>
       <c r="B117" s="342" t="s">
         <v>378</v>
@@ -21345,7 +21334,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6">
       <c r="A118" s="385"/>
       <c r="B118" s="395" t="str">
         <f>DCF!B90</f>
@@ -21361,14 +21350,14 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>231.45 HKD</v>
+        <v>233.27 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6">
       <c r="A119" s="385"/>
       <c r="B119" s="400" t="str">
         <f>DCF!B91</f>
@@ -21384,14 +21373,14 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>198.83 HKD</v>
+        <v>200.39 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6">
       <c r="B120" s="400" t="str">
         <f>DCF!B92</f>
         <v>Base</v>
@@ -21406,14 +21395,14 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>184.34 HKD</v>
+        <v>185.79 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
         <v>0.44</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6">
       <c r="B121" s="400" t="str">
         <f>DCF!B93</f>
         <v>Pessimistic</v>
@@ -21428,14 +21417,14 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>170.95 HKD</v>
+        <v>172.3 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6">
       <c r="B122" s="400" t="str">
         <f>DCF!B94</f>
         <v>Devil's advocate</v>
@@ -21450,14 +21439,14 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>158.59 HKD</v>
+        <v>159.84 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6">
       <c r="B124" s="471" t="s">
         <v>519</v>
       </c>
@@ -21466,29 +21455,29 @@
       <c r="E124" s="471"/>
       <c r="F124" s="471"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6">
       <c r="B125" s="372" t="s">
         <v>218</v>
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>189.75850798139936</v>
+        <v>191.25237241198982</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B127" s="473" t="s">
+    <row r="127" spans="1:6">
+      <c r="B127" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="473"/>
-      <c r="D127" s="473"/>
-      <c r="E127" s="473"/>
-      <c r="F127" s="473"/>
-    </row>
-    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C127" s="476"/>
+      <c r="D127" s="476"/>
+      <c r="E127" s="476"/>
+      <c r="F127" s="476"/>
+    </row>
+    <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
         <v>492</v>
       </c>
@@ -21498,30 +21487,30 @@
       <c r="E129" s="345"/>
       <c r="F129" s="345"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B131" s="474" t="s">
+    <row r="131" spans="1:6">
+      <c r="B131" s="477" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="474"/>
-      <c r="D131" s="474"/>
-      <c r="E131" s="474"/>
-      <c r="F131" s="474"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="475" t="s">
+      <c r="C131" s="477"/>
+      <c r="D131" s="477"/>
+      <c r="E131" s="477"/>
+      <c r="F131" s="477"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B132" s="472" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="475"/>
-      <c r="D132" s="475"/>
-      <c r="E132" s="475"/>
-      <c r="F132" s="475"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C132" s="472"/>
+      <c r="D132" s="472"/>
+      <c r="E132" s="472"/>
+      <c r="F132" s="472"/>
+    </row>
+    <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6">
       <c r="B135" s="343" t="s">
         <v>382</v>
       </c>
@@ -21530,7 +21519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6">
       <c r="B136" s="343" t="s">
         <v>383</v>
       </c>
@@ -21543,14 +21532,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6">
       <c r="B138" s="369" t="s">
         <v>493</v>
       </c>
       <c r="C138" s="407"/>
       <c r="D138" s="407"/>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -21569,7 +21558,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6">
       <c r="B140" s="408" t="s">
         <v>312</v>
       </c>
@@ -21579,18 +21568,18 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>87.446317042119546</v>
+        <v>88.134733830410084</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>93.869096074266068</v>
+        <v>94.557512862556607</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6">
       <c r="B141" s="408" t="s">
         <v>313</v>
       </c>
@@ -21600,18 +21589,18 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>109.60780244412965</v>
+        <v>110.47068442569814</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>116.99285629904411</v>
+        <v>117.8557382806126</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -21630,7 +21619,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6">
       <c r="B144" s="408" t="s">
         <v>315</v>
       </c>
@@ -21640,18 +21629,18 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>136.01138275865037</v>
+        <v>137.08212561503123</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>144.47961973069502</v>
+        <v>145.55036258707588</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6">
       <c r="B145" s="408" t="s">
         <v>314</v>
       </c>
@@ -21661,18 +21650,18 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>153.81877714019512</v>
+        <v>155.02970782452144</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>162.9882141875724</v>
+        <v>164.19914487189874</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="345" t="s">
         <v>475</v>
       </c>
@@ -21682,50 +21671,50 @@
       <c r="E147" s="345"/>
       <c r="F147" s="345"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B149" s="476" t="s">
+    <row r="149" spans="1:6">
+      <c r="B149" s="478" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="475"/>
-      <c r="D149" s="475"/>
-      <c r="E149" s="475"/>
-      <c r="F149" s="475"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C149" s="472"/>
+      <c r="D149" s="472"/>
+      <c r="E149" s="472"/>
+      <c r="F149" s="472"/>
+    </row>
+    <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B152" s="477" t="s">
+    <row r="152" spans="1:6">
+      <c r="B152" s="474" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="477"/>
-      <c r="D152" s="477"/>
-      <c r="E152" s="477"/>
-      <c r="F152" s="477"/>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C152" s="474"/>
+      <c r="D152" s="474"/>
+      <c r="E152" s="474"/>
+      <c r="F152" s="474"/>
+    </row>
+    <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6">
       <c r="B154" s="412" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6">
       <c r="B155" s="412" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6">
       <c r="B157" s="343" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:6" ht="24.5" customHeight="1">
       <c r="B158" s="471" t="s">
         <v>439</v>
       </c>
@@ -21734,57 +21723,60 @@
       <c r="E158" s="471"/>
       <c r="F158" s="471"/>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6">
       <c r="B160" s="343" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B161" s="472" t="s">
+    <row r="161" spans="2:6">
+      <c r="B161" s="475" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="472"/>
-      <c r="D161" s="472"/>
-      <c r="E161" s="472"/>
-      <c r="F161" s="472"/>
-    </row>
-    <row r="162" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B162" s="472" t="s">
+      <c r="C161" s="475"/>
+      <c r="D161" s="475"/>
+      <c r="E161" s="475"/>
+      <c r="F161" s="475"/>
+    </row>
+    <row r="162" spans="2:6">
+      <c r="B162" s="475" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="472"/>
-      <c r="D162" s="472"/>
-      <c r="E162" s="472"/>
-      <c r="F162" s="472"/>
-    </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C162" s="475"/>
+      <c r="D162" s="475"/>
+      <c r="E162" s="475"/>
+      <c r="F162" s="475"/>
+    </row>
+    <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:6">
       <c r="B165" s="412" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:6">
       <c r="B166" s="412" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:6">
       <c r="B167" s="412" t="s">
         <v>392</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21799,15 +21791,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9618.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9618.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4309445F-B5DD-43F0-AC3B-7640CFB9C12D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A981BE-63F4-46A4-B180-14F6B60F6BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4995,30 +4995,30 @@
     <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5028,6 +5028,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5037,16 +5046,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5416,7 +5416,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>106.6</v>
+        <v>103.7</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5434,14 +5434,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>300398.8</v>
+        <v>292226.59999999998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.21044921126099864</v>
+        <v>0.22009541234569296</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5449,13 +5449,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="463" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="463"/>
-      <c r="D12" s="463"/>
-      <c r="E12" s="463"/>
-      <c r="F12" s="463"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5490,7 +5490,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1343930029869078</v>
+        <v>1.1290652091503142</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>176.15732589242754</v>
+        <v>175.32998482747979</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>87.601270226813611</v>
+        <v>87.220007063243216</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>109.13657783610009</v>
+        <v>108.65869130039019</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>134.73083111113769</v>
+        <v>134.13782580426846</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>151.96305795693928</v>
+        <v>151.29241297642221</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5633,22 +5633,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="463" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="463"/>
-      <c r="D29" s="463"/>
-      <c r="E29" s="463"/>
-      <c r="F29" s="463"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="467" t="s">
+      <c r="B30" s="463" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="467"/>
-      <c r="D30" s="467"/>
-      <c r="E30" s="467"/>
-      <c r="F30" s="467"/>
+      <c r="C30" s="463"/>
+      <c r="D30" s="463"/>
+      <c r="E30" s="463"/>
+      <c r="F30" s="463"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5660,13 +5660,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="464" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="464"/>
-      <c r="D33" s="464"/>
-      <c r="E33" s="464"/>
-      <c r="F33" s="464"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5686,13 +5686,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="464" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="464"/>
-      <c r="D36" s="464"/>
-      <c r="E36" s="464"/>
-      <c r="F36" s="464"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="464" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="464"/>
-      <c r="D40" s="464"/>
-      <c r="E40" s="464"/>
-      <c r="F40" s="464"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5743,13 +5743,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="464" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="464"/>
-      <c r="D43" s="464"/>
-      <c r="E43" s="464"/>
-      <c r="F43" s="464"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5813,13 +5813,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="464" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="464"/>
-      <c r="D51" s="464"/>
-      <c r="E51" s="464"/>
-      <c r="F51" s="464"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5835,7 +5835,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="464" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5857,22 +5857,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="463" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="463"/>
-      <c r="D57" s="463"/>
-      <c r="E57" s="463"/>
-      <c r="F57" s="463"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="463" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="463"/>
-      <c r="D58" s="463"/>
-      <c r="E58" s="463"/>
-      <c r="F58" s="463"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>-1.0767885741549313E-2</v>
+        <v>-1.1017025968613736E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.2926829268292684E-2</v>
+        <v>3.3847637415621981E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6007,13 +6007,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="463" t="s">
+      <c r="B73" s="461" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="463"/>
-      <c r="D73" s="463"/>
-      <c r="E73" s="463"/>
-      <c r="F73" s="463"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6032,13 +6032,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="463" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="463"/>
-      <c r="D77" s="463"/>
-      <c r="E77" s="463"/>
-      <c r="F77" s="463"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-42.913306351104801</v>
+        <v>-42.71175957808763</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>16.108857157597306</v>
+        <v>16.03320024711493</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>32.907943962659452</v>
+        <v>32.753388406906211</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.1034947691519532</v>
+        <v>6.0748290759335122</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6207,31 +6207,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="463" t="s">
+      <c r="B96" s="461" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="463"/>
-      <c r="D96" s="463"/>
-      <c r="E96" s="463"/>
-      <c r="F96" s="463"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="467" t="s">
+      <c r="B97" s="463" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="467"/>
-      <c r="D97" s="467"/>
-      <c r="E97" s="467"/>
-      <c r="F97" s="467"/>
+      <c r="C97" s="463"/>
+      <c r="D97" s="463"/>
+      <c r="E97" s="463"/>
+      <c r="F97" s="463"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="467" t="s">
+      <c r="B98" s="463" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="467"/>
-      <c r="D98" s="467"/>
-      <c r="E98" s="467"/>
-      <c r="F98" s="467"/>
+      <c r="C98" s="463"/>
+      <c r="D98" s="463"/>
+      <c r="E98" s="463"/>
+      <c r="F98" s="463"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6281,22 +6281,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="463" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="463"/>
-      <c r="D107" s="463"/>
-      <c r="E107" s="463"/>
-      <c r="F107" s="463"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="463" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="463"/>
-      <c r="D108" s="463"/>
-      <c r="E108" s="463"/>
-      <c r="F108" s="463"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-67.049167954985663</v>
+        <v>-66.734264616514139</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>-16.197719563231665</v>
+        <v>-16.121645301288378</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6330,13 +6330,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="463" t="s">
+      <c r="B114" s="461" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="463"/>
-      <c r="D114" s="463"/>
-      <c r="E114" s="463"/>
-      <c r="F114" s="463"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>250.52 HKD</v>
+        <v>249.35 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-9.4957616264526146E-2</v>
+        <v>-9.4883131303035162E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>193.61 HKD</v>
+        <v>192.7 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-1.2295657497526534E-2</v>
+        <v>-1.2207415547441898E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>162.65 HKD</v>
+        <v>161.89 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>4.7976785714594565E-2</v>
+        <v>4.8076039547412644E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>148.97 HKD</v>
+        <v>148.27 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.978339287258443E-2</v>
+        <v>7.9888804669229499E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>124.81 HKD</v>
+        <v>124.22 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6467,17 +6467,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.14694767986382479</v>
+        <v>0.14706690951238025</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="464" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="464"/>
-      <c r="D124" s="464"/>
-      <c r="E124" s="464"/>
-      <c r="F124" s="464"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>176.15732589242754</v>
+        <v>175.32998482747979</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6512,22 +6512,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="468" t="s">
+      <c r="B131" s="464" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="468"/>
-      <c r="D131" s="468"/>
-      <c r="E131" s="468"/>
-      <c r="F131" s="468"/>
+      <c r="C131" s="464"/>
+      <c r="D131" s="464"/>
+      <c r="E131" s="464"/>
+      <c r="F131" s="464"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="463" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="463"/>
-      <c r="D132" s="463"/>
-      <c r="E132" s="463"/>
-      <c r="F132" s="463"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6592,11 +6592,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>81.178491194667089</v>
+        <v>80.797228031096694</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>87.601270226813611</v>
+        <v>87.220007063243216</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6613,11 +6613,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>101.75152398118563</v>
+        <v>101.27363744547573</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>109.13657783610009</v>
+        <v>108.65869130039019</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6660,11 +6660,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>126.26259413909303</v>
+        <v>125.66958883222379</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>134.73083111113769</v>
+        <v>134.13782580426846</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6681,11 +6681,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>142.79362090956198</v>
+        <v>142.12297592904494</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>151.96305795693928</v>
+        <v>151.29241297642221</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6703,13 +6703,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="462" t="s">
+      <c r="B149" s="468" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="463"/>
-      <c r="D149" s="463"/>
-      <c r="E149" s="463"/>
-      <c r="F149" s="463"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6746,13 +6746,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="464" t="s">
+      <c r="B158" s="462" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="464"/>
-      <c r="D158" s="464"/>
-      <c r="E158" s="464"/>
-      <c r="F158" s="464"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6760,22 +6760,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="461" t="s">
+      <c r="B161" s="467" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="461"/>
-      <c r="D161" s="461"/>
-      <c r="E161" s="461"/>
-      <c r="F161" s="461"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="461" t="s">
+      <c r="B162" s="467" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="461"/>
-      <c r="D162" s="461"/>
-      <c r="E162" s="461"/>
-      <c r="F162" s="461"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6799,6 +6799,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6815,18 +6827,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10113,11 +10113,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>90.590419230721707</v>
+        <v>90.164951975580806</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-67.049167954985663</v>
+        <v>-66.734264616514139</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10523,11 +10523,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-120929.69729741334</v>
+        <v>-120361.73849105094</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-42.913306351104808</v>
+        <v>-42.71175957808763</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10540,11 +10540,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>45394.759470109209</v>
+        <v>45181.558296369869</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>16.108857157597306</v>
+        <v>16.033200247114927</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10557,11 +10557,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>92734.586086774332</v>
+        <v>92299.048530661705</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>32.907943962659452</v>
+        <v>32.753388406906211</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10574,11 +10574,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>17199.64825947021</v>
+        <v>17118.868335980631</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.1034947691519505</v>
+        <v>6.0748290759335077</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14162,24 +14162,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.2926829268292684E-2</v>
+        <v>3.3847637415621981E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.2926829268292684E-2</v>
+        <v>3.3847637415621981E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>3.2926829268292684E-2</v>
+        <v>3.3847637415621981E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>2.5024390243902444E-2</v>
+        <v>2.572420443587271E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>2.0414634146341464E-2</v>
+        <v>2.0985535197685631E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -15325,34 +15325,34 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>-1.1478566200491569</v>
+        <v>-1.1424655929452443</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>-0.99752514599061659</v>
+        <v>-0.99284016617263249</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>11.602368748079721</v>
+        <v>11.547877025596293</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>7.5059942986848416</v>
+        <v>7.4707416216525049</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>3.9719857205364866</v>
+        <v>3.9533308795905429</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>5.0721617592743212E-2</v>
+        <v>5.0483398279964363E-2</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>4.9827950997061548</v>
+        <v>4.9593928881698321</v>
       </c>
       <c r="M123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15382,34 +15382,34 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>-1.0767885741549313E-2</v>
+        <v>-1.1017025968613736E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>-9.3576467728950907E-3</v>
+        <v>-9.5741578223011801E-3</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.10884023215834636</v>
+        <v>0.11135850555059106</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>7.0412704490476943E-2</v>
+        <v>7.2041867132618176E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>3.7260654038803818E-2</v>
+        <v>3.8122766437710155E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>4.7581254777432659E-4</v>
+        <v>4.868215841848058E-4</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>4.6742918383735038E-2</v>
+        <v>4.7824425151107346E-2</v>
       </c>
       <c r="M124" s="74" t="str">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
@@ -15439,27 +15439,27 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7037591361882943E-2</v>
+        <v>7.9191969519544075E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14866903596152847</v>
+        <v>0.1528266078447342</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7420415793937922E-2</v>
+        <v>7.9585499745745247E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.226044844386862E-2</v>
+        <v>3.3162621061874585E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-1.4870232504257673E-2</v>
+        <v>-1.5286082786440386E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16423833916779962</v>
+        <v>0.1688313110442376</v>
       </c>
       <c r="M125" s="22" t="str">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.1034947691519532</v>
+        <v>6.0748290759335122</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16389,7 +16389,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1343930029869078</v>
+        <v>1.1290652091503142</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>-45645.173729186834</v>
+        <v>-45430.796459030651</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16436,7 +16436,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>-16.197719563231665</v>
+        <v>-16.121645301288378</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>154.11277289196647</v>
+        <v>153.38896634574107</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18747,23 +18747,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>-16.197719563231665</v>
+        <v>-16.121645301288378</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>-16.197719563231665</v>
+        <v>-16.121645301288378</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>-16.197719563231665</v>
+        <v>-16.121645301288378</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>-16.197719563231665</v>
+        <v>-16.121645301288378</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>-16.197719563231665</v>
+        <v>-16.121645301288378</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18778,23 +18778,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>158.16745813841032</v>
+        <v>157.4246083443789</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>161.20873740579552</v>
+        <v>160.45160392974785</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>162.7293770394881</v>
+        <v>161.96510172243231</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>165.77065630687326</v>
+        <v>164.99209730780117</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>170.33257520795098</v>
+        <v>169.53259068585453</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18809,23 +18809,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>157.9643332631062</v>
+        <v>157.22243746601927</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>164.12364940947026</v>
+        <v>163.35282574830464</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>167.24922070877705</v>
+        <v>166.46371747936618</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>173.59218975964023</v>
+        <v>172.77689612132707</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>183.33620946655887</v>
+        <v>182.47515203386274</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18840,23 +18840,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>157.66195343413358</v>
+        <v>156.92147779512669</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>166.780627687003</v>
+        <v>165.99732525308954</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>171.47358076785449</v>
+        <v>170.66823739536528</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>181.13099979187601</v>
+        <v>180.28029935405047</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>196.30875334415882</v>
+        <v>195.3867690200467</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18871,23 +18871,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>157.48536245685861</v>
+        <v>156.74571619560516</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>169.41714841759952</v>
+        <v>168.62146329191916</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>175.64230590953369</v>
+        <v>174.81738368909865</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>188.62779942384984</v>
+        <v>187.74188949269328</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>209.49489251900809</v>
+        <v>208.51097813111804</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18902,23 +18902,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>145.95585475527736</v>
+        <v>145.27035801708132</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>160.10061447710305</v>
+        <v>159.34868541477633</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>167.58886308983116</v>
+        <v>166.80176469491798</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>183.43757188310647</v>
+        <v>182.57603839135786</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>209.51727662374449</v>
+        <v>208.53325710659593</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18933,23 +18933,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>145.80233159269946</v>
+        <v>145.11755589188394</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>162.48533194167899</v>
+        <v>161.7222028076167</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>171.43374591729454</v>
+        <v>170.62858963329296</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>190.62311996793639</v>
+        <v>189.72783880787696</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>222.88848215602837</v>
+        <v>221.84166339185063</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18965,23 +18965,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>135.06258588426653</v>
+        <v>134.42825050778421</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>153.50811768881505</v>
+        <v>152.787150968167</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>163.54707587117724</v>
+        <v>162.7789601471512</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>185.39103255563882</v>
+        <v>184.52032443419506</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>223.00452772675791</v>
+        <v>221.95716394257843</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18996,23 +18996,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>134.92911722232455</v>
+        <v>134.29540869519042</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>155.66508058307863</v>
+        <v>154.93398346354454</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>167.09327367854058</v>
+        <v>166.3085028704549</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>192.27825161097968</v>
+        <v>191.37519695430723</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>236.56339700728216</v>
+        <v>235.45235259390824</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19028,23 +19028,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>124.92439066713368</v>
+        <v>124.33767037100695</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>147.02172478832802</v>
+        <v>146.331222081497</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>159.3786036978284</v>
+        <v>158.6300656336563</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>187.01144115721962</v>
+        <v>186.13312261951137</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>236.7750713531953</v>
+        <v>235.66303278940566</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19060,23 +19060,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>124.80835681646612</v>
+        <v>124.22218148529667</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>148.97268501583545</v>
+        <v>148.27301942290748</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>162.64931946558167</v>
+        <v>161.8854201471857</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>193.61271718463817</v>
+        <v>192.70339507264839</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>250.52423822692751</v>
+        <v>249.34762528165342</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19092,23 +19092,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>98.524763530913546</v>
+        <v>98.062031808741679</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>128.3407534722169</v>
+        <v>127.73798787552099</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>146.37229489029573</v>
+        <v>145.68484229801842</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>190.06100487876222</v>
+        <v>189.1683637502436</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>279.83313980901761</v>
+        <v>278.51887458204288</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19124,23 +19124,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>83.761355116221949</v>
+        <v>83.367961265627031</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>117.81550025191402</v>
+        <v>117.26216759343977</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>139.68110708925542</v>
+        <v>139.02508035118561</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>196.0959191204567</v>
+        <v>195.17493439424609</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>324.78327669700383</v>
+        <v>323.25789851214302</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19156,23 +19156,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>65.33725643516496</v>
+        <v>65.030393265858876</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>100.30990628971793</v>
+        <v>99.838790460307436</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>124.21379739642778</v>
+        <v>123.63041447494813</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>190.09819586992376</v>
+        <v>189.20538007007607</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>357.70882950592676</v>
+        <v>356.02881306354857</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19188,23 +19188,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>55.002565273146978</v>
+        <v>54.744240047684976</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>90.990338894855213</v>
+        <v>90.562993375729889</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>116.97485250285135</v>
+        <v>116.42546803330669</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>193.00479243645904</v>
+        <v>192.09832550580234</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>406.92160577214042</v>
+        <v>405.01045644602402</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19251,7 +19251,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>250.52423822692751</v>
+        <v>249.34762528165342</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19279,7 +19279,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>193.61271718463817</v>
+        <v>192.70339507264839</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19307,7 +19307,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>162.64931946558167</v>
+        <v>161.8854201471857</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19335,7 +19335,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>148.97268501583545</v>
+        <v>148.27301942290748</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>124.80835681646612</v>
+        <v>124.22218148529667</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19723,7 +19723,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>193.61271718463817</v>
+        <v>192.70339507264839</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>162.64931946558167</v>
+        <v>161.8854201471857</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19770,7 +19770,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>148.97268501583545</v>
+        <v>148.27301942290748</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19786,7 +19786,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>165.42284039695642</v>
+        <v>164.64591495120868</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19833,7 +19833,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>250.52423822692751</v>
+        <v>249.34762528165342</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>124.80835681646612</v>
+        <v>124.22218148529667</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>106.6</v>
+        <v>103.7</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19912,7 +19912,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.21044921126099864</v>
+        <v>0.22009541234569296</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19921,7 +19921,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>-16.197719563231665</v>
+        <v>-16.121645301288378</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>176.15732589242754</v>
+        <v>175.32998482747979</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20044,7 +20044,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>154.11277289196647</v>
+        <v>153.38896634574107</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20111,7 +20111,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>3.464797582633105E-2</v>
+        <v>3.4647975826331043E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20189,11 +20189,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>81.178491194667089</v>
+        <v>80.797228031096694</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>87.601270226813611</v>
+        <v>87.220007063243216</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20201,7 +20201,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.50271003613946585</v>
+        <v>0.50253798773173075</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20214,11 +20214,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>101.75152398118563</v>
+        <v>101.27363744547573</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>109.13657783610009</v>
+        <v>108.65869130039019</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20226,7 +20226,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.38045961311455434</v>
+        <v>0.38026178803752508</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20260,11 +20260,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>126.26259413909303</v>
+        <v>125.66958883222379</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>134.73083111113769</v>
+        <v>134.13782580426846</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20272,7 +20272,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.23516759562181022</v>
+        <v>0.23494075507816514</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20285,11 +20285,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>142.79362090956198</v>
+        <v>142.12297592904494</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>151.96305795693928</v>
+        <v>151.29241297642221</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20297,7 +20297,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.13734465945664254</v>
+        <v>0.13709903571091919</v>
       </c>
     </row>
   </sheetData>
@@ -20408,7 +20408,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>106.6</v>
+        <v>103.7</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20426,14 +20426,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>300398.8</v>
+        <v>292226.59999999998</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.21044921126099864</v>
+        <v>0.22009541234569296</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20441,13 +20441,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="475" t="s">
+      <c r="B12" s="472" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="475"/>
-      <c r="D12" s="475"/>
-      <c r="E12" s="475"/>
-      <c r="F12" s="475"/>
+      <c r="C12" s="472"/>
+      <c r="D12" s="472"/>
+      <c r="E12" s="472"/>
+      <c r="F12" s="472"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20485,7 +20485,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1343930029869078</v>
+        <v>1.1290652091503142</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20511,7 +20511,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>176.15732589242754</v>
+        <v>175.32998482747979</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20563,7 +20563,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>87.601270226813611</v>
+        <v>87.220007063243216</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20579,7 +20579,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>109.13657783610009</v>
+        <v>108.65869130039019</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20595,7 +20595,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>134.73083111113769</v>
+        <v>134.13782580426846</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20611,7 +20611,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>151.96305795693928</v>
+        <v>151.29241297642221</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20632,22 +20632,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="475" t="s">
+      <c r="B29" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="475"/>
-      <c r="D29" s="475"/>
-      <c r="E29" s="475"/>
-      <c r="F29" s="475"/>
+      <c r="C29" s="472"/>
+      <c r="D29" s="472"/>
+      <c r="E29" s="472"/>
+      <c r="F29" s="472"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="478" t="s">
+      <c r="B30" s="473" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="478"/>
-      <c r="D30" s="478"/>
-      <c r="E30" s="478"/>
-      <c r="F30" s="478"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20837,10 +20837,10 @@
       <c r="B54" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="477"/>
-      <c r="D54" s="477"/>
-      <c r="E54" s="477"/>
-      <c r="F54" s="477"/>
+      <c r="C54" s="474"/>
+      <c r="D54" s="474"/>
+      <c r="E54" s="474"/>
+      <c r="F54" s="474"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20856,22 +20856,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="475" t="s">
+      <c r="B57" s="472" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="475"/>
-      <c r="D57" s="475"/>
-      <c r="E57" s="475"/>
-      <c r="F57" s="475"/>
+      <c r="C57" s="472"/>
+      <c r="D57" s="472"/>
+      <c r="E57" s="472"/>
+      <c r="F57" s="472"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="475" t="s">
+      <c r="B58" s="472" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="475"/>
-      <c r="D58" s="475"/>
-      <c r="E58" s="475"/>
-      <c r="F58" s="475"/>
+      <c r="C58" s="472"/>
+      <c r="D58" s="472"/>
+      <c r="E58" s="472"/>
+      <c r="F58" s="472"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20905,7 +20905,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>-1.0767885741549313E-2</v>
+        <v>-1.1017025968613736E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20915,7 +20915,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.2926829268292684E-2</v>
+        <v>3.3847637415621981E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21006,22 +21006,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="475" t="s">
+      <c r="B73" s="472" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="475"/>
-      <c r="D73" s="475"/>
-      <c r="E73" s="475"/>
-      <c r="F73" s="475"/>
+      <c r="C73" s="472"/>
+      <c r="D73" s="472"/>
+      <c r="E73" s="472"/>
+      <c r="F73" s="472"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="478" t="s">
+      <c r="B74" s="473" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="478"/>
-      <c r="D74" s="478"/>
-      <c r="E74" s="478"/>
-      <c r="F74" s="478"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21029,13 +21029,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="475" t="s">
+      <c r="B77" s="472" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="475"/>
-      <c r="D77" s="475"/>
-      <c r="E77" s="475"/>
-      <c r="F77" s="475"/>
+      <c r="C77" s="472"/>
+      <c r="D77" s="472"/>
+      <c r="E77" s="472"/>
+      <c r="F77" s="472"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21056,7 +21056,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-42.913306351104801</v>
+        <v>-42.71175957808763</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21118,7 +21118,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>16.108857157597306</v>
+        <v>16.03320024711493</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21149,7 +21149,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>32.907943962659452</v>
+        <v>32.753388406906211</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21162,7 +21162,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>6.1034947691519532</v>
+        <v>6.0748290759335122</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21184,33 +21184,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="475" t="s">
+      <c r="B96" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="475"/>
-      <c r="D96" s="475"/>
-      <c r="E96" s="475"/>
-      <c r="F96" s="475"/>
+      <c r="C96" s="472"/>
+      <c r="D96" s="472"/>
+      <c r="E96" s="472"/>
+      <c r="F96" s="472"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="478" t="s">
+      <c r="B97" s="473" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="478"/>
-      <c r="D97" s="478"/>
-      <c r="E97" s="478"/>
-      <c r="F97" s="478"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="478" t="s">
+      <c r="B98" s="473" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="478"/>
-      <c r="D98" s="478"/>
-      <c r="E98" s="478"/>
-      <c r="F98" s="478"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21273,23 +21273,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="475" t="s">
+      <c r="B107" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="475"/>
-      <c r="D107" s="475"/>
-      <c r="E107" s="475"/>
-      <c r="F107" s="475"/>
+      <c r="C107" s="472"/>
+      <c r="D107" s="472"/>
+      <c r="E107" s="472"/>
+      <c r="F107" s="472"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="475" t="s">
+      <c r="B108" s="472" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="475"/>
-      <c r="D108" s="475"/>
-      <c r="E108" s="475"/>
-      <c r="F108" s="475"/>
+      <c r="C108" s="472"/>
+      <c r="D108" s="472"/>
+      <c r="E108" s="472"/>
+      <c r="F108" s="472"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21307,7 +21307,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-67.049167954985663</v>
+        <v>-66.734264616514139</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21321,7 +21321,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>-16.197719563231665</v>
+        <v>-16.121645301288378</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21333,13 +21333,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="475" t="s">
+      <c r="B114" s="472" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="475"/>
-      <c r="D114" s="475"/>
-      <c r="E114" s="475"/>
-      <c r="F114" s="475"/>
+      <c r="C114" s="472"/>
+      <c r="D114" s="472"/>
+      <c r="E114" s="472"/>
+      <c r="F114" s="472"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21384,7 +21384,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>250.52 HKD</v>
+        <v>249.35 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21407,7 +21407,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>193.61 HKD</v>
+        <v>192.7 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21429,7 +21429,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>162.65 HKD</v>
+        <v>161.89 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21451,7 +21451,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>148.97 HKD</v>
+        <v>148.27 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21473,7 +21473,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>124.81 HKD</v>
+        <v>124.22 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21495,7 +21495,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>176.15732589242754</v>
+        <v>175.32998482747979</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21503,13 +21503,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="473" t="s">
+      <c r="B127" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="473"/>
-      <c r="D127" s="473"/>
-      <c r="E127" s="473"/>
-      <c r="F127" s="473"/>
+      <c r="C127" s="476"/>
+      <c r="D127" s="476"/>
+      <c r="E127" s="476"/>
+      <c r="F127" s="476"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21522,22 +21522,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="474" t="s">
+      <c r="B131" s="477" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="474"/>
-      <c r="D131" s="474"/>
-      <c r="E131" s="474"/>
-      <c r="F131" s="474"/>
+      <c r="C131" s="477"/>
+      <c r="D131" s="477"/>
+      <c r="E131" s="477"/>
+      <c r="F131" s="477"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="475" t="s">
+      <c r="B132" s="472" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="475"/>
-      <c r="D132" s="475"/>
-      <c r="E132" s="475"/>
-      <c r="F132" s="475"/>
+      <c r="C132" s="472"/>
+      <c r="D132" s="472"/>
+      <c r="E132" s="472"/>
+      <c r="F132" s="472"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21602,11 +21602,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>81.178491194667089</v>
+        <v>80.797228031096694</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>87.601270226813611</v>
+        <v>87.220007063243216</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21623,11 +21623,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>101.75152398118563</v>
+        <v>101.27363744547573</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>109.13657783610009</v>
+        <v>108.65869130039019</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21663,11 +21663,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>126.26259413909303</v>
+        <v>125.66958883222379</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>134.73083111113769</v>
+        <v>134.13782580426846</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21684,11 +21684,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>142.79362090956198</v>
+        <v>142.12297592904494</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>151.96305795693928</v>
+        <v>151.29241297642221</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21706,13 +21706,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="476" t="s">
+      <c r="B149" s="478" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="475"/>
-      <c r="D149" s="475"/>
-      <c r="E149" s="475"/>
-      <c r="F149" s="475"/>
+      <c r="C149" s="472"/>
+      <c r="D149" s="472"/>
+      <c r="E149" s="472"/>
+      <c r="F149" s="472"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21720,13 +21720,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="477" t="s">
+      <c r="B152" s="474" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="477"/>
-      <c r="D152" s="477"/>
-      <c r="E152" s="477"/>
-      <c r="F152" s="477"/>
+      <c r="C152" s="474"/>
+      <c r="D152" s="474"/>
+      <c r="E152" s="474"/>
+      <c r="F152" s="474"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21763,22 +21763,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="472" t="s">
+      <c r="B161" s="475" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="472"/>
-      <c r="D161" s="472"/>
-      <c r="E161" s="472"/>
-      <c r="F161" s="472"/>
+      <c r="C161" s="475"/>
+      <c r="D161" s="475"/>
+      <c r="E161" s="475"/>
+      <c r="F161" s="475"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="472" t="s">
+      <c r="B162" s="475" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="472"/>
-      <c r="D162" s="472"/>
-      <c r="E162" s="472"/>
-      <c r="F162" s="472"/>
+      <c r="C162" s="475"/>
+      <c r="D162" s="475"/>
+      <c r="E162" s="475"/>
+      <c r="F162" s="475"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21802,12 +21802,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21822,15 +21825,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9618.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9618.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A981BE-63F4-46A4-B180-14F6B60F6BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6C5CD7-499E-4B5F-9F10-8415C1A62134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4995,30 +4995,30 @@
     <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5028,25 +5028,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5416,7 +5416,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>103.7</v>
+        <v>108.6</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5434,14 +5434,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>292226.59999999998</v>
+        <v>306034.8</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.22009541234569296</v>
+        <v>0.20453888280005972</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5449,13 +5449,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+      <c r="B12" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="C12" s="463"/>
+      <c r="D12" s="463"/>
+      <c r="E12" s="463"/>
+      <c r="F12" s="463"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5490,7 +5490,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1290652091503142</v>
+        <v>1.1396112205505371</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>175.32998482747979</v>
+        <v>176.96765110557101</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>87.220007063243216</v>
+        <v>87.974691984022584</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>108.65869130039019</v>
+        <v>109.60463572094829</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>134.13782580426846</v>
+        <v>135.31164012938021</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>151.29241297642221</v>
+        <v>152.61990984040693</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5633,22 +5633,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+      <c r="B29" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="463"/>
+      <c r="D29" s="463"/>
+      <c r="E29" s="463"/>
+      <c r="F29" s="463"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="463" t="s">
+      <c r="B30" s="467" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="463"/>
-      <c r="D30" s="463"/>
-      <c r="E30" s="463"/>
-      <c r="F30" s="463"/>
+      <c r="C30" s="467"/>
+      <c r="D30" s="467"/>
+      <c r="E30" s="467"/>
+      <c r="F30" s="467"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5660,13 +5660,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+      <c r="B33" s="464" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="C33" s="464"/>
+      <c r="D33" s="464"/>
+      <c r="E33" s="464"/>
+      <c r="F33" s="464"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5686,13 +5686,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+      <c r="B36" s="464" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="C36" s="464"/>
+      <c r="D36" s="464"/>
+      <c r="E36" s="464"/>
+      <c r="F36" s="464"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+      <c r="B40" s="464" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="C40" s="464"/>
+      <c r="D40" s="464"/>
+      <c r="E40" s="464"/>
+      <c r="F40" s="464"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5743,13 +5743,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+      <c r="B43" s="464" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="C43" s="464"/>
+      <c r="D43" s="464"/>
+      <c r="E43" s="464"/>
+      <c r="F43" s="464"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5813,13 +5813,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+      <c r="B51" s="464" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="C51" s="464"/>
+      <c r="D51" s="464"/>
+      <c r="E51" s="464"/>
+      <c r="F51" s="464"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5835,7 +5835,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+      <c r="B54" s="464" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5857,22 +5857,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+      <c r="B57" s="463" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="C57" s="463"/>
+      <c r="D57" s="463"/>
+      <c r="E57" s="463"/>
+      <c r="F57" s="463"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="B58" s="463" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="C58" s="463"/>
+      <c r="D58" s="463"/>
+      <c r="E58" s="463"/>
+      <c r="F58" s="463"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>-1.1017025968613736E-2</v>
+        <v>-1.0618202305405061E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.3847637415621981E-2</v>
+        <v>3.2320441988950274E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6007,13 +6007,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
+      <c r="B73" s="463" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="C73" s="463"/>
+      <c r="D73" s="463"/>
+      <c r="E73" s="463"/>
+      <c r="F73" s="463"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6032,13 +6032,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="463" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="C77" s="463"/>
+      <c r="D77" s="463"/>
+      <c r="E77" s="463"/>
+      <c r="F77" s="463"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-42.71175957808763</v>
+        <v>-43.110707929151495</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>16.03320024711493</v>
+        <v>16.182958038974782</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>32.753388406906211</v>
+        <v>33.059320787725127</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.0748290759335122</v>
+        <v>6.1315708975484151</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6207,31 +6207,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
+      <c r="B96" s="463" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="C96" s="463"/>
+      <c r="D96" s="463"/>
+      <c r="E96" s="463"/>
+      <c r="F96" s="463"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="463" t="s">
+      <c r="B97" s="467" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="463"/>
-      <c r="D97" s="463"/>
-      <c r="E97" s="463"/>
-      <c r="F97" s="463"/>
+      <c r="C97" s="467"/>
+      <c r="D97" s="467"/>
+      <c r="E97" s="467"/>
+      <c r="F97" s="467"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="463" t="s">
+      <c r="B98" s="467" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="463"/>
-      <c r="D98" s="463"/>
-      <c r="E98" s="463"/>
-      <c r="F98" s="463"/>
+      <c r="C98" s="467"/>
+      <c r="D98" s="467"/>
+      <c r="E98" s="467"/>
+      <c r="F98" s="467"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6281,22 +6281,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="463" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
+      <c r="C107" s="463"/>
+      <c r="D107" s="463"/>
+      <c r="E107" s="463"/>
+      <c r="F107" s="463"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="B108" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="463"/>
+      <c r="D108" s="463"/>
+      <c r="E108" s="463"/>
+      <c r="F108" s="463"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-66.734264616514139</v>
+        <v>-67.35759470385328</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>-16.121645301288378</v>
+        <v>-16.272229212438813</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6330,13 +6330,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
+      <c r="B114" s="463" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="C114" s="463"/>
+      <c r="D114" s="463"/>
+      <c r="E114" s="463"/>
+      <c r="F114" s="463"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>249.35 HKD</v>
+        <v>251.68 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-9.4883131303035162E-2</v>
+        <v>-9.5029895097454825E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>192.7 HKD</v>
+        <v>194.5 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-1.2207415547441898E-2</v>
+        <v>-1.2381285096508474E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>161.89 HKD</v>
+        <v>163.4 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>4.8076039547412644E-2</v>
+        <v>4.7880473150503283E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>148.27 HKD</v>
+        <v>149.66 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.9888804669229499E-2</v>
+        <v>7.9681105218030582E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>124.22 HKD</v>
+        <v>125.38 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6467,17 +6467,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.14706690951238025</v>
+        <v>0.14683198485275545</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+      <c r="B124" s="464" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="C124" s="464"/>
+      <c r="D124" s="464"/>
+      <c r="E124" s="464"/>
+      <c r="F124" s="464"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>175.32998482747979</v>
+        <v>176.96765110557101</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6512,22 +6512,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="464" t="s">
+      <c r="B131" s="468" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="464"/>
-      <c r="D131" s="464"/>
-      <c r="E131" s="464"/>
-      <c r="F131" s="464"/>
+      <c r="C131" s="468"/>
+      <c r="D131" s="468"/>
+      <c r="E131" s="468"/>
+      <c r="F131" s="468"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="B132" s="463" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="C132" s="463"/>
+      <c r="D132" s="463"/>
+      <c r="E132" s="463"/>
+      <c r="F132" s="463"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6592,11 +6592,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>80.797228031096694</v>
+        <v>81.551912951876062</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>87.220007063243216</v>
+        <v>87.974691984022584</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6613,11 +6613,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>101.27363744547573</v>
+        <v>102.21958186603383</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>108.65869130039019</v>
+        <v>109.60463572094829</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6660,11 +6660,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>125.66958883222379</v>
+        <v>126.84340315733554</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>134.13782580426846</v>
+        <v>135.31164012938021</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6681,11 +6681,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>142.12297592904494</v>
+        <v>143.45047279302966</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>151.29241297642221</v>
+        <v>152.61990984040693</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6703,13 +6703,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="468" t="s">
+      <c r="B149" s="462" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="C149" s="463"/>
+      <c r="D149" s="463"/>
+      <c r="E149" s="463"/>
+      <c r="F149" s="463"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6746,13 +6746,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
+      <c r="B158" s="464" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="C158" s="464"/>
+      <c r="D158" s="464"/>
+      <c r="E158" s="464"/>
+      <c r="F158" s="464"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6760,22 +6760,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="461" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="461"/>
+      <c r="D161" s="461"/>
+      <c r="E161" s="461"/>
+      <c r="F161" s="461"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="461" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="461"/>
+      <c r="D162" s="461"/>
+      <c r="E162" s="461"/>
+      <c r="F162" s="461"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6799,18 +6799,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6827,6 +6815,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10113,11 +10113,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>90.164951975580806</v>
+        <v>91.007135937790238</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-66.734264616514139</v>
+        <v>-67.35759470385328</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10523,11 +10523,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-120361.73849105094</v>
+        <v>-121485.97494434891</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-42.71175957808763</v>
+        <v>-43.110707929151495</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10540,11 +10540,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>45181.558296369869</v>
+        <v>45603.575753830926</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>16.033200247114927</v>
+        <v>16.182958038974778</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10557,11 +10557,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>92299.048530661705</v>
+        <v>93161.165979809419</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>32.753388406906211</v>
+        <v>33.059320787725127</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10574,11 +10574,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>17118.868335980631</v>
+        <v>17278.766789291432</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.0748290759335077</v>
+        <v>6.1315708975484107</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14162,24 +14162,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.3847637415621981E-2</v>
+        <v>3.2320441988950274E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.3847637415621981E-2</v>
+        <v>3.2320441988950274E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>3.3847637415621981E-2</v>
+        <v>3.2320441988950274E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>2.572420443587271E-2</v>
+        <v>2.4563535911602211E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>2.0985535197685631E-2</v>
+        <v>2.0038674033149174E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -15325,34 +15325,34 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>-1.1424655929452443</v>
+        <v>-1.1531367703669897</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>-0.99284016617263249</v>
+        <v>-1.0021137702357101</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>11.547877025596293</v>
+        <v>11.655739744041014</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>7.4707416216525049</v>
+        <v>7.5405219369713681</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>3.9533308795905429</v>
+        <v>3.9902568889894074</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>5.0483398279964363E-2</v>
+        <v>5.0954937469612376E-2</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>4.9593928881698321</v>
+        <v>5.0057159999909677</v>
       </c>
       <c r="M123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15382,34 +15382,34 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>-1.1017025968613736E-2</v>
+        <v>-1.0618202305405061E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>-9.5741578223011801E-3</v>
+        <v>-9.2275669450802046E-3</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.11135850555059106</v>
+        <v>0.1073272536283703</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>7.2041867132618176E-2</v>
+        <v>6.9433903655353305E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>3.8122766437710155E-2</v>
+        <v>3.6742696952020329E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>4.868215841848058E-4</v>
+        <v>4.691983192413663E-4</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>4.7824425151107346E-2</v>
+        <v>4.609314917118755E-2</v>
       </c>
       <c r="M124" s="74" t="str">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
@@ -15439,27 +15439,27 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9191969519544075E-2</v>
+        <v>7.5618851189472563E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1528266078447342</v>
+        <v>0.14593111633056111</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9585499745745247E-2</v>
+        <v>7.5994625447824884E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3162621061874585E-2</v>
+        <v>3.1666333371237518E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-1.5286082786440386E-2</v>
+        <v>-1.4596379235302652E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1688313110442376</v>
+        <v>0.16121369203763755</v>
       </c>
       <c r="M125" s="22" t="str">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.0748290759335122</v>
+        <v>6.1315708975484151</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16389,7 +16389,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1290652091503142</v>
+        <v>1.1396112205505371</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>-45430.796459030651</v>
+        <v>-45855.141920652575</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16436,7 +16436,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>-16.121645301288378</v>
+        <v>-16.272229212438813</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>153.38896634574107</v>
+        <v>154.82169297183913</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18747,23 +18747,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>-16.121645301288378</v>
+        <v>-16.272229212438813</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>-16.121645301288378</v>
+        <v>-16.272229212438813</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>-16.121645301288378</v>
+        <v>-16.272229212438813</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>-16.121645301288378</v>
+        <v>-16.272229212438813</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>-16.121645301288378</v>
+        <v>-16.272229212438813</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18778,23 +18778,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>157.4246083443789</v>
+        <v>158.89502980526586</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>160.45160392974785</v>
+        <v>161.95029898342025</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>161.96510172243231</v>
+        <v>163.47793357249742</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>164.99209730780117</v>
+        <v>166.53320275065175</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>169.53259068585453</v>
+        <v>171.11610651788325</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18809,23 +18809,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>157.22243746601927</v>
+        <v>158.69097055378953</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>163.35282574830464</v>
+        <v>164.87861960736498</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>166.46371747936618</v>
+        <v>168.0185685615123</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>172.77689612132707</v>
+        <v>174.39071532452604</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>182.47515203386274</v>
+        <v>184.17955760584448</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18840,23 +18840,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>156.92147779512669</v>
+        <v>158.38719977500475</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>165.99732525308954</v>
+        <v>167.5478200078106</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>170.66823739536528</v>
+        <v>172.26236071316902</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>180.28029935405047</v>
+        <v>181.96420394770473</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>195.3867690200467</v>
+        <v>197.21177529677789</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18871,23 +18871,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>156.74571619560516</v>
+        <v>158.20979647771654</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>168.62146329191916</v>
+        <v>170.19646875642823</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>174.81738368909865</v>
+        <v>176.45026202632934</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>187.74188949269328</v>
+        <v>189.49548892241918</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>208.51097813111804</v>
+        <v>210.4585708251638</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18902,23 +18902,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>145.27035801708132</v>
+        <v>146.6272529416141</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>159.34868541477633</v>
+        <v>160.83707867973169</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>166.80176469491798</v>
+        <v>168.35977330043841</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>182.57603839135786</v>
+        <v>184.28138629037937</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>208.53325710659593</v>
+        <v>210.48105789697436</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18933,23 +18933,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>145.11755589188394</v>
+        <v>146.47302357116885</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>161.7222028076167</v>
+        <v>163.23276586514089</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>170.62858963329296</v>
+        <v>172.22234262195414</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>189.72783880787696</v>
+        <v>191.49998795815793</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>221.84166339185063</v>
+        <v>223.91377108962971</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18965,23 +18965,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>134.42825050778421</v>
+        <v>135.68387494017108</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>152.787150968167</v>
+        <v>154.21425634955634</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>162.7789601471512</v>
+        <v>164.2993938258403</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>184.52032443419506</v>
+        <v>186.24383289879498</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>221.95716394257843</v>
+        <v>224.030350470982</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18996,23 +18996,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>134.29540869519042</v>
+        <v>135.54979232123705</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>154.93398346354454</v>
+        <v>156.38114129167221</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>166.3085028704549</v>
+        <v>167.8619041735964</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>191.37519695430723</v>
+        <v>193.16273322098476</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>235.45235259390824</v>
+        <v>237.65159066673252</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19028,23 +19028,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>124.33767037100695</v>
+        <v>125.49904393790359</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>146.331222081497</v>
+        <v>147.69802598597775</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>158.6300656336563</v>
+        <v>160.11174664466682</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>186.13312261951137</v>
+        <v>187.87169539387017</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>235.66303278940566</v>
+        <v>237.86423871645616</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19060,23 +19060,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>124.22218148529667</v>
+        <v>125.38247633052566</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>148.27301942290748</v>
+        <v>149.65796064729986</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>161.8854201471857</v>
+        <v>163.39750773306295</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>192.70339507264839</v>
+        <v>194.50333734775154</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>249.34762528165342</v>
+        <v>251.67665187597896</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19092,23 +19092,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>98.062031808741679</v>
+        <v>98.977978289957122</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>127.73798787552099</v>
+        <v>128.93112204125316</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>145.68484229801842</v>
+        <v>147.0456087048328</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>189.1683637502436</v>
+        <v>190.93528713474228</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>278.51887458204288</v>
+        <v>281.12037465725109</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19124,23 +19124,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>83.367961265627031</v>
+        <v>84.146658069669286</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>117.26216759343977</v>
+        <v>118.35745256567438</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>139.02508035118561</v>
+        <v>140.32364138239822</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>195.17493439424609</v>
+        <v>196.99796203381749</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>323.25789851214302</v>
+        <v>326.27728256125982</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19156,23 +19156,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>65.030393265858876</v>
+        <v>65.637808376327868</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>99.838790460307436</v>
+        <v>100.77133272079497</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>123.63041447494813</v>
+        <v>124.78518193204502</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>189.20538007007607</v>
+        <v>190.97264920478281</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>356.02881306354857</v>
+        <v>359.35429319609256</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19188,23 +19188,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>54.744240047684976</v>
+        <v>55.255577546139918</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>90.562993375729889</v>
+        <v>91.40889523581599</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>116.42546803330669</v>
+        <v>117.51293782974081</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>192.09832550580234</v>
+        <v>193.89261614050579</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>405.01045644602402</v>
+        <v>408.79344865610511</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19251,7 +19251,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>249.34762528165342</v>
+        <v>251.67665187597896</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19279,7 +19279,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>192.70339507264839</v>
+        <v>194.50333734775154</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19307,7 +19307,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>161.8854201471857</v>
+        <v>163.39750773306295</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19335,7 +19335,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>148.27301942290748</v>
+        <v>149.65796064729986</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>124.22218148529667</v>
+        <v>125.38247633052566</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19723,7 +19723,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>192.70339507264839</v>
+        <v>194.50333734775154</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>161.8854201471857</v>
+        <v>163.39750773306295</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19770,7 +19770,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>148.27301942290748</v>
+        <v>149.65796064729986</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19786,7 +19786,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>164.64591495120868</v>
+        <v>166.18378688455988</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19833,7 +19833,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>249.34762528165342</v>
+        <v>251.67665187597896</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>124.22218148529667</v>
+        <v>125.38247633052566</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>103.7</v>
+        <v>108.6</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19912,7 +19912,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.22009541234569296</v>
+        <v>0.20453888280005972</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19921,7 +19921,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>-16.121645301288378</v>
+        <v>-16.272229212438813</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>175.32998482747979</v>
+        <v>176.96765110557101</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20044,7 +20044,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>153.38896634574107</v>
+        <v>154.82169297183913</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20189,11 +20189,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>80.797228031096694</v>
+        <v>81.551912951876062</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>87.220007063243216</v>
+        <v>87.974691984022584</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20201,7 +20201,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.50253798773173075</v>
+        <v>0.50287698664463365</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20214,11 +20214,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>101.27363744547573</v>
+        <v>102.21958186603383</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>108.65869130039019</v>
+        <v>109.60463572094829</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20226,7 +20226,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.38026178803752508</v>
+        <v>0.38065157651008741</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20260,11 +20260,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>125.66958883222379</v>
+        <v>126.84340315733554</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>134.13782580426846</v>
+        <v>135.31164012938021</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20272,7 +20272,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.23494075507816514</v>
+        <v>0.23538771473742781</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20285,11 +20285,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>142.12297592904494</v>
+        <v>143.45047279302966</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>151.29241297642221</v>
+        <v>152.61990984040693</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20297,7 +20297,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.13709903571091919</v>
+        <v>0.13758300521624311</v>
       </c>
     </row>
   </sheetData>
@@ -20408,7 +20408,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>103.7</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20426,14 +20426,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>292226.59999999998</v>
+        <v>306034.8</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.22009541234569296</v>
+        <v>0.20453888280005972</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20441,13 +20441,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="472" t="s">
+      <c r="B12" s="475" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="472"/>
-      <c r="D12" s="472"/>
-      <c r="E12" s="472"/>
-      <c r="F12" s="472"/>
+      <c r="C12" s="475"/>
+      <c r="D12" s="475"/>
+      <c r="E12" s="475"/>
+      <c r="F12" s="475"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20485,7 +20485,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1290652091503142</v>
+        <v>1.1396112205505371</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20511,7 +20511,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>175.32998482747979</v>
+        <v>176.96765110557101</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20563,7 +20563,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>87.220007063243216</v>
+        <v>87.974691984022584</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20579,7 +20579,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>108.65869130039019</v>
+        <v>109.60463572094829</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20595,7 +20595,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>134.13782580426846</v>
+        <v>135.31164012938021</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20611,7 +20611,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>151.29241297642221</v>
+        <v>152.61990984040693</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20632,22 +20632,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="472" t="s">
+      <c r="B29" s="475" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="472"/>
-      <c r="D29" s="472"/>
-      <c r="E29" s="472"/>
-      <c r="F29" s="472"/>
+      <c r="C29" s="475"/>
+      <c r="D29" s="475"/>
+      <c r="E29" s="475"/>
+      <c r="F29" s="475"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="478" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="478"/>
+      <c r="D30" s="478"/>
+      <c r="E30" s="478"/>
+      <c r="F30" s="478"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20837,10 +20837,10 @@
       <c r="B54" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="474"/>
-      <c r="D54" s="474"/>
-      <c r="E54" s="474"/>
-      <c r="F54" s="474"/>
+      <c r="C54" s="477"/>
+      <c r="D54" s="477"/>
+      <c r="E54" s="477"/>
+      <c r="F54" s="477"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20856,22 +20856,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="472" t="s">
+      <c r="B57" s="475" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="472"/>
-      <c r="D57" s="472"/>
-      <c r="E57" s="472"/>
-      <c r="F57" s="472"/>
+      <c r="C57" s="475"/>
+      <c r="D57" s="475"/>
+      <c r="E57" s="475"/>
+      <c r="F57" s="475"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="472" t="s">
+      <c r="B58" s="475" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="472"/>
-      <c r="D58" s="472"/>
-      <c r="E58" s="472"/>
-      <c r="F58" s="472"/>
+      <c r="C58" s="475"/>
+      <c r="D58" s="475"/>
+      <c r="E58" s="475"/>
+      <c r="F58" s="475"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20905,7 +20905,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>-1.1017025968613736E-2</v>
+        <v>-1.0618202305405061E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20915,7 +20915,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.3847637415621981E-2</v>
+        <v>3.2320441988950274E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21006,22 +21006,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="472" t="s">
+      <c r="B73" s="475" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="472"/>
-      <c r="D73" s="472"/>
-      <c r="E73" s="472"/>
-      <c r="F73" s="472"/>
+      <c r="C73" s="475"/>
+      <c r="D73" s="475"/>
+      <c r="E73" s="475"/>
+      <c r="F73" s="475"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="478" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="478"/>
+      <c r="D74" s="478"/>
+      <c r="E74" s="478"/>
+      <c r="F74" s="478"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21029,13 +21029,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="472" t="s">
+      <c r="B77" s="475" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="472"/>
-      <c r="D77" s="472"/>
-      <c r="E77" s="472"/>
-      <c r="F77" s="472"/>
+      <c r="C77" s="475"/>
+      <c r="D77" s="475"/>
+      <c r="E77" s="475"/>
+      <c r="F77" s="475"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21056,7 +21056,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-42.71175957808763</v>
+        <v>-43.110707929151495</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21118,7 +21118,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>16.03320024711493</v>
+        <v>16.182958038974782</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21149,7 +21149,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>32.753388406906211</v>
+        <v>33.059320787725127</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21162,7 +21162,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>6.0748290759335122</v>
+        <v>6.1315708975484151</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21184,33 +21184,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="472" t="s">
+      <c r="B96" s="475" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="472"/>
-      <c r="D96" s="472"/>
-      <c r="E96" s="472"/>
-      <c r="F96" s="472"/>
+      <c r="C96" s="475"/>
+      <c r="D96" s="475"/>
+      <c r="E96" s="475"/>
+      <c r="F96" s="475"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="478" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="478"/>
+      <c r="D97" s="478"/>
+      <c r="E97" s="478"/>
+      <c r="F97" s="478"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="478" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="478"/>
+      <c r="D98" s="478"/>
+      <c r="E98" s="478"/>
+      <c r="F98" s="478"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21273,23 +21273,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="472" t="s">
+      <c r="B107" s="475" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="472"/>
-      <c r="D107" s="472"/>
-      <c r="E107" s="472"/>
-      <c r="F107" s="472"/>
+      <c r="C107" s="475"/>
+      <c r="D107" s="475"/>
+      <c r="E107" s="475"/>
+      <c r="F107" s="475"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="472" t="s">
+      <c r="B108" s="475" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="472"/>
-      <c r="D108" s="472"/>
-      <c r="E108" s="472"/>
-      <c r="F108" s="472"/>
+      <c r="C108" s="475"/>
+      <c r="D108" s="475"/>
+      <c r="E108" s="475"/>
+      <c r="F108" s="475"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21307,7 +21307,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-66.734264616514139</v>
+        <v>-67.35759470385328</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21321,7 +21321,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>-16.121645301288378</v>
+        <v>-16.272229212438813</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21333,13 +21333,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="472" t="s">
+      <c r="B114" s="475" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="472"/>
-      <c r="D114" s="472"/>
-      <c r="E114" s="472"/>
-      <c r="F114" s="472"/>
+      <c r="C114" s="475"/>
+      <c r="D114" s="475"/>
+      <c r="E114" s="475"/>
+      <c r="F114" s="475"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21384,7 +21384,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>249.35 HKD</v>
+        <v>251.68 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21407,7 +21407,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>192.7 HKD</v>
+        <v>194.5 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21429,7 +21429,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>161.89 HKD</v>
+        <v>163.4 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21451,7 +21451,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>148.27 HKD</v>
+        <v>149.66 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21473,7 +21473,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>124.22 HKD</v>
+        <v>125.38 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21495,7 +21495,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>175.32998482747979</v>
+        <v>176.96765110557101</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21503,13 +21503,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="476" t="s">
+      <c r="B127" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="476"/>
-      <c r="D127" s="476"/>
-      <c r="E127" s="476"/>
-      <c r="F127" s="476"/>
+      <c r="C127" s="473"/>
+      <c r="D127" s="473"/>
+      <c r="E127" s="473"/>
+      <c r="F127" s="473"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21522,22 +21522,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="477" t="s">
+      <c r="B131" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="477"/>
-      <c r="D131" s="477"/>
-      <c r="E131" s="477"/>
-      <c r="F131" s="477"/>
+      <c r="C131" s="474"/>
+      <c r="D131" s="474"/>
+      <c r="E131" s="474"/>
+      <c r="F131" s="474"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="472" t="s">
+      <c r="B132" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="472"/>
-      <c r="D132" s="472"/>
-      <c r="E132" s="472"/>
-      <c r="F132" s="472"/>
+      <c r="C132" s="475"/>
+      <c r="D132" s="475"/>
+      <c r="E132" s="475"/>
+      <c r="F132" s="475"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21602,11 +21602,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>80.797228031096694</v>
+        <v>81.551912951876062</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>87.220007063243216</v>
+        <v>87.974691984022584</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21623,11 +21623,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>101.27363744547573</v>
+        <v>102.21958186603383</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>108.65869130039019</v>
+        <v>109.60463572094829</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21663,11 +21663,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>125.66958883222379</v>
+        <v>126.84340315733554</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>134.13782580426846</v>
+        <v>135.31164012938021</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21684,11 +21684,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>142.12297592904494</v>
+        <v>143.45047279302966</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>151.29241297642221</v>
+        <v>152.61990984040693</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21706,13 +21706,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="478" t="s">
+      <c r="B149" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="472"/>
-      <c r="D149" s="472"/>
-      <c r="E149" s="472"/>
-      <c r="F149" s="472"/>
+      <c r="C149" s="475"/>
+      <c r="D149" s="475"/>
+      <c r="E149" s="475"/>
+      <c r="F149" s="475"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21720,13 +21720,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="474" t="s">
+      <c r="B152" s="477" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="474"/>
-      <c r="D152" s="474"/>
-      <c r="E152" s="474"/>
-      <c r="F152" s="474"/>
+      <c r="C152" s="477"/>
+      <c r="D152" s="477"/>
+      <c r="E152" s="477"/>
+      <c r="F152" s="477"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21763,22 +21763,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="475" t="s">
+      <c r="B161" s="472" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="475"/>
-      <c r="D161" s="475"/>
-      <c r="E161" s="475"/>
-      <c r="F161" s="475"/>
+      <c r="C161" s="472"/>
+      <c r="D161" s="472"/>
+      <c r="E161" s="472"/>
+      <c r="F161" s="472"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="475" t="s">
+      <c r="B162" s="472" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="475"/>
-      <c r="D162" s="475"/>
-      <c r="E162" s="475"/>
-      <c r="F162" s="475"/>
+      <c r="C162" s="472"/>
+      <c r="D162" s="472"/>
+      <c r="E162" s="472"/>
+      <c r="F162" s="472"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21802,15 +21802,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21825,12 +21822,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9618.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9618.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6C5CD7-499E-4B5F-9F10-8415C1A62134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A789E03-7B0B-40B5-93D3-5691AF64DB04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4995,30 +4995,30 @@
     <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5028,6 +5028,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5037,16 +5046,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5416,7 +5416,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>108.6</v>
+        <v>109.6</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5434,14 +5434,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>306034.8</v>
+        <v>308852.8</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.20453888280005972</v>
+        <v>0.19916464749874935</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5449,13 +5449,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="463" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="463"/>
-      <c r="D12" s="463"/>
-      <c r="E12" s="463"/>
-      <c r="F12" s="463"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5490,7 +5490,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1396112205505371</v>
+        <v>1.1348424911499022</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>176.96765110557101</v>
+        <v>176.2271258934897</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>87.974691984022584</v>
+        <v>87.633436125920596</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>109.60463572094829</v>
+        <v>109.17689552624429</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>135.31164012938021</v>
+        <v>134.78086098733144</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>152.61990984040693</v>
+        <v>152.01963803296314</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5633,22 +5633,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="463" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="463"/>
-      <c r="D29" s="463"/>
-      <c r="E29" s="463"/>
-      <c r="F29" s="463"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="467" t="s">
+      <c r="B30" s="463" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="467"/>
-      <c r="D30" s="467"/>
-      <c r="E30" s="467"/>
-      <c r="F30" s="467"/>
+      <c r="C30" s="463"/>
+      <c r="D30" s="463"/>
+      <c r="E30" s="463"/>
+      <c r="F30" s="463"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5660,13 +5660,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="464" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="464"/>
-      <c r="D33" s="464"/>
-      <c r="E33" s="464"/>
-      <c r="F33" s="464"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5686,13 +5686,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="464" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="464"/>
-      <c r="D36" s="464"/>
-      <c r="E36" s="464"/>
-      <c r="F36" s="464"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="464" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="464"/>
-      <c r="D40" s="464"/>
-      <c r="E40" s="464"/>
-      <c r="F40" s="464"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5743,13 +5743,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="464" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="464"/>
-      <c r="D43" s="464"/>
-      <c r="E43" s="464"/>
-      <c r="F43" s="464"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5813,13 +5813,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="464" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="464"/>
-      <c r="D51" s="464"/>
-      <c r="E51" s="464"/>
-      <c r="F51" s="464"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5835,7 +5835,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="464" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5857,22 +5857,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="463" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="463"/>
-      <c r="D57" s="463"/>
-      <c r="E57" s="463"/>
-      <c r="F57" s="463"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="463" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="463"/>
-      <c r="D58" s="463"/>
-      <c r="E58" s="463"/>
-      <c r="F58" s="463"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>-1.0618202305405061E-2</v>
+        <v>-1.0477294187879734E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.2320441988950274E-2</v>
+        <v>3.2025547445255473E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6007,13 +6007,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="463" t="s">
+      <c r="B73" s="461" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="463"/>
-      <c r="D73" s="463"/>
-      <c r="E73" s="463"/>
-      <c r="F73" s="463"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6032,13 +6032,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="463" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="463"/>
-      <c r="D77" s="463"/>
-      <c r="E77" s="463"/>
-      <c r="F77" s="463"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-43.110707929151495</v>
+        <v>-42.930310178869064</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>16.182958038974782</v>
+        <v>16.115240078324639</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>33.059320787725127</v>
+        <v>32.920983298445861</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.1315708975484151</v>
+        <v>6.1059131979014332</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6207,31 +6207,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="463" t="s">
+      <c r="B96" s="461" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="463"/>
-      <c r="D96" s="463"/>
-      <c r="E96" s="463"/>
-      <c r="F96" s="463"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="467" t="s">
+      <c r="B97" s="463" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="467"/>
-      <c r="D97" s="467"/>
-      <c r="E97" s="467"/>
-      <c r="F97" s="467"/>
+      <c r="C97" s="463"/>
+      <c r="D97" s="463"/>
+      <c r="E97" s="463"/>
+      <c r="F97" s="463"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="467" t="s">
+      <c r="B98" s="463" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="467"/>
-      <c r="D98" s="467"/>
-      <c r="E98" s="467"/>
-      <c r="F98" s="467"/>
+      <c r="C98" s="463"/>
+      <c r="D98" s="463"/>
+      <c r="E98" s="463"/>
+      <c r="F98" s="463"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6281,22 +6281,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="463" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="463"/>
-      <c r="D107" s="463"/>
-      <c r="E107" s="463"/>
-      <c r="F107" s="463"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="463" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="463"/>
-      <c r="D108" s="463"/>
-      <c r="E108" s="463"/>
-      <c r="F108" s="463"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-67.35759470385328</v>
+        <v>-67.075735297392598</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>-16.272229212438813</v>
+        <v>-16.204137694507164</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6330,13 +6330,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="463" t="s">
+      <c r="B114" s="461" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="463"/>
-      <c r="D114" s="463"/>
-      <c r="E114" s="463"/>
-      <c r="F114" s="463"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>251.68 HKD</v>
+        <v>250.62 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-9.5029895097454825E-2</v>
+        <v>-9.4963868364053863E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>194.5 HKD</v>
+        <v>193.69 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-1.2381285096508474E-2</v>
+        <v>-1.2303064291365599E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>163.4 HKD</v>
+        <v>162.71 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>4.7880473150503283E-2</v>
+        <v>4.7968454644473565E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>149.66 HKD</v>
+        <v>149.03 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.9681105218030582E-2</v>
+        <v>7.9774544939914205E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>125.38 HKD</v>
+        <v>124.86 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6467,17 +6467,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.14683198485275545</v>
+        <v>0.14693767215048675</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="464" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="464"/>
-      <c r="D124" s="464"/>
-      <c r="E124" s="464"/>
-      <c r="F124" s="464"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>176.96765110557101</v>
+        <v>176.2271258934897</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6512,22 +6512,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="468" t="s">
+      <c r="B131" s="464" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="468"/>
-      <c r="D131" s="468"/>
-      <c r="E131" s="468"/>
-      <c r="F131" s="468"/>
+      <c r="C131" s="464"/>
+      <c r="D131" s="464"/>
+      <c r="E131" s="464"/>
+      <c r="F131" s="464"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="463" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="463"/>
-      <c r="D132" s="463"/>
-      <c r="E132" s="463"/>
-      <c r="F132" s="463"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6592,11 +6592,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>81.551912951876062</v>
+        <v>81.210657093774074</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>87.974691984022584</v>
+        <v>87.633436125920596</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6613,11 +6613,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>102.21958186603383</v>
+        <v>101.79184167132983</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>109.60463572094829</v>
+        <v>109.17689552624429</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6660,11 +6660,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>126.84340315733554</v>
+        <v>126.31262401528677</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>135.31164012938021</v>
+        <v>134.78086098733144</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6681,11 +6681,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>143.45047279302966</v>
+        <v>142.85020098558587</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>152.61990984040693</v>
+        <v>152.01963803296314</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6703,13 +6703,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="462" t="s">
+      <c r="B149" s="468" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="463"/>
-      <c r="D149" s="463"/>
-      <c r="E149" s="463"/>
-      <c r="F149" s="463"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6746,13 +6746,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="464" t="s">
+      <c r="B158" s="462" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="464"/>
-      <c r="D158" s="464"/>
-      <c r="E158" s="464"/>
-      <c r="F158" s="464"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6760,22 +6760,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="461" t="s">
+      <c r="B161" s="467" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="461"/>
-      <c r="D161" s="461"/>
-      <c r="E161" s="461"/>
-      <c r="F161" s="461"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="461" t="s">
+      <c r="B162" s="467" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="461"/>
-      <c r="D162" s="461"/>
-      <c r="E162" s="461"/>
-      <c r="F162" s="461"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6799,6 +6799,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6815,18 +6827,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10113,11 +10113,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>91.007135937790238</v>
+        <v>90.626314481325053</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-67.35759470385328</v>
+        <v>-67.075735297392598</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10523,11 +10523,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-121485.97494434891</v>
+        <v>-120977.61408405303</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-43.110707929151495</v>
+        <v>-42.930310178869064</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10540,11 +10540,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>45603.575753830926</v>
+        <v>45412.746540718836</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>16.182958038974778</v>
+        <v>16.115240078324639</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10557,11 +10557,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>93161.165979809419</v>
+        <v>92771.330935020436</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>33.059320787725127</v>
+        <v>32.920983298445861</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10574,11 +10574,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>17278.766789291432</v>
+        <v>17206.463391686237</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.1315708975484107</v>
+        <v>6.1059131979014367</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14162,24 +14162,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.2320441988950274E-2</v>
+        <v>3.2025547445255473E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.2320441988950274E-2</v>
+        <v>3.2025547445255473E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>3.2320441988950274E-2</v>
+        <v>3.2025547445255473E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>2.4563535911602211E-2</v>
+        <v>2.4339416058394164E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>2.0038674033149174E-2</v>
+        <v>1.9855839416058396E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -15325,34 +15325,34 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>-1.1531367703669897</v>
+        <v>-1.1483114429916188</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>-1.0021137702357101</v>
+        <v>-0.99792040208284516</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>11.655739744041014</v>
+        <v>11.606966032619759</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>7.5405219369713681</v>
+        <v>7.5089684492480755</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>3.9902568889894074</v>
+        <v>3.9735595671313289</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>5.0954937469612376E-2</v>
+        <v>5.0741715360144671E-2</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>5.0057159999909677</v>
+        <v>4.9847694660942121</v>
       </c>
       <c r="M123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15382,34 +15382,34 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>-1.0618202305405061E-2</v>
+        <v>-1.0477294187879734E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>-9.2275669450802046E-3</v>
+        <v>-9.105113157690194E-3</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.1073272536283703</v>
+        <v>0.10590297475018029</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>6.9433903655353305E-2</v>
+        <v>6.8512485850803606E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>3.6742696952020329E-2</v>
+        <v>3.6255105539519425E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>4.691983192413663E-4</v>
+        <v>4.6297185547577259E-4</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>4.609314917118755E-2</v>
+        <v>4.5481473230786607E-2</v>
       </c>
       <c r="M124" s="74" t="str">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
@@ -15439,27 +15439,27 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5618851189472563E-2</v>
+        <v>7.4928898167670815E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14593111633056111</v>
+        <v>0.14459962804287349</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5994625447824884E-2</v>
+        <v>7.5301243828775385E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1666333371237518E-2</v>
+        <v>3.1377406971864912E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-1.4596379235302652E-2</v>
+        <v>-1.4463200592644781E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16121369203763755</v>
+        <v>0.15974276419057881</v>
       </c>
       <c r="M125" s="22" t="str">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.1315708975484151</v>
+        <v>6.1059131979014332</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16389,7 +16389,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1396112205505371</v>
+        <v>1.1348424911499022</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>-45855.141920652575</v>
+        <v>-45663.260023121184</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16436,7 +16436,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>-16.272229212438813</v>
+        <v>-16.204137694507164</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>154.82169297183913</v>
+        <v>154.17383803164802</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18747,23 +18747,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>-16.272229212438813</v>
+        <v>-16.204137694507164</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>-16.272229212438813</v>
+        <v>-16.204137694507164</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>-16.272229212438813</v>
+        <v>-16.204137694507164</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>-16.272229212438813</v>
+        <v>-16.204137694507164</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>-16.272229212438813</v>
+        <v>-16.204137694507164</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18778,23 +18778,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>158.89502980526586</v>
+        <v>158.23012989327563</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>161.95029898342025</v>
+        <v>161.27261422718317</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>163.47793357249742</v>
+        <v>162.7938563941369</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>166.53320275065175</v>
+        <v>165.83634072804438</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>171.11610651788325</v>
+        <v>170.40006722890556</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18809,23 +18809,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>158.69097055378953</v>
+        <v>158.02692453243711</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>164.87861960736498</v>
+        <v>164.1886812260301</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>168.0185685615123</v>
+        <v>167.31549099145747</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>174.39071532452604</v>
+        <v>173.66097335957411</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>184.17955760584448</v>
+        <v>183.40885400490362</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18840,23 +18840,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>158.38719977500475</v>
+        <v>157.7244248894728</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>167.5478200078106</v>
+        <v>166.84671229592132</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>172.26236071316902</v>
+        <v>171.54152489710992</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>181.96420394770473</v>
+        <v>181.20277054517177</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>197.21177529677789</v>
+        <v>196.38653808074309</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18871,23 +18871,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>158.20979647771654</v>
+        <v>157.54776394036818</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>170.19646875642823</v>
+        <v>169.48427771284503</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>176.45026202632934</v>
+        <v>175.71190184076696</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>189.49548892241918</v>
+        <v>188.70254068444424</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>210.4585708251638</v>
+        <v>209.57790208813196</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18902,23 +18902,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>146.6272529416141</v>
+        <v>146.01368782446897</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>160.83707867973169</v>
+        <v>160.16405221949577</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>168.35977330043841</v>
+        <v>167.65526795129472</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>184.28138629037937</v>
+        <v>183.51025658496269</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>210.48105789697436</v>
+        <v>209.60029506227261</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18933,23 +18933,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>146.47302357116885</v>
+        <v>145.86010383037666</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>163.23276586514089</v>
+        <v>162.54971459669864</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>172.22234262195414</v>
+        <v>171.50167426251946</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>191.49998795815793</v>
+        <v>190.69865184779906</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>223.91377108962971</v>
+        <v>222.97679875718256</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18965,23 +18965,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>135.68387494017108</v>
+        <v>135.11610264032774</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>154.21425634955634</v>
+        <v>153.56894324190202</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>164.2993938258403</v>
+        <v>163.61187922812925</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>186.24383289879498</v>
+        <v>185.46449129034508</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>224.030350470982</v>
+        <v>223.09289030942847</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18996,23 +18996,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>135.54979232123705</v>
+        <v>134.98258109320091</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>156.38114129167221</v>
+        <v>155.72676080406856</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>167.8619041735964</v>
+        <v>167.15948216928123</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>193.16273322098476</v>
+        <v>192.35443931477619</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>237.65159066673252</v>
+        <v>236.65713211184692</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19028,23 +19028,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>125.49904393790359</v>
+        <v>124.97389029797266</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>147.69802598597775</v>
+        <v>147.07998019436573</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>160.11174664466682</v>
+        <v>159.44175535303793</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>187.87169539387017</v>
+        <v>187.08554195731568</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>237.86423871645616</v>
+        <v>236.86889033090867</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19060,23 +19060,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>125.38247633052566</v>
+        <v>124.85781047043265</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>149.65796064729986</v>
+        <v>149.0317134639551</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>163.39750773306295</v>
+        <v>162.71376709847996</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>194.50333734775154</v>
+        <v>193.68943365269689</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>251.67665187597896</v>
+        <v>250.62350512942928</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19092,23 +19092,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>98.977978289957122</v>
+        <v>98.563802660079858</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>128.93112204125316</v>
+        <v>128.39160679144899</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>147.0456087048328</v>
+        <v>146.43029296836065</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>190.93528713474228</v>
+        <v>190.13631402798555</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>281.12037465725109</v>
+        <v>279.94401997455685</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19124,23 +19124,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>84.146658069669286</v>
+        <v>83.79454444085809</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>118.35745256567438</v>
+        <v>117.86218307933015</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>140.32364138239822</v>
+        <v>139.73645387301136</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>196.99796203381749</v>
+        <v>196.17361952430622</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>326.27728256125982</v>
+        <v>324.91196775735898</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19156,23 +19156,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>65.637808376327868</v>
+        <v>65.36314545536591</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>100.77133272079497</v>
+        <v>100.3496527579962</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>124.78518193204502</v>
+        <v>124.26301546411972</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>190.97264920478281</v>
+        <v>190.17351975558341</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>359.35429319609256</v>
+        <v>357.85056687933979</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19188,23 +19188,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>55.255577546139918</v>
+        <v>55.024359309216941</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>91.40889523581599</v>
+        <v>91.026392608314652</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>117.51293782974081</v>
+        <v>117.02120223476049</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>193.89261614050579</v>
+        <v>193.08126802240938</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>408.79344865610511</v>
+        <v>407.08284305461626</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19251,7 +19251,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>251.67665187597896</v>
+        <v>250.62350512942928</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19279,7 +19279,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>194.50333734775154</v>
+        <v>193.68943365269689</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19307,7 +19307,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>163.39750773306295</v>
+        <v>162.71376709847996</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19335,7 +19335,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>149.65796064729986</v>
+        <v>149.0317134639551</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>125.38247633052566</v>
+        <v>124.85781047043265</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19723,7 +19723,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>194.50333734775154</v>
+        <v>193.68943365269689</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>163.39750773306295</v>
+        <v>162.71376709847996</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19770,7 +19770,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>149.65796064729986</v>
+        <v>149.0317134639551</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19786,7 +19786,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>166.18378688455988</v>
+        <v>165.48838700069211</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19833,7 +19833,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>251.67665187597896</v>
+        <v>250.62350512942928</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>125.38247633052566</v>
+        <v>124.85781047043265</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>108.6</v>
+        <v>109.6</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19912,7 +19912,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.20453888280005972</v>
+        <v>0.19916464749874935</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19921,7 +19921,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>-16.272229212438813</v>
+        <v>-16.204137694507164</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>176.96765110557101</v>
+        <v>176.2271258934897</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20044,7 +20044,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>154.82169297183913</v>
+        <v>154.17383803164802</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20111,7 +20111,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>3.4647975826331043E-2</v>
+        <v>3.4647975826331091E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20189,11 +20189,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>81.551912951876062</v>
+        <v>81.210657093774074</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>87.974691984022584</v>
+        <v>87.633436125920596</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20201,7 +20201,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.50287698664463365</v>
+        <v>0.50272447739466875</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20214,11 +20214,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>102.21958186603383</v>
+        <v>101.79184167132983</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>109.60463572094829</v>
+        <v>109.17689552624429</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20226,7 +20226,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.38065157651008741</v>
+        <v>0.38047621799024312</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20260,11 +20260,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>126.84340315733554</v>
+        <v>126.31262401528677</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>135.31164012938021</v>
+        <v>134.78086098733144</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20272,7 +20272,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.23538771473742781</v>
+        <v>0.23518663597344291</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20285,11 +20285,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>143.45047279302966</v>
+        <v>142.85020098558587</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>152.61990984040693</v>
+        <v>152.01963803296314</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20297,7 +20297,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.13758300521624311</v>
+        <v>0.13736527641696528</v>
       </c>
     </row>
   </sheetData>
@@ -20408,7 +20408,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>108.6</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20426,14 +20426,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>306034.8</v>
+        <v>308852.8</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.20453888280005972</v>
+        <v>0.19916464749874935</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20441,13 +20441,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="475" t="s">
+      <c r="B12" s="472" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="475"/>
-      <c r="D12" s="475"/>
-      <c r="E12" s="475"/>
-      <c r="F12" s="475"/>
+      <c r="C12" s="472"/>
+      <c r="D12" s="472"/>
+      <c r="E12" s="472"/>
+      <c r="F12" s="472"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20485,7 +20485,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1396112205505371</v>
+        <v>1.1348424911499022</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20511,7 +20511,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>176.96765110557101</v>
+        <v>176.2271258934897</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20563,7 +20563,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>87.974691984022584</v>
+        <v>87.633436125920596</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20579,7 +20579,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>109.60463572094829</v>
+        <v>109.17689552624429</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20595,7 +20595,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>135.31164012938021</v>
+        <v>134.78086098733144</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20611,7 +20611,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>152.61990984040693</v>
+        <v>152.01963803296314</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20632,22 +20632,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="475" t="s">
+      <c r="B29" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="475"/>
-      <c r="D29" s="475"/>
-      <c r="E29" s="475"/>
-      <c r="F29" s="475"/>
+      <c r="C29" s="472"/>
+      <c r="D29" s="472"/>
+      <c r="E29" s="472"/>
+      <c r="F29" s="472"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="478" t="s">
+      <c r="B30" s="473" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="478"/>
-      <c r="D30" s="478"/>
-      <c r="E30" s="478"/>
-      <c r="F30" s="478"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20837,10 +20837,10 @@
       <c r="B54" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="477"/>
-      <c r="D54" s="477"/>
-      <c r="E54" s="477"/>
-      <c r="F54" s="477"/>
+      <c r="C54" s="474"/>
+      <c r="D54" s="474"/>
+      <c r="E54" s="474"/>
+      <c r="F54" s="474"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20856,22 +20856,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="475" t="s">
+      <c r="B57" s="472" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="475"/>
-      <c r="D57" s="475"/>
-      <c r="E57" s="475"/>
-      <c r="F57" s="475"/>
+      <c r="C57" s="472"/>
+      <c r="D57" s="472"/>
+      <c r="E57" s="472"/>
+      <c r="F57" s="472"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="475" t="s">
+      <c r="B58" s="472" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="475"/>
-      <c r="D58" s="475"/>
-      <c r="E58" s="475"/>
-      <c r="F58" s="475"/>
+      <c r="C58" s="472"/>
+      <c r="D58" s="472"/>
+      <c r="E58" s="472"/>
+      <c r="F58" s="472"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20905,7 +20905,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>-1.0618202305405061E-2</v>
+        <v>-1.0477294187879734E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20915,7 +20915,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.2320441988950274E-2</v>
+        <v>3.2025547445255473E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21006,22 +21006,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="475" t="s">
+      <c r="B73" s="472" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="475"/>
-      <c r="D73" s="475"/>
-      <c r="E73" s="475"/>
-      <c r="F73" s="475"/>
+      <c r="C73" s="472"/>
+      <c r="D73" s="472"/>
+      <c r="E73" s="472"/>
+      <c r="F73" s="472"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="478" t="s">
+      <c r="B74" s="473" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="478"/>
-      <c r="D74" s="478"/>
-      <c r="E74" s="478"/>
-      <c r="F74" s="478"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21029,13 +21029,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="475" t="s">
+      <c r="B77" s="472" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="475"/>
-      <c r="D77" s="475"/>
-      <c r="E77" s="475"/>
-      <c r="F77" s="475"/>
+      <c r="C77" s="472"/>
+      <c r="D77" s="472"/>
+      <c r="E77" s="472"/>
+      <c r="F77" s="472"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21056,7 +21056,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-43.110707929151495</v>
+        <v>-42.930310178869064</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21118,7 +21118,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>16.182958038974782</v>
+        <v>16.115240078324639</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21149,7 +21149,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>33.059320787725127</v>
+        <v>32.920983298445861</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21162,7 +21162,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>6.1315708975484151</v>
+        <v>6.1059131979014332</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21184,33 +21184,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="475" t="s">
+      <c r="B96" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="475"/>
-      <c r="D96" s="475"/>
-      <c r="E96" s="475"/>
-      <c r="F96" s="475"/>
+      <c r="C96" s="472"/>
+      <c r="D96" s="472"/>
+      <c r="E96" s="472"/>
+      <c r="F96" s="472"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="478" t="s">
+      <c r="B97" s="473" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="478"/>
-      <c r="D97" s="478"/>
-      <c r="E97" s="478"/>
-      <c r="F97" s="478"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="478" t="s">
+      <c r="B98" s="473" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="478"/>
-      <c r="D98" s="478"/>
-      <c r="E98" s="478"/>
-      <c r="F98" s="478"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21273,23 +21273,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="475" t="s">
+      <c r="B107" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="475"/>
-      <c r="D107" s="475"/>
-      <c r="E107" s="475"/>
-      <c r="F107" s="475"/>
+      <c r="C107" s="472"/>
+      <c r="D107" s="472"/>
+      <c r="E107" s="472"/>
+      <c r="F107" s="472"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="475" t="s">
+      <c r="B108" s="472" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="475"/>
-      <c r="D108" s="475"/>
-      <c r="E108" s="475"/>
-      <c r="F108" s="475"/>
+      <c r="C108" s="472"/>
+      <c r="D108" s="472"/>
+      <c r="E108" s="472"/>
+      <c r="F108" s="472"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21307,7 +21307,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-67.35759470385328</v>
+        <v>-67.075735297392598</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21321,7 +21321,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>-16.272229212438813</v>
+        <v>-16.204137694507164</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21333,13 +21333,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="475" t="s">
+      <c r="B114" s="472" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="475"/>
-      <c r="D114" s="475"/>
-      <c r="E114" s="475"/>
-      <c r="F114" s="475"/>
+      <c r="C114" s="472"/>
+      <c r="D114" s="472"/>
+      <c r="E114" s="472"/>
+      <c r="F114" s="472"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21384,7 +21384,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>251.68 HKD</v>
+        <v>250.62 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21407,7 +21407,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>194.5 HKD</v>
+        <v>193.69 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21429,7 +21429,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>163.4 HKD</v>
+        <v>162.71 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21451,7 +21451,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>149.66 HKD</v>
+        <v>149.03 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21473,7 +21473,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>125.38 HKD</v>
+        <v>124.86 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21495,7 +21495,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>176.96765110557101</v>
+        <v>176.2271258934897</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21503,13 +21503,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="473" t="s">
+      <c r="B127" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="473"/>
-      <c r="D127" s="473"/>
-      <c r="E127" s="473"/>
-      <c r="F127" s="473"/>
+      <c r="C127" s="476"/>
+      <c r="D127" s="476"/>
+      <c r="E127" s="476"/>
+      <c r="F127" s="476"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21522,22 +21522,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="474" t="s">
+      <c r="B131" s="477" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="474"/>
-      <c r="D131" s="474"/>
-      <c r="E131" s="474"/>
-      <c r="F131" s="474"/>
+      <c r="C131" s="477"/>
+      <c r="D131" s="477"/>
+      <c r="E131" s="477"/>
+      <c r="F131" s="477"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="475" t="s">
+      <c r="B132" s="472" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="475"/>
-      <c r="D132" s="475"/>
-      <c r="E132" s="475"/>
-      <c r="F132" s="475"/>
+      <c r="C132" s="472"/>
+      <c r="D132" s="472"/>
+      <c r="E132" s="472"/>
+      <c r="F132" s="472"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21602,11 +21602,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>81.551912951876062</v>
+        <v>81.210657093774074</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>87.974691984022584</v>
+        <v>87.633436125920596</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21623,11 +21623,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>102.21958186603383</v>
+        <v>101.79184167132983</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>109.60463572094829</v>
+        <v>109.17689552624429</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21663,11 +21663,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>126.84340315733554</v>
+        <v>126.31262401528677</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>135.31164012938021</v>
+        <v>134.78086098733144</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21684,11 +21684,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>143.45047279302966</v>
+        <v>142.85020098558587</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>152.61990984040693</v>
+        <v>152.01963803296314</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21706,13 +21706,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="476" t="s">
+      <c r="B149" s="478" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="475"/>
-      <c r="D149" s="475"/>
-      <c r="E149" s="475"/>
-      <c r="F149" s="475"/>
+      <c r="C149" s="472"/>
+      <c r="D149" s="472"/>
+      <c r="E149" s="472"/>
+      <c r="F149" s="472"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21720,13 +21720,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="477" t="s">
+      <c r="B152" s="474" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="477"/>
-      <c r="D152" s="477"/>
-      <c r="E152" s="477"/>
-      <c r="F152" s="477"/>
+      <c r="C152" s="474"/>
+      <c r="D152" s="474"/>
+      <c r="E152" s="474"/>
+      <c r="F152" s="474"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21763,22 +21763,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="472" t="s">
+      <c r="B161" s="475" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="472"/>
-      <c r="D161" s="472"/>
-      <c r="E161" s="472"/>
-      <c r="F161" s="472"/>
+      <c r="C161" s="475"/>
+      <c r="D161" s="475"/>
+      <c r="E161" s="475"/>
+      <c r="F161" s="475"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="472" t="s">
+      <c r="B162" s="475" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="472"/>
-      <c r="D162" s="472"/>
-      <c r="E162" s="472"/>
-      <c r="F162" s="472"/>
+      <c r="C162" s="475"/>
+      <c r="D162" s="475"/>
+      <c r="E162" s="475"/>
+      <c r="F162" s="475"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21802,12 +21802,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21822,15 +21825,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9618.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9618.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A789E03-7B0B-40B5-93D3-5691AF64DB04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B855A6CF-B487-4830-AE70-C8CB3FA73A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4995,30 +4995,30 @@
     <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5028,25 +5028,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5416,7 +5416,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>109.6</v>
+        <v>113.5</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5434,14 +5434,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>308852.8</v>
+        <v>319843</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.19916464749874935</v>
+        <v>0.18597230762732159</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5449,13 +5449,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+      <c r="B12" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="C12" s="463"/>
+      <c r="D12" s="463"/>
+      <c r="E12" s="463"/>
+      <c r="F12" s="463"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5490,7 +5490,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1348424911499022</v>
+        <v>1.138018667316437</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>176.2271258934897</v>
+        <v>176.72034711275569</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5564,13 +5564,13 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>87.633436125920596</v>
+        <v>86.811673697203304</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5579,13 +5579,13 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>109.17689552624429</v>
+        <v>109.66246939395583</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
       </c>
       <c r="E23" s="443">
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>134.78086098733144</v>
+        <v>135.13438242229577</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>152.01963803296314</v>
+        <v>152.41944453236147</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5633,22 +5633,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+      <c r="B29" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="463"/>
+      <c r="D29" s="463"/>
+      <c r="E29" s="463"/>
+      <c r="F29" s="463"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="463" t="s">
+      <c r="B30" s="467" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="463"/>
-      <c r="D30" s="463"/>
-      <c r="E30" s="463"/>
-      <c r="F30" s="463"/>
+      <c r="C30" s="467"/>
+      <c r="D30" s="467"/>
+      <c r="E30" s="467"/>
+      <c r="F30" s="467"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5660,13 +5660,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+      <c r="B33" s="464" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="C33" s="464"/>
+      <c r="D33" s="464"/>
+      <c r="E33" s="464"/>
+      <c r="F33" s="464"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5686,13 +5686,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+      <c r="B36" s="464" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="C36" s="464"/>
+      <c r="D36" s="464"/>
+      <c r="E36" s="464"/>
+      <c r="F36" s="464"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+      <c r="B40" s="464" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="C40" s="464"/>
+      <c r="D40" s="464"/>
+      <c r="E40" s="464"/>
+      <c r="F40" s="464"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5743,13 +5743,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+      <c r="B43" s="464" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="C43" s="464"/>
+      <c r="D43" s="464"/>
+      <c r="E43" s="464"/>
+      <c r="F43" s="464"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5813,13 +5813,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+      <c r="B51" s="464" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="C51" s="464"/>
+      <c r="D51" s="464"/>
+      <c r="E51" s="464"/>
+      <c r="F51" s="464"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5835,7 +5835,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+      <c r="B54" s="464" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5857,22 +5857,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+      <c r="B57" s="463" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="C57" s="463"/>
+      <c r="D57" s="463"/>
+      <c r="E57" s="463"/>
+      <c r="F57" s="463"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="B58" s="463" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="C58" s="463"/>
+      <c r="D58" s="463"/>
+      <c r="E58" s="463"/>
+      <c r="F58" s="463"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>-1.0477294187879734E-2</v>
+        <v>-1.0145597496135292E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.2025547445255473E-2</v>
+        <v>3.0925110132158588E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6007,13 +6007,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
+      <c r="B73" s="463" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="C73" s="463"/>
+      <c r="D73" s="463"/>
+      <c r="E73" s="463"/>
+      <c r="F73" s="463"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6032,13 +6032,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="463" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="C77" s="463"/>
+      <c r="D77" s="463"/>
+      <c r="E77" s="463"/>
+      <c r="F77" s="463"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-42.930310178869064</v>
+        <v>-43.050462736669317</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>16.115240078324639</v>
+        <v>16.160343114079755</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>32.920983298445861</v>
+        <v>33.013121937373157</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.1059131979014332</v>
+        <v>6.1230023147835952</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6207,31 +6207,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
+      <c r="B96" s="463" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="C96" s="463"/>
+      <c r="D96" s="463"/>
+      <c r="E96" s="463"/>
+      <c r="F96" s="463"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="463" t="s">
+      <c r="B97" s="467" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="463"/>
-      <c r="D97" s="463"/>
-      <c r="E97" s="463"/>
-      <c r="F97" s="463"/>
+      <c r="C97" s="467"/>
+      <c r="D97" s="467"/>
+      <c r="E97" s="467"/>
+      <c r="F97" s="467"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="463" t="s">
+      <c r="B98" s="467" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="463"/>
-      <c r="D98" s="463"/>
-      <c r="E98" s="463"/>
-      <c r="F98" s="463"/>
+      <c r="C98" s="467"/>
+      <c r="D98" s="467"/>
+      <c r="E98" s="467"/>
+      <c r="F98" s="467"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6281,22 +6281,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="463" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
+      <c r="C107" s="463"/>
+      <c r="D107" s="463"/>
+      <c r="E107" s="463"/>
+      <c r="F107" s="463"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="B108" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="463"/>
+      <c r="D108" s="463"/>
+      <c r="E108" s="463"/>
+      <c r="F108" s="463"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-67.075735297392598</v>
+        <v>-67.263465624258046</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>-16.204137694507164</v>
+        <v>-16.249489535265599</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6330,13 +6330,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
+      <c r="B114" s="463" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="C114" s="463"/>
+      <c r="D114" s="463"/>
+      <c r="E114" s="463"/>
+      <c r="F114" s="463"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>250.62 HKD</v>
+        <v>251.32 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-9.4963868364053863E-2</v>
+        <v>-9.5007906429065161E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>193.69 HKD</v>
+        <v>194.23 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-1.2303064291365599E-2</v>
+        <v>-1.2355235545605961E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>162.71 HKD</v>
+        <v>163.17 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>4.7968454644473565E-2</v>
+        <v>4.7909773202239908E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>149.03 HKD</v>
+        <v>149.45 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.9774544939914205E-2</v>
+        <v>7.9712222961475676E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>124.86 HKD</v>
+        <v>125.21 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6467,17 +6467,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.14693767215048675</v>
+        <v>0.14686718125408987</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+      <c r="B124" s="464" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="C124" s="464"/>
+      <c r="D124" s="464"/>
+      <c r="E124" s="464"/>
+      <c r="F124" s="464"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>176.2271258934897</v>
+        <v>176.72034711275569</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6512,22 +6512,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="464" t="s">
+      <c r="B131" s="468" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="464"/>
-      <c r="D131" s="464"/>
-      <c r="E131" s="464"/>
-      <c r="F131" s="464"/>
+      <c r="C131" s="468"/>
+      <c r="D131" s="468"/>
+      <c r="E131" s="468"/>
+      <c r="F131" s="468"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="B132" s="463" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="C132" s="463"/>
+      <c r="D132" s="463"/>
+      <c r="E132" s="463"/>
+      <c r="F132" s="463"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6588,19 +6588,19 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>6.4227790321465186</v>
+        <v>6.3745562130177529</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>81.210657093774074</v>
+        <v>80.437117484185549</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>87.633436125920596</v>
+        <v>86.811673697203304</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6609,19 +6609,19 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>7.3850538549144646</v>
+        <v>7.3937499999999998</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>101.79184167132983</v>
+        <v>102.26871939395583</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>109.17689552624429</v>
+        <v>109.66246939395583</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6660,11 +6660,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>126.31262401528677</v>
+        <v>126.66614545025111</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>134.78086098733144</v>
+        <v>135.13438242229577</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6681,11 +6681,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>142.85020098558587</v>
+        <v>143.2500074849842</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>152.01963803296314</v>
+        <v>152.41944453236147</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6703,13 +6703,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="468" t="s">
+      <c r="B149" s="462" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="C149" s="463"/>
+      <c r="D149" s="463"/>
+      <c r="E149" s="463"/>
+      <c r="F149" s="463"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6746,13 +6746,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
+      <c r="B158" s="464" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="C158" s="464"/>
+      <c r="D158" s="464"/>
+      <c r="E158" s="464"/>
+      <c r="F158" s="464"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6760,22 +6760,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="461" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="461"/>
+      <c r="D161" s="461"/>
+      <c r="E161" s="461"/>
+      <c r="F161" s="461"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="461" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="461"/>
+      <c r="D162" s="461"/>
+      <c r="E162" s="461"/>
+      <c r="F162" s="461"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6799,18 +6799,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6827,6 +6815,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10113,11 +10113,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>90.626314481325053</v>
+        <v>90.879957733460259</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-67.075735297392598</v>
+        <v>-67.263465624258046</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10523,11 +10523,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-120977.61408405303</v>
+        <v>-121316.20399193413</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-42.930310178869064</v>
+        <v>-43.050462736669317</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10540,11 +10540,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>45412.746540718836</v>
+        <v>45539.846895476752</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>16.115240078324639</v>
+        <v>16.160343114079755</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10557,11 +10557,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>92771.330935020436</v>
+        <v>93030.977619517551</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>32.920983298445861</v>
+        <v>33.013121937373157</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10574,11 +10574,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>17206.463391686237</v>
+        <v>17254.620523060163</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.1059131979014367</v>
+        <v>6.1230023147835944</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14162,24 +14162,24 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.2025547445255473E-2</v>
+        <v>3.0925110132158588E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.2025547445255473E-2</v>
+        <v>3.0925110132158588E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>3.2025547445255473E-2</v>
+        <v>3.0925110132158588E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>2.4339416058394164E-2</v>
+        <v>2.3503083700440529E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>1.9855839416058396E-2</v>
+        <v>1.9173568281938329E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
@@ -15325,34 +15325,34 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>-1.1483114429916188</v>
+        <v>-1.1515253158113556</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>-0.99792040208284516</v>
+        <v>-1.0007133632399328</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>11.606966032619759</v>
+        <v>11.63945139439118</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>7.5089684492480755</v>
+        <v>7.52998441120734</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>3.9735595671313289</v>
+        <v>3.9846806921260765</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>5.0741715360144671E-2</v>
+        <v>5.0883730334233872E-2</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>4.9847694660942121</v>
+        <v>4.9987207466440227</v>
       </c>
       <c r="M123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15382,34 +15382,34 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>-1.0477294187879734E-2</v>
+        <v>-1.0145597496135292E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>-9.105113157690194E-3</v>
+        <v>-8.8168578259024914E-3</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.10590297475018029</v>
+        <v>0.10255023254970203</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>6.8512485850803606E-2</v>
+        <v>6.6343474988610929E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>3.6255105539519425E-2</v>
+        <v>3.5107318873357503E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>4.6297185547577259E-4</v>
+        <v>4.4831480470690637E-4</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>4.5481473230786607E-2</v>
+        <v>4.4041592481445131E-2</v>
       </c>
       <c r="M124" s="74" t="str">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
@@ -15439,27 +15439,27 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4928898167670815E-2</v>
+        <v>7.2354248803319129E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14459962804287349</v>
+        <v>0.1396310064625457</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5301243828775385E-2</v>
+        <v>7.2713800208227167E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1377406971864912E-2</v>
+        <v>3.0299240564902154E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-1.4463200592644781E-2</v>
+        <v>-1.3966227180210291E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15974276419057881</v>
+        <v>0.1542538057734576</v>
       </c>
       <c r="M125" s="22" t="str">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.1059131979014332</v>
+        <v>6.1230023147835952</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16389,7 +16389,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1348424911499022</v>
+        <v>1.138018667316437</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>-45663.260023121184</v>
+        <v>-45791.061510378466</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16436,7 +16436,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>-16.204137694507164</v>
+        <v>-16.249489535265599</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>154.17383803164802</v>
+        <v>154.60533691689253</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18747,23 +18747,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>-16.204137694507164</v>
+        <v>-16.249489535265599</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>-16.204137694507164</v>
+        <v>-16.249489535265599</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>-16.204137694507164</v>
+        <v>-16.249489535265599</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>-16.204137694507164</v>
+        <v>-16.249489535265599</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>-16.204137694507164</v>
+        <v>-16.249489535265599</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18778,23 +18778,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>158.23012989327563</v>
+        <v>158.67298145312998</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>161.27261422718317</v>
+        <v>161.72398103589694</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>162.7938563941369</v>
+        <v>163.24948082728042</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>165.83634072804438</v>
+        <v>166.30048041004733</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>170.40006722890556</v>
+        <v>170.87697978419769</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18809,23 +18809,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>158.02692453243711</v>
+        <v>158.46920736488741</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>164.1886812260301</v>
+        <v>164.64820946910501</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>167.31549099145747</v>
+        <v>167.78377049184934</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>173.66097335957411</v>
+        <v>174.14701247860904</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>183.40885400490362</v>
+        <v>183.9221753119262</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18840,23 +18840,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>157.7244248894728</v>
+        <v>158.16586109151942</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>166.84671229592132</v>
+        <v>167.31367978717381</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>171.54152489710992</v>
+        <v>172.02163214300373</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>181.20277054517177</v>
+        <v>181.70991750662583</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>196.38653808074309</v>
+        <v>196.93618108983441</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18871,23 +18871,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>157.54776394036818</v>
+        <v>157.98870570701916</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>169.48427771284503</v>
+        <v>169.95862717338423</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>175.71190184076696</v>
+        <v>176.20368106048724</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>188.70254068444424</v>
+        <v>189.23067786379781</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>209.57790208813196</v>
+        <v>210.16446484273078</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18902,23 +18902,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>146.01368782446897</v>
+        <v>146.42234823229879</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>160.16405221949577</v>
+        <v>160.61231640537389</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>167.65526795129472</v>
+        <v>168.12449841315495</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>183.51025658496269</v>
+        <v>184.02386169565011</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>209.60029506227261</v>
+        <v>210.18692048991312</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18933,23 +18933,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>145.86010383037666</v>
+        <v>146.26833439016553</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>162.54971459669864</v>
+        <v>163.00465573029678</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>171.50167426251946</v>
+        <v>171.98166997519448</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>190.69865184779906</v>
+        <v>191.2323757061431</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>222.97679875718256</v>
+        <v>223.60086209586242</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18965,23 +18965,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>135.11610264032774</v>
+        <v>135.49426308837937</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>153.56894324190202</v>
+        <v>153.99874915880122</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>163.61187922812925</v>
+        <v>164.0697931284449</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>185.46449129034508</v>
+        <v>185.98356587696725</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>223.09289030942847</v>
+        <v>223.71727856299674</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18996,23 +18996,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>134.98258109320091</v>
+        <v>135.36036784361696</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>155.72676080406856</v>
+        <v>156.16260598083522</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>167.15948216928123</v>
+        <v>167.62732503506817</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>192.35443931477619</v>
+        <v>192.8927973604462</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>236.65713211184692</v>
+        <v>237.31948371439617</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19028,23 +19028,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>124.97389029797266</v>
+        <v>125.32366490977921</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>147.07998019436573</v>
+        <v>147.49162492155111</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>159.44175535303793</v>
+        <v>159.88799798781068</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>187.08554195731568</v>
+        <v>187.60915351055067</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>236.86889033090867</v>
+        <v>237.53183459844331</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19060,23 +19060,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>124.85781047043265</v>
+        <v>125.20726020016569</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>149.0317134639551</v>
+        <v>149.44882066610299</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>162.71376709847996</v>
+        <v>163.16916737918464</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>193.68943365269689</v>
+        <v>194.23152805581881</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>250.62350512942928</v>
+        <v>251.32494555836396</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19092,23 +19092,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>98.563802660079858</v>
+        <v>98.83966120726447</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>128.39160679144899</v>
+        <v>128.75094684494036</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>146.43029296836065</v>
+        <v>146.84011936295886</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>190.13631402798555</v>
+        <v>190.66846402564428</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>279.94401997455685</v>
+        <v>280.72752211793022</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19124,23 +19124,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>83.79454444085809</v>
+        <v>84.029067061410501</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>117.86218307933015</v>
+        <v>118.19205357655925</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>139.73645387301136</v>
+        <v>140.12754567460388</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>196.17361952430622</v>
+        <v>196.72266662088137</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>324.91196775735898</v>
+        <v>325.82132536095662</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19156,23 +19156,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>65.36314545536591</v>
+        <v>65.546082617469096</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>100.3496527579962</v>
+        <v>100.63050950939174</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>124.26301546411972</v>
+        <v>124.61080049259444</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>190.17351975558341</v>
+        <v>190.70577388394415</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>357.85056687933979</v>
+        <v>358.85211242470569</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19188,23 +19188,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>55.024359309216941</v>
+        <v>55.178360467950156</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>91.026392608314652</v>
+        <v>91.281155591709123</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>117.02120223476049</v>
+        <v>117.34871901036226</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>193.08126802240938</v>
+        <v>193.62166030281799</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>407.08284305461626</v>
+        <v>408.22217898360952</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19251,7 +19251,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>250.62350512942928</v>
+        <v>251.32494555836396</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19279,7 +19279,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>193.68943365269689</v>
+        <v>194.23152805581881</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19307,7 +19307,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>162.71376709847996</v>
+        <v>163.16916737918464</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19335,7 +19335,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>149.0317134639551</v>
+        <v>149.44882066610299</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>124.85781047043265</v>
+        <v>125.20726020016569</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19723,7 +19723,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>193.68943365269689</v>
+        <v>194.23152805581881</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>162.71376709847996</v>
+        <v>163.16916737918464</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19770,7 +19770,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>149.0317134639551</v>
+        <v>149.44882066610299</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19786,7 +19786,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>165.48838700069211</v>
+        <v>165.95155283624106</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19833,7 +19833,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>250.62350512942928</v>
+        <v>251.32494555836396</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>124.85781047043265</v>
+        <v>125.20726020016569</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>109.6</v>
+        <v>113.5</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19912,7 +19912,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19916464749874935</v>
+        <v>0.18597230762732159</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19921,7 +19921,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>-16.204137694507164</v>
+        <v>-16.249489535265599</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>176.2271258934897</v>
+        <v>176.72034711275569</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20044,7 +20044,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>154.17383803164802</v>
+        <v>154.60533691689253</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20111,7 +20111,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>3.4647975826331091E-2</v>
+        <v>3.4647975826331071E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20185,23 +20185,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>6.4227790321465186</v>
+        <v>6.3745562130177529</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>81.210657093774074</v>
+        <v>80.437117484185549</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>87.633436125920596</v>
+        <v>86.811673697203304</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.50272447739466875</v>
+        <v>0.50876243106395957</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20210,23 +20210,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>7.3850538549144646</v>
+        <v>7.3937499999999998</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>101.79184167132983</v>
+        <v>102.26871939395583</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>109.17689552624429</v>
+        <v>109.66246939395583</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.38047621799024312</v>
+        <v>0.37945759395783585</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20260,11 +20260,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>126.31262401528677</v>
+        <v>126.66614545025111</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>134.78086098733144</v>
+        <v>135.13438242229577</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20272,7 +20272,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.23518663597344291</v>
+        <v>0.23532075038267186</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20285,11 +20285,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>142.85020098558587</v>
+        <v>143.2500074849842</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>152.01963803296314</v>
+        <v>152.41944453236147</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20297,7 +20297,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.13736527641696528</v>
+        <v>0.13751049597525478</v>
       </c>
     </row>
   </sheetData>
@@ -20408,7 +20408,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>109.6</v>
+        <v>113.5</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20426,14 +20426,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>308852.8</v>
+        <v>319843</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.19916464749874935</v>
+        <v>0.18597230762732159</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20441,13 +20441,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="472" t="s">
+      <c r="B12" s="475" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="472"/>
-      <c r="D12" s="472"/>
-      <c r="E12" s="472"/>
-      <c r="F12" s="472"/>
+      <c r="C12" s="475"/>
+      <c r="D12" s="475"/>
+      <c r="E12" s="475"/>
+      <c r="F12" s="475"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20485,7 +20485,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1348424911499022</v>
+        <v>1.138018667316437</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20511,7 +20511,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>176.2271258934897</v>
+        <v>176.72034711275569</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20563,14 +20563,14 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>87.633436125920596</v>
+        <v>86.811673697203304</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20579,14 +20579,14 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>109.17689552624429</v>
+        <v>109.66246939395583</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20595,7 +20595,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>134.78086098733144</v>
+        <v>135.13438242229577</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20611,7 +20611,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>152.01963803296314</v>
+        <v>152.41944453236147</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20632,22 +20632,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="472" t="s">
+      <c r="B29" s="475" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="472"/>
-      <c r="D29" s="472"/>
-      <c r="E29" s="472"/>
-      <c r="F29" s="472"/>
+      <c r="C29" s="475"/>
+      <c r="D29" s="475"/>
+      <c r="E29" s="475"/>
+      <c r="F29" s="475"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="478" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="478"/>
+      <c r="D30" s="478"/>
+      <c r="E30" s="478"/>
+      <c r="F30" s="478"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20837,10 +20837,10 @@
       <c r="B54" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="474"/>
-      <c r="D54" s="474"/>
-      <c r="E54" s="474"/>
-      <c r="F54" s="474"/>
+      <c r="C54" s="477"/>
+      <c r="D54" s="477"/>
+      <c r="E54" s="477"/>
+      <c r="F54" s="477"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20856,22 +20856,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="472" t="s">
+      <c r="B57" s="475" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="472"/>
-      <c r="D57" s="472"/>
-      <c r="E57" s="472"/>
-      <c r="F57" s="472"/>
+      <c r="C57" s="475"/>
+      <c r="D57" s="475"/>
+      <c r="E57" s="475"/>
+      <c r="F57" s="475"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="472" t="s">
+      <c r="B58" s="475" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="472"/>
-      <c r="D58" s="472"/>
-      <c r="E58" s="472"/>
-      <c r="F58" s="472"/>
+      <c r="C58" s="475"/>
+      <c r="D58" s="475"/>
+      <c r="E58" s="475"/>
+      <c r="F58" s="475"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20905,7 +20905,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>-1.0477294187879734E-2</v>
+        <v>-1.0145597496135292E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20915,7 +20915,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.2025547445255473E-2</v>
+        <v>3.0925110132158588E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21006,22 +21006,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="472" t="s">
+      <c r="B73" s="475" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="472"/>
-      <c r="D73" s="472"/>
-      <c r="E73" s="472"/>
-      <c r="F73" s="472"/>
+      <c r="C73" s="475"/>
+      <c r="D73" s="475"/>
+      <c r="E73" s="475"/>
+      <c r="F73" s="475"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="478" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="478"/>
+      <c r="D74" s="478"/>
+      <c r="E74" s="478"/>
+      <c r="F74" s="478"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21029,13 +21029,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="472" t="s">
+      <c r="B77" s="475" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="472"/>
-      <c r="D77" s="472"/>
-      <c r="E77" s="472"/>
-      <c r="F77" s="472"/>
+      <c r="C77" s="475"/>
+      <c r="D77" s="475"/>
+      <c r="E77" s="475"/>
+      <c r="F77" s="475"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21056,7 +21056,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-42.930310178869064</v>
+        <v>-43.050462736669317</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21118,7 +21118,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>16.115240078324639</v>
+        <v>16.160343114079755</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21149,7 +21149,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>32.920983298445861</v>
+        <v>33.013121937373157</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21162,7 +21162,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>6.1059131979014332</v>
+        <v>6.1230023147835952</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21184,33 +21184,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="472" t="s">
+      <c r="B96" s="475" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="472"/>
-      <c r="D96" s="472"/>
-      <c r="E96" s="472"/>
-      <c r="F96" s="472"/>
+      <c r="C96" s="475"/>
+      <c r="D96" s="475"/>
+      <c r="E96" s="475"/>
+      <c r="F96" s="475"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="478" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="478"/>
+      <c r="D97" s="478"/>
+      <c r="E97" s="478"/>
+      <c r="F97" s="478"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="478" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="478"/>
+      <c r="D98" s="478"/>
+      <c r="E98" s="478"/>
+      <c r="F98" s="478"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21273,23 +21273,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="472" t="s">
+      <c r="B107" s="475" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="472"/>
-      <c r="D107" s="472"/>
-      <c r="E107" s="472"/>
-      <c r="F107" s="472"/>
+      <c r="C107" s="475"/>
+      <c r="D107" s="475"/>
+      <c r="E107" s="475"/>
+      <c r="F107" s="475"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="472" t="s">
+      <c r="B108" s="475" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="472"/>
-      <c r="D108" s="472"/>
-      <c r="E108" s="472"/>
-      <c r="F108" s="472"/>
+      <c r="C108" s="475"/>
+      <c r="D108" s="475"/>
+      <c r="E108" s="475"/>
+      <c r="F108" s="475"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21307,7 +21307,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-67.075735297392598</v>
+        <v>-67.263465624258046</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21321,7 +21321,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>-16.204137694507164</v>
+        <v>-16.249489535265599</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21333,13 +21333,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="472" t="s">
+      <c r="B114" s="475" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="472"/>
-      <c r="D114" s="472"/>
-      <c r="E114" s="472"/>
-      <c r="F114" s="472"/>
+      <c r="C114" s="475"/>
+      <c r="D114" s="475"/>
+      <c r="E114" s="475"/>
+      <c r="F114" s="475"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21384,7 +21384,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>250.62 HKD</v>
+        <v>251.32 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21407,7 +21407,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>193.69 HKD</v>
+        <v>194.23 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21429,7 +21429,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>162.71 HKD</v>
+        <v>163.17 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21451,7 +21451,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>149.03 HKD</v>
+        <v>149.45 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21473,7 +21473,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>124.86 HKD</v>
+        <v>125.21 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21495,7 +21495,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>176.2271258934897</v>
+        <v>176.72034711275569</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21503,13 +21503,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="476" t="s">
+      <c r="B127" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="476"/>
-      <c r="D127" s="476"/>
-      <c r="E127" s="476"/>
-      <c r="F127" s="476"/>
+      <c r="C127" s="473"/>
+      <c r="D127" s="473"/>
+      <c r="E127" s="473"/>
+      <c r="F127" s="473"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21522,22 +21522,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="477" t="s">
+      <c r="B131" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="477"/>
-      <c r="D131" s="477"/>
-      <c r="E131" s="477"/>
-      <c r="F131" s="477"/>
+      <c r="C131" s="474"/>
+      <c r="D131" s="474"/>
+      <c r="E131" s="474"/>
+      <c r="F131" s="474"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="472" t="s">
+      <c r="B132" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="472"/>
-      <c r="D132" s="472"/>
-      <c r="E132" s="472"/>
-      <c r="F132" s="472"/>
+      <c r="C132" s="475"/>
+      <c r="D132" s="475"/>
+      <c r="E132" s="475"/>
+      <c r="F132" s="475"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21598,19 +21598,19 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>6.4227790321465186</v>
+        <v>6.3745562130177529</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>81.210657093774074</v>
+        <v>80.437117484185549</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>87.633436125920596</v>
+        <v>86.811673697203304</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21619,19 +21619,19 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>7.3850538549144646</v>
+        <v>7.3937499999999998</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>101.79184167132983</v>
+        <v>102.26871939395583</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>109.17689552624429</v>
+        <v>109.66246939395583</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21663,11 +21663,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>126.31262401528677</v>
+        <v>126.66614545025111</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>134.78086098733144</v>
+        <v>135.13438242229577</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21684,11 +21684,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>142.85020098558587</v>
+        <v>143.2500074849842</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>152.01963803296314</v>
+        <v>152.41944453236147</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21706,13 +21706,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="478" t="s">
+      <c r="B149" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="472"/>
-      <c r="D149" s="472"/>
-      <c r="E149" s="472"/>
-      <c r="F149" s="472"/>
+      <c r="C149" s="475"/>
+      <c r="D149" s="475"/>
+      <c r="E149" s="475"/>
+      <c r="F149" s="475"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21720,13 +21720,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="474" t="s">
+      <c r="B152" s="477" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="474"/>
-      <c r="D152" s="474"/>
-      <c r="E152" s="474"/>
-      <c r="F152" s="474"/>
+      <c r="C152" s="477"/>
+      <c r="D152" s="477"/>
+      <c r="E152" s="477"/>
+      <c r="F152" s="477"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21763,22 +21763,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="475" t="s">
+      <c r="B161" s="472" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="475"/>
-      <c r="D161" s="475"/>
-      <c r="E161" s="475"/>
-      <c r="F161" s="475"/>
+      <c r="C161" s="472"/>
+      <c r="D161" s="472"/>
+      <c r="E161" s="472"/>
+      <c r="F161" s="472"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="475" t="s">
+      <c r="B162" s="472" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="475"/>
-      <c r="D162" s="475"/>
-      <c r="E162" s="475"/>
-      <c r="F162" s="475"/>
+      <c r="C162" s="472"/>
+      <c r="D162" s="472"/>
+      <c r="E162" s="472"/>
+      <c r="F162" s="472"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21802,15 +21802,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21825,12 +21822,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9618.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9618.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B855A6CF-B487-4830-AE70-C8CB3FA73A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19111550-A575-426C-BE9E-86E57C462448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4995,30 +4995,30 @@
     <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5028,6 +5028,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5037,16 +5046,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5416,7 +5416,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>113.5</v>
+        <v>112.1</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5434,14 +5434,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>319843</v>
+        <v>315897.8</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.18597230762732159</v>
+        <v>0.19094132328974045</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5449,13 +5449,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="463" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="463"/>
-      <c r="D12" s="463"/>
-      <c r="E12" s="463"/>
-      <c r="F12" s="463"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5490,7 +5490,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.138018667316437</v>
+        <v>1.1377999782562256</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>176.72034711275569</v>
+        <v>176.68638738279677</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>86.811673697203304</v>
+        <v>86.796216378150532</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>109.66246939395583</v>
+        <v>109.64281677245184</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>135.13438242229577</v>
+        <v>135.11004143290373</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>152.41944453236147</v>
+        <v>152.39191668030435</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5633,22 +5633,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="463" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="463"/>
-      <c r="D29" s="463"/>
-      <c r="E29" s="463"/>
-      <c r="F29" s="463"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="467" t="s">
+      <c r="B30" s="463" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="467"/>
-      <c r="D30" s="467"/>
-      <c r="E30" s="467"/>
-      <c r="F30" s="467"/>
+      <c r="C30" s="463"/>
+      <c r="D30" s="463"/>
+      <c r="E30" s="463"/>
+      <c r="F30" s="463"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5660,13 +5660,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="464" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="464"/>
-      <c r="D33" s="464"/>
-      <c r="E33" s="464"/>
-      <c r="F33" s="464"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5686,13 +5686,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="464" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="464"/>
-      <c r="D36" s="464"/>
-      <c r="E36" s="464"/>
-      <c r="F36" s="464"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="464" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="464"/>
-      <c r="D40" s="464"/>
-      <c r="E40" s="464"/>
-      <c r="F40" s="464"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5743,13 +5743,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="464" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="464"/>
-      <c r="D43" s="464"/>
-      <c r="E43" s="464"/>
-      <c r="F43" s="464"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5813,13 +5813,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="464" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="464"/>
-      <c r="D51" s="464"/>
-      <c r="E51" s="464"/>
-      <c r="F51" s="464"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5835,7 +5835,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="464" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5857,22 +5857,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="463" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="463"/>
-      <c r="D57" s="463"/>
-      <c r="E57" s="463"/>
-      <c r="F57" s="463"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="463" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="463"/>
-      <c r="D58" s="463"/>
-      <c r="E58" s="463"/>
-      <c r="F58" s="463"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>-1.0145597496135292E-2</v>
+        <v>-1.0270330340997539E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.0925110132158588E-2</v>
+        <v>3.1311329170383588E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6007,13 +6007,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="463" t="s">
+      <c r="B73" s="461" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="463"/>
-      <c r="D73" s="463"/>
-      <c r="E73" s="463"/>
-      <c r="F73" s="463"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6032,13 +6032,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="463" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="463"/>
-      <c r="D77" s="463"/>
-      <c r="E77" s="463"/>
-      <c r="F77" s="463"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-43.050462736669317</v>
+        <v>-43.042189880073956</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>16.160343114079755</v>
+        <v>16.157237637561835</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>33.013121937373157</v>
+        <v>33.006777921393038</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.1230023147835952</v>
+        <v>6.1218256788809082</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6207,31 +6207,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="463" t="s">
+      <c r="B96" s="461" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="463"/>
-      <c r="D96" s="463"/>
-      <c r="E96" s="463"/>
-      <c r="F96" s="463"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="467" t="s">
+      <c r="B97" s="463" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="467"/>
-      <c r="D97" s="467"/>
-      <c r="E97" s="467"/>
-      <c r="F97" s="467"/>
+      <c r="C97" s="463"/>
+      <c r="D97" s="463"/>
+      <c r="E97" s="463"/>
+      <c r="F97" s="463"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="467" t="s">
+      <c r="B98" s="463" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="467"/>
-      <c r="D98" s="467"/>
-      <c r="E98" s="467"/>
-      <c r="F98" s="467"/>
+      <c r="C98" s="463"/>
+      <c r="D98" s="463"/>
+      <c r="E98" s="463"/>
+      <c r="F98" s="463"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6281,22 +6281,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="463" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="463"/>
-      <c r="D107" s="463"/>
-      <c r="E107" s="463"/>
-      <c r="F107" s="463"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="463" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="463"/>
-      <c r="D108" s="463"/>
-      <c r="E108" s="463"/>
-      <c r="F108" s="463"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-67.263465624258046</v>
+        <v>-67.250539839728859</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>-16.249489535265599</v>
+        <v>-16.246366927792245</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6330,13 +6330,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="463" t="s">
+      <c r="B114" s="461" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="463"/>
-      <c r="D114" s="463"/>
-      <c r="E114" s="463"/>
-      <c r="F114" s="463"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>251.32 HKD</v>
+        <v>251.28 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-9.5007906429065161E-2</v>
+        <v>-9.5004882149774719E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>194.23 HKD</v>
+        <v>194.19 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-1.2355235545605961E-2</v>
+        <v>-1.2351652734886859E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>163.17 HKD</v>
+        <v>163.14 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>4.7909773202239908E-2</v>
+        <v>4.7913803086051539E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>149.45 HKD</v>
+        <v>149.42 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.9712222961475676E-2</v>
+        <v>7.9716502850571913E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>125.21 HKD</v>
+        <v>125.18 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6467,17 +6467,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.14686718125408987</v>
+        <v>0.14687202212275915</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="464" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="464"/>
-      <c r="D124" s="464"/>
-      <c r="E124" s="464"/>
-      <c r="F124" s="464"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>176.72034711275569</v>
+        <v>176.68638738279677</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6512,22 +6512,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="468" t="s">
+      <c r="B131" s="464" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="468"/>
-      <c r="D131" s="468"/>
-      <c r="E131" s="468"/>
-      <c r="F131" s="468"/>
+      <c r="C131" s="464"/>
+      <c r="D131" s="464"/>
+      <c r="E131" s="464"/>
+      <c r="F131" s="464"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="463" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="463"/>
-      <c r="D132" s="463"/>
-      <c r="E132" s="463"/>
-      <c r="F132" s="463"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6592,11 +6592,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>80.437117484185549</v>
+        <v>80.421660165132778</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>86.811673697203304</v>
+        <v>86.796216378150532</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6613,11 +6613,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>102.26871939395583</v>
+        <v>102.24906677245184</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>109.66246939395583</v>
+        <v>109.64281677245184</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6660,11 +6660,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>126.66614545025111</v>
+        <v>126.64180446085906</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>135.13438242229577</v>
+        <v>135.11004143290373</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6681,11 +6681,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>143.2500074849842</v>
+        <v>143.22247963292705</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>152.41944453236147</v>
+        <v>152.39191668030435</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6703,13 +6703,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="462" t="s">
+      <c r="B149" s="468" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="463"/>
-      <c r="D149" s="463"/>
-      <c r="E149" s="463"/>
-      <c r="F149" s="463"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6746,13 +6746,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="464" t="s">
+      <c r="B158" s="462" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="464"/>
-      <c r="D158" s="464"/>
-      <c r="E158" s="464"/>
-      <c r="F158" s="464"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6760,22 +6760,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="461" t="s">
+      <c r="B161" s="467" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="461"/>
-      <c r="D161" s="461"/>
-      <c r="E161" s="461"/>
-      <c r="F161" s="461"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="461" t="s">
+      <c r="B162" s="467" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="461"/>
-      <c r="D162" s="461"/>
-      <c r="E162" s="461"/>
-      <c r="F162" s="461"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6799,6 +6799,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref=